--- a/s60_signal/position-2474-2382-800.xlsx
+++ b/s60_signal/position-2474-2382-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="475">
   <si>
     <t>trade_time</t>
   </si>
@@ -409,12 +409,12 @@
     <t>2020-12-24</t>
   </si>
   <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
     <t>2020-12-29</t>
   </si>
   <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
     <t>2021-01-19</t>
   </si>
   <si>
@@ -760,13 +760,7 @@
     <t>2021-02-18</t>
   </si>
   <si>
-    <t>2021-03-18</t>
-  </si>
-  <si>
     <t>2021-03-23</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
   </si>
   <si>
     <t>2021-03-25</t>
@@ -1899,7 +1893,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1949,7 +1943,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1999,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2049,7 +2043,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2099,7 +2093,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2149,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2199,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2249,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2299,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2349,7 +2343,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2399,7 +2393,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2449,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2499,7 +2493,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2549,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2599,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2649,7 +2643,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2699,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2749,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2799,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2849,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2899,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2949,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2999,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3049,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3099,7 +3093,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3149,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3178,7 +3172,7 @@
         <v>59.3</v>
       </c>
       <c r="P28" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3207,7 +3201,7 @@
         <v>65.5</v>
       </c>
       <c r="P29" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3257,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3307,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3336,7 +3330,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="P32" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3386,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3436,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3486,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3515,7 +3509,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="P36" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3544,7 +3538,7 @@
         <v>70.09999999999999</v>
       </c>
       <c r="P37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3594,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3644,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3694,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3744,7 +3738,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3794,7 +3788,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3844,7 +3838,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3894,7 +3888,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3944,7 +3938,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3994,7 +3988,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4044,7 +4038,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4094,7 +4088,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4144,7 +4138,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4194,7 +4188,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4244,7 +4238,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4294,7 +4288,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4344,7 +4338,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4594,7 +4588,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4694,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4744,7 +4738,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4794,7 +4788,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4844,7 +4838,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4994,7 +4988,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5044,7 +5038,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5094,7 +5088,7 @@
         <v>0</v>
       </c>
       <c r="P68" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5144,7 +5138,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5194,7 +5188,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5244,7 +5238,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5294,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="P72" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5344,7 +5338,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5394,7 +5388,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5444,7 +5438,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5494,7 +5488,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5544,7 +5538,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5594,7 +5588,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5644,7 +5638,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5694,7 +5688,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5744,7 +5738,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5794,7 +5788,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5844,7 +5838,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5894,7 +5888,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5944,7 +5938,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5994,7 +5988,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6044,7 +6038,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6194,7 +6188,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6244,7 +6238,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6294,7 +6288,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6344,7 +6338,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6394,7 +6388,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6444,7 +6438,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6494,7 +6488,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6544,7 +6538,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6594,7 +6588,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6644,7 +6638,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6694,7 +6688,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6744,7 +6738,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6794,7 +6788,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6844,7 +6838,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6894,7 +6888,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6944,7 +6938,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6994,7 +6988,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7044,7 +7038,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7094,7 +7088,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7144,7 +7138,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7194,7 +7188,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7244,7 +7238,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7294,7 +7288,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7344,7 +7338,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7394,7 +7388,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7444,7 +7438,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7494,7 +7488,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7544,7 +7538,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7594,7 +7588,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7644,7 +7638,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7744,7 +7738,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7794,7 +7788,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7844,7 +7838,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7894,7 +7888,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7944,7 +7938,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7994,7 +7988,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8044,7 +8038,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8094,7 +8088,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8144,7 +8138,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8194,7 +8188,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8244,7 +8238,7 @@
         <v>0</v>
       </c>
       <c r="P131" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8294,7 +8288,7 @@
         <v>0</v>
       </c>
       <c r="P132" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8444,7 +8438,7 @@
         <v>0</v>
       </c>
       <c r="P135" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8494,7 +8488,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8544,7 +8538,7 @@
         <v>0</v>
       </c>
       <c r="P137" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8594,7 +8588,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8644,7 +8638,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8694,7 +8688,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8744,7 +8738,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8794,7 +8788,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8844,7 +8838,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8894,7 +8888,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8944,7 +8938,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8994,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9044,7 +9038,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9094,7 +9088,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9144,7 +9138,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9194,7 +9188,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9244,7 +9238,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9344,7 +9338,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9444,7 +9438,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9494,7 +9488,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9544,7 +9538,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9594,7 +9588,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9644,7 +9638,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9694,7 +9688,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9744,7 +9738,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9794,7 +9788,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9844,7 +9838,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9894,7 +9888,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9944,7 +9938,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9994,7 +9988,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10044,7 +10038,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10244,7 +10238,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10294,7 +10288,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10344,7 +10338,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10394,7 +10388,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10444,7 +10438,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10494,7 +10488,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10544,7 +10538,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10594,7 +10588,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10644,7 +10638,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10673,7 +10667,7 @@
         <v>71.40000000000001</v>
       </c>
       <c r="P180" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10702,7 +10696,7 @@
         <v>72.09999999999999</v>
       </c>
       <c r="P181" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10802,7 +10796,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10852,7 +10846,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10902,7 +10896,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10952,7 +10946,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11002,7 +10996,7 @@
         <v>0</v>
       </c>
       <c r="P187" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11052,7 +11046,7 @@
         <v>0</v>
       </c>
       <c r="P188" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11102,7 +11096,7 @@
         <v>0</v>
       </c>
       <c r="P189" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11152,7 +11146,7 @@
         <v>0</v>
       </c>
       <c r="P190" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11202,7 +11196,7 @@
         <v>0</v>
       </c>
       <c r="P191" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11252,7 +11246,7 @@
         <v>0</v>
       </c>
       <c r="P192" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11302,7 +11296,7 @@
         <v>0</v>
       </c>
       <c r="P193" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11352,7 +11346,7 @@
         <v>0</v>
       </c>
       <c r="P194" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11402,7 +11396,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11452,7 +11446,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11502,7 +11496,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11552,7 +11546,7 @@
         <v>0</v>
       </c>
       <c r="P198" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11602,7 +11596,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11652,7 +11646,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11752,7 +11746,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11802,7 +11796,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11852,7 +11846,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11952,7 +11946,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12002,7 +11996,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12052,7 +12046,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12102,7 +12096,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12202,7 +12196,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12252,7 +12246,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12302,7 +12296,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12352,7 +12346,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12402,7 +12396,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12452,7 +12446,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12502,7 +12496,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12552,7 +12546,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12602,7 +12596,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12652,7 +12646,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12702,7 +12696,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12752,7 +12746,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12902,7 +12896,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -13002,7 +12996,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13202,7 +13196,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13252,7 +13246,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13302,7 +13296,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13352,7 +13346,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13402,7 +13396,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13452,7 +13446,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13502,7 +13496,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13552,7 +13546,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13602,7 +13596,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13652,7 +13646,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13702,7 +13696,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13752,7 +13746,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13802,7 +13796,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13852,7 +13846,7 @@
         <v>0</v>
       </c>
       <c r="P244" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13902,7 +13896,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13952,7 +13946,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13981,7 +13975,7 @@
         <v>59.4</v>
       </c>
       <c r="P247" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14031,7 +14025,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14081,7 +14075,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14131,7 +14125,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14160,7 +14154,7 @@
         <v>59.5</v>
       </c>
       <c r="P251" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14210,7 +14204,7 @@
         <v>0</v>
       </c>
       <c r="P252" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14260,7 +14254,7 @@
         <v>0</v>
       </c>
       <c r="P253" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14310,7 +14304,7 @@
         <v>0</v>
       </c>
       <c r="P254" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14360,7 +14354,7 @@
         <v>0</v>
       </c>
       <c r="P255" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14410,7 +14404,7 @@
         <v>0</v>
       </c>
       <c r="P256" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14460,7 +14454,7 @@
         <v>0</v>
       </c>
       <c r="P257" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14510,7 +14504,7 @@
         <v>0</v>
       </c>
       <c r="P258" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14560,7 +14554,7 @@
         <v>0</v>
       </c>
       <c r="P259" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14610,7 +14604,7 @@
         <v>0</v>
       </c>
       <c r="P260" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14660,7 +14654,7 @@
         <v>0</v>
       </c>
       <c r="P261" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14710,7 +14704,7 @@
         <v>0</v>
       </c>
       <c r="P262" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14760,7 +14754,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14810,7 +14804,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14860,7 +14854,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14910,7 +14904,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14960,7 +14954,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15010,7 +15004,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15060,7 +15054,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15110,7 +15104,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15160,7 +15154,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15260,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15310,7 +15304,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15360,7 +15354,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15560,7 +15554,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15660,7 +15654,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15710,7 +15704,7 @@
         <v>0</v>
       </c>
       <c r="P282" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15760,7 +15754,7 @@
         <v>0</v>
       </c>
       <c r="P283" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15810,7 +15804,7 @@
         <v>0</v>
       </c>
       <c r="P284" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15860,7 +15854,7 @@
         <v>0</v>
       </c>
       <c r="P285" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16360,7 +16354,7 @@
         <v>0</v>
       </c>
       <c r="P295" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16410,7 +16404,7 @@
         <v>0</v>
       </c>
       <c r="P296" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16460,7 +16454,7 @@
         <v>0</v>
       </c>
       <c r="P297" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16510,7 +16504,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16560,7 +16554,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16610,7 +16604,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16660,7 +16654,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16710,7 +16704,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16810,7 +16804,7 @@
         <v>0</v>
       </c>
       <c r="P304" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16860,7 +16854,7 @@
         <v>0</v>
       </c>
       <c r="P305" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16910,7 +16904,7 @@
         <v>0</v>
       </c>
       <c r="P306" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16960,7 +16954,7 @@
         <v>0</v>
       </c>
       <c r="P307" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17010,7 +17004,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17060,7 +17054,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17110,7 +17104,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17160,7 +17154,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17210,7 +17204,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17260,7 +17254,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17310,7 +17304,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17360,7 +17354,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17410,7 +17404,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17460,7 +17454,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17510,7 +17504,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17560,7 +17554,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17610,7 +17604,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17660,7 +17654,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17710,7 +17704,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17760,7 +17754,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17810,7 +17804,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17860,7 +17854,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17910,7 +17904,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17960,7 +17954,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18010,7 +18004,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18060,7 +18054,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18089,7 +18083,7 @@
         <v>64.5</v>
       </c>
       <c r="P330" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18139,7 +18133,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18189,7 +18183,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18239,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18289,7 +18283,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18339,7 +18333,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18389,7 +18383,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18439,7 +18433,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18489,7 +18483,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18539,7 +18533,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18589,7 +18583,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18639,7 +18633,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18689,7 +18683,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18739,7 +18733,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18789,7 +18783,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18839,7 +18833,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18889,7 +18883,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18939,7 +18933,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18989,7 +18983,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19039,7 +19033,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19089,7 +19083,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19139,7 +19133,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19189,7 +19183,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19239,7 +19233,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19289,7 +19283,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19339,7 +19333,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19389,7 +19383,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19439,7 +19433,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19489,7 +19483,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19539,7 +19533,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19589,107 +19583,107 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="361" spans="1:16">
       <c r="A361" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B361" t="s">
         <v>131</v>
       </c>
       <c r="C361">
-        <v>22.69572269649692</v>
+        <v>23.26568193365754</v>
       </c>
       <c r="D361" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E361">
-        <v>34.21898145422433</v>
+        <v>34.82839660303404</v>
       </c>
       <c r="F361">
         <v>1</v>
       </c>
       <c r="G361">
-        <v>0.1381042773035031</v>
+        <v>0.1389343180663425</v>
       </c>
       <c r="H361">
-        <v>0.1487810185457757</v>
+        <v>0.142971603396966</v>
       </c>
       <c r="I361">
-        <v>11.5232587577274</v>
+        <v>11.5627146693765</v>
       </c>
       <c r="J361">
-        <v>0.2821725051516043</v>
+        <v>0.2787196051389998</v>
       </c>
       <c r="K361">
-        <v>204.5</v>
+        <v>207.5</v>
       </c>
       <c r="L361">
-        <v>80.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="M361">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="N361">
-        <v>91.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O361">
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="362" spans="1:16">
       <c r="A362" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B362" t="s">
         <v>132</v>
       </c>
       <c r="C362">
-        <v>22.5492051810421</v>
+        <v>22.69572269649692</v>
       </c>
       <c r="D362" t="s">
         <v>248</v>
       </c>
       <c r="E362">
-        <v>34.21898145422433</v>
+        <v>35.27246393876952</v>
       </c>
       <c r="F362">
         <v>1</v>
       </c>
       <c r="G362">
-        <v>0.1396507948189579</v>
+        <v>0.1381042773035031</v>
       </c>
       <c r="H362">
-        <v>0.1487810185457757</v>
+        <v>0.1515275360612305</v>
       </c>
       <c r="I362">
-        <v>11.66977627318222</v>
+        <v>12.5767412422726</v>
       </c>
       <c r="J362">
         <v>0.2821725051516043</v>
       </c>
       <c r="K362">
-        <v>207.5</v>
+        <v>204.5</v>
       </c>
       <c r="L362">
-        <v>81.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="M362">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N362">
-        <v>91.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="O362">
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19697,13 +19691,13 @@
         <v>0</v>
       </c>
       <c r="B363" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C363">
         <v>21.6518845469621</v>
       </c>
       <c r="D363" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E363">
         <v>34.22096927469043</v>
@@ -19747,13 +19741,13 @@
         <v>0</v>
       </c>
       <c r="B364" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C364">
         <v>20.6287291557878</v>
       </c>
       <c r="D364" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E364">
         <v>33.1903090762459</v>
@@ -19789,7 +19783,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19797,13 +19791,13 @@
         <v>0</v>
       </c>
       <c r="B365" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C365">
         <v>18.55332655028487</v>
       </c>
       <c r="D365" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E365">
         <v>31.09968346874662</v>
@@ -19839,7 +19833,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19853,7 +19847,7 @@
         <v>17.31085877987343</v>
       </c>
       <c r="D366" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E366">
         <v>28.73863898391312</v>
@@ -19889,7 +19883,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19903,7 +19897,7 @@
         <v>15.37197148226591</v>
       </c>
       <c r="D367" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E367">
         <v>26.81839483339797</v>
@@ -19939,7 +19933,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19953,10 +19947,10 @@
         <v>15.09009948164395</v>
       </c>
       <c r="D368" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E368">
-        <v>26.03693115694988</v>
+        <v>26.31992973578353</v>
       </c>
       <c r="F368">
         <v>1</v>
@@ -19965,10 +19959,10 @@
         <v>0.1527099005183561</v>
       </c>
       <c r="H368">
-        <v>0.1613630688430502</v>
+        <v>0.1596800702642165</v>
       </c>
       <c r="I368">
-        <v>10.94683167530593</v>
+        <v>11.22983025413959</v>
       </c>
       <c r="J368">
         <v>0.3276661929445527</v>
@@ -19980,16 +19974,16 @@
         <v>83.90000000000001</v>
       </c>
       <c r="M368">
-        <v>206.5</v>
+        <v>203.5</v>
       </c>
       <c r="N368">
-        <v>93.7</v>
+        <v>93</v>
       </c>
       <c r="O368">
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20003,10 +19997,10 @@
         <v>14.98793542044889</v>
       </c>
       <c r="D369" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E369">
-        <v>26.03693115694988</v>
+        <v>26.31992973578353</v>
       </c>
       <c r="F369">
         <v>1</v>
@@ -20015,10 +20009,10 @@
         <v>0.1562120645795511</v>
       </c>
       <c r="H369">
-        <v>0.1613630688430502</v>
+        <v>0.1596800702642165</v>
       </c>
       <c r="I369">
-        <v>11.04899573650098</v>
+        <v>11.33199431533464</v>
       </c>
       <c r="J369">
         <v>0.3276661929445527</v>
@@ -20030,16 +20024,16 @@
         <v>85.59999999999999</v>
       </c>
       <c r="M369">
-        <v>206.5</v>
+        <v>203.5</v>
       </c>
       <c r="N369">
-        <v>93.7</v>
+        <v>93</v>
       </c>
       <c r="O369">
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20053,10 +20047,10 @@
         <v>15.04543186753304</v>
       </c>
       <c r="D370" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E370">
-        <v>26.03693115694988</v>
+        <v>26.31992973578353</v>
       </c>
       <c r="F370">
         <v>1</v>
@@ -20065,10 +20059,10 @@
         <v>0.151354568132467</v>
       </c>
       <c r="H370">
-        <v>0.1613630688430502</v>
+        <v>0.1596800702642165</v>
       </c>
       <c r="I370">
-        <v>10.99149928941684</v>
+        <v>11.27449786825049</v>
       </c>
       <c r="J370">
         <v>0.3276661929445527</v>
@@ -20080,54 +20074,54 @@
         <v>83.2</v>
       </c>
       <c r="M370">
-        <v>206.5</v>
+        <v>203.5</v>
       </c>
       <c r="N370">
-        <v>93.7</v>
+        <v>93</v>
       </c>
       <c r="O370">
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="371" spans="1:16">
       <c r="A371" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B371" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C371">
-        <v>13.45577889447236</v>
+        <v>15.21142902520036</v>
       </c>
       <c r="D371" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E371">
-        <v>24.7361952620244</v>
+        <v>26.31992973578353</v>
       </c>
       <c r="F371">
         <v>1</v>
       </c>
       <c r="G371">
-        <v>0.1543442211055276</v>
+        <v>0.1475885709747997</v>
       </c>
       <c r="H371">
-        <v>0.1612638047379756</v>
+        <v>0.1596800702642165</v>
       </c>
       <c r="I371">
-        <v>11.28041636755204</v>
+        <v>11.10850071058317</v>
       </c>
       <c r="J371">
-        <v>0.335448671931084</v>
+        <v>0.3276661929445527</v>
       </c>
       <c r="K371">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="L371">
-        <v>83.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M371">
         <v>203.5</v>
@@ -20139,21 +20133,21 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>471</v>
+        <v>131</v>
       </c>
     </row>
     <row r="372" spans="1:16">
       <c r="A372" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B372" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C372">
-        <v>13.31081119885138</v>
+        <v>13.45577889447236</v>
       </c>
       <c r="D372" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E372">
         <v>24.7361952620244</v>
@@ -20162,22 +20156,22 @@
         <v>1</v>
       </c>
       <c r="G372">
-        <v>0.1578891888011486</v>
+        <v>0.1543442211055276</v>
       </c>
       <c r="H372">
         <v>0.1612638047379756</v>
       </c>
       <c r="I372">
-        <v>11.42538406317301</v>
+        <v>11.28041636755204</v>
       </c>
       <c r="J372">
         <v>0.335448671931084</v>
       </c>
       <c r="K372">
-        <v>215.5</v>
+        <v>210</v>
       </c>
       <c r="L372">
-        <v>85.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="M372">
         <v>203.5</v>
@@ -20189,21 +20183,21 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="373" spans="1:16">
       <c r="A373" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B373" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C373">
-        <v>13.42667623833452</v>
+        <v>13.31081119885138</v>
       </c>
       <c r="D373" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E373">
         <v>24.7361952620244</v>
@@ -20212,22 +20206,22 @@
         <v>1</v>
       </c>
       <c r="G373">
-        <v>0.1529733237616655</v>
+        <v>0.1578891888011486</v>
       </c>
       <c r="H373">
         <v>0.1612638047379756</v>
       </c>
       <c r="I373">
-        <v>11.30951902368987</v>
+        <v>11.42538406317301</v>
       </c>
       <c r="J373">
         <v>0.335448671931084</v>
       </c>
       <c r="K373">
-        <v>208</v>
+        <v>215.5</v>
       </c>
       <c r="L373">
-        <v>83.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M373">
         <v>203.5</v>
@@ -20239,21 +20233,21 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="374" spans="1:16">
       <c r="A374" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B374" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C374">
-        <v>13.63936826992104</v>
+        <v>13.42667623833452</v>
       </c>
       <c r="D374" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E374">
         <v>24.7361952620244</v>
@@ -20262,22 +20256,22 @@
         <v>1</v>
       </c>
       <c r="G374">
-        <v>0.149160631730079</v>
+        <v>0.1529733237616655</v>
       </c>
       <c r="H374">
         <v>0.1612638047379756</v>
       </c>
       <c r="I374">
-        <v>11.09682699210336</v>
+        <v>11.30951902368987</v>
       </c>
       <c r="J374">
         <v>0.335448671931084</v>
       </c>
       <c r="K374">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="L374">
-        <v>81.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="M374">
         <v>203.5</v>
@@ -20289,62 +20283,62 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="375" spans="1:16">
       <c r="A375" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B375" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C375">
-        <v>10.59259053965798</v>
+        <v>13.63936826992104</v>
       </c>
       <c r="D375" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E375">
-        <v>22.78708795281059</v>
+        <v>24.7361952620244</v>
       </c>
       <c r="F375">
         <v>1</v>
       </c>
       <c r="G375">
-        <v>0.157207409460342</v>
+        <v>0.149160631730079</v>
       </c>
       <c r="H375">
-        <v>0.1652129120471894</v>
+        <v>0.1612638047379756</v>
       </c>
       <c r="I375">
-        <v>12.19449741315262</v>
+        <v>11.09682699210336</v>
       </c>
       <c r="J375">
-        <v>0.3490829021921049</v>
+        <v>0.335448671931084</v>
       </c>
       <c r="K375">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="L375">
-        <v>83.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M375">
-        <v>204</v>
+        <v>203.5</v>
       </c>
       <c r="N375">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O375">
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="376" spans="1:16">
       <c r="A376" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B376" t="s">
         <v>135</v>
@@ -20353,7 +20347,7 @@
         <v>10.37263457760139</v>
       </c>
       <c r="D376" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E376">
         <v>22.78708795281059</v>
@@ -20389,12 +20383,12 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="377" spans="1:16">
       <c r="A377" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B377" t="s">
         <v>136</v>
@@ -20403,7 +20397,7 @@
         <v>10.59075634404218</v>
       </c>
       <c r="D377" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E377">
         <v>22.78708795281059</v>
@@ -20439,12 +20433,12 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="378" spans="1:16">
       <c r="A378" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B378" t="s">
         <v>137</v>
@@ -20453,7 +20447,7 @@
         <v>10.88525375719482</v>
       </c>
       <c r="D378" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E378">
         <v>22.78708795281059</v>
@@ -20489,45 +20483,45 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="379" spans="1:16">
       <c r="A379" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B379" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C379">
-        <v>8.066617110777202</v>
+        <v>11.23800505061848</v>
       </c>
       <c r="D379" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E379">
-        <v>20.60412942273109</v>
+        <v>22.78708795281059</v>
       </c>
       <c r="F379">
         <v>1</v>
       </c>
       <c r="G379">
-        <v>0.1631333828892228</v>
+        <v>0.1543619949493815</v>
       </c>
       <c r="H379">
-        <v>0.1673958705772689</v>
+        <v>0.1652129120471894</v>
       </c>
       <c r="I379">
-        <v>12.53751231195389</v>
+        <v>11.54908290219211</v>
       </c>
       <c r="J379">
-        <v>0.3597836793003378</v>
+        <v>0.3490829021921049</v>
       </c>
       <c r="K379">
-        <v>215.5</v>
+        <v>205</v>
       </c>
       <c r="L379">
-        <v>85.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="M379">
         <v>204</v>
@@ -20539,21 +20533,21 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>134</v>
+        <v>470</v>
       </c>
     </row>
     <row r="380" spans="1:16">
       <c r="A380" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B380" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C380">
-        <v>8.364994705529739</v>
+        <v>8.066617110777202</v>
       </c>
       <c r="D380" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E380">
         <v>20.60412942273109</v>
@@ -20562,22 +20556,22 @@
         <v>1</v>
       </c>
       <c r="G380">
-        <v>0.1580350052944703</v>
+        <v>0.1631333828892228</v>
       </c>
       <c r="H380">
         <v>0.1673958705772689</v>
       </c>
       <c r="I380">
-        <v>12.23913471720135</v>
+        <v>12.53751231195389</v>
       </c>
       <c r="J380">
         <v>0.3597836793003378</v>
       </c>
       <c r="K380">
-        <v>208</v>
+        <v>215.5</v>
       </c>
       <c r="L380">
-        <v>83.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M380">
         <v>204</v>
@@ -20594,7 +20588,7 @@
     </row>
     <row r="381" spans="1:16">
       <c r="A381" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B381" t="s">
         <v>138</v>
@@ -20603,7 +20597,7 @@
         <v>9.044345743430753</v>
       </c>
       <c r="D381" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E381">
         <v>20.60412942273109</v>
@@ -20653,7 +20647,7 @@
         <v>-2.124244140274371</v>
       </c>
       <c r="D382" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E382">
         <v>10.72424068728326</v>
@@ -20703,7 +20697,7 @@
         <v>13.16161645214643</v>
       </c>
       <c r="D383" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E383">
         <v>9.280369598044189</v>
@@ -20739,7 +20733,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20753,7 +20747,7 @@
         <v>-21.82338146012957</v>
       </c>
       <c r="D384" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E384">
         <v>-26.74300800979539</v>
@@ -20789,7 +20783,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20803,7 +20797,7 @@
         <v>32.20533098261782</v>
       </c>
       <c r="D385" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E385">
         <v>28.32229381498548</v>
@@ -20839,7 +20833,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20853,7 +20847,7 @@
         <v>30.11806288540985</v>
       </c>
       <c r="D386" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E386">
         <v>26.85846428286341</v>
@@ -20889,7 +20883,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-2474-2382-800.xlsx
+++ b/s60_signal/position-2474-2382-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="474">
   <si>
     <t>trade_time</t>
   </si>
@@ -406,1009 +406,1006 @@
     <t>2020-11-12</t>
   </si>
   <si>
+    <t>2020-12-29</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>2021-01-19</t>
+  </si>
+  <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>2021-01-21</t>
+  </si>
+  <si>
+    <t>2021-01-28</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-05-17</t>
+  </si>
+  <si>
+    <t>2021-05-14</t>
+  </si>
+  <si>
+    <t>2021-07-12</t>
+  </si>
+  <si>
+    <t>2010-10-22</t>
+  </si>
+  <si>
+    <t>2010-10-25</t>
+  </si>
+  <si>
+    <t>2010-10-28</t>
+  </si>
+  <si>
+    <t>2011-05-13</t>
+  </si>
+  <si>
+    <t>2011-05-16</t>
+  </si>
+  <si>
+    <t>2011-05-17</t>
+  </si>
+  <si>
+    <t>2011-05-18</t>
+  </si>
+  <si>
+    <t>2011-05-19</t>
+  </si>
+  <si>
+    <t>2011-05-20</t>
+  </si>
+  <si>
+    <t>2011-05-23</t>
+  </si>
+  <si>
+    <t>2011-05-24</t>
+  </si>
+  <si>
+    <t>2011-05-25</t>
+  </si>
+  <si>
+    <t>2011-05-26</t>
+  </si>
+  <si>
+    <t>2011-05-27</t>
+  </si>
+  <si>
+    <t>2011-05-30</t>
+  </si>
+  <si>
+    <t>2011-05-31</t>
+  </si>
+  <si>
+    <t>2011-06-02</t>
+  </si>
+  <si>
+    <t>2011-06-03</t>
+  </si>
+  <si>
+    <t>2011-07-22</t>
+  </si>
+  <si>
+    <t>2011-07-25</t>
+  </si>
+  <si>
+    <t>2011-07-27</t>
+  </si>
+  <si>
+    <t>2011-07-28</t>
+  </si>
+  <si>
+    <t>2011-07-29</t>
+  </si>
+  <si>
+    <t>2011-10-07</t>
+  </si>
+  <si>
+    <t>2011-10-05</t>
+  </si>
+  <si>
+    <t>2012-02-29</t>
+  </si>
+  <si>
+    <t>2012-07-18</t>
+  </si>
+  <si>
+    <t>2012-05-02</t>
+  </si>
+  <si>
+    <t>2012-05-25</t>
+  </si>
+  <si>
+    <t>2012-11-13</t>
+  </si>
+  <si>
+    <t>2012-11-14</t>
+  </si>
+  <si>
+    <t>2012-12-14</t>
+  </si>
+  <si>
+    <t>2012-08-01</t>
+  </si>
+  <si>
+    <t>2013-06-14</t>
+  </si>
+  <si>
+    <t>2013-06-17</t>
+  </si>
+  <si>
+    <t>2013-06-18</t>
+  </si>
+  <si>
+    <t>2013-05-20</t>
+  </si>
+  <si>
+    <t>2013-08-06</t>
+  </si>
+  <si>
+    <t>2013-05-16</t>
+  </si>
+  <si>
+    <t>2013-11-28</t>
+  </si>
+  <si>
+    <t>2013-12-04</t>
+  </si>
+  <si>
+    <t>2014-02-17</t>
+  </si>
+  <si>
+    <t>2014-02-19</t>
+  </si>
+  <si>
+    <t>2013-08-07</t>
+  </si>
+  <si>
+    <t>2013-08-08</t>
+  </si>
+  <si>
+    <t>2013-08-09</t>
+  </si>
+  <si>
+    <t>2013-09-23</t>
+  </si>
+  <si>
+    <t>2014-04-25</t>
+  </si>
+  <si>
+    <t>2014-04-24</t>
+  </si>
+  <si>
+    <t>2014-09-15</t>
+  </si>
+  <si>
+    <t>2014-12-02</t>
+  </si>
+  <si>
+    <t>2014-09-10</t>
+  </si>
+  <si>
+    <t>2014-09-04</t>
+  </si>
+  <si>
+    <t>2014-11-11</t>
+  </si>
+  <si>
+    <t>2014-09-03</t>
+  </si>
+  <si>
+    <t>2014-11-03</t>
+  </si>
+  <si>
+    <t>2014-11-27</t>
+  </si>
+  <si>
+    <t>2015-03-18</t>
+  </si>
+  <si>
+    <t>2015-08-07</t>
+  </si>
+  <si>
+    <t>2016-03-16</t>
+  </si>
+  <si>
+    <t>2016-03-17</t>
+  </si>
+  <si>
+    <t>2016-02-01</t>
+  </si>
+  <si>
+    <t>2016-02-02</t>
+  </si>
+  <si>
+    <t>2016-07-18</t>
+  </si>
+  <si>
+    <t>2016-06-30</t>
+  </si>
+  <si>
+    <t>2016-08-03</t>
+  </si>
+  <si>
+    <t>2016-07-01</t>
+  </si>
+  <si>
+    <t>2017-02-08</t>
+  </si>
+  <si>
+    <t>2017-06-23</t>
+  </si>
+  <si>
+    <t>2017-03-29</t>
+  </si>
+  <si>
+    <t>2017-11-15</t>
+  </si>
+  <si>
+    <t>2018-03-08</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>2018-04-18</t>
+  </si>
+  <si>
+    <t>2018-04-19</t>
+  </si>
+  <si>
+    <t>2018-04-20</t>
+  </si>
+  <si>
+    <t>2018-04-23</t>
+  </si>
+  <si>
+    <t>2018-05-04</t>
+  </si>
+  <si>
+    <t>2018-05-07</t>
+  </si>
+  <si>
+    <t>2018-05-08</t>
+  </si>
+  <si>
+    <t>2018-04-12</t>
+  </si>
+  <si>
+    <t>2018-11-16</t>
+  </si>
+  <si>
+    <t>2018-11-30</t>
+  </si>
+  <si>
+    <t>2018-12-03</t>
+  </si>
+  <si>
+    <t>2018-12-27</t>
+  </si>
+  <si>
+    <t>2019-01-03</t>
+  </si>
+  <si>
+    <t>2019-02-14</t>
+  </si>
+  <si>
+    <t>2019-02-20</t>
+  </si>
+  <si>
+    <t>2019-09-12</t>
+  </si>
+  <si>
+    <t>2019-09-16</t>
+  </si>
+  <si>
+    <t>2019-09-17</t>
+  </si>
+  <si>
+    <t>2019-09-18</t>
+  </si>
+  <si>
+    <t>2019-09-19</t>
+  </si>
+  <si>
+    <t>2019-09-23</t>
+  </si>
+  <si>
+    <t>2019-10-30</t>
+  </si>
+  <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
+    <t>2019-11-11</t>
+  </si>
+  <si>
+    <t>2019-11-14</t>
+  </si>
+  <si>
+    <t>2019-11-05</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2020-05-29</t>
+  </si>
+  <si>
+    <t>2020-06-03</t>
+  </si>
+  <si>
+    <t>2020-06-04</t>
+  </si>
+  <si>
+    <t>2021-02-17</t>
+  </si>
+  <si>
+    <t>2021-03-18</t>
+  </si>
+  <si>
+    <t>2021-03-23</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>2021-03-29</t>
+  </si>
+  <si>
+    <t>2021-05-24</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>2010-08-03</t>
+  </si>
+  <si>
+    <t>2010-08-19</t>
+  </si>
+  <si>
+    <t>2010-08-26</t>
+  </si>
+  <si>
+    <t>2010-08-27</t>
+  </si>
+  <si>
+    <t>2010-08-30</t>
+  </si>
+  <si>
+    <t>2010-09-17</t>
+  </si>
+  <si>
+    <t>2010-09-20</t>
+  </si>
+  <si>
+    <t>2010-09-21</t>
+  </si>
+  <si>
+    <t>2010-09-23</t>
+  </si>
+  <si>
+    <t>2010-09-24</t>
+  </si>
+  <si>
+    <t>2010-09-27</t>
+  </si>
+  <si>
+    <t>2010-09-28</t>
+  </si>
+  <si>
+    <t>2010-09-29</t>
+  </si>
+  <si>
+    <t>2010-09-30</t>
+  </si>
+  <si>
+    <t>2010-10-01</t>
+  </si>
+  <si>
+    <t>2010-10-04</t>
+  </si>
+  <si>
+    <t>2010-10-05</t>
+  </si>
+  <si>
+    <t>2010-10-06</t>
+  </si>
+  <si>
+    <t>2010-10-07</t>
+  </si>
+  <si>
+    <t>2010-10-08</t>
+  </si>
+  <si>
+    <t>2010-10-11</t>
+  </si>
+  <si>
+    <t>2010-11-24</t>
+  </si>
+  <si>
+    <t>2010-11-25</t>
+  </si>
+  <si>
+    <t>2010-11-26</t>
+  </si>
+  <si>
+    <t>2010-11-29</t>
+  </si>
+  <si>
+    <t>2010-11-30</t>
+  </si>
+  <si>
+    <t>2010-12-01</t>
+  </si>
+  <si>
+    <t>2010-12-02</t>
+  </si>
+  <si>
+    <t>2010-12-03</t>
+  </si>
+  <si>
+    <t>2011-06-24</t>
+  </si>
+  <si>
+    <t>2011-06-27</t>
+  </si>
+  <si>
+    <t>2011-06-30</t>
+  </si>
+  <si>
+    <t>2011-07-07</t>
+  </si>
+  <si>
+    <t>2011-12-02</t>
+  </si>
+  <si>
+    <t>2011-12-05</t>
+  </si>
+  <si>
+    <t>2012-02-24</t>
+  </si>
+  <si>
+    <t>2012-03-02</t>
+  </si>
+  <si>
+    <t>2012-03-06</t>
+  </si>
+  <si>
+    <t>2012-03-07</t>
+  </si>
+  <si>
+    <t>2012-03-12</t>
+  </si>
+  <si>
+    <t>2012-03-13</t>
+  </si>
+  <si>
+    <t>2012-03-29</t>
+  </si>
+  <si>
+    <t>2012-03-30</t>
+  </si>
+  <si>
+    <t>2012-05-03</t>
+  </si>
+  <si>
+    <t>2012-05-15</t>
+  </si>
+  <si>
+    <t>2012-05-16</t>
+  </si>
+  <si>
+    <t>2012-05-17</t>
+  </si>
+  <si>
+    <t>2012-05-18</t>
+  </si>
+  <si>
+    <t>2012-05-21</t>
+  </si>
+  <si>
+    <t>2012-05-22</t>
+  </si>
+  <si>
+    <t>2012-05-23</t>
+  </si>
+  <si>
+    <t>2012-05-24</t>
+  </si>
+  <si>
+    <t>2012-05-28</t>
+  </si>
+  <si>
+    <t>2012-05-29</t>
+  </si>
+  <si>
+    <t>2012-05-30</t>
+  </si>
+  <si>
+    <t>2012-05-31</t>
+  </si>
+  <si>
+    <t>2012-06-01</t>
+  </si>
+  <si>
+    <t>2012-06-04</t>
+  </si>
+  <si>
+    <t>2012-06-05</t>
+  </si>
+  <si>
+    <t>2012-06-06</t>
+  </si>
+  <si>
+    <t>2012-06-07</t>
+  </si>
+  <si>
+    <t>2012-06-08</t>
+  </si>
+  <si>
+    <t>2012-06-11</t>
+  </si>
+  <si>
+    <t>2012-06-12</t>
+  </si>
+  <si>
+    <t>2012-06-13</t>
+  </si>
+  <si>
+    <t>2012-06-14</t>
+  </si>
+  <si>
+    <t>2012-06-15</t>
+  </si>
+  <si>
+    <t>2012-06-19</t>
+  </si>
+  <si>
+    <t>2012-06-20</t>
+  </si>
+  <si>
+    <t>2012-06-22</t>
+  </si>
+  <si>
+    <t>2012-10-18</t>
+  </si>
+  <si>
+    <t>2012-10-19</t>
+  </si>
+  <si>
+    <t>2012-10-22</t>
+  </si>
+  <si>
+    <t>2013-04-08</t>
+  </si>
+  <si>
+    <t>2013-04-12</t>
+  </si>
+  <si>
+    <t>2013-06-25</t>
+  </si>
+  <si>
+    <t>2013-06-27</t>
+  </si>
+  <si>
+    <t>2013-06-28</t>
+  </si>
+  <si>
+    <t>2013-07-01</t>
+  </si>
+  <si>
+    <t>2013-07-02</t>
+  </si>
+  <si>
+    <t>2013-07-03</t>
+  </si>
+  <si>
+    <t>2013-07-04</t>
+  </si>
+  <si>
+    <t>2013-10-28</t>
+  </si>
+  <si>
+    <t>2014-01-22</t>
+  </si>
+  <si>
+    <t>2014-01-23</t>
+  </si>
+  <si>
+    <t>2014-01-24</t>
+  </si>
+  <si>
+    <t>2014-01-27</t>
+  </si>
+  <si>
+    <t>2014-02-06</t>
+  </si>
+  <si>
+    <t>2014-02-07</t>
+  </si>
+  <si>
+    <t>2014-02-10</t>
+  </si>
+  <si>
+    <t>2014-02-11</t>
+  </si>
+  <si>
+    <t>2014-02-18</t>
+  </si>
+  <si>
+    <t>2014-02-20</t>
+  </si>
+  <si>
+    <t>2014-02-21</t>
+  </si>
+  <si>
+    <t>2014-07-08</t>
+  </si>
+  <si>
+    <t>2014-07-10</t>
+  </si>
+  <si>
+    <t>2014-07-11</t>
+  </si>
+  <si>
+    <t>2014-07-16</t>
+  </si>
+  <si>
+    <t>2014-07-17</t>
+  </si>
+  <si>
+    <t>2014-07-18</t>
+  </si>
+  <si>
+    <t>2014-10-15</t>
+  </si>
+  <si>
+    <t>2014-11-04</t>
+  </si>
+  <si>
+    <t>2015-06-11</t>
+  </si>
+  <si>
+    <t>2015-06-12</t>
+  </si>
+  <si>
+    <t>2015-06-15</t>
+  </si>
+  <si>
+    <t>2015-07-22</t>
+  </si>
+  <si>
+    <t>2015-07-23</t>
+  </si>
+  <si>
+    <t>2015-10-15</t>
+  </si>
+  <si>
+    <t>2015-10-16</t>
+  </si>
+  <si>
+    <t>2015-11-19</t>
+  </si>
+  <si>
+    <t>2016-04-01</t>
+  </si>
+  <si>
+    <t>2016-04-07</t>
+  </si>
+  <si>
+    <t>2016-04-08</t>
+  </si>
+  <si>
+    <t>2016-04-15</t>
+  </si>
+  <si>
+    <t>2016-04-18</t>
+  </si>
+  <si>
+    <t>2016-04-19</t>
+  </si>
+  <si>
+    <t>2016-04-21</t>
+  </si>
+  <si>
+    <t>2016-04-22</t>
+  </si>
+  <si>
+    <t>2016-04-27</t>
+  </si>
+  <si>
+    <t>2016-04-28</t>
+  </si>
+  <si>
+    <t>2016-05-03</t>
+  </si>
+  <si>
+    <t>2016-05-05</t>
+  </si>
+  <si>
+    <t>2016-05-10</t>
+  </si>
+  <si>
+    <t>2016-05-11</t>
+  </si>
+  <si>
+    <t>2016-05-12</t>
+  </si>
+  <si>
+    <t>2016-05-13</t>
+  </si>
+  <si>
+    <t>2016-05-16</t>
+  </si>
+  <si>
+    <t>2016-05-17</t>
+  </si>
+  <si>
+    <t>2016-10-27</t>
+  </si>
+  <si>
+    <t>2016-12-15</t>
+  </si>
+  <si>
+    <t>2017-06-26</t>
+  </si>
+  <si>
+    <t>2017-06-27</t>
+  </si>
+  <si>
+    <t>2017-07-11</t>
+  </si>
+  <si>
+    <t>2017-07-12</t>
+  </si>
+  <si>
+    <t>2017-07-13</t>
+  </si>
+  <si>
+    <t>2017-07-14</t>
+  </si>
+  <si>
+    <t>2017-07-17</t>
+  </si>
+  <si>
+    <t>2017-08-21</t>
+  </si>
+  <si>
+    <t>2017-08-22</t>
+  </si>
+  <si>
+    <t>2017-08-23</t>
+  </si>
+  <si>
+    <t>2017-08-24</t>
+  </si>
+  <si>
+    <t>2017-08-25</t>
+  </si>
+  <si>
+    <t>2017-09-06</t>
+  </si>
+  <si>
+    <t>2017-09-07</t>
+  </si>
+  <si>
+    <t>2017-09-08</t>
+  </si>
+  <si>
+    <t>2018-01-12</t>
+  </si>
+  <si>
+    <t>2018-01-15</t>
+  </si>
+  <si>
+    <t>2018-01-16</t>
+  </si>
+  <si>
+    <t>2018-01-17</t>
+  </si>
+  <si>
+    <t>2018-01-30</t>
+  </si>
+  <si>
+    <t>2018-01-31</t>
+  </si>
+  <si>
+    <t>2018-02-06</t>
+  </si>
+  <si>
+    <t>2018-02-22</t>
+  </si>
+  <si>
+    <t>2018-03-30</t>
+  </si>
+  <si>
+    <t>2018-05-16</t>
+  </si>
+  <si>
+    <t>2018-05-21</t>
+  </si>
+  <si>
+    <t>2018-11-20</t>
+  </si>
+  <si>
+    <t>2018-12-28</t>
+  </si>
+  <si>
+    <t>2019-01-09</t>
+  </si>
+  <si>
+    <t>2019-01-10</t>
+  </si>
+  <si>
+    <t>2019-01-15</t>
+  </si>
+  <si>
+    <t>2019-01-16</t>
+  </si>
+  <si>
+    <t>2019-01-17</t>
+  </si>
+  <si>
+    <t>2019-01-18</t>
+  </si>
+  <si>
+    <t>2019-01-22</t>
+  </si>
+  <si>
+    <t>2019-01-23</t>
+  </si>
+  <si>
+    <t>2019-01-24</t>
+  </si>
+  <si>
+    <t>2019-01-25</t>
+  </si>
+  <si>
+    <t>2019-01-29</t>
+  </si>
+  <si>
+    <t>2019-03-11</t>
+  </si>
+  <si>
+    <t>2019-03-12</t>
+  </si>
+  <si>
+    <t>2019-03-13</t>
+  </si>
+  <si>
+    <t>2019-04-09</t>
+  </si>
+  <si>
+    <t>2019-04-10</t>
+  </si>
+  <si>
+    <t>2019-04-18</t>
+  </si>
+  <si>
+    <t>2019-04-19</t>
+  </si>
+  <si>
+    <t>2019-04-25</t>
+  </si>
+  <si>
+    <t>2019-04-26</t>
+  </si>
+  <si>
+    <t>2019-05-02</t>
+  </si>
+  <si>
+    <t>2019-05-07</t>
+  </si>
+  <si>
+    <t>2019-05-08</t>
+  </si>
+  <si>
+    <t>2019-05-09</t>
+  </si>
+  <si>
+    <t>2019-05-10</t>
+  </si>
+  <si>
+    <t>2019-05-13</t>
+  </si>
+  <si>
+    <t>2019-07-29</t>
+  </si>
+  <si>
+    <t>2019-08-29</t>
+  </si>
+  <si>
+    <t>2019-08-30</t>
+  </si>
+  <si>
+    <t>2019-09-02</t>
+  </si>
+  <si>
+    <t>2019-09-03</t>
+  </si>
+  <si>
+    <t>2019-09-04</t>
+  </si>
+  <si>
+    <t>2019-09-05</t>
+  </si>
+  <si>
+    <t>2019-09-06</t>
+  </si>
+  <si>
+    <t>2019-09-10</t>
+  </si>
+  <si>
+    <t>2020-02-20</t>
+  </si>
+  <si>
+    <t>2020-02-21</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>2020-02-27</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-03-04</t>
+  </si>
+  <si>
+    <t>2020-03-05</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2020-03-09</t>
+  </si>
+  <si>
+    <t>2020-03-12</t>
+  </si>
+  <si>
+    <t>2020-11-02</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
     <t>2020-12-24</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>2020-12-29</t>
-  </si>
-  <si>
-    <t>2021-01-19</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-14</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>2021-01-21</t>
-  </si>
-  <si>
-    <t>2021-01-28</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-05-17</t>
-  </si>
-  <si>
-    <t>2021-05-14</t>
-  </si>
-  <si>
-    <t>2021-07-12</t>
-  </si>
-  <si>
-    <t>2010-10-22</t>
-  </si>
-  <si>
-    <t>2010-10-25</t>
-  </si>
-  <si>
-    <t>2010-10-28</t>
-  </si>
-  <si>
-    <t>2011-05-13</t>
-  </si>
-  <si>
-    <t>2011-05-16</t>
-  </si>
-  <si>
-    <t>2011-05-17</t>
-  </si>
-  <si>
-    <t>2011-05-18</t>
-  </si>
-  <si>
-    <t>2011-05-19</t>
-  </si>
-  <si>
-    <t>2011-05-20</t>
-  </si>
-  <si>
-    <t>2011-05-23</t>
-  </si>
-  <si>
-    <t>2011-05-24</t>
-  </si>
-  <si>
-    <t>2011-05-25</t>
-  </si>
-  <si>
-    <t>2011-05-26</t>
-  </si>
-  <si>
-    <t>2011-05-27</t>
-  </si>
-  <si>
-    <t>2011-05-30</t>
-  </si>
-  <si>
-    <t>2011-05-31</t>
-  </si>
-  <si>
-    <t>2011-06-02</t>
-  </si>
-  <si>
-    <t>2011-06-03</t>
-  </si>
-  <si>
-    <t>2011-07-22</t>
-  </si>
-  <si>
-    <t>2011-07-25</t>
-  </si>
-  <si>
-    <t>2011-07-27</t>
-  </si>
-  <si>
-    <t>2011-07-28</t>
-  </si>
-  <si>
-    <t>2011-07-29</t>
-  </si>
-  <si>
-    <t>2011-10-07</t>
-  </si>
-  <si>
-    <t>2011-10-05</t>
-  </si>
-  <si>
-    <t>2012-02-29</t>
-  </si>
-  <si>
-    <t>2012-07-18</t>
-  </si>
-  <si>
-    <t>2012-05-02</t>
-  </si>
-  <si>
-    <t>2012-05-25</t>
-  </si>
-  <si>
-    <t>2012-11-13</t>
-  </si>
-  <si>
-    <t>2012-11-14</t>
-  </si>
-  <si>
-    <t>2012-12-14</t>
-  </si>
-  <si>
-    <t>2012-08-01</t>
-  </si>
-  <si>
-    <t>2013-06-14</t>
-  </si>
-  <si>
-    <t>2013-06-17</t>
-  </si>
-  <si>
-    <t>2013-06-18</t>
-  </si>
-  <si>
-    <t>2013-05-20</t>
-  </si>
-  <si>
-    <t>2013-08-06</t>
-  </si>
-  <si>
-    <t>2013-05-16</t>
-  </si>
-  <si>
-    <t>2013-11-28</t>
-  </si>
-  <si>
-    <t>2013-12-04</t>
-  </si>
-  <si>
-    <t>2014-02-17</t>
-  </si>
-  <si>
-    <t>2014-02-19</t>
-  </si>
-  <si>
-    <t>2013-08-07</t>
-  </si>
-  <si>
-    <t>2013-08-08</t>
-  </si>
-  <si>
-    <t>2013-08-09</t>
-  </si>
-  <si>
-    <t>2013-09-23</t>
-  </si>
-  <si>
-    <t>2014-04-25</t>
-  </si>
-  <si>
-    <t>2014-04-24</t>
-  </si>
-  <si>
-    <t>2014-09-15</t>
-  </si>
-  <si>
-    <t>2014-12-02</t>
-  </si>
-  <si>
-    <t>2014-09-10</t>
-  </si>
-  <si>
-    <t>2014-09-04</t>
-  </si>
-  <si>
-    <t>2014-11-11</t>
-  </si>
-  <si>
-    <t>2014-09-03</t>
-  </si>
-  <si>
-    <t>2014-11-03</t>
-  </si>
-  <si>
-    <t>2014-11-27</t>
-  </si>
-  <si>
-    <t>2015-03-18</t>
-  </si>
-  <si>
-    <t>2015-08-07</t>
-  </si>
-  <si>
-    <t>2016-03-16</t>
-  </si>
-  <si>
-    <t>2016-03-17</t>
-  </si>
-  <si>
-    <t>2016-02-01</t>
-  </si>
-  <si>
-    <t>2016-02-02</t>
-  </si>
-  <si>
-    <t>2016-07-18</t>
-  </si>
-  <si>
-    <t>2016-06-30</t>
-  </si>
-  <si>
-    <t>2016-08-03</t>
-  </si>
-  <si>
-    <t>2016-07-01</t>
-  </si>
-  <si>
-    <t>2017-02-08</t>
-  </si>
-  <si>
-    <t>2017-06-23</t>
-  </si>
-  <si>
-    <t>2017-03-29</t>
-  </si>
-  <si>
-    <t>2017-11-15</t>
-  </si>
-  <si>
-    <t>2018-03-08</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>2018-04-18</t>
-  </si>
-  <si>
-    <t>2018-04-19</t>
-  </si>
-  <si>
-    <t>2018-04-20</t>
-  </si>
-  <si>
-    <t>2018-04-23</t>
-  </si>
-  <si>
-    <t>2018-05-04</t>
-  </si>
-  <si>
-    <t>2018-05-07</t>
-  </si>
-  <si>
-    <t>2018-05-08</t>
-  </si>
-  <si>
-    <t>2018-04-12</t>
-  </si>
-  <si>
-    <t>2018-11-16</t>
-  </si>
-  <si>
-    <t>2018-11-30</t>
-  </si>
-  <si>
-    <t>2018-12-03</t>
-  </si>
-  <si>
-    <t>2018-12-27</t>
-  </si>
-  <si>
-    <t>2019-01-03</t>
-  </si>
-  <si>
-    <t>2019-02-14</t>
-  </si>
-  <si>
-    <t>2019-02-20</t>
-  </si>
-  <si>
-    <t>2019-09-12</t>
-  </si>
-  <si>
-    <t>2019-09-16</t>
-  </si>
-  <si>
-    <t>2019-09-17</t>
-  </si>
-  <si>
-    <t>2019-09-18</t>
-  </si>
-  <si>
-    <t>2019-09-19</t>
-  </si>
-  <si>
-    <t>2019-09-23</t>
-  </si>
-  <si>
-    <t>2019-10-30</t>
-  </si>
-  <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
-    <t>2019-11-11</t>
-  </si>
-  <si>
-    <t>2019-11-14</t>
-  </si>
-  <si>
-    <t>2019-11-05</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2020-05-29</t>
-  </si>
-  <si>
-    <t>2020-06-03</t>
-  </si>
-  <si>
-    <t>2020-06-04</t>
-  </si>
-  <si>
-    <t>2021-02-17</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>2021-03-23</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>2021-03-29</t>
-  </si>
-  <si>
-    <t>2021-05-21</t>
-  </si>
-  <si>
-    <t>2021-05-24</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>2021-07-15</t>
-  </si>
-  <si>
-    <t>2010-08-03</t>
-  </si>
-  <si>
-    <t>2010-08-19</t>
-  </si>
-  <si>
-    <t>2010-08-26</t>
-  </si>
-  <si>
-    <t>2010-08-27</t>
-  </si>
-  <si>
-    <t>2010-08-30</t>
-  </si>
-  <si>
-    <t>2010-09-17</t>
-  </si>
-  <si>
-    <t>2010-09-20</t>
-  </si>
-  <si>
-    <t>2010-09-21</t>
-  </si>
-  <si>
-    <t>2010-09-23</t>
-  </si>
-  <si>
-    <t>2010-09-24</t>
-  </si>
-  <si>
-    <t>2010-09-27</t>
-  </si>
-  <si>
-    <t>2010-09-28</t>
-  </si>
-  <si>
-    <t>2010-09-29</t>
-  </si>
-  <si>
-    <t>2010-09-30</t>
-  </si>
-  <si>
-    <t>2010-10-01</t>
-  </si>
-  <si>
-    <t>2010-10-04</t>
-  </si>
-  <si>
-    <t>2010-10-05</t>
-  </si>
-  <si>
-    <t>2010-10-06</t>
-  </si>
-  <si>
-    <t>2010-10-07</t>
-  </si>
-  <si>
-    <t>2010-10-08</t>
-  </si>
-  <si>
-    <t>2010-10-11</t>
-  </si>
-  <si>
-    <t>2010-11-24</t>
-  </si>
-  <si>
-    <t>2010-11-25</t>
-  </si>
-  <si>
-    <t>2010-11-26</t>
-  </si>
-  <si>
-    <t>2010-11-29</t>
-  </si>
-  <si>
-    <t>2010-11-30</t>
-  </si>
-  <si>
-    <t>2010-12-01</t>
-  </si>
-  <si>
-    <t>2010-12-02</t>
-  </si>
-  <si>
-    <t>2010-12-03</t>
-  </si>
-  <si>
-    <t>2011-06-24</t>
-  </si>
-  <si>
-    <t>2011-06-27</t>
-  </si>
-  <si>
-    <t>2011-06-30</t>
-  </si>
-  <si>
-    <t>2011-07-07</t>
-  </si>
-  <si>
-    <t>2011-12-02</t>
-  </si>
-  <si>
-    <t>2011-12-05</t>
-  </si>
-  <si>
-    <t>2012-02-24</t>
-  </si>
-  <si>
-    <t>2012-03-02</t>
-  </si>
-  <si>
-    <t>2012-03-06</t>
-  </si>
-  <si>
-    <t>2012-03-07</t>
-  </si>
-  <si>
-    <t>2012-03-12</t>
-  </si>
-  <si>
-    <t>2012-03-13</t>
-  </si>
-  <si>
-    <t>2012-03-29</t>
-  </si>
-  <si>
-    <t>2012-03-30</t>
-  </si>
-  <si>
-    <t>2012-05-03</t>
-  </si>
-  <si>
-    <t>2012-05-15</t>
-  </si>
-  <si>
-    <t>2012-05-16</t>
-  </si>
-  <si>
-    <t>2012-05-17</t>
-  </si>
-  <si>
-    <t>2012-05-18</t>
-  </si>
-  <si>
-    <t>2012-05-21</t>
-  </si>
-  <si>
-    <t>2012-05-22</t>
-  </si>
-  <si>
-    <t>2012-05-23</t>
-  </si>
-  <si>
-    <t>2012-05-24</t>
-  </si>
-  <si>
-    <t>2012-05-28</t>
-  </si>
-  <si>
-    <t>2012-05-29</t>
-  </si>
-  <si>
-    <t>2012-05-30</t>
-  </si>
-  <si>
-    <t>2012-05-31</t>
-  </si>
-  <si>
-    <t>2012-06-01</t>
-  </si>
-  <si>
-    <t>2012-06-04</t>
-  </si>
-  <si>
-    <t>2012-06-05</t>
-  </si>
-  <si>
-    <t>2012-06-06</t>
-  </si>
-  <si>
-    <t>2012-06-07</t>
-  </si>
-  <si>
-    <t>2012-06-08</t>
-  </si>
-  <si>
-    <t>2012-06-11</t>
-  </si>
-  <si>
-    <t>2012-06-12</t>
-  </si>
-  <si>
-    <t>2012-06-13</t>
-  </si>
-  <si>
-    <t>2012-06-14</t>
-  </si>
-  <si>
-    <t>2012-06-15</t>
-  </si>
-  <si>
-    <t>2012-06-19</t>
-  </si>
-  <si>
-    <t>2012-06-20</t>
-  </si>
-  <si>
-    <t>2012-06-22</t>
-  </si>
-  <si>
-    <t>2012-10-18</t>
-  </si>
-  <si>
-    <t>2012-10-19</t>
-  </si>
-  <si>
-    <t>2012-10-22</t>
-  </si>
-  <si>
-    <t>2013-04-08</t>
-  </si>
-  <si>
-    <t>2013-04-12</t>
-  </si>
-  <si>
-    <t>2013-06-25</t>
-  </si>
-  <si>
-    <t>2013-06-27</t>
-  </si>
-  <si>
-    <t>2013-06-28</t>
-  </si>
-  <si>
-    <t>2013-07-01</t>
-  </si>
-  <si>
-    <t>2013-07-02</t>
-  </si>
-  <si>
-    <t>2013-07-03</t>
-  </si>
-  <si>
-    <t>2013-07-04</t>
-  </si>
-  <si>
-    <t>2013-10-28</t>
-  </si>
-  <si>
-    <t>2014-01-22</t>
-  </si>
-  <si>
-    <t>2014-01-23</t>
-  </si>
-  <si>
-    <t>2014-01-24</t>
-  </si>
-  <si>
-    <t>2014-01-27</t>
-  </si>
-  <si>
-    <t>2014-02-06</t>
-  </si>
-  <si>
-    <t>2014-02-07</t>
-  </si>
-  <si>
-    <t>2014-02-10</t>
-  </si>
-  <si>
-    <t>2014-02-11</t>
-  </si>
-  <si>
-    <t>2014-02-18</t>
-  </si>
-  <si>
-    <t>2014-02-20</t>
-  </si>
-  <si>
-    <t>2014-02-21</t>
-  </si>
-  <si>
-    <t>2014-07-08</t>
-  </si>
-  <si>
-    <t>2014-07-10</t>
-  </si>
-  <si>
-    <t>2014-07-11</t>
-  </si>
-  <si>
-    <t>2014-07-16</t>
-  </si>
-  <si>
-    <t>2014-07-17</t>
-  </si>
-  <si>
-    <t>2014-07-18</t>
-  </si>
-  <si>
-    <t>2014-10-15</t>
-  </si>
-  <si>
-    <t>2014-11-04</t>
-  </si>
-  <si>
-    <t>2015-06-11</t>
-  </si>
-  <si>
-    <t>2015-06-12</t>
-  </si>
-  <si>
-    <t>2015-06-15</t>
-  </si>
-  <si>
-    <t>2015-07-22</t>
-  </si>
-  <si>
-    <t>2015-07-23</t>
-  </si>
-  <si>
-    <t>2015-10-15</t>
-  </si>
-  <si>
-    <t>2015-10-16</t>
-  </si>
-  <si>
-    <t>2015-11-19</t>
-  </si>
-  <si>
-    <t>2016-04-01</t>
-  </si>
-  <si>
-    <t>2016-04-07</t>
-  </si>
-  <si>
-    <t>2016-04-08</t>
-  </si>
-  <si>
-    <t>2016-04-15</t>
-  </si>
-  <si>
-    <t>2016-04-18</t>
-  </si>
-  <si>
-    <t>2016-04-19</t>
-  </si>
-  <si>
-    <t>2016-04-21</t>
-  </si>
-  <si>
-    <t>2016-04-22</t>
-  </si>
-  <si>
-    <t>2016-04-27</t>
-  </si>
-  <si>
-    <t>2016-04-28</t>
-  </si>
-  <si>
-    <t>2016-05-03</t>
-  </si>
-  <si>
-    <t>2016-05-05</t>
-  </si>
-  <si>
-    <t>2016-05-10</t>
-  </si>
-  <si>
-    <t>2016-05-11</t>
-  </si>
-  <si>
-    <t>2016-05-12</t>
-  </si>
-  <si>
-    <t>2016-05-13</t>
-  </si>
-  <si>
-    <t>2016-05-16</t>
-  </si>
-  <si>
-    <t>2016-05-17</t>
-  </si>
-  <si>
-    <t>2016-10-27</t>
-  </si>
-  <si>
-    <t>2016-12-15</t>
-  </si>
-  <si>
-    <t>2017-06-26</t>
-  </si>
-  <si>
-    <t>2017-06-27</t>
-  </si>
-  <si>
-    <t>2017-07-11</t>
-  </si>
-  <si>
-    <t>2017-07-12</t>
-  </si>
-  <si>
-    <t>2017-07-13</t>
-  </si>
-  <si>
-    <t>2017-07-14</t>
-  </si>
-  <si>
-    <t>2017-07-17</t>
-  </si>
-  <si>
-    <t>2017-08-21</t>
-  </si>
-  <si>
-    <t>2017-08-22</t>
-  </si>
-  <si>
-    <t>2017-08-23</t>
-  </si>
-  <si>
-    <t>2017-08-24</t>
-  </si>
-  <si>
-    <t>2017-08-25</t>
-  </si>
-  <si>
-    <t>2017-09-06</t>
-  </si>
-  <si>
-    <t>2017-09-07</t>
-  </si>
-  <si>
-    <t>2017-09-08</t>
-  </si>
-  <si>
-    <t>2018-01-12</t>
-  </si>
-  <si>
-    <t>2018-01-15</t>
-  </si>
-  <si>
-    <t>2018-01-16</t>
-  </si>
-  <si>
-    <t>2018-01-17</t>
-  </si>
-  <si>
-    <t>2018-01-30</t>
-  </si>
-  <si>
-    <t>2018-01-31</t>
-  </si>
-  <si>
-    <t>2018-02-06</t>
-  </si>
-  <si>
-    <t>2018-02-22</t>
-  </si>
-  <si>
-    <t>2018-03-30</t>
-  </si>
-  <si>
-    <t>2018-05-16</t>
-  </si>
-  <si>
-    <t>2018-05-21</t>
-  </si>
-  <si>
-    <t>2018-11-20</t>
-  </si>
-  <si>
-    <t>2018-12-28</t>
-  </si>
-  <si>
-    <t>2019-01-09</t>
-  </si>
-  <si>
-    <t>2019-01-10</t>
-  </si>
-  <si>
-    <t>2019-01-15</t>
-  </si>
-  <si>
-    <t>2019-01-16</t>
-  </si>
-  <si>
-    <t>2019-01-17</t>
-  </si>
-  <si>
-    <t>2019-01-18</t>
-  </si>
-  <si>
-    <t>2019-01-22</t>
-  </si>
-  <si>
-    <t>2019-01-23</t>
-  </si>
-  <si>
-    <t>2019-01-24</t>
-  </si>
-  <si>
-    <t>2019-01-25</t>
-  </si>
-  <si>
-    <t>2019-01-29</t>
-  </si>
-  <si>
-    <t>2019-03-11</t>
-  </si>
-  <si>
-    <t>2019-03-12</t>
-  </si>
-  <si>
-    <t>2019-03-13</t>
-  </si>
-  <si>
-    <t>2019-04-09</t>
-  </si>
-  <si>
-    <t>2019-04-10</t>
-  </si>
-  <si>
-    <t>2019-04-18</t>
-  </si>
-  <si>
-    <t>2019-04-19</t>
-  </si>
-  <si>
-    <t>2019-04-25</t>
-  </si>
-  <si>
-    <t>2019-04-26</t>
-  </si>
-  <si>
-    <t>2019-05-02</t>
-  </si>
-  <si>
-    <t>2019-05-07</t>
-  </si>
-  <si>
-    <t>2019-05-08</t>
-  </si>
-  <si>
-    <t>2019-05-09</t>
-  </si>
-  <si>
-    <t>2019-05-10</t>
-  </si>
-  <si>
-    <t>2019-05-13</t>
-  </si>
-  <si>
-    <t>2019-07-29</t>
-  </si>
-  <si>
-    <t>2019-08-29</t>
-  </si>
-  <si>
-    <t>2019-08-30</t>
-  </si>
-  <si>
-    <t>2019-09-02</t>
-  </si>
-  <si>
-    <t>2019-09-03</t>
-  </si>
-  <si>
-    <t>2019-09-04</t>
-  </si>
-  <si>
-    <t>2019-09-05</t>
-  </si>
-  <si>
-    <t>2019-09-06</t>
-  </si>
-  <si>
-    <t>2019-09-10</t>
-  </si>
-  <si>
-    <t>2020-02-20</t>
-  </si>
-  <si>
-    <t>2020-02-21</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-02-26</t>
-  </si>
-  <si>
-    <t>2020-02-27</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-03-04</t>
-  </si>
-  <si>
-    <t>2020-03-05</t>
-  </si>
-  <si>
-    <t>2020-03-06</t>
-  </si>
-  <si>
-    <t>2020-03-09</t>
-  </si>
-  <si>
-    <t>2020-03-12</t>
-  </si>
-  <si>
-    <t>2020-11-02</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-23</t>
   </si>
   <si>
     <t>2020-12-25</t>
@@ -1796,7 +1793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P386"/>
+  <dimension ref="A1:P388"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1857,7 +1854,7 @@
         <v>39.24967816269653</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E2">
         <v>47.58658728904034</v>
@@ -1893,7 +1890,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1907,7 +1904,7 @@
         <v>41.7045814878046</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E3">
         <v>51.36624085194781</v>
@@ -1943,7 +1940,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1957,7 +1954,7 @@
         <v>47.73273319613877</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E4">
         <v>59.43490802303255</v>
@@ -1993,7 +1990,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2007,7 +2004,7 @@
         <v>47.24820828667414</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5">
         <v>58.87563172501095</v>
@@ -2043,7 +2040,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2057,7 +2054,7 @@
         <v>47.16470096247878</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E6">
         <v>58.77924108291729</v>
@@ -2093,7 +2090,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2107,7 +2104,7 @@
         <v>-15.1664654510749</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E7">
         <v>-7.294892481790129</v>
@@ -2143,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2157,7 +2154,7 @@
         <v>-14.45834344229912</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E8">
         <v>-7.294892481790129</v>
@@ -2193,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2207,7 +2204,7 @@
         <v>-13.39336737209288</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E9">
         <v>-7.294892481790129</v>
@@ -2243,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2257,7 +2254,7 @@
         <v>-16.33245230627455</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E10">
         <v>-7.294892481790129</v>
@@ -2293,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2307,7 +2304,7 @@
         <v>-29.63643996743208</v>
       </c>
       <c r="D11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E11">
         <v>-21.37792699357366</v>
@@ -2343,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2357,7 +2354,7 @@
         <v>-29.01030081710592</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E12">
         <v>-21.37792699357366</v>
@@ -2393,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2407,7 +2404,7 @@
         <v>-28.60118761449661</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E13">
         <v>-21.37792699357366</v>
@@ -2443,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2457,7 +2454,7 @@
         <v>-49.08464630848418</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E14">
         <v>-42.77667080227592</v>
@@ -2493,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2507,7 +2504,7 @@
         <v>-48.56869529606767</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E15">
         <v>-42.77667080227592</v>
@@ -2543,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2557,7 +2554,7 @@
         <v>-49.0410871967355</v>
       </c>
       <c r="D16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E16">
         <v>-42.77667080227592</v>
@@ -2593,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2607,7 +2604,7 @@
         <v>-65.70804604683664</v>
       </c>
       <c r="D17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E17">
         <v>-56.94115587886895</v>
@@ -2643,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2657,7 +2654,7 @@
         <v>-65.6116252316011</v>
       </c>
       <c r="D18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E18">
         <v>-56.94115587886895</v>
@@ -2693,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2707,7 +2704,7 @@
         <v>-79.57406496333017</v>
       </c>
       <c r="D19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E19">
         <v>-67.54165070713992</v>
@@ -2743,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2757,7 +2754,7 @@
         <v>-113.1125372679468</v>
       </c>
       <c r="D20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E20">
         <v>-103.9345101187686</v>
@@ -2793,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2807,7 +2804,7 @@
         <v>-150.4700278614179</v>
       </c>
       <c r="D21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E21">
         <v>-141.3269680910878</v>
@@ -2843,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2857,7 +2854,7 @@
         <v>-191.2456393652701</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E22">
         <v>-165.2314426418361</v>
@@ -2893,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2907,7 +2904,7 @@
         <v>-208.9753900042601</v>
       </c>
       <c r="D23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E23">
         <v>-181.8698454183375</v>
@@ -2943,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2957,7 +2954,7 @@
         <v>-222.2487414251906</v>
       </c>
       <c r="D24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E24">
         <v>-206.4607237347662</v>
@@ -2993,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3007,7 +3004,7 @@
         <v>-239.7112109310854</v>
       </c>
       <c r="D25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E25">
         <v>-219.5184020745525</v>
@@ -3043,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3057,7 +3054,7 @@
         <v>-263.1154559964206</v>
       </c>
       <c r="D26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E26">
         <v>-240.6747187530921</v>
@@ -3093,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3107,7 +3104,7 @@
         <v>-268.6224791106823</v>
       </c>
       <c r="D27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E27">
         <v>-252.6279978948062</v>
@@ -3143,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3172,7 +3169,7 @@
         <v>59.3</v>
       </c>
       <c r="P28" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3201,7 +3198,7 @@
         <v>65.5</v>
       </c>
       <c r="P29" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3215,7 +3212,7 @@
         <v>-254.0793405031437</v>
       </c>
       <c r="D30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E30">
         <v>-235.7082244929039</v>
@@ -3251,7 +3248,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3265,7 +3262,7 @@
         <v>-238.7059320352077</v>
       </c>
       <c r="D31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E31">
         <v>-223.7765478327873</v>
@@ -3301,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3330,7 +3327,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="P32" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3380,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3394,7 +3391,7 @@
         <v>-85.8076603763717</v>
       </c>
       <c r="D34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E34">
         <v>-85.31060902491748</v>
@@ -3430,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3444,7 +3441,7 @@
         <v>-78.41701518144652</v>
       </c>
       <c r="D35" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E35">
         <v>-77.28396586589429</v>
@@ -3480,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3509,7 +3506,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="P36" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3538,7 +3535,7 @@
         <v>70.09999999999999</v>
       </c>
       <c r="P37" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3552,7 +3549,7 @@
         <v>-77.43890142953504</v>
       </c>
       <c r="D38" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E38">
         <v>-86.03210595388953</v>
@@ -3588,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3602,7 +3599,7 @@
         <v>-75.24842836769179</v>
       </c>
       <c r="D39" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E39">
         <v>-82.41442691778926</v>
@@ -3638,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3652,7 +3649,7 @@
         <v>-75.26941837884658</v>
       </c>
       <c r="D40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E40">
         <v>-76.41687497573176</v>
@@ -3688,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3702,7 +3699,7 @@
         <v>2.405986219478436</v>
       </c>
       <c r="D41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E41">
         <v>22.3137495724129</v>
@@ -3738,7 +3735,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3752,7 +3749,7 @@
         <v>-1.953147134466214</v>
       </c>
       <c r="D42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E42">
         <v>19.32012787151115</v>
@@ -3788,7 +3785,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3802,7 +3799,7 @@
         <v>-16.2502130791469</v>
       </c>
       <c r="D43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E43">
         <v>8.401660897453333</v>
@@ -3838,7 +3835,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3852,7 +3849,7 @@
         <v>-14.74859467309044</v>
       </c>
       <c r="D44" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E44">
         <v>8.401660897453333</v>
@@ -3888,7 +3885,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3902,7 +3899,7 @@
         <v>-29.86968571903745</v>
       </c>
       <c r="D45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E45">
         <v>-0.9514709154835543</v>
@@ -3938,7 +3935,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3952,7 +3949,7 @@
         <v>60.63454015125168</v>
       </c>
       <c r="D46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E46">
         <v>75.91925407409063</v>
@@ -3988,7 +3985,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4002,7 +3999,7 @@
         <v>61.36441721922468</v>
       </c>
       <c r="D47" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E47">
         <v>75.91925407409063</v>
@@ -4038,7 +4035,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4052,7 +4049,7 @@
         <v>89.12505313226613</v>
       </c>
       <c r="D48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E48">
         <v>73.92461224371841</v>
@@ -4088,7 +4085,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4102,7 +4099,7 @@
         <v>60.18080332327113</v>
       </c>
       <c r="D49" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E49">
         <v>75.16419394721952</v>
@@ -4138,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4152,7 +4149,7 @@
         <v>60.90367287266527</v>
       </c>
       <c r="D50" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E50">
         <v>75.16419394721952</v>
@@ -4188,7 +4185,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4202,7 +4199,7 @@
         <v>88.41554187615753</v>
       </c>
       <c r="D51" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E51">
         <v>73.33247692380556</v>
@@ -4238,7 +4235,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4252,7 +4249,7 @@
         <v>39.99810912339372</v>
       </c>
       <c r="D52" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E52">
         <v>55.15583755182445</v>
@@ -4288,7 +4285,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4302,7 +4299,7 @@
         <v>41.30719414984996</v>
       </c>
       <c r="D53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E53">
         <v>55.15583755182445</v>
@@ -4338,7 +4335,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4352,7 +4349,7 @@
         <v>43.08151977105167</v>
       </c>
       <c r="D54" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E54">
         <v>55.9485635535138</v>
@@ -4388,7 +4385,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4402,7 +4399,7 @@
         <v>42.16532004667869</v>
       </c>
       <c r="D55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E55">
         <v>55.9485635535138</v>
@@ -4438,7 +4435,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4452,7 +4449,7 @@
         <v>42.55008107334416</v>
       </c>
       <c r="D56" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E56">
         <v>56.30400099154195</v>
@@ -4502,7 +4499,7 @@
         <v>43.58368103616133</v>
       </c>
       <c r="D57" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E57">
         <v>56.30400099154195</v>
@@ -4552,7 +4549,7 @@
         <v>44.27504780738504</v>
       </c>
       <c r="D58" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E58">
         <v>56.96559598792828</v>
@@ -4588,7 +4585,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4602,7 +4599,7 @@
         <v>44.76828997217422</v>
       </c>
       <c r="D59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E59">
         <v>57.43759805949687</v>
@@ -4652,7 +4649,7 @@
         <v>46.95250922066406</v>
       </c>
       <c r="D60" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E60">
         <v>58.6275946856681</v>
@@ -4688,7 +4685,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4702,7 +4699,7 @@
         <v>47.37813227189867</v>
       </c>
       <c r="D61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E61">
         <v>59.01897220404476</v>
@@ -4738,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4752,7 +4749,7 @@
         <v>48.93720072957618</v>
       </c>
       <c r="D62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E62">
         <v>59.68207127489522</v>
@@ -4788,7 +4785,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4802,7 +4799,7 @@
         <v>48.94662890110423</v>
       </c>
       <c r="D63" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E63">
         <v>59.69094484809811</v>
@@ -4838,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4852,7 +4849,7 @@
         <v>54.08932335660573</v>
       </c>
       <c r="D64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E64">
         <v>62.52278850035134</v>
@@ -4902,7 +4899,7 @@
         <v>67.18932335660573</v>
       </c>
       <c r="D65" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E65">
         <v>59.01736085156006</v>
@@ -4952,7 +4949,7 @@
         <v>54.27142458878302</v>
       </c>
       <c r="D66" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E66">
         <v>62.70264156916842</v>
@@ -4988,7 +4985,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5002,7 +4999,7 @@
         <v>67.37142458878301</v>
       </c>
       <c r="D67" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E67">
         <v>59.17608118479113</v>
@@ -5038,7 +5035,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5052,7 +5049,7 @@
         <v>54.44666418857609</v>
       </c>
       <c r="D68" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E68">
         <v>57.92296041603655</v>
@@ -5088,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="P68" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5102,7 +5099,7 @@
         <v>54.38623819452964</v>
       </c>
       <c r="D69" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E69">
         <v>62.81603772299223</v>
@@ -5138,7 +5135,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5152,7 +5149,7 @@
         <v>54.68320045790918</v>
       </c>
       <c r="D70" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E70">
         <v>62.81603772299223</v>
@@ -5188,7 +5185,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5202,7 +5199,7 @@
         <v>67.48623819452963</v>
       </c>
       <c r="D71" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E71">
         <v>59.27615329054065</v>
@@ -5238,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5252,7 +5249,7 @@
         <v>54.5181037654851</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E72">
         <v>55.68274527440479</v>
@@ -5288,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="P72" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5302,7 +5299,7 @@
         <v>101.1269386779503</v>
       </c>
       <c r="D73" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E73">
         <v>83.94100067443752</v>
@@ -5338,7 +5335,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5352,7 +5349,7 @@
         <v>75.45009517739128</v>
       </c>
       <c r="D74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E74">
         <v>80.27451240300203</v>
@@ -5388,7 +5385,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5402,7 +5399,7 @@
         <v>121.9136696617972</v>
       </c>
       <c r="D75" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E75">
         <v>104.5517569407011</v>
@@ -5438,7 +5435,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5452,7 +5449,7 @@
         <v>124.0730248787269</v>
       </c>
       <c r="D76" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E76">
         <v>106.3319083146578</v>
@@ -5488,7 +5485,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5502,7 +5499,7 @@
         <v>125.8987716223492</v>
       </c>
       <c r="D77" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E77">
         <v>107.8370361179367</v>
@@ -5538,7 +5535,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5552,7 +5549,7 @@
         <v>127.8315078706938</v>
       </c>
       <c r="D78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E78">
         <v>102.3788447068554</v>
@@ -5588,7 +5585,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5602,7 +5599,7 @@
         <v>127.8608026942557</v>
       </c>
       <c r="D79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E79">
         <v>102.3788447068554</v>
@@ -5638,7 +5635,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5652,7 +5649,7 @@
         <v>126.3344628429377</v>
       </c>
       <c r="D80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E80">
         <v>101.3477167540643</v>
@@ -5688,7 +5685,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5702,7 +5699,7 @@
         <v>126.3293867347399</v>
       </c>
       <c r="D81" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E81">
         <v>101.3477167540643</v>
@@ -5738,7 +5735,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5752,7 +5749,7 @@
         <v>126.0311094090764</v>
       </c>
       <c r="D82" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E82">
         <v>101.1387743378843</v>
@@ -5788,7 +5785,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5802,7 +5799,7 @@
         <v>126.0190685536726</v>
       </c>
       <c r="D83" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E83">
         <v>101.1387743378843</v>
@@ -5838,7 +5835,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5852,7 +5849,7 @@
         <v>126.620958855311</v>
       </c>
       <c r="D84" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E84">
         <v>101.5450481911581</v>
@@ -5888,7 +5885,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5902,7 +5899,7 @@
         <v>126.6224604616829</v>
       </c>
       <c r="D85" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E85">
         <v>101.5450481911581</v>
@@ -5938,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5952,7 +5949,7 @@
         <v>125.7796367080902</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E86">
         <v>100.9655660999601</v>
@@ -5988,7 +5985,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6002,7 +5999,7 @@
         <v>125.7618222447556</v>
       </c>
       <c r="D87" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E87">
         <v>100.9655660999601</v>
@@ -6038,7 +6035,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6052,7 +6049,7 @@
         <v>125.0669218669525</v>
       </c>
       <c r="D88" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E88">
         <v>100.4746655716255</v>
@@ -6088,7 +6085,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6102,7 +6099,7 @@
         <v>125.0327440526733</v>
       </c>
       <c r="D89" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E89">
         <v>100.4746655716255</v>
@@ -6138,7 +6135,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6152,7 +6149,7 @@
         <v>123.2289469739378</v>
       </c>
       <c r="D90" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E90">
         <v>99.20871347694691</v>
@@ -6188,7 +6185,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6202,7 +6199,7 @@
         <v>123.1525707565027</v>
       </c>
       <c r="D91" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E91">
         <v>99.20871347694691</v>
@@ -6238,7 +6235,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6252,7 +6249,7 @@
         <v>122.9583501275863</v>
       </c>
       <c r="D92" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E92">
         <v>99.02233299604161</v>
@@ -6288,7 +6285,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6302,7 +6299,7 @@
         <v>122.8757612274544</v>
       </c>
       <c r="D93" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E93">
         <v>99.02233299604161</v>
@@ -6338,7 +6335,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6352,7 +6349,7 @@
         <v>124.3519741722009</v>
       </c>
       <c r="D94" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E94">
         <v>99.98222710840369</v>
@@ -6388,7 +6385,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6402,7 +6399,7 @@
         <v>124.3013817424811</v>
       </c>
       <c r="D95" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E95">
         <v>99.98222710840369</v>
@@ -6438,7 +6435,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6452,7 +6449,7 @@
         <v>124.6891745905705</v>
       </c>
       <c r="D96" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E96">
         <v>100.2144824986073</v>
@@ -6488,7 +6485,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6502,7 +6499,7 @@
         <v>124.6463240071908</v>
       </c>
       <c r="D97" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E97">
         <v>100.2144824986073</v>
@@ -6538,7 +6535,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6552,7 +6549,7 @@
         <v>124.4800191586875</v>
       </c>
       <c r="D98" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E98">
         <v>100.0704213593001</v>
@@ -6588,7 +6585,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6602,7 +6599,7 @@
         <v>124.4323665373309</v>
       </c>
       <c r="D99" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E99">
         <v>100.0704213593001</v>
@@ -6638,7 +6635,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6652,7 +6649,7 @@
         <v>123.0108457893896</v>
       </c>
       <c r="D100" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E100">
         <v>99.05849072228368</v>
@@ -6688,7 +6685,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6702,7 +6699,7 @@
         <v>122.9294621467991</v>
       </c>
       <c r="D101" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E101">
         <v>99.05849072228368</v>
@@ -6738,7 +6735,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6752,7 +6749,7 @@
         <v>121.6453568496303</v>
       </c>
       <c r="D102" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E102">
         <v>98.11797538112289</v>
@@ -6788,7 +6785,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6802,7 +6799,7 @@
         <v>121.5326226956677</v>
       </c>
       <c r="D103" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E103">
         <v>98.11797538112289</v>
@@ -6838,7 +6835,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6852,7 +6849,7 @@
         <v>121.0299428079651</v>
       </c>
       <c r="D104" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E104">
         <v>97.69409326058823</v>
@@ -6888,7 +6885,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6902,7 +6899,7 @@
         <v>120.9030792499847</v>
       </c>
       <c r="D105" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E105">
         <v>97.69409326058823</v>
@@ -6938,7 +6935,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6952,7 +6949,7 @@
         <v>120.2680139970007</v>
       </c>
       <c r="D106" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E106">
         <v>97.169295355077</v>
@@ -6988,7 +6985,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7002,7 +6999,7 @@
         <v>120.1236571755032</v>
       </c>
       <c r="D107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E107">
         <v>97.169295355077</v>
@@ -7038,7 +7035,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7052,7 +7049,7 @@
         <v>119.3894537106139</v>
       </c>
       <c r="D108" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E108">
         <v>96.56416454557592</v>
@@ -7088,7 +7085,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7102,7 +7099,7 @@
         <v>119.2249258621331</v>
       </c>
       <c r="D109" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E109">
         <v>96.56416454557592</v>
@@ -7138,7 +7135,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7152,7 +7149,7 @@
         <v>118.0996069245826</v>
       </c>
       <c r="D110" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E110">
         <v>95.67574966744206</v>
@@ -7188,7 +7185,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7202,7 +7199,7 @@
         <v>117.9054652468306</v>
       </c>
       <c r="D111" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E111">
         <v>95.67574966744206</v>
@@ -7238,7 +7235,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7252,7 +7249,7 @@
         <v>117.1017444652623</v>
       </c>
       <c r="D112" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E112">
         <v>94.98844644291023</v>
@@ -7288,7 +7285,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7302,7 +7299,7 @@
         <v>116.8846926800259</v>
       </c>
       <c r="D113" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E113">
         <v>94.98844644291023</v>
@@ -7338,7 +7335,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7352,7 +7349,7 @@
         <v>115.7903395541055</v>
       </c>
       <c r="D114" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E114">
         <v>94.08518285614407</v>
@@ -7388,7 +7385,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7402,7 +7399,7 @@
         <v>115.5431789826436</v>
       </c>
       <c r="D115" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E115">
         <v>94.08518285614407</v>
@@ -7438,7 +7435,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7452,7 +7449,7 @@
         <v>114.3600161010092</v>
       </c>
       <c r="D116" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E116">
         <v>93.10001108998082</v>
@@ -7488,7 +7485,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7502,7 +7499,7 @@
         <v>114.0800164706752</v>
       </c>
       <c r="D117" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E117">
         <v>93.10001108998082</v>
@@ -7538,7 +7535,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7552,7 +7549,7 @@
         <v>112.9215721869154</v>
       </c>
       <c r="D118" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E118">
         <v>92.10924614915092</v>
@@ -7588,7 +7585,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7602,7 +7599,7 @@
         <v>112.6085470585538</v>
       </c>
       <c r="D119" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E119">
         <v>92.10924614915092</v>
@@ -7638,7 +7635,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7652,7 +7649,7 @@
         <v>111.0753114680939</v>
       </c>
       <c r="D120" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E120">
         <v>91.07689300844227</v>
@@ -7702,7 +7699,7 @@
         <v>109.3637030177276</v>
       </c>
       <c r="D121" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E121">
         <v>89.92443844086398</v>
@@ -7738,7 +7735,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7752,7 +7749,7 @@
         <v>106.6367917601738</v>
       </c>
       <c r="D122" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E122">
         <v>88.08836352929409</v>
@@ -7788,7 +7785,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7802,7 +7799,7 @@
         <v>99.96873044828921</v>
       </c>
       <c r="D123" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E123">
         <v>83.59864643650396</v>
@@ -7838,7 +7835,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7852,7 +7849,7 @@
         <v>39.91051382546476</v>
       </c>
       <c r="D124" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E124">
         <v>42.55014562583152</v>
@@ -7888,7 +7885,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7902,7 +7899,7 @@
         <v>34.76754143004694</v>
       </c>
       <c r="D125" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E125">
         <v>38.11145388461416</v>
@@ -7938,7 +7935,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7952,7 +7949,7 @@
         <v>27.87373902743889</v>
       </c>
       <c r="D126" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E126">
         <v>28.73232502982488</v>
@@ -7988,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8002,7 +7999,7 @@
         <v>52.34452590842368</v>
       </c>
       <c r="D127" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E127">
         <v>60.02089394070224</v>
@@ -8038,7 +8035,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8052,7 +8049,7 @@
         <v>66.2681578761451</v>
       </c>
       <c r="D128" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E128">
         <v>59.00746128062423</v>
@@ -8088,7 +8085,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8102,7 +8099,7 @@
         <v>65.90298372726488</v>
       </c>
       <c r="D129" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E129">
         <v>59.00746128062423</v>
@@ -8138,7 +8135,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8152,7 +8149,7 @@
         <v>75.19054270184851</v>
       </c>
       <c r="D130" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E130">
         <v>82.88620847856147</v>
@@ -8188,7 +8185,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8202,7 +8199,7 @@
         <v>91.01410438583636</v>
       </c>
       <c r="D131" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E131">
         <v>85.34034548895417</v>
@@ -8238,7 +8235,7 @@
         <v>0</v>
       </c>
       <c r="P131" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8252,7 +8249,7 @@
         <v>90.69117289103272</v>
       </c>
       <c r="D132" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E132">
         <v>85.34034548895417</v>
@@ -8288,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="P132" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8302,7 +8299,7 @@
         <v>106.425283452306</v>
       </c>
       <c r="D133" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E133">
         <v>102.4841645631825</v>
@@ -8352,7 +8349,7 @@
         <v>106.7743510447031</v>
       </c>
       <c r="D134" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E134">
         <v>102.4841645631825</v>
@@ -8402,7 +8399,7 @@
         <v>64.83381773702186</v>
       </c>
       <c r="D135" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E135">
         <v>61.17785949472258</v>
@@ -8438,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="P135" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8452,7 +8449,7 @@
         <v>53.81062761975522</v>
       </c>
       <c r="D136" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E136">
         <v>45.81713512679965</v>
@@ -8488,7 +8485,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8502,7 +8499,7 @@
         <v>53.43128846396477</v>
       </c>
       <c r="D137" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E137">
         <v>47.7894228477703</v>
@@ -8538,7 +8535,7 @@
         <v>0</v>
       </c>
       <c r="P137" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8552,7 +8549,7 @@
         <v>48.70129852147022</v>
       </c>
       <c r="D138" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E138">
         <v>39.19252273181839</v>
@@ -8588,7 +8585,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8602,7 +8599,7 @@
         <v>44.87334693499027</v>
       </c>
       <c r="D139" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E139">
         <v>34.44403390958535</v>
@@ -8638,7 +8635,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8652,7 +8649,7 @@
         <v>40.45906823400685</v>
       </c>
       <c r="D140" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E140">
         <v>29.40254968722779</v>
@@ -8688,7 +8685,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8702,7 +8699,7 @@
         <v>37.79538016242914</v>
       </c>
       <c r="D141" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E141">
         <v>25.15160114518396</v>
@@ -8738,7 +8735,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8752,7 +8749,7 @@
         <v>37.68076952930594</v>
       </c>
       <c r="D142" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E142">
         <v>25.01802919408082</v>
@@ -8788,7 +8785,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8802,7 +8799,7 @@
         <v>63.15408222226404</v>
       </c>
       <c r="D143" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E143">
         <v>53.56243089690908</v>
@@ -8838,7 +8835,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8852,7 +8849,7 @@
         <v>31.1030054990203</v>
       </c>
       <c r="D144" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E144">
         <v>14.08734435244297</v>
@@ -8888,7 +8885,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8902,7 +8899,7 @@
         <v>25.05484991241799</v>
       </c>
       <c r="D145" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E145">
         <v>6.922187058405115</v>
@@ -8938,7 +8935,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8952,7 +8949,7 @@
         <v>18.81638310475921</v>
       </c>
       <c r="D146" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E146">
         <v>-0.4684290245420044</v>
@@ -8988,7 +8985,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9002,7 +8999,7 @@
         <v>13.01676813424353</v>
       </c>
       <c r="D147" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E147">
         <v>-7.339144057179965</v>
@@ -9038,7 +9035,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9052,7 +9049,7 @@
         <v>8.024396355482963</v>
       </c>
       <c r="D148" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E148">
         <v>-13.25353044372964</v>
@@ -9088,7 +9085,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9102,7 +9099,7 @@
         <v>7.720504878426524</v>
       </c>
       <c r="D149" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E149">
         <v>-13.61354602240461</v>
@@ -9138,7 +9135,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9152,7 +9149,7 @@
         <v>10.31388326476601</v>
       </c>
       <c r="D150" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E150">
         <v>-10.54121036651594</v>
@@ -9188,7 +9185,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9202,7 +9199,7 @@
         <v>11.14758883248732</v>
       </c>
       <c r="D151" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E151">
         <v>-9.553532148900146</v>
@@ -9238,7 +9235,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9252,7 +9249,7 @@
         <v>20.84560393192861</v>
       </c>
       <c r="D152" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E152">
         <v>1.935557811248756</v>
@@ -9288,7 +9285,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9302,7 +9299,7 @@
         <v>21.43389351871438</v>
       </c>
       <c r="D153" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E153">
         <v>2.632495474873352</v>
@@ -9338,7 +9335,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9352,7 +9349,7 @@
         <v>22.6162561113628</v>
       </c>
       <c r="D154" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E154">
         <v>4.033222330128012</v>
@@ -9388,7 +9385,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9402,7 +9399,7 @@
         <v>23.86897930913528</v>
       </c>
       <c r="D155" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E155">
         <v>5.517304316678292</v>
@@ -9438,7 +9435,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9452,7 +9449,7 @@
         <v>24.29022509961407</v>
       </c>
       <c r="D156" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E156">
         <v>6.016347753146405</v>
@@ -9488,7 +9485,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9502,7 +9499,7 @@
         <v>80.77258742920839</v>
       </c>
       <c r="D157" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E157">
         <v>71.50140757768273</v>
@@ -9538,7 +9535,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9552,7 +9549,7 @@
         <v>80.87119828430862</v>
       </c>
       <c r="D158" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E158">
         <v>71.50140757768273</v>
@@ -9588,7 +9585,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9602,7 +9599,7 @@
         <v>82.15331534782203</v>
       </c>
       <c r="D159" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E159">
         <v>71.50140757768273</v>
@@ -9638,7 +9635,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9652,7 +9649,7 @@
         <v>76.19581669669289</v>
       </c>
       <c r="D160" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E160">
         <v>66.74547500154564</v>
@@ -9688,7 +9685,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9702,7 +9699,7 @@
         <v>75.21863715900577</v>
       </c>
       <c r="D161" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E161">
         <v>66.74547500154564</v>
@@ -9738,7 +9735,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9752,7 +9749,7 @@
         <v>77.89414970172665</v>
       </c>
       <c r="D162" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E162">
         <v>66.74547500154564</v>
@@ -9788,7 +9785,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9802,7 +9799,7 @@
         <v>60.11863715900578</v>
       </c>
       <c r="D163" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E163">
         <v>68.03744024109169</v>
@@ -9838,7 +9835,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9852,7 +9849,7 @@
         <v>72.44565132750211</v>
       </c>
       <c r="D164" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E164">
         <v>62.8485060058029</v>
@@ -9888,7 +9885,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9902,7 +9899,7 @@
         <v>71.50850914251097</v>
       </c>
       <c r="D165" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E165">
         <v>62.8485060058029</v>
@@ -9938,7 +9935,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9952,7 +9949,7 @@
         <v>74.40422712505978</v>
       </c>
       <c r="D166" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E166">
         <v>62.8485060058029</v>
@@ -9988,7 +9985,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10002,7 +9999,7 @@
         <v>56.40850914251097</v>
       </c>
       <c r="D167" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E167">
         <v>64.59422790923679</v>
@@ -10038,7 +10035,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10052,7 +10049,7 @@
         <v>67.88820949982238</v>
       </c>
       <c r="D168" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E168">
         <v>60.43722302948107</v>
@@ -10102,7 +10099,7 @@
         <v>70.99880138202717</v>
       </c>
       <c r="D169" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E169">
         <v>60.43722302948107</v>
@@ -10152,7 +10149,7 @@
         <v>52.78820949982239</v>
       </c>
       <c r="D170" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E170">
         <v>61.23438147825242</v>
@@ -10202,7 +10199,7 @@
         <v>64.41272601732022</v>
       </c>
       <c r="D171" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E171">
         <v>56.61794172047242</v>
@@ -10238,7 +10235,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10252,7 +10249,7 @@
         <v>49.31272601732023</v>
       </c>
       <c r="D172" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E172">
         <v>58.0089327786641</v>
@@ -10288,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10302,7 +10299,7 @@
         <v>61.16879231159055</v>
       </c>
       <c r="D173" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E173">
         <v>53.82441738118666</v>
@@ -10338,7 +10335,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10352,7 +10349,7 @@
         <v>46.06879231159056</v>
       </c>
       <c r="D174" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E174">
         <v>54.08446933112747</v>
@@ -10388,7 +10385,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10402,7 +10399,7 @@
         <v>58.07192781203269</v>
       </c>
       <c r="D175" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E175">
         <v>50.68812094147531</v>
@@ -10438,7 +10435,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10452,7 +10449,7 @@
         <v>42.9719278120327</v>
       </c>
       <c r="D176" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E176">
         <v>51.29394934141796</v>
@@ -10488,7 +10485,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10502,7 +10499,7 @@
         <v>72.62623022483724</v>
       </c>
       <c r="D177" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E177">
         <v>78.13274022613687</v>
@@ -10538,7 +10535,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10552,7 +10549,7 @@
         <v>72.14377020837516</v>
       </c>
       <c r="D178" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E178">
         <v>78.53925022743653</v>
@@ -10588,7 +10585,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10602,7 +10599,7 @@
         <v>83.25643025082999</v>
       </c>
       <c r="D179" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E179">
         <v>77.7759602547289</v>
@@ -10638,7 +10635,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10667,7 +10664,7 @@
         <v>71.40000000000001</v>
       </c>
       <c r="P180" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10696,7 +10693,7 @@
         <v>72.09999999999999</v>
       </c>
       <c r="P181" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10710,7 +10707,7 @@
         <v>66.25534327603719</v>
       </c>
       <c r="D182" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E182">
         <v>53.25789242985769</v>
@@ -10760,7 +10757,7 @@
         <v>66.50153349826817</v>
       </c>
       <c r="D183" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E183">
         <v>53.49926887679366</v>
@@ -10796,7 +10793,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10810,7 +10807,7 @@
         <v>65.13958707494101</v>
       </c>
       <c r="D184" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E184">
         <v>53.20617458032149</v>
@@ -10846,7 +10843,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10860,7 +10857,7 @@
         <v>65.2660759255686</v>
       </c>
       <c r="D185" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E185">
         <v>53.20617458032149</v>
@@ -10896,7 +10893,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10910,7 +10907,7 @@
         <v>63.88275361614285</v>
       </c>
       <c r="D186" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E186">
         <v>51.96525040581191</v>
@@ -10946,7 +10943,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10960,7 +10957,7 @@
         <v>82.52792611826956</v>
       </c>
       <c r="D187" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E187">
         <v>99.94767772279653</v>
@@ -10996,7 +10993,7 @@
         <v>0</v>
       </c>
       <c r="P187" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11010,7 +11007,7 @@
         <v>80.81507949145069</v>
       </c>
       <c r="D188" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E188">
         <v>99.94767772279653</v>
@@ -11046,7 +11043,7 @@
         <v>0</v>
       </c>
       <c r="P188" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11060,7 +11057,7 @@
         <v>82.55697724266327</v>
       </c>
       <c r="D189" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E189">
         <v>99.94767772279653</v>
@@ -11096,7 +11093,7 @@
         <v>0</v>
       </c>
       <c r="P189" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11110,7 +11107,7 @@
         <v>80.68386776738032</v>
       </c>
       <c r="D190" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E190">
         <v>99.94767772279653</v>
@@ -11146,7 +11143,7 @@
         <v>0</v>
       </c>
       <c r="P190" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11160,7 +11157,7 @@
         <v>83.46212404051099</v>
       </c>
       <c r="D191" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E191">
         <v>101.9293746430213</v>
@@ -11196,7 +11193,7 @@
         <v>0</v>
       </c>
       <c r="P191" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11210,7 +11207,7 @@
         <v>81.65627098338047</v>
       </c>
       <c r="D192" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E192">
         <v>101.9293746430213</v>
@@ -11246,7 +11243,7 @@
         <v>0</v>
       </c>
       <c r="P192" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11260,7 +11257,7 @@
         <v>83.46017302146748</v>
       </c>
       <c r="D193" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E193">
         <v>101.9293746430213</v>
@@ -11296,7 +11293,7 @@
         <v>0</v>
       </c>
       <c r="P193" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11310,7 +11307,7 @@
         <v>81.57259587924717</v>
       </c>
       <c r="D194" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E194">
         <v>101.9293746430213</v>
@@ -11346,7 +11343,7 @@
         <v>0</v>
       </c>
       <c r="P194" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11396,7 +11393,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11410,7 +11407,7 @@
         <v>33.77481800214022</v>
       </c>
       <c r="D196" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E196">
         <v>39.96346245740297</v>
@@ -11446,7 +11443,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11460,7 +11457,7 @@
         <v>24.63764534106641</v>
       </c>
       <c r="D197" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E197">
         <v>34.16939555445761</v>
@@ -11496,7 +11493,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11510,7 +11507,7 @@
         <v>43.28817453279771</v>
       </c>
       <c r="D198" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E198">
         <v>46.14425779500065</v>
@@ -11546,7 +11543,7 @@
         <v>0</v>
       </c>
       <c r="P198" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11560,7 +11557,7 @@
         <v>24.23598497532834</v>
       </c>
       <c r="D199" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E199">
         <v>33.03819935984974</v>
@@ -11596,7 +11593,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11610,7 +11607,7 @@
         <v>24.17071464201896</v>
       </c>
       <c r="D200" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E200">
         <v>33.03819935984974</v>
@@ -11646,7 +11643,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11660,7 +11657,7 @@
         <v>23.32366123264667</v>
       </c>
       <c r="D201" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E201">
         <v>32.29172372079252</v>
@@ -11710,7 +11707,7 @@
         <v>22.94912669441385</v>
       </c>
       <c r="D202" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E202">
         <v>31.49029169144093</v>
@@ -11746,7 +11743,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11760,7 +11757,7 @@
         <v>22.44844130251504</v>
       </c>
       <c r="D203" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E203">
         <v>30.75050022869873</v>
@@ -11796,7 +11793,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11810,7 +11807,7 @@
         <v>22.12056025614258</v>
       </c>
       <c r="D204" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E204">
         <v>30.75050022869873</v>
@@ -11846,7 +11843,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11860,7 +11857,7 @@
         <v>21.00936580829927</v>
       </c>
       <c r="D205" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E205">
         <v>29.75836232883863</v>
@@ -11910,7 +11907,7 @@
         <v>22.21712321587968</v>
       </c>
       <c r="D206" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E206">
         <v>29.83950116198865</v>
@@ -11946,7 +11943,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11960,7 +11957,7 @@
         <v>22.36605537346383</v>
       </c>
       <c r="D207" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E207">
         <v>29.99532225197207</v>
@@ -11996,7 +11993,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12010,7 +12007,7 @@
         <v>21.71901729202467</v>
       </c>
       <c r="D208" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E208">
         <v>28.96097369076485</v>
@@ -12046,7 +12043,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12060,7 +12057,7 @@
         <v>21.37743590654157</v>
       </c>
       <c r="D209" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E209">
         <v>28.96097369076485</v>
@@ -12096,7 +12093,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12110,7 +12107,7 @@
         <v>21.5505095382167</v>
       </c>
       <c r="D210" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E210">
         <v>29.1420529309536</v>
@@ -12160,7 +12157,7 @@
         <v>21.4477218260166</v>
       </c>
       <c r="D211" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E211">
         <v>29.03451072105261</v>
@@ -12196,7 +12193,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12210,7 +12207,7 @@
         <v>21.93200329930192</v>
       </c>
       <c r="D212" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E212">
         <v>29.03451072105261</v>
@@ -12246,7 +12243,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12260,7 +12257,7 @@
         <v>21.82005829590757</v>
       </c>
       <c r="D213" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E213">
         <v>29.42406980298699</v>
@@ -12296,7 +12293,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12310,7 +12307,7 @@
         <v>22.28137628646834</v>
       </c>
       <c r="D214" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E214">
         <v>29.42406980298699</v>
@@ -12346,7 +12343,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12360,7 +12357,7 @@
         <v>25.08434479788652</v>
       </c>
       <c r="D215" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E215">
         <v>32.83934753082841</v>
@@ -12396,7 +12393,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12410,7 +12407,7 @@
         <v>25.82576998567276</v>
       </c>
       <c r="D216" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E216">
         <v>32.83934753082841</v>
@@ -12446,7 +12443,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12460,7 +12457,7 @@
         <v>25.62576998567276</v>
       </c>
       <c r="D217" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E217">
         <v>32.83934753082841</v>
@@ -12496,7 +12493,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12510,7 +12507,7 @@
         <v>39.54291961010028</v>
       </c>
       <c r="D218" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E218">
         <v>32.24005830276027</v>
@@ -12546,7 +12543,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12560,7 +12557,7 @@
         <v>27.32311840696546</v>
       </c>
       <c r="D219" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E219">
         <v>35.18167674737576</v>
@@ -12596,7 +12593,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12610,7 +12607,7 @@
         <v>27.936331890267</v>
       </c>
       <c r="D220" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E220">
         <v>35.18167674737576</v>
@@ -12646,7 +12643,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12660,7 +12657,7 @@
         <v>27.736331890267</v>
       </c>
       <c r="D221" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E221">
         <v>35.18167674737576</v>
@@ -12696,7 +12693,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12710,7 +12707,7 @@
         <v>41.90990492366392</v>
       </c>
       <c r="D222" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E222">
         <v>34.44924459541966</v>
@@ -12746,7 +12743,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12760,7 +12757,7 @@
         <v>29.32582523799188</v>
       </c>
       <c r="D223" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E223">
         <v>36.94571726179005</v>
@@ -12810,7 +12807,7 @@
         <v>43.69251428559836</v>
       </c>
       <c r="D224" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E224">
         <v>36.11301333322514</v>
@@ -12860,7 +12857,7 @@
         <v>44.11030807122381</v>
       </c>
       <c r="D225" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E225">
         <v>36.50295419980888</v>
@@ -12896,7 +12893,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12910,7 +12907,7 @@
         <v>45.39200591893177</v>
       </c>
       <c r="D226" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E226">
         <v>37.69920552433632</v>
@@ -12960,7 +12957,7 @@
         <v>46.2461284866414</v>
       </c>
       <c r="D227" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E227">
         <v>38.49638658753197</v>
@@ -12996,7 +12993,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13010,7 +13007,7 @@
         <v>46.90307634880546</v>
       </c>
       <c r="D228" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E228">
         <v>39.10953792555176</v>
@@ -13060,7 +13057,7 @@
         <v>33.83569560835785</v>
       </c>
       <c r="D229" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E229">
         <v>40.9206360962427</v>
@@ -13110,7 +13107,7 @@
         <v>46.73201951087134</v>
       </c>
       <c r="D230" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E230">
         <v>38.94988487681324</v>
@@ -13160,7 +13157,7 @@
         <v>33.22416759327695</v>
       </c>
       <c r="D231" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E231">
         <v>40.34408700115657</v>
@@ -13196,7 +13193,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13210,7 +13207,7 @@
         <v>46.15305807647522</v>
       </c>
       <c r="D232" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E232">
         <v>38.40952087137686</v>
@@ -13246,7 +13243,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13260,7 +13257,7 @@
         <v>33.50490381338868</v>
       </c>
       <c r="D233" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E233">
         <v>40.17087450822464</v>
@@ -13296,7 +13293,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13310,7 +13307,7 @@
         <v>45.97912084507914</v>
       </c>
       <c r="D234" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E234">
         <v>38.24717945540719</v>
@@ -13346,7 +13343,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13360,7 +13357,7 @@
         <v>34.16379673036971</v>
       </c>
       <c r="D235" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E235">
         <v>40.85258622752538</v>
@@ -13396,7 +13393,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13410,7 +13407,7 @@
         <v>46.66368491466983</v>
       </c>
       <c r="D236" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E236">
         <v>38.8861059203585</v>
@@ -13446,7 +13443,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13460,7 +13457,7 @@
         <v>35.00523304555671</v>
       </c>
       <c r="D237" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E237">
         <v>41.72316319432058</v>
@@ -13496,7 +13493,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13510,7 +13507,7 @@
         <v>47.53790446291606</v>
       </c>
       <c r="D238" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E238">
         <v>39.70204416538832</v>
@@ -13546,7 +13543,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13560,7 +13557,7 @@
         <v>35.77509163864829</v>
       </c>
       <c r="D239" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E239">
         <v>42.51968355686988</v>
@@ -13596,7 +13593,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13610,7 +13607,7 @@
         <v>48.33775754664758</v>
       </c>
       <c r="D240" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E240">
         <v>40.4485737102044</v>
@@ -13646,7 +13643,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13660,7 +13657,7 @@
         <v>36.40438752667171</v>
       </c>
       <c r="D241" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E241">
         <v>43.17077324188112</v>
@@ -13696,7 +13693,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13710,7 +13707,7 @@
         <v>48.9915714562823</v>
       </c>
       <c r="D242" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E242">
         <v>41.05880002586348</v>
@@ -13746,7 +13743,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13760,7 +13757,7 @@
         <v>32.86635202836143</v>
       </c>
       <c r="D243" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E243">
         <v>23.40810673803942</v>
@@ -13796,7 +13793,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13810,7 +13807,7 @@
         <v>14.22574367387871</v>
       </c>
       <c r="D244" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E244">
         <v>19.5340376774239</v>
@@ -13846,7 +13843,7 @@
         <v>0</v>
       </c>
       <c r="P244" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13860,7 +13857,7 @@
         <v>24.88800304387275</v>
       </c>
       <c r="D245" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E245">
         <v>11.91657154564347</v>
@@ -13896,7 +13893,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13910,7 +13907,7 @@
         <v>39.44906102636678</v>
       </c>
       <c r="D246" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E246">
         <v>28.36395585832523</v>
@@ -13946,7 +13943,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13975,7 +13972,7 @@
         <v>59.4</v>
       </c>
       <c r="P247" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13989,7 +13986,7 @@
         <v>36.85113379578714</v>
       </c>
       <c r="D248" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E248">
         <v>25.5208599983697</v>
@@ -14025,7 +14022,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14039,7 +14036,7 @@
         <v>33.94646019309421</v>
       </c>
       <c r="D249" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E249">
         <v>22.34206984707826</v>
@@ -14075,7 +14072,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14089,7 +14086,7 @@
         <v>33.30875742504994</v>
       </c>
       <c r="D250" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E250">
         <v>21.64418651979802</v>
@@ -14125,7 +14122,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14154,7 +14151,7 @@
         <v>59.5</v>
       </c>
       <c r="P251" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14204,7 +14201,7 @@
         <v>0</v>
       </c>
       <c r="P252" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14218,7 +14215,7 @@
         <v>9.926891175013289</v>
       </c>
       <c r="D253" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E253">
         <v>9.938904864210649</v>
@@ -14254,7 +14251,7 @@
         <v>0</v>
       </c>
       <c r="P253" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14268,7 +14265,7 @@
         <v>8.61566853605617</v>
       </c>
       <c r="D254" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E254">
         <v>9.007561895624264</v>
@@ -14304,7 +14301,7 @@
         <v>0</v>
       </c>
       <c r="P254" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14354,7 +14351,7 @@
         <v>0</v>
       </c>
       <c r="P255" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14368,7 +14365,7 @@
         <v>15.27625616990661</v>
       </c>
       <c r="D256" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E256">
         <v>13.96823074035395</v>
@@ -14404,7 +14401,7 @@
         <v>0</v>
       </c>
       <c r="P256" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14418,7 +14415,7 @@
         <v>14.49984262437423</v>
       </c>
       <c r="D257" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E257">
         <v>14.19011246930496</v>
@@ -14454,7 +14451,7 @@
         <v>0</v>
       </c>
       <c r="P257" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14468,7 +14465,7 @@
         <v>13.68984307357539</v>
       </c>
       <c r="D258" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E258">
         <v>15.44321014679792</v>
@@ -14504,7 +14501,7 @@
         <v>0</v>
       </c>
       <c r="P258" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14518,7 +14515,7 @@
         <v>14.26953725404694</v>
       </c>
       <c r="D259" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E259">
         <v>17.46734434330768</v>
@@ -14554,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="P259" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14568,7 +14565,7 @@
         <v>59.06263065139578</v>
       </c>
       <c r="D260" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E260">
         <v>59.07357361272927</v>
@@ -14604,7 +14601,7 @@
         <v>0</v>
       </c>
       <c r="P260" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14618,7 +14615,7 @@
         <v>60.66257075424956</v>
       </c>
       <c r="D261" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E261">
         <v>61.38454095582109</v>
@@ -14654,7 +14651,7 @@
         <v>0</v>
       </c>
       <c r="P261" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14668,7 +14665,7 @@
         <v>61.58779745865752</v>
       </c>
       <c r="D262" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E262">
         <v>62.08864679971672</v>
@@ -14704,7 +14701,7 @@
         <v>0</v>
       </c>
       <c r="P262" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14754,7 +14751,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14804,7 +14801,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14854,7 +14851,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14904,7 +14901,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14954,7 +14951,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15004,7 +15001,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15054,7 +15051,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15104,7 +15101,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15154,7 +15151,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15168,7 +15165,7 @@
         <v>-12.91711279591523</v>
       </c>
       <c r="D272" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E272">
         <v>-24.080705554696</v>
@@ -15218,7 +15215,7 @@
         <v>-13.89288092370901</v>
       </c>
       <c r="D273" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E273">
         <v>-24.64699491908532</v>
@@ -15254,7 +15251,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15268,7 +15265,7 @@
         <v>-13.4171424523624</v>
       </c>
       <c r="D274" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E274">
         <v>-24.64699491908532</v>
@@ -15304,7 +15301,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15318,7 +15315,7 @@
         <v>-7.909028461817627</v>
       </c>
       <c r="D275" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E275">
         <v>-18.4089921717041</v>
@@ -15354,7 +15351,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15368,7 +15365,7 @@
         <v>-3.803879058776658</v>
       </c>
       <c r="D276" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E276">
         <v>-13.75986303266694</v>
@@ -15418,7 +15415,7 @@
         <v>-7.200798160312672</v>
       </c>
       <c r="D277" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E277">
         <v>-16.37029482433257</v>
@@ -15468,7 +15465,7 @@
         <v>1.814674940949821</v>
       </c>
       <c r="D278" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E278">
         <v>-6.106103736501311</v>
@@ -15554,7 +15551,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15654,7 +15651,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15668,7 +15665,7 @@
         <v>68.89152801060949</v>
       </c>
       <c r="D282" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E282">
         <v>67.76768139345658</v>
@@ -15704,7 +15701,7 @@
         <v>0</v>
       </c>
       <c r="P282" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15718,7 +15715,7 @@
         <v>68.93096321131679</v>
       </c>
       <c r="D283" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E283">
         <v>67.76768139345658</v>
@@ -15754,7 +15751,7 @@
         <v>0</v>
       </c>
       <c r="P283" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15768,7 +15765,7 @@
         <v>68.53130803182968</v>
       </c>
       <c r="D284" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E284">
         <v>67.76768139345658</v>
@@ -15804,7 +15801,7 @@
         <v>0</v>
       </c>
       <c r="P284" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15818,7 +15815,7 @@
         <v>69.00549946949548</v>
       </c>
       <c r="D285" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E285">
         <v>67.76768139345658</v>
@@ -15854,7 +15851,7 @@
         <v>0</v>
       </c>
       <c r="P285" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15868,7 +15865,7 @@
         <v>77.0344578684535</v>
       </c>
       <c r="D286" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E286">
         <v>79.16818364992574</v>
@@ -15918,7 +15915,7 @@
         <v>76.35596494832328</v>
       </c>
       <c r="D287" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E287">
         <v>79.16818364992574</v>
@@ -15968,7 +15965,7 @@
         <v>77.32922500711149</v>
       </c>
       <c r="D288" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E288">
         <v>79.16818364992574</v>
@@ -16018,7 +16015,7 @@
         <v>79.78847196430716</v>
       </c>
       <c r="D289" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E289">
         <v>84.66094269739213</v>
@@ -16054,7 +16051,7 @@
         <v>0</v>
       </c>
       <c r="P289" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16068,7 +16065,7 @@
         <v>79.029452316228</v>
       </c>
       <c r="D290" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E290">
         <v>84.66094269739213</v>
@@ -16104,7 +16101,7 @@
         <v>0</v>
       </c>
       <c r="P290" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16118,7 +16115,7 @@
         <v>80.07787065443522</v>
       </c>
       <c r="D291" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E291">
         <v>84.66094269739213</v>
@@ -16154,7 +16151,7 @@
         <v>0</v>
       </c>
       <c r="P291" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16204,7 +16201,7 @@
         <v>0</v>
       </c>
       <c r="P292" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16254,7 +16251,7 @@
         <v>0</v>
       </c>
       <c r="P293" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16304,7 +16301,7 @@
         <v>0</v>
       </c>
       <c r="P294" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16318,7 +16315,7 @@
         <v>26.32548638029413</v>
       </c>
       <c r="D295" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E295">
         <v>26.99422663021349</v>
@@ -16354,7 +16351,7 @@
         <v>0</v>
       </c>
       <c r="P295" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16368,7 +16365,7 @@
         <v>22.18948293316849</v>
       </c>
       <c r="D296" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E296">
         <v>24.84672272180288</v>
@@ -16404,7 +16401,7 @@
         <v>0</v>
       </c>
       <c r="P296" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16418,7 +16415,7 @@
         <v>21.86052377863092</v>
       </c>
       <c r="D297" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E297">
         <v>24.84672272180288</v>
@@ -16454,7 +16451,7 @@
         <v>0</v>
       </c>
       <c r="P297" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16468,7 +16465,7 @@
         <v>40.77814878274022</v>
       </c>
       <c r="D298" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E298">
         <v>48.87821615334129</v>
@@ -16504,7 +16501,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16518,7 +16515,7 @@
         <v>40.67981251944272</v>
       </c>
       <c r="D299" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E299">
         <v>48.87821615334129</v>
@@ -16554,7 +16551,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16568,7 +16565,7 @@
         <v>56.75038402863819</v>
       </c>
       <c r="D300" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E300">
         <v>62.17870887338118</v>
@@ -16604,7 +16601,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16618,7 +16615,7 @@
         <v>59.81014784804309</v>
       </c>
       <c r="D301" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E301">
         <v>65.19117101289457</v>
@@ -16654,7 +16651,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16668,7 +16665,7 @@
         <v>60.36835189313004</v>
       </c>
       <c r="D302" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E302">
         <v>65.519432176365</v>
@@ -16704,7 +16701,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16718,7 +16715,7 @@
         <v>61.49835591209959</v>
       </c>
       <c r="D303" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E303">
         <v>65.45054113973049</v>
@@ -16768,7 +16765,7 @@
         <v>61.74303834428476</v>
       </c>
       <c r="D304" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E304">
         <v>65.59070564276428</v>
@@ -16804,7 +16801,7 @@
         <v>0</v>
       </c>
       <c r="P304" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16818,7 +16815,7 @@
         <v>62.08800405152936</v>
       </c>
       <c r="D305" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E305">
         <v>65.70367105582346</v>
@@ -16854,7 +16851,7 @@
         <v>0</v>
       </c>
       <c r="P305" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16868,7 +16865,7 @@
         <v>62.52195117925444</v>
       </c>
       <c r="D306" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E306">
         <v>66.54562713332096</v>
@@ -16904,7 +16901,7 @@
         <v>0</v>
       </c>
       <c r="P306" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16918,7 +16915,7 @@
         <v>63.12382871565654</v>
       </c>
       <c r="D307" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E307">
         <v>66.7862115872222</v>
@@ -16954,7 +16951,7 @@
         <v>0</v>
       </c>
       <c r="P307" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16968,7 +16965,7 @@
         <v>63.43713576842169</v>
       </c>
       <c r="D308" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E308">
         <v>68.73084934526386</v>
@@ -17004,7 +17001,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17018,7 +17015,7 @@
         <v>63.67236578705479</v>
       </c>
       <c r="D309" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E309">
         <v>68.98960236576026</v>
@@ -17054,7 +17051,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17068,7 +17065,7 @@
         <v>63.92214730715632</v>
       </c>
       <c r="D310" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E310">
         <v>69.26436203787196</v>
@@ -17104,7 +17101,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17118,7 +17115,7 @@
         <v>64.84267428552164</v>
       </c>
       <c r="D311" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E311">
         <v>70.2769417140738</v>
@@ -17154,7 +17151,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17168,7 +17165,7 @@
         <v>67.02639425410899</v>
       </c>
       <c r="D312" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E312">
         <v>72.67903367951989</v>
@@ -17204,7 +17201,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17218,7 +17215,7 @@
         <v>48.8201383647419</v>
       </c>
       <c r="D313" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E313">
         <v>53.28068312873989</v>
@@ -17254,7 +17251,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17268,7 +17265,7 @@
         <v>43.78661428769819</v>
       </c>
       <c r="D314" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E314">
         <v>49.20590413019019</v>
@@ -17304,7 +17301,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17318,7 +17315,7 @@
         <v>43.50856722084519</v>
       </c>
       <c r="D315" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E315">
         <v>49.20590413019019</v>
@@ -17354,7 +17351,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17368,7 +17365,7 @@
         <v>38.43277181447034</v>
       </c>
       <c r="D316" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E316">
         <v>43.81134802598723</v>
@@ -17404,7 +17401,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17418,7 +17415,7 @@
         <v>39.10060265112747</v>
       </c>
       <c r="D317" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E317">
         <v>43.81134802598723</v>
@@ -17454,7 +17451,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17468,7 +17465,7 @@
         <v>28.12299460113455</v>
       </c>
       <c r="D318" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E318">
         <v>35.22229514558674</v>
@@ -17504,7 +17501,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17518,7 +17515,7 @@
         <v>27.81471186440677</v>
       </c>
       <c r="D319" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E319">
         <v>34.92338983050847</v>
@@ -17554,7 +17551,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17568,7 +17565,7 @@
         <v>31.34037664954478</v>
       </c>
       <c r="D320" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E320">
         <v>38.34181005944457</v>
@@ -17604,7 +17601,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17618,7 +17615,7 @@
         <v>31.06966226989418</v>
       </c>
       <c r="D321" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E321">
         <v>38.07933033773011</v>
@@ -17654,7 +17651,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17668,7 +17665,7 @@
         <v>30.73117805425061</v>
       </c>
       <c r="D322" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E322">
         <v>37.75114221990079</v>
@@ -17704,7 +17701,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17718,7 +17715,7 @@
         <v>30.23209518986696</v>
       </c>
       <c r="D323" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E323">
         <v>37.26724058333109</v>
@@ -17754,7 +17751,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17768,7 +17765,7 @@
         <v>29.66328200930995</v>
       </c>
       <c r="D324" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E324">
         <v>36.71572970484425</v>
@@ -17804,7 +17801,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17818,7 +17815,7 @@
         <v>29.90527095369034</v>
       </c>
       <c r="D325" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E325">
         <v>36.95035776878722</v>
@@ -17854,7 +17851,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17868,7 +17865,7 @@
         <v>29.61163508265873</v>
       </c>
       <c r="D326" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E326">
         <v>36.66565378736873</v>
@@ -17904,7 +17901,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17918,7 +17915,7 @@
         <v>29.60796663375891</v>
       </c>
       <c r="D327" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E327">
         <v>38.73216492329536</v>
@@ -17954,7 +17951,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17968,7 +17965,7 @@
         <v>29.99267097270676</v>
       </c>
       <c r="D328" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E328">
         <v>39.11028686861102</v>
@@ -18004,7 +18001,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18018,7 +18015,7 @@
         <v>30.47592970891776</v>
       </c>
       <c r="D329" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E329">
         <v>39.58527691922146</v>
@@ -18054,7 +18051,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18083,7 +18080,7 @@
         <v>64.5</v>
       </c>
       <c r="P330" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18097,7 +18094,7 @@
         <v>37.15547839433958</v>
       </c>
       <c r="D331" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E331">
         <v>43.97524497646168</v>
@@ -18133,7 +18130,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18147,7 +18144,7 @@
         <v>37.01610527202449</v>
       </c>
       <c r="D332" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E332">
         <v>43.97524497646168</v>
@@ -18183,7 +18180,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18197,7 +18194,7 @@
         <v>25.78116025897209</v>
       </c>
       <c r="D333" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E333">
         <v>34.97083622412276</v>
@@ -18233,7 +18230,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18247,7 +18244,7 @@
         <v>21.78292834045364</v>
       </c>
       <c r="D334" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E334">
         <v>32.11135258573889</v>
@@ -18283,7 +18280,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18297,7 +18294,7 @@
         <v>16.20611168178342</v>
       </c>
       <c r="D335" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E335">
         <v>27.00103770079773</v>
@@ -18333,7 +18330,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18347,7 +18344,7 @@
         <v>16.50484318653699</v>
       </c>
       <c r="D336" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E336">
         <v>27.00103770079773</v>
@@ -18383,7 +18380,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18397,7 +18394,7 @@
         <v>7.513223702566968</v>
       </c>
       <c r="D337" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E337">
         <v>19.03531145368304</v>
@@ -18433,7 +18430,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18447,7 +18444,7 @@
         <v>7.993745640345985</v>
       </c>
       <c r="D338" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E338">
         <v>19.03531145368304</v>
@@ -18483,7 +18480,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18497,7 +18494,7 @@
         <v>-3.101932223543415</v>
       </c>
       <c r="D339" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E339">
         <v>9.308115338882274</v>
@@ -18533,7 +18530,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18547,7 +18544,7 @@
         <v>-2.399420332936991</v>
       </c>
       <c r="D340" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E340">
         <v>9.308115338882274</v>
@@ -18583,7 +18580,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18597,7 +18594,7 @@
         <v>-2.646016646848999</v>
       </c>
       <c r="D341" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E341">
         <v>9.308115338882274</v>
@@ -18633,7 +18630,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18647,7 +18644,7 @@
         <v>-9.121415898188509</v>
       </c>
       <c r="D342" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E342">
         <v>3.792162618009769</v>
@@ -18683,7 +18680,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18697,7 +18694,7 @@
         <v>-8.59683700961601</v>
       </c>
       <c r="D343" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E343">
         <v>3.792162618009769</v>
@@ -18733,7 +18730,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18747,7 +18744,7 @@
         <v>-12.89770073310627</v>
       </c>
       <c r="D344" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E344">
         <v>0.3317647274577595</v>
@@ -18783,7 +18780,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18797,7 +18794,7 @@
         <v>-14.09288737405897</v>
       </c>
       <c r="D345" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E345">
         <v>-0.7634443237574615</v>
@@ -18833,7 +18830,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18847,7 +18844,7 @@
         <v>59.56360813550708</v>
       </c>
       <c r="D346" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E346">
         <v>75.18159673719033</v>
@@ -18883,7 +18880,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18897,7 +18894,7 @@
         <v>60.31956868780029</v>
       </c>
       <c r="D347" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E347">
         <v>76.03992694760657</v>
@@ -18933,7 +18930,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18947,7 +18944,7 @@
         <v>62.79431714399279</v>
       </c>
       <c r="D348" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E348">
         <v>77.62631903124894</v>
@@ -18983,7 +18980,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18997,7 +18994,7 @@
         <v>64.08298118239738</v>
       </c>
       <c r="D349" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E349">
         <v>79.11665728256037</v>
@@ -19033,7 +19030,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19047,7 +19044,7 @@
         <v>64.68906100731142</v>
       </c>
       <c r="D350" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E350">
         <v>79.81758779625406</v>
@@ -19083,7 +19080,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19097,7 +19094,7 @@
         <v>66.03163316666149</v>
       </c>
       <c r="D351" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E351">
         <v>81.37027071794273</v>
@@ -19133,7 +19130,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19147,7 +19144,7 @@
         <v>65.93064756206419</v>
       </c>
       <c r="D352" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E352">
         <v>81.25348100015911</v>
@@ -19183,7 +19180,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19197,7 +19194,7 @@
         <v>64.84418812133572</v>
       </c>
       <c r="D353" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E353">
         <v>80.16577874075962</v>
@@ -19233,7 +19230,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19247,7 +19244,7 @@
         <v>63.26616721431549</v>
       </c>
       <c r="D354" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E354">
         <v>79.97190339753475</v>
@@ -19283,7 +19280,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19297,7 +19294,7 @@
         <v>61.66554474645639</v>
       </c>
       <c r="D355" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E355">
         <v>78.05285470927927</v>
@@ -19333,7 +19330,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19347,7 +19344,7 @@
         <v>60.62679073828761</v>
       </c>
       <c r="D356" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E356">
         <v>76.80745202574536</v>
@@ -19383,7 +19380,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19397,7 +19394,7 @@
         <v>59.7052486970962</v>
       </c>
       <c r="D357" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E357">
         <v>75.70257933975458</v>
@@ -19433,7 +19430,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19447,7 +19444,7 @@
         <v>50.59926427854958</v>
       </c>
       <c r="D358" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E358">
         <v>64.78505955942813</v>
@@ -19483,7 +19480,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19497,7 +19494,7 @@
         <v>54.80887863487924</v>
       </c>
       <c r="D359" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E359">
         <v>72.15232554251514</v>
@@ -19533,7 +19530,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19544,46 +19541,46 @@
         <v>130</v>
       </c>
       <c r="C360">
-        <v>22.63799956449154</v>
+        <v>23.40184074907454</v>
       </c>
       <c r="D360" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E360">
-        <v>34.82839660303404</v>
+        <v>34.91992015678304</v>
       </c>
       <c r="F360">
         <v>1</v>
       </c>
       <c r="G360">
-        <v>0.1349620004355085</v>
+        <v>0.1373981592509255</v>
       </c>
       <c r="H360">
-        <v>0.142971603396966</v>
+        <v>0.148080079843217</v>
       </c>
       <c r="I360">
-        <v>12.19039703854251</v>
+        <v>11.5180794077085</v>
       </c>
       <c r="J360">
         <v>0.2787196051389998</v>
       </c>
       <c r="K360">
-        <v>201.5</v>
+        <v>204.5</v>
       </c>
       <c r="L360">
-        <v>78.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="M360">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="N360">
-        <v>88.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="O360">
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19597,10 +19594,10 @@
         <v>23.26568193365754</v>
       </c>
       <c r="D361" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E361">
-        <v>34.82839660303404</v>
+        <v>34.91992015678304</v>
       </c>
       <c r="F361">
         <v>1</v>
@@ -19609,10 +19606,10 @@
         <v>0.1389343180663425</v>
       </c>
       <c r="H361">
-        <v>0.142971603396966</v>
+        <v>0.148080079843217</v>
       </c>
       <c r="I361">
-        <v>11.5627146693765</v>
+        <v>11.6542382231255</v>
       </c>
       <c r="J361">
         <v>0.2787196051389998</v>
@@ -19624,16 +19621,16 @@
         <v>81.09999999999999</v>
       </c>
       <c r="M361">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="N361">
-        <v>88.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="O361">
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19641,13 +19638,13 @@
         <v>0</v>
       </c>
       <c r="B362" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C362">
         <v>22.69572269649692</v>
       </c>
       <c r="D362" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E362">
         <v>35.27246393876952</v>
@@ -19683,7 +19680,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19691,13 +19688,13 @@
         <v>0</v>
       </c>
       <c r="B363" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C363">
         <v>21.6518845469621</v>
       </c>
       <c r="D363" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E363">
         <v>34.22096927469043</v>
@@ -19733,7 +19730,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>130</v>
+        <v>463</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19741,13 +19738,13 @@
         <v>0</v>
       </c>
       <c r="B364" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C364">
         <v>20.6287291557878</v>
       </c>
       <c r="D364" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E364">
         <v>33.1903090762459</v>
@@ -19783,7 +19780,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19791,13 +19788,13 @@
         <v>0</v>
       </c>
       <c r="B365" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C365">
         <v>18.55332655028487</v>
       </c>
       <c r="D365" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E365">
         <v>31.09968346874662</v>
@@ -19833,7 +19830,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19841,31 +19838,31 @@
         <v>0</v>
       </c>
       <c r="B366" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C366">
-        <v>17.31085877987343</v>
+        <v>17.94046356612628</v>
       </c>
       <c r="D366" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E366">
-        <v>28.73863898391312</v>
+        <v>29.36218987799047</v>
       </c>
       <c r="F366">
         <v>1</v>
       </c>
       <c r="G366">
-        <v>0.1478891412201266</v>
+        <v>0.1472595364338737</v>
       </c>
       <c r="H366">
-        <v>0.1580613610160869</v>
+        <v>0.1574378101220095</v>
       </c>
       <c r="I366">
-        <v>11.42778020403969</v>
+        <v>11.42172631186419</v>
       </c>
       <c r="J366">
-        <v>0.3138901020198392</v>
+        <v>0.3108631559320851</v>
       </c>
       <c r="K366">
         <v>208</v>
@@ -19883,7 +19880,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>467</v>
+        <v>130</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19891,31 +19888,31 @@
         <v>0</v>
       </c>
       <c r="B367" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C367">
-        <v>15.37197148226591</v>
+        <v>17.31085877987343</v>
       </c>
       <c r="D367" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E367">
-        <v>26.81839483339797</v>
+        <v>28.73863898391312</v>
       </c>
       <c r="F367">
         <v>1</v>
       </c>
       <c r="G367">
-        <v>0.1498280285177341</v>
+        <v>0.1478891412201266</v>
       </c>
       <c r="H367">
-        <v>0.159981605166602</v>
+        <v>0.1580613610160869</v>
       </c>
       <c r="I367">
-        <v>11.44642335113207</v>
+        <v>11.42778020403969</v>
       </c>
       <c r="J367">
-        <v>0.3232116755660293</v>
+        <v>0.3138901020198392</v>
       </c>
       <c r="K367">
         <v>208</v>
@@ -19933,7 +19930,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19941,49 +19938,49 @@
         <v>0</v>
       </c>
       <c r="B368" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C368">
-        <v>15.09009948164395</v>
+        <v>15.94788391552069</v>
       </c>
       <c r="D368" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E368">
-        <v>26.31992973578353</v>
+        <v>26.95678899561496</v>
       </c>
       <c r="F368">
         <v>1</v>
       </c>
       <c r="G368">
-        <v>0.1527099005183561</v>
+        <v>0.1552521160844793</v>
       </c>
       <c r="H368">
-        <v>0.1596800702642165</v>
+        <v>0.1604432110043851</v>
       </c>
       <c r="I368">
-        <v>11.22983025413959</v>
+        <v>11.00890508009427</v>
       </c>
       <c r="J368">
-        <v>0.3276661929445527</v>
+        <v>0.3232116755660293</v>
       </c>
       <c r="K368">
-        <v>210</v>
+        <v>215.5</v>
       </c>
       <c r="L368">
-        <v>83.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M368">
-        <v>203.5</v>
+        <v>206.5</v>
       </c>
       <c r="N368">
-        <v>93</v>
+        <v>93.7</v>
       </c>
       <c r="O368">
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>131</v>
+        <v>467</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19991,60 +19988,60 @@
         <v>1</v>
       </c>
       <c r="B369" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C369">
-        <v>14.98793542044889</v>
+        <v>15.37197148226591</v>
       </c>
       <c r="D369" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E369">
-        <v>26.31992973578353</v>
+        <v>26.95678899561496</v>
       </c>
       <c r="F369">
         <v>1</v>
       </c>
       <c r="G369">
-        <v>0.1562120645795511</v>
+        <v>0.1498280285177341</v>
       </c>
       <c r="H369">
-        <v>0.1596800702642165</v>
+        <v>0.1604432110043851</v>
       </c>
       <c r="I369">
-        <v>11.33199431533464</v>
+        <v>11.58481751334905</v>
       </c>
       <c r="J369">
-        <v>0.3276661929445527</v>
+        <v>0.3232116755660293</v>
       </c>
       <c r="K369">
-        <v>215.5</v>
+        <v>208</v>
       </c>
       <c r="L369">
-        <v>85.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="M369">
-        <v>203.5</v>
+        <v>206.5</v>
       </c>
       <c r="N369">
-        <v>93</v>
+        <v>93.7</v>
       </c>
       <c r="O369">
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>131</v>
+        <v>467</v>
       </c>
     </row>
     <row r="370" spans="1:16">
       <c r="A370" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B370" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C370">
-        <v>15.04543186753304</v>
+        <v>15.09009948164395</v>
       </c>
       <c r="D370" t="s">
         <v>249</v>
@@ -20056,22 +20053,22 @@
         <v>1</v>
       </c>
       <c r="G370">
-        <v>0.151354568132467</v>
+        <v>0.1527099005183561</v>
       </c>
       <c r="H370">
         <v>0.1596800702642165</v>
       </c>
       <c r="I370">
-        <v>11.27449786825049</v>
+        <v>11.22983025413959</v>
       </c>
       <c r="J370">
         <v>0.3276661929445527</v>
       </c>
       <c r="K370">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L370">
-        <v>83.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="M370">
         <v>203.5</v>
@@ -20088,13 +20085,13 @@
     </row>
     <row r="371" spans="1:16">
       <c r="A371" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B371" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C371">
-        <v>15.21142902520036</v>
+        <v>14.98793542044889</v>
       </c>
       <c r="D371" t="s">
         <v>249</v>
@@ -20106,22 +20103,22 @@
         <v>1</v>
       </c>
       <c r="G371">
-        <v>0.1475885709747997</v>
+        <v>0.1562120645795511</v>
       </c>
       <c r="H371">
         <v>0.1596800702642165</v>
       </c>
       <c r="I371">
-        <v>11.10850071058317</v>
+        <v>11.33199431533464</v>
       </c>
       <c r="J371">
         <v>0.3276661929445527</v>
       </c>
       <c r="K371">
-        <v>202</v>
+        <v>215.5</v>
       </c>
       <c r="L371">
-        <v>81.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M371">
         <v>203.5</v>
@@ -20138,40 +20135,40 @@
     </row>
     <row r="372" spans="1:16">
       <c r="A372" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B372" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C372">
-        <v>13.45577889447236</v>
+        <v>15.04543186753304</v>
       </c>
       <c r="D372" t="s">
         <v>249</v>
       </c>
       <c r="E372">
-        <v>24.7361952620244</v>
+        <v>26.31992973578353</v>
       </c>
       <c r="F372">
         <v>1</v>
       </c>
       <c r="G372">
-        <v>0.1543442211055276</v>
+        <v>0.151354568132467</v>
       </c>
       <c r="H372">
-        <v>0.1612638047379756</v>
+        <v>0.1596800702642165</v>
       </c>
       <c r="I372">
-        <v>11.28041636755204</v>
+        <v>11.27449786825049</v>
       </c>
       <c r="J372">
-        <v>0.335448671931084</v>
+        <v>0.3276661929445527</v>
       </c>
       <c r="K372">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L372">
-        <v>83.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="M372">
         <v>203.5</v>
@@ -20183,45 +20180,45 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>469</v>
+        <v>131</v>
       </c>
     </row>
     <row r="373" spans="1:16">
       <c r="A373" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B373" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C373">
-        <v>13.31081119885138</v>
+        <v>15.21142902520036</v>
       </c>
       <c r="D373" t="s">
         <v>249</v>
       </c>
       <c r="E373">
-        <v>24.7361952620244</v>
+        <v>26.31992973578353</v>
       </c>
       <c r="F373">
         <v>1</v>
       </c>
       <c r="G373">
-        <v>0.1578891888011486</v>
+        <v>0.1475885709747997</v>
       </c>
       <c r="H373">
-        <v>0.1612638047379756</v>
+        <v>0.1596800702642165</v>
       </c>
       <c r="I373">
-        <v>11.42538406317301</v>
+        <v>11.10850071058317</v>
       </c>
       <c r="J373">
-        <v>0.335448671931084</v>
+        <v>0.3276661929445527</v>
       </c>
       <c r="K373">
-        <v>215.5</v>
+        <v>202</v>
       </c>
       <c r="L373">
-        <v>85.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M373">
         <v>203.5</v>
@@ -20233,18 +20230,18 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>469</v>
+        <v>131</v>
       </c>
     </row>
     <row r="374" spans="1:16">
       <c r="A374" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B374" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C374">
-        <v>13.42667623833452</v>
+        <v>13.45577889447236</v>
       </c>
       <c r="D374" t="s">
         <v>249</v>
@@ -20256,22 +20253,22 @@
         <v>1</v>
       </c>
       <c r="G374">
-        <v>0.1529733237616655</v>
+        <v>0.1543442211055276</v>
       </c>
       <c r="H374">
         <v>0.1612638047379756</v>
       </c>
       <c r="I374">
-        <v>11.30951902368987</v>
+        <v>11.28041636755204</v>
       </c>
       <c r="J374">
         <v>0.335448671931084</v>
       </c>
       <c r="K374">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L374">
-        <v>83.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="M374">
         <v>203.5</v>
@@ -20283,18 +20280,18 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="375" spans="1:16">
       <c r="A375" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B375" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C375">
-        <v>13.63936826992104</v>
+        <v>13.31081119885138</v>
       </c>
       <c r="D375" t="s">
         <v>249</v>
@@ -20306,22 +20303,22 @@
         <v>1</v>
       </c>
       <c r="G375">
-        <v>0.149160631730079</v>
+        <v>0.1578891888011486</v>
       </c>
       <c r="H375">
         <v>0.1612638047379756</v>
       </c>
       <c r="I375">
-        <v>11.09682699210336</v>
+        <v>11.42538406317301</v>
       </c>
       <c r="J375">
         <v>0.335448671931084</v>
       </c>
       <c r="K375">
-        <v>202</v>
+        <v>215.5</v>
       </c>
       <c r="L375">
-        <v>81.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M375">
         <v>203.5</v>
@@ -20333,118 +20330,118 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="376" spans="1:16">
       <c r="A376" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B376" t="s">
         <v>135</v>
       </c>
       <c r="C376">
-        <v>10.37263457760139</v>
+        <v>13.42667623833452</v>
       </c>
       <c r="D376" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E376">
-        <v>22.78708795281059</v>
+        <v>24.7361952620244</v>
       </c>
       <c r="F376">
         <v>1</v>
       </c>
       <c r="G376">
-        <v>0.1608273654223986</v>
+        <v>0.1529733237616655</v>
       </c>
       <c r="H376">
-        <v>0.1652129120471894</v>
+        <v>0.1612638047379756</v>
       </c>
       <c r="I376">
-        <v>12.41445337520921</v>
+        <v>11.30951902368987</v>
       </c>
       <c r="J376">
-        <v>0.3490829021921049</v>
+        <v>0.335448671931084</v>
       </c>
       <c r="K376">
-        <v>215.5</v>
+        <v>208</v>
       </c>
       <c r="L376">
-        <v>85.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="M376">
-        <v>204</v>
+        <v>203.5</v>
       </c>
       <c r="N376">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O376">
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="377" spans="1:16">
       <c r="A377" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B377" t="s">
         <v>136</v>
       </c>
       <c r="C377">
-        <v>10.59075634404218</v>
+        <v>13.63936826992104</v>
       </c>
       <c r="D377" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E377">
-        <v>22.78708795281059</v>
+        <v>24.7361952620244</v>
       </c>
       <c r="F377">
         <v>1</v>
       </c>
       <c r="G377">
-        <v>0.1558092436559578</v>
+        <v>0.149160631730079</v>
       </c>
       <c r="H377">
-        <v>0.1652129120471894</v>
+        <v>0.1612638047379756</v>
       </c>
       <c r="I377">
-        <v>12.19633160876842</v>
+        <v>11.09682699210336</v>
       </c>
       <c r="J377">
-        <v>0.3490829021921049</v>
+        <v>0.335448671931084</v>
       </c>
       <c r="K377">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="L377">
-        <v>83.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M377">
-        <v>204</v>
+        <v>203.5</v>
       </c>
       <c r="N377">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O377">
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="378" spans="1:16">
       <c r="A378" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B378" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C378">
-        <v>10.88525375719482</v>
+        <v>10.37263457760139</v>
       </c>
       <c r="D378" t="s">
         <v>250</v>
@@ -20456,22 +20453,22 @@
         <v>1</v>
       </c>
       <c r="G378">
-        <v>0.1519147462428052</v>
+        <v>0.1608273654223986</v>
       </c>
       <c r="H378">
         <v>0.1652129120471894</v>
       </c>
       <c r="I378">
-        <v>11.90183419561578</v>
+        <v>12.41445337520921</v>
       </c>
       <c r="J378">
         <v>0.3490829021921049</v>
       </c>
       <c r="K378">
-        <v>202</v>
+        <v>215.5</v>
       </c>
       <c r="L378">
-        <v>81.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M378">
         <v>204</v>
@@ -20483,18 +20480,18 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="379" spans="1:16">
       <c r="A379" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B379" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C379">
-        <v>11.23800505061848</v>
+        <v>10.59075634404218</v>
       </c>
       <c r="D379" t="s">
         <v>250</v>
@@ -20506,22 +20503,22 @@
         <v>1</v>
       </c>
       <c r="G379">
-        <v>0.1543619949493815</v>
+        <v>0.1558092436559578</v>
       </c>
       <c r="H379">
         <v>0.1652129120471894</v>
       </c>
       <c r="I379">
-        <v>11.54908290219211</v>
+        <v>12.19633160876842</v>
       </c>
       <c r="J379">
         <v>0.3490829021921049</v>
       </c>
       <c r="K379">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L379">
-        <v>82.8</v>
+        <v>83.2</v>
       </c>
       <c r="M379">
         <v>204</v>
@@ -20533,45 +20530,45 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="380" spans="1:16">
       <c r="A380" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B380" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C380">
-        <v>8.066617110777202</v>
+        <v>10.88525375719482</v>
       </c>
       <c r="D380" t="s">
         <v>250</v>
       </c>
       <c r="E380">
-        <v>20.60412942273109</v>
+        <v>22.78708795281059</v>
       </c>
       <c r="F380">
         <v>1</v>
       </c>
       <c r="G380">
-        <v>0.1631333828892228</v>
+        <v>0.1519147462428052</v>
       </c>
       <c r="H380">
-        <v>0.1673958705772689</v>
+        <v>0.1652129120471894</v>
       </c>
       <c r="I380">
-        <v>12.53751231195389</v>
+        <v>11.90183419561578</v>
       </c>
       <c r="J380">
-        <v>0.3597836793003378</v>
+        <v>0.3490829021921049</v>
       </c>
       <c r="K380">
-        <v>215.5</v>
+        <v>202</v>
       </c>
       <c r="L380">
-        <v>85.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M380">
         <v>204</v>
@@ -20583,39 +20580,39 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>134</v>
+        <v>469</v>
       </c>
     </row>
     <row r="381" spans="1:16">
       <c r="A381" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B381" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C381">
-        <v>9.044345743430753</v>
+        <v>11.23800505061848</v>
       </c>
       <c r="D381" t="s">
         <v>250</v>
       </c>
       <c r="E381">
-        <v>20.60412942273109</v>
+        <v>22.78708795281059</v>
       </c>
       <c r="F381">
         <v>1</v>
       </c>
       <c r="G381">
-        <v>0.1565556542565693</v>
+        <v>0.1543619949493815</v>
       </c>
       <c r="H381">
-        <v>0.1673958705772689</v>
+        <v>0.1652129120471894</v>
       </c>
       <c r="I381">
-        <v>11.55978367930034</v>
+        <v>11.54908290219211</v>
       </c>
       <c r="J381">
-        <v>0.3597836793003378</v>
+        <v>0.3490829021921049</v>
       </c>
       <c r="K381">
         <v>205</v>
@@ -20633,7 +20630,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>134</v>
+        <v>469</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20641,99 +20638,99 @@
         <v>0</v>
       </c>
       <c r="B382" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C382">
-        <v>-2.124244140274371</v>
+        <v>8.066617110777202</v>
       </c>
       <c r="D382" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E382">
-        <v>10.72424068728326</v>
+        <v>20.60412942273109</v>
       </c>
       <c r="F382">
         <v>1</v>
       </c>
       <c r="G382">
-        <v>0.1703242441402744</v>
+        <v>0.1631333828892228</v>
       </c>
       <c r="H382">
-        <v>0.1852757593127167</v>
+        <v>0.1673958705772689</v>
       </c>
       <c r="I382">
-        <v>12.84848482755763</v>
+        <v>12.53751231195389</v>
       </c>
       <c r="J382">
-        <v>0.4206060689769481</v>
+        <v>0.3597836793003378</v>
       </c>
       <c r="K382">
-        <v>205</v>
+        <v>215.5</v>
       </c>
       <c r="L382">
-        <v>84.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M382">
-        <v>207.5</v>
+        <v>204</v>
       </c>
       <c r="N382">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="O382">
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="383" spans="1:16">
       <c r="A383" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B383" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C383">
-        <v>13.16161645214643</v>
+        <v>9.044345743430753</v>
       </c>
       <c r="D383" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E383">
-        <v>9.280369598044189</v>
+        <v>20.60412942273109</v>
       </c>
       <c r="F383">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G383">
-        <v>0.1634383835478536</v>
+        <v>0.1565556542565693</v>
       </c>
       <c r="H383">
-        <v>0.1683196304019558</v>
+        <v>0.1673958705772689</v>
       </c>
       <c r="I383">
-        <v>3.881246854102244</v>
+        <v>11.55978367930034</v>
       </c>
       <c r="J383">
-        <v>0.4381246854102249</v>
+        <v>0.3597836793003378</v>
       </c>
       <c r="K383">
-        <v>171.5</v>
+        <v>205</v>
       </c>
       <c r="L383">
-        <v>88.3</v>
+        <v>82.8</v>
       </c>
       <c r="M383">
-        <v>181.5</v>
+        <v>204</v>
       </c>
       <c r="N383">
-        <v>88.8</v>
+        <v>94</v>
       </c>
       <c r="O383">
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>471</v>
+        <v>134</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20741,49 +20738,49 @@
         <v>0</v>
       </c>
       <c r="B384" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C384">
-        <v>-21.82338146012957</v>
+        <v>-2.124244140274371</v>
       </c>
       <c r="D384" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E384">
-        <v>-26.74300800979539</v>
+        <v>10.72424068728326</v>
       </c>
       <c r="F384">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G384">
-        <v>0.2024233814601296</v>
+        <v>0.1703242441402744</v>
       </c>
       <c r="H384">
-        <v>0.2025430080097954</v>
+        <v>0.1852757593127167</v>
       </c>
       <c r="I384">
-        <v>4.919626549665821</v>
+        <v>12.84848482755763</v>
       </c>
       <c r="J384">
-        <v>0.6299066374164582</v>
+        <v>0.4206060689769481</v>
       </c>
       <c r="K384">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="L384">
-        <v>90.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M384">
-        <v>182</v>
+        <v>207.5</v>
       </c>
       <c r="N384">
-        <v>87.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="O384">
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>472</v>
+        <v>133</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20791,49 +20788,49 @@
         <v>0</v>
       </c>
       <c r="B385" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C385">
-        <v>32.20533098261782</v>
+        <v>13.16161645214643</v>
       </c>
       <c r="D385" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E385">
-        <v>28.32229381498548</v>
+        <v>8.161307255339082</v>
       </c>
       <c r="F385">
         <v>-1</v>
       </c>
       <c r="G385">
-        <v>0.1503946690173822</v>
+        <v>0.1634383835478536</v>
       </c>
       <c r="H385">
-        <v>0.1530777061850145</v>
+        <v>0.1676386927446609</v>
       </c>
       <c r="I385">
-        <v>3.883037167632338</v>
+        <v>5.000309196807351</v>
       </c>
       <c r="J385">
-        <v>0.3283037167632343</v>
+        <v>0.4381246854102249</v>
       </c>
       <c r="K385">
-        <v>180</v>
+        <v>171.5</v>
       </c>
       <c r="L385">
-        <v>91.3</v>
+        <v>88.3</v>
       </c>
       <c r="M385">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="N385">
-        <v>90.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="O385">
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20841,49 +20838,149 @@
         <v>0</v>
       </c>
       <c r="B386" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C386">
-        <v>30.11806288540985</v>
+        <v>-21.82338146012957</v>
       </c>
       <c r="D386" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E386">
-        <v>26.85846428286341</v>
+        <v>-26.74300800979539</v>
       </c>
       <c r="F386">
         <v>-1</v>
       </c>
       <c r="G386">
+        <v>0.2024233814601296</v>
+      </c>
+      <c r="H386">
+        <v>0.2025430080097954</v>
+      </c>
+      <c r="I386">
+        <v>4.919626549665821</v>
+      </c>
+      <c r="J386">
+        <v>0.6299066374164582</v>
+      </c>
+      <c r="K386">
+        <v>178</v>
+      </c>
+      <c r="L386">
+        <v>90.3</v>
+      </c>
+      <c r="M386">
+        <v>182</v>
+      </c>
+      <c r="N386">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="O386">
+        <v>1</v>
+      </c>
+      <c r="P386" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="387" spans="1:16">
+      <c r="A387" s="1">
+        <v>0</v>
+      </c>
+      <c r="B387" t="s">
+        <v>141</v>
+      </c>
+      <c r="C387">
+        <v>32.20533098261782</v>
+      </c>
+      <c r="D387" t="s">
+        <v>253</v>
+      </c>
+      <c r="E387">
+        <v>28.32229381498548</v>
+      </c>
+      <c r="F387">
+        <v>-1</v>
+      </c>
+      <c r="G387">
+        <v>0.1503946690173822</v>
+      </c>
+      <c r="H387">
+        <v>0.1530777061850145</v>
+      </c>
+      <c r="I387">
+        <v>3.883037167632338</v>
+      </c>
+      <c r="J387">
+        <v>0.3283037167632343</v>
+      </c>
+      <c r="K387">
+        <v>180</v>
+      </c>
+      <c r="L387">
+        <v>91.3</v>
+      </c>
+      <c r="M387">
+        <v>190</v>
+      </c>
+      <c r="N387">
+        <v>90.7</v>
+      </c>
+      <c r="O387">
+        <v>1</v>
+      </c>
+      <c r="P387" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="388" spans="1:16">
+      <c r="A388" s="1">
+        <v>0</v>
+      </c>
+      <c r="B388" t="s">
+        <v>141</v>
+      </c>
+      <c r="C388">
+        <v>30.11806288540985</v>
+      </c>
+      <c r="D388" t="s">
+        <v>253</v>
+      </c>
+      <c r="E388">
+        <v>26.11906637904373</v>
+      </c>
+      <c r="F388">
+        <v>-1</v>
+      </c>
+      <c r="G388">
         <v>0.1524819371145902</v>
       </c>
-      <c r="H386">
-        <v>0.1519415357171366</v>
-      </c>
-      <c r="I386">
-        <v>3.25959860254644</v>
-      </c>
-      <c r="J386">
+      <c r="H388">
+        <v>0.1552809336209563</v>
+      </c>
+      <c r="I388">
+        <v>3.998996506366119</v>
+      </c>
+      <c r="J388">
         <v>0.3398996506366119</v>
       </c>
-      <c r="K386">
+      <c r="K388">
         <v>180</v>
       </c>
-      <c r="L386">
+      <c r="L388">
         <v>91.3</v>
       </c>
-      <c r="M386">
-        <v>184</v>
-      </c>
-      <c r="N386">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="O386">
-        <v>1</v>
-      </c>
-      <c r="P386" t="s">
-        <v>474</v>
+      <c r="M388">
+        <v>190</v>
+      </c>
+      <c r="N388">
+        <v>90.7</v>
+      </c>
+      <c r="O388">
+        <v>1</v>
+      </c>
+      <c r="P388" t="s">
+        <v>473</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-2474-2382-800.xlsx
+++ b/s60_signal/position-2474-2382-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="469">
   <si>
     <t>trade_time</t>
   </si>
@@ -406,21 +406,27 @@
     <t>2020-11-12</t>
   </si>
   <si>
+    <t>2020-12-24</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
     <t>2020-12-29</t>
   </si>
   <si>
-    <t>2021-01-04</t>
+    <t>2020-12-31</t>
   </si>
   <si>
     <t>2021-01-19</t>
   </si>
   <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
     <t>2021-01-14</t>
   </si>
   <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
     <t>2021-01-18</t>
   </si>
   <si>
@@ -433,13 +439,7 @@
     <t>2021-01-27</t>
   </si>
   <si>
-    <t>2021-05-17</t>
-  </si>
-  <si>
-    <t>2021-05-14</t>
-  </si>
-  <si>
-    <t>2021-07-12</t>
+    <t>2021-07-26</t>
   </si>
   <si>
     <t>2010-10-22</t>
@@ -754,7 +754,7 @@
     <t>2021-02-17</t>
   </si>
   <si>
-    <t>2021-03-18</t>
+    <t>2021-02-18</t>
   </si>
   <si>
     <t>2021-03-23</t>
@@ -772,10 +772,7 @@
     <t>2021-03-29</t>
   </si>
   <si>
-    <t>2021-05-24</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
+    <t>2021-07-28</t>
   </si>
   <si>
     <t>2010-08-03</t>
@@ -1405,37 +1402,25 @@
     <t>2020-12-23</t>
   </si>
   <si>
-    <t>2020-12-24</t>
-  </si>
-  <si>
     <t>2020-12-25</t>
   </si>
   <si>
     <t>2020-12-28</t>
   </si>
   <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
     <t>2021-01-05</t>
   </si>
   <si>
     <t>2021-01-06</t>
   </si>
   <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
     <t>2021-04-21</t>
   </si>
   <si>
     <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>2021-06-17</t>
-  </si>
-  <si>
-    <t>2021-06-18</t>
   </si>
 </sst>
 </file>
@@ -1793,7 +1778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P388"/>
+  <dimension ref="A1:P382"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1890,7 +1875,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1940,7 +1925,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1990,7 +1975,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2040,7 +2025,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2090,7 +2075,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2140,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2190,7 +2175,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2240,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2290,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2340,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2390,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2440,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2490,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2540,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2590,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2640,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2690,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2740,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2790,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2840,7 +2825,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2890,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2940,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2990,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3040,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3090,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3140,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3169,7 +3154,7 @@
         <v>59.3</v>
       </c>
       <c r="P28" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3198,7 +3183,7 @@
         <v>65.5</v>
       </c>
       <c r="P29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3248,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3298,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3327,7 +3312,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="P32" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3377,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3427,7 +3412,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3477,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3506,7 +3491,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="P36" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3535,7 +3520,7 @@
         <v>70.09999999999999</v>
       </c>
       <c r="P37" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3585,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3635,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3685,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3735,7 +3720,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3785,7 +3770,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3835,7 +3820,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3885,7 +3870,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3935,7 +3920,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3985,7 +3970,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4035,7 +4020,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4085,7 +4070,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4135,7 +4120,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4185,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4235,7 +4220,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4285,7 +4270,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4335,7 +4320,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4585,7 +4570,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4685,7 +4670,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4735,7 +4720,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4785,7 +4770,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4835,7 +4820,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4985,7 +4970,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5035,7 +5020,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5085,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="P68" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5135,7 +5120,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5185,7 +5170,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5235,7 +5220,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5285,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="P72" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5335,7 +5320,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5385,7 +5370,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5435,7 +5420,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5485,7 +5470,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5535,7 +5520,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5585,7 +5570,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5635,7 +5620,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5685,7 +5670,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5735,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5785,7 +5770,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5835,7 +5820,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5885,7 +5870,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5935,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5985,7 +5970,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6035,7 +6020,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6185,7 +6170,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6235,7 +6220,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6285,7 +6270,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6335,7 +6320,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6385,7 +6370,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6435,7 +6420,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6485,7 +6470,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6535,7 +6520,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6585,7 +6570,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6635,7 +6620,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6685,7 +6670,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6735,7 +6720,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6785,7 +6770,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6835,7 +6820,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6885,7 +6870,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6935,7 +6920,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6985,7 +6970,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7035,7 +7020,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7085,7 +7070,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7135,7 +7120,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7185,7 +7170,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7235,7 +7220,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7285,7 +7270,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7335,7 +7320,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7385,7 +7370,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7435,7 +7420,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7485,7 +7470,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7535,7 +7520,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7585,7 +7570,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7635,7 +7620,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7735,7 +7720,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7785,7 +7770,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7835,7 +7820,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7885,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7935,7 +7920,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7985,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8035,7 +8020,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8085,7 +8070,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8135,7 +8120,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8185,7 +8170,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8235,7 +8220,7 @@
         <v>0</v>
       </c>
       <c r="P131" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8285,7 +8270,7 @@
         <v>0</v>
       </c>
       <c r="P132" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8435,7 +8420,7 @@
         <v>0</v>
       </c>
       <c r="P135" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8485,7 +8470,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8535,7 +8520,7 @@
         <v>0</v>
       </c>
       <c r="P137" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8585,7 +8570,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8635,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8685,7 +8670,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8735,7 +8720,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8785,7 +8770,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8835,7 +8820,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8885,7 +8870,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8935,7 +8920,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8985,7 +8970,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9035,7 +9020,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9085,7 +9070,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9135,7 +9120,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9185,7 +9170,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9235,7 +9220,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9335,7 +9320,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9435,7 +9420,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9485,7 +9470,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9535,7 +9520,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9585,7 +9570,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9635,7 +9620,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9685,7 +9670,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9735,7 +9720,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9785,7 +9770,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9835,7 +9820,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9885,7 +9870,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9935,7 +9920,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9985,7 +9970,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10035,7 +10020,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10235,7 +10220,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10285,7 +10270,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10335,7 +10320,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10385,7 +10370,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10435,7 +10420,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10485,7 +10470,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10535,7 +10520,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10585,7 +10570,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10635,7 +10620,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10664,7 +10649,7 @@
         <v>71.40000000000001</v>
       </c>
       <c r="P180" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10693,7 +10678,7 @@
         <v>72.09999999999999</v>
       </c>
       <c r="P181" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10793,7 +10778,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10843,7 +10828,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10893,7 +10878,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10943,7 +10928,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10993,7 +10978,7 @@
         <v>0</v>
       </c>
       <c r="P187" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11043,7 +11028,7 @@
         <v>0</v>
       </c>
       <c r="P188" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11093,7 +11078,7 @@
         <v>0</v>
       </c>
       <c r="P189" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11143,7 +11128,7 @@
         <v>0</v>
       </c>
       <c r="P190" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11193,7 +11178,7 @@
         <v>0</v>
       </c>
       <c r="P191" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11243,7 +11228,7 @@
         <v>0</v>
       </c>
       <c r="P192" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11293,7 +11278,7 @@
         <v>0</v>
       </c>
       <c r="P193" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11343,7 +11328,7 @@
         <v>0</v>
       </c>
       <c r="P194" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11393,7 +11378,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11443,7 +11428,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11493,7 +11478,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11543,7 +11528,7 @@
         <v>0</v>
       </c>
       <c r="P198" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11593,7 +11578,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11643,7 +11628,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11743,7 +11728,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11793,7 +11778,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11843,7 +11828,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11943,7 +11928,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11993,7 +11978,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12043,7 +12028,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12093,7 +12078,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12193,7 +12178,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12243,7 +12228,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12293,7 +12278,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12343,7 +12328,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12393,7 +12378,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12443,7 +12428,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12493,7 +12478,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12543,7 +12528,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12593,7 +12578,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12643,7 +12628,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12693,7 +12678,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12743,7 +12728,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12893,7 +12878,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12993,7 +12978,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13193,7 +13178,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13243,7 +13228,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13293,7 +13278,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13343,7 +13328,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13393,7 +13378,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13443,7 +13428,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13493,7 +13478,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13543,7 +13528,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13593,7 +13578,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13643,7 +13628,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13693,7 +13678,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13743,7 +13728,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13793,7 +13778,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13843,7 +13828,7 @@
         <v>0</v>
       </c>
       <c r="P244" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13893,7 +13878,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13943,7 +13928,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13972,7 +13957,7 @@
         <v>59.4</v>
       </c>
       <c r="P247" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14022,7 +14007,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14072,7 +14057,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14122,7 +14107,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14151,7 +14136,7 @@
         <v>59.5</v>
       </c>
       <c r="P251" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14201,7 +14186,7 @@
         <v>0</v>
       </c>
       <c r="P252" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14251,7 +14236,7 @@
         <v>0</v>
       </c>
       <c r="P253" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14301,7 +14286,7 @@
         <v>0</v>
       </c>
       <c r="P254" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14351,7 +14336,7 @@
         <v>0</v>
       </c>
       <c r="P255" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14401,7 +14386,7 @@
         <v>0</v>
       </c>
       <c r="P256" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14451,7 +14436,7 @@
         <v>0</v>
       </c>
       <c r="P257" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14501,7 +14486,7 @@
         <v>0</v>
       </c>
       <c r="P258" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14551,7 +14536,7 @@
         <v>0</v>
       </c>
       <c r="P259" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14601,7 +14586,7 @@
         <v>0</v>
       </c>
       <c r="P260" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14651,7 +14636,7 @@
         <v>0</v>
       </c>
       <c r="P261" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14701,7 +14686,7 @@
         <v>0</v>
       </c>
       <c r="P262" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14751,7 +14736,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14801,7 +14786,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14851,7 +14836,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14901,7 +14886,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14951,7 +14936,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15001,7 +14986,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15051,7 +15036,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15101,7 +15086,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15151,7 +15136,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15251,7 +15236,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15301,7 +15286,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15351,7 +15336,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15551,7 +15536,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15651,7 +15636,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15701,7 +15686,7 @@
         <v>0</v>
       </c>
       <c r="P282" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15751,7 +15736,7 @@
         <v>0</v>
       </c>
       <c r="P283" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15801,7 +15786,7 @@
         <v>0</v>
       </c>
       <c r="P284" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15851,7 +15836,7 @@
         <v>0</v>
       </c>
       <c r="P285" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16351,7 +16336,7 @@
         <v>0</v>
       </c>
       <c r="P295" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16401,7 +16386,7 @@
         <v>0</v>
       </c>
       <c r="P296" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16451,7 +16436,7 @@
         <v>0</v>
       </c>
       <c r="P297" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16501,7 +16486,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16551,7 +16536,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16601,7 +16586,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16651,7 +16636,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16701,7 +16686,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16801,7 +16786,7 @@
         <v>0</v>
       </c>
       <c r="P304" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16851,7 +16836,7 @@
         <v>0</v>
       </c>
       <c r="P305" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16901,7 +16886,7 @@
         <v>0</v>
       </c>
       <c r="P306" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16951,7 +16936,7 @@
         <v>0</v>
       </c>
       <c r="P307" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17001,7 +16986,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17051,7 +17036,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17101,7 +17086,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17151,7 +17136,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17201,7 +17186,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17251,7 +17236,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17301,7 +17286,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17351,7 +17336,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17401,7 +17386,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17451,7 +17436,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17501,7 +17486,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17551,7 +17536,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17601,7 +17586,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17651,7 +17636,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17701,7 +17686,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17751,7 +17736,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17801,7 +17786,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17851,7 +17836,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17901,7 +17886,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17951,7 +17936,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18001,7 +17986,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18051,7 +18036,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18080,7 +18065,7 @@
         <v>64.5</v>
       </c>
       <c r="P330" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18130,7 +18115,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18180,7 +18165,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18230,7 +18215,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18280,7 +18265,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18330,7 +18315,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18380,7 +18365,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18430,7 +18415,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18480,7 +18465,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18530,7 +18515,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18580,7 +18565,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18630,7 +18615,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18680,7 +18665,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18730,7 +18715,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18780,7 +18765,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18830,7 +18815,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18880,7 +18865,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18930,7 +18915,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18980,7 +18965,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19030,7 +19015,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19080,7 +19065,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19130,7 +19115,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19180,7 +19165,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19230,7 +19215,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19280,7 +19265,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19330,7 +19315,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19380,7 +19365,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19430,7 +19415,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19480,7 +19465,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19530,7 +19515,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19541,90 +19526,90 @@
         <v>130</v>
       </c>
       <c r="C360">
-        <v>23.40184074907454</v>
+        <v>22.63799956449154</v>
       </c>
       <c r="D360" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E360">
-        <v>34.91992015678304</v>
+        <v>34.76775640560354</v>
       </c>
       <c r="F360">
         <v>1</v>
       </c>
       <c r="G360">
-        <v>0.1373981592509255</v>
+        <v>0.1349620004355085</v>
       </c>
       <c r="H360">
-        <v>0.148080079843217</v>
+        <v>0.1426322435943965</v>
       </c>
       <c r="I360">
-        <v>11.5180794077085</v>
+        <v>12.12975684111201</v>
       </c>
       <c r="J360">
         <v>0.2787196051389998</v>
       </c>
       <c r="K360">
-        <v>204.5</v>
+        <v>201.5</v>
       </c>
       <c r="L360">
-        <v>80.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="M360">
-        <v>203</v>
+        <v>193.5</v>
       </c>
       <c r="N360">
-        <v>91.5</v>
+        <v>88.7</v>
       </c>
       <c r="O360">
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="361" spans="1:16">
       <c r="A361" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B361" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C361">
-        <v>23.26568193365754</v>
+        <v>21.94224021195173</v>
       </c>
       <c r="D361" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E361">
-        <v>34.91992015678304</v>
+        <v>34.09962025316457</v>
       </c>
       <c r="F361">
         <v>1</v>
       </c>
       <c r="G361">
-        <v>0.1389343180663425</v>
+        <v>0.1356577597880483</v>
       </c>
       <c r="H361">
-        <v>0.148080079843217</v>
+        <v>0.1433003797468354</v>
       </c>
       <c r="I361">
-        <v>11.6542382231255</v>
+        <v>12.15738004121285</v>
       </c>
       <c r="J361">
-        <v>0.2787196051389998</v>
+        <v>0.2821725051516043</v>
       </c>
       <c r="K361">
-        <v>207.5</v>
+        <v>201.5</v>
       </c>
       <c r="L361">
-        <v>81.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="M361">
-        <v>203</v>
+        <v>193.5</v>
       </c>
       <c r="N361">
-        <v>91.5</v>
+        <v>88.7</v>
       </c>
       <c r="O361">
         <v>1</v>
@@ -19635,52 +19620,52 @@
     </row>
     <row r="362" spans="1:16">
       <c r="A362" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B362" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C362">
-        <v>22.69572269649692</v>
+        <v>22.5492051810421</v>
       </c>
       <c r="D362" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E362">
-        <v>35.27246393876952</v>
+        <v>34.09962025316457</v>
       </c>
       <c r="F362">
         <v>1</v>
       </c>
       <c r="G362">
-        <v>0.1381042773035031</v>
+        <v>0.1396507948189579</v>
       </c>
       <c r="H362">
-        <v>0.1515275360612305</v>
+        <v>0.1433003797468354</v>
       </c>
       <c r="I362">
-        <v>12.5767412422726</v>
+        <v>11.55041507212247</v>
       </c>
       <c r="J362">
         <v>0.2821725051516043</v>
       </c>
       <c r="K362">
-        <v>204.5</v>
+        <v>207.5</v>
       </c>
       <c r="L362">
-        <v>80.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="M362">
-        <v>206</v>
+        <v>193.5</v>
       </c>
       <c r="N362">
-        <v>93.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="O362">
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19688,16 +19673,16 @@
         <v>0</v>
       </c>
       <c r="B363" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C363">
         <v>21.6518845469621</v>
       </c>
       <c r="D363" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E363">
-        <v>34.22096927469043</v>
+        <v>33.16829145286381</v>
       </c>
       <c r="F363">
         <v>1</v>
@@ -19706,10 +19691,10 @@
         <v>0.1391481154530379</v>
       </c>
       <c r="H363">
-        <v>0.1525790307253096</v>
+        <v>0.1446317085471362</v>
       </c>
       <c r="I363">
-        <v>12.56908472772833</v>
+        <v>11.5164069059017</v>
       </c>
       <c r="J363">
         <v>0.2872768481811144</v>
@@ -19721,66 +19706,66 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M363">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N363">
-        <v>93.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O363">
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>463</v>
+        <v>130</v>
       </c>
     </row>
     <row r="364" spans="1:16">
       <c r="A364" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B364" t="s">
+        <v>133</v>
+      </c>
+      <c r="C364">
+        <v>21.72096927469043</v>
+      </c>
+      <c r="D364" t="s">
+        <v>246</v>
+      </c>
+      <c r="E364">
+        <v>33.16829145286381</v>
+      </c>
+      <c r="F364">
+        <v>1</v>
+      </c>
+      <c r="G364">
+        <v>0.1400790307253096</v>
+      </c>
+      <c r="H364">
+        <v>0.1446317085471362</v>
+      </c>
+      <c r="I364">
+        <v>11.44732217817337</v>
+      </c>
+      <c r="J364">
+        <v>0.2872768481811144</v>
+      </c>
+      <c r="K364">
+        <v>206</v>
+      </c>
+      <c r="L364">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="M364">
+        <v>194</v>
+      </c>
+      <c r="N364">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="O364">
+        <v>1</v>
+      </c>
+      <c r="P364" t="s">
         <v>130</v>
-      </c>
-      <c r="C364">
-        <v>20.6287291557878</v>
-      </c>
-      <c r="D364" t="s">
-        <v>247</v>
-      </c>
-      <c r="E364">
-        <v>33.1903090762459</v>
-      </c>
-      <c r="F364">
-        <v>1</v>
-      </c>
-      <c r="G364">
-        <v>0.1401712708442122</v>
-      </c>
-      <c r="H364">
-        <v>0.1536096909237541</v>
-      </c>
-      <c r="I364">
-        <v>12.5615799204581</v>
-      </c>
-      <c r="J364">
-        <v>0.2922800530279325</v>
-      </c>
-      <c r="K364">
-        <v>204.5</v>
-      </c>
-      <c r="L364">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="M364">
-        <v>206</v>
-      </c>
-      <c r="N364">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="O364">
-        <v>1</v>
-      </c>
-      <c r="P364" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19788,31 +19773,31 @@
         <v>0</v>
       </c>
       <c r="B365" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C365">
-        <v>18.55332655028487</v>
+        <v>20.6287291557878</v>
       </c>
       <c r="D365" t="s">
         <v>247</v>
       </c>
       <c r="E365">
-        <v>31.09968346874662</v>
+        <v>33.1903090762459</v>
       </c>
       <c r="F365">
         <v>1</v>
       </c>
       <c r="G365">
-        <v>0.1422466734497151</v>
+        <v>0.1401712708442122</v>
       </c>
       <c r="H365">
-        <v>0.1557003165312534</v>
+        <v>0.1536096909237541</v>
       </c>
       <c r="I365">
-        <v>12.54635691846175</v>
+        <v>12.5615799204581</v>
       </c>
       <c r="J365">
-        <v>0.3024287210255019</v>
+        <v>0.2922800530279325</v>
       </c>
       <c r="K365">
         <v>204.5</v>
@@ -19830,7 +19815,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19841,34 +19826,34 @@
         <v>132</v>
       </c>
       <c r="C366">
-        <v>17.94046356612628</v>
+        <v>18.55332655028487</v>
       </c>
       <c r="D366" t="s">
         <v>247</v>
       </c>
       <c r="E366">
-        <v>29.36218987799047</v>
+        <v>31.09968346874662</v>
       </c>
       <c r="F366">
         <v>1</v>
       </c>
       <c r="G366">
-        <v>0.1472595364338737</v>
+        <v>0.1422466734497151</v>
       </c>
       <c r="H366">
-        <v>0.1574378101220095</v>
+        <v>0.1557003165312534</v>
       </c>
       <c r="I366">
-        <v>11.42172631186419</v>
+        <v>12.54635691846175</v>
       </c>
       <c r="J366">
-        <v>0.3108631559320851</v>
+        <v>0.3024287210255019</v>
       </c>
       <c r="K366">
-        <v>208</v>
+        <v>204.5</v>
       </c>
       <c r="L366">
-        <v>82.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="M366">
         <v>206</v>
@@ -19880,7 +19865,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>130</v>
+        <v>463</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19888,31 +19873,31 @@
         <v>0</v>
       </c>
       <c r="B367" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C367">
-        <v>17.31085877987343</v>
+        <v>15.37197148226591</v>
       </c>
       <c r="D367" t="s">
         <v>247</v>
       </c>
       <c r="E367">
-        <v>28.73863898391312</v>
+        <v>26.81839483339797</v>
       </c>
       <c r="F367">
         <v>1</v>
       </c>
       <c r="G367">
-        <v>0.1478891412201266</v>
+        <v>0.1498280285177341</v>
       </c>
       <c r="H367">
-        <v>0.1580613610160869</v>
+        <v>0.159981605166602</v>
       </c>
       <c r="I367">
-        <v>11.42778020403969</v>
+        <v>11.44642335113207</v>
       </c>
       <c r="J367">
-        <v>0.3138901020198392</v>
+        <v>0.3232116755660293</v>
       </c>
       <c r="K367">
         <v>208</v>
@@ -19930,7 +19915,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>466</v>
+        <v>133</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19938,87 +19923,87 @@
         <v>0</v>
       </c>
       <c r="B368" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C368">
-        <v>15.94788391552069</v>
+        <v>14.44543186753303</v>
       </c>
       <c r="D368" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E368">
-        <v>26.95678899561496</v>
+        <v>25.90076425342215</v>
       </c>
       <c r="F368">
         <v>1</v>
       </c>
       <c r="G368">
-        <v>0.1552521160844793</v>
+        <v>0.150754568132467</v>
       </c>
       <c r="H368">
-        <v>0.1604432110043851</v>
+        <v>0.1608992357465779</v>
       </c>
       <c r="I368">
-        <v>11.00890508009427</v>
+        <v>11.45533238588912</v>
       </c>
       <c r="J368">
-        <v>0.3232116755660293</v>
+        <v>0.3276661929445527</v>
       </c>
       <c r="K368">
-        <v>215.5</v>
+        <v>208</v>
       </c>
       <c r="L368">
-        <v>85.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="M368">
-        <v>206.5</v>
+        <v>206</v>
       </c>
       <c r="N368">
-        <v>93.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="O368">
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>467</v>
+        <v>131</v>
       </c>
     </row>
     <row r="369" spans="1:16">
       <c r="A369" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B369" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C369">
-        <v>15.37197148226591</v>
+        <v>13.45577889447236</v>
       </c>
       <c r="D369" t="s">
         <v>248</v>
       </c>
       <c r="E369">
-        <v>26.95678899561496</v>
+        <v>24.42984924623116</v>
       </c>
       <c r="F369">
         <v>1</v>
       </c>
       <c r="G369">
-        <v>0.1498280285177341</v>
+        <v>0.1543442211055276</v>
       </c>
       <c r="H369">
-        <v>0.1604432110043851</v>
+        <v>0.1629701507537689</v>
       </c>
       <c r="I369">
-        <v>11.58481751334905</v>
+        <v>10.9740703517588</v>
       </c>
       <c r="J369">
-        <v>0.3232116755660293</v>
+        <v>0.335448671931084</v>
       </c>
       <c r="K369">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L369">
-        <v>82.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="M369">
         <v>206.5</v>
@@ -20030,145 +20015,145 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="370" spans="1:16">
       <c r="A370" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B370" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C370">
-        <v>15.09009948164395</v>
+        <v>13.31081119885138</v>
       </c>
       <c r="D370" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E370">
-        <v>26.31992973578353</v>
+        <v>24.42984924623116</v>
       </c>
       <c r="F370">
         <v>1</v>
       </c>
       <c r="G370">
-        <v>0.1527099005183561</v>
+        <v>0.1578891888011486</v>
       </c>
       <c r="H370">
-        <v>0.1596800702642165</v>
+        <v>0.1629701507537689</v>
       </c>
       <c r="I370">
-        <v>11.22983025413959</v>
+        <v>11.11903804737977</v>
       </c>
       <c r="J370">
-        <v>0.3276661929445527</v>
+        <v>0.335448671931084</v>
       </c>
       <c r="K370">
-        <v>210</v>
+        <v>215.5</v>
       </c>
       <c r="L370">
-        <v>83.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M370">
-        <v>203.5</v>
+        <v>206.5</v>
       </c>
       <c r="N370">
-        <v>93</v>
+        <v>93.7</v>
       </c>
       <c r="O370">
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>131</v>
+        <v>464</v>
       </c>
     </row>
     <row r="371" spans="1:16">
       <c r="A371" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B371" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C371">
-        <v>14.98793542044889</v>
+        <v>13.42667623833452</v>
       </c>
       <c r="D371" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E371">
-        <v>26.31992973578353</v>
+        <v>24.42984924623116</v>
       </c>
       <c r="F371">
         <v>1</v>
       </c>
       <c r="G371">
-        <v>0.1562120645795511</v>
+        <v>0.1529733237616655</v>
       </c>
       <c r="H371">
-        <v>0.1596800702642165</v>
+        <v>0.1629701507537689</v>
       </c>
       <c r="I371">
-        <v>11.33199431533464</v>
+        <v>11.00317300789663</v>
       </c>
       <c r="J371">
-        <v>0.3276661929445527</v>
+        <v>0.335448671931084</v>
       </c>
       <c r="K371">
-        <v>215.5</v>
+        <v>208</v>
       </c>
       <c r="L371">
-        <v>85.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="M371">
-        <v>203.5</v>
+        <v>206.5</v>
       </c>
       <c r="N371">
-        <v>93</v>
+        <v>93.7</v>
       </c>
       <c r="O371">
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>131</v>
+        <v>464</v>
       </c>
     </row>
     <row r="372" spans="1:16">
       <c r="A372" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B372" t="s">
         <v>135</v>
       </c>
       <c r="C372">
-        <v>15.04543186753304</v>
+        <v>10.59259053965798</v>
       </c>
       <c r="D372" t="s">
         <v>249</v>
       </c>
       <c r="E372">
-        <v>26.31992973578353</v>
+        <v>21.96162940390666</v>
       </c>
       <c r="F372">
         <v>1</v>
       </c>
       <c r="G372">
-        <v>0.151354568132467</v>
+        <v>0.157207409460342</v>
       </c>
       <c r="H372">
-        <v>0.1596800702642165</v>
+        <v>0.1640383705960933</v>
       </c>
       <c r="I372">
-        <v>11.27449786825049</v>
+        <v>11.36903886424868</v>
       </c>
       <c r="J372">
-        <v>0.3276661929445527</v>
+        <v>0.3490829021921049</v>
       </c>
       <c r="K372">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L372">
-        <v>83.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="M372">
         <v>203.5</v>
@@ -20180,45 +20165,45 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>131</v>
+        <v>465</v>
       </c>
     </row>
     <row r="373" spans="1:16">
       <c r="A373" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B373" t="s">
         <v>136</v>
       </c>
       <c r="C373">
-        <v>15.21142902520036</v>
+        <v>10.37263457760139</v>
       </c>
       <c r="D373" t="s">
         <v>249</v>
       </c>
       <c r="E373">
-        <v>26.31992973578353</v>
+        <v>21.96162940390666</v>
       </c>
       <c r="F373">
         <v>1</v>
       </c>
       <c r="G373">
-        <v>0.1475885709747997</v>
+        <v>0.1608273654223986</v>
       </c>
       <c r="H373">
-        <v>0.1596800702642165</v>
+        <v>0.1640383705960933</v>
       </c>
       <c r="I373">
-        <v>11.10850071058317</v>
+        <v>11.58899482630527</v>
       </c>
       <c r="J373">
-        <v>0.3276661929445527</v>
+        <v>0.3490829021921049</v>
       </c>
       <c r="K373">
-        <v>202</v>
+        <v>215.5</v>
       </c>
       <c r="L373">
-        <v>81.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M373">
         <v>203.5</v>
@@ -20230,45 +20215,45 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>131</v>
+        <v>465</v>
       </c>
     </row>
     <row r="374" spans="1:16">
       <c r="A374" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B374" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C374">
-        <v>13.45577889447236</v>
+        <v>10.59075634404218</v>
       </c>
       <c r="D374" t="s">
         <v>249</v>
       </c>
       <c r="E374">
-        <v>24.7361952620244</v>
+        <v>21.96162940390666</v>
       </c>
       <c r="F374">
         <v>1</v>
       </c>
       <c r="G374">
-        <v>0.1543442211055276</v>
+        <v>0.1558092436559578</v>
       </c>
       <c r="H374">
-        <v>0.1612638047379756</v>
+        <v>0.1640383705960933</v>
       </c>
       <c r="I374">
-        <v>11.28041636755204</v>
+        <v>11.37087305986448</v>
       </c>
       <c r="J374">
-        <v>0.335448671931084</v>
+        <v>0.3490829021921049</v>
       </c>
       <c r="K374">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L374">
-        <v>83.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="M374">
         <v>203.5</v>
@@ -20280,45 +20265,45 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="375" spans="1:16">
       <c r="A375" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B375" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C375">
-        <v>13.31081119885138</v>
+        <v>10.88525375719482</v>
       </c>
       <c r="D375" t="s">
         <v>249</v>
       </c>
       <c r="E375">
-        <v>24.7361952620244</v>
+        <v>21.96162940390666</v>
       </c>
       <c r="F375">
         <v>1</v>
       </c>
       <c r="G375">
-        <v>0.1578891888011486</v>
+        <v>0.1519147462428052</v>
       </c>
       <c r="H375">
-        <v>0.1612638047379756</v>
+        <v>0.1640383705960933</v>
       </c>
       <c r="I375">
-        <v>11.42538406317301</v>
+        <v>11.07637564671184</v>
       </c>
       <c r="J375">
-        <v>0.335448671931084</v>
+        <v>0.3490829021921049</v>
       </c>
       <c r="K375">
-        <v>215.5</v>
+        <v>202</v>
       </c>
       <c r="L375">
-        <v>85.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M375">
         <v>203.5</v>
@@ -20330,145 +20315,145 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="376" spans="1:16">
       <c r="A376" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B376" t="s">
+        <v>136</v>
+      </c>
+      <c r="C376">
+        <v>8.066617110777202</v>
+      </c>
+      <c r="D376" t="s">
+        <v>250</v>
+      </c>
+      <c r="E376">
+        <v>20.60412942273109</v>
+      </c>
+      <c r="F376">
+        <v>1</v>
+      </c>
+      <c r="G376">
+        <v>0.1631333828892228</v>
+      </c>
+      <c r="H376">
+        <v>0.1673958705772689</v>
+      </c>
+      <c r="I376">
+        <v>12.53751231195389</v>
+      </c>
+      <c r="J376">
+        <v>0.3597836793003378</v>
+      </c>
+      <c r="K376">
+        <v>215.5</v>
+      </c>
+      <c r="L376">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="M376">
+        <v>204</v>
+      </c>
+      <c r="N376">
+        <v>94</v>
+      </c>
+      <c r="O376">
+        <v>1</v>
+      </c>
+      <c r="P376" t="s">
         <v>135</v>
-      </c>
-      <c r="C376">
-        <v>13.42667623833452</v>
-      </c>
-      <c r="D376" t="s">
-        <v>249</v>
-      </c>
-      <c r="E376">
-        <v>24.7361952620244</v>
-      </c>
-      <c r="F376">
-        <v>1</v>
-      </c>
-      <c r="G376">
-        <v>0.1529733237616655</v>
-      </c>
-      <c r="H376">
-        <v>0.1612638047379756</v>
-      </c>
-      <c r="I376">
-        <v>11.30951902368987</v>
-      </c>
-      <c r="J376">
-        <v>0.335448671931084</v>
-      </c>
-      <c r="K376">
-        <v>208</v>
-      </c>
-      <c r="L376">
-        <v>83.2</v>
-      </c>
-      <c r="M376">
-        <v>203.5</v>
-      </c>
-      <c r="N376">
-        <v>93</v>
-      </c>
-      <c r="O376">
-        <v>1</v>
-      </c>
-      <c r="P376" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="377" spans="1:16">
       <c r="A377" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B377" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C377">
-        <v>13.63936826992104</v>
+        <v>8.364994705529739</v>
       </c>
       <c r="D377" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E377">
-        <v>24.7361952620244</v>
+        <v>20.60412942273109</v>
       </c>
       <c r="F377">
         <v>1</v>
       </c>
       <c r="G377">
-        <v>0.149160631730079</v>
+        <v>0.1580350052944703</v>
       </c>
       <c r="H377">
-        <v>0.1612638047379756</v>
+        <v>0.1673958705772689</v>
       </c>
       <c r="I377">
-        <v>11.09682699210336</v>
+        <v>12.23913471720135</v>
       </c>
       <c r="J377">
-        <v>0.335448671931084</v>
+        <v>0.3597836793003378</v>
       </c>
       <c r="K377">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="L377">
-        <v>81.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="M377">
-        <v>203.5</v>
+        <v>204</v>
       </c>
       <c r="N377">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O377">
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>468</v>
+        <v>135</v>
       </c>
     </row>
     <row r="378" spans="1:16">
       <c r="A378" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B378" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C378">
-        <v>10.37263457760139</v>
+        <v>8.723696781331768</v>
       </c>
       <c r="D378" t="s">
         <v>250</v>
       </c>
       <c r="E378">
-        <v>22.78708795281059</v>
+        <v>20.60412942273109</v>
       </c>
       <c r="F378">
         <v>1</v>
       </c>
       <c r="G378">
-        <v>0.1608273654223986</v>
+        <v>0.1540763032186682</v>
       </c>
       <c r="H378">
-        <v>0.1652129120471894</v>
+        <v>0.1673958705772689</v>
       </c>
       <c r="I378">
-        <v>12.41445337520921</v>
+        <v>11.88043264139932</v>
       </c>
       <c r="J378">
-        <v>0.3490829021921049</v>
+        <v>0.3597836793003378</v>
       </c>
       <c r="K378">
-        <v>215.5</v>
+        <v>202</v>
       </c>
       <c r="L378">
-        <v>85.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M378">
         <v>204</v>
@@ -20480,157 +20465,157 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>469</v>
+        <v>135</v>
       </c>
     </row>
     <row r="379" spans="1:16">
       <c r="A379" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B379" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C379">
-        <v>10.59075634404218</v>
+        <v>-3.424244140274368</v>
       </c>
       <c r="D379" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E379">
-        <v>22.78708795281059</v>
+        <v>10.72424068728326</v>
       </c>
       <c r="F379">
         <v>1</v>
       </c>
       <c r="G379">
-        <v>0.1558092436559578</v>
+        <v>0.1690242441402744</v>
       </c>
       <c r="H379">
-        <v>0.1652129120471894</v>
+        <v>0.1852757593127167</v>
       </c>
       <c r="I379">
-        <v>12.19633160876842</v>
+        <v>14.14848482755762</v>
       </c>
       <c r="J379">
-        <v>0.3490829021921049</v>
+        <v>0.4206060689769481</v>
       </c>
       <c r="K379">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L379">
-        <v>83.2</v>
+        <v>82.8</v>
       </c>
       <c r="M379">
-        <v>204</v>
+        <v>207.5</v>
       </c>
       <c r="N379">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="O379">
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>469</v>
+        <v>136</v>
       </c>
     </row>
     <row r="380" spans="1:16">
       <c r="A380" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B380" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C380">
-        <v>10.88525375719482</v>
+        <v>-2.10269534440512</v>
       </c>
       <c r="D380" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E380">
-        <v>22.78708795281059</v>
+        <v>10.74605227334604</v>
       </c>
       <c r="F380">
         <v>1</v>
       </c>
       <c r="G380">
-        <v>0.1519147462428052</v>
+        <v>0.1703026953444051</v>
       </c>
       <c r="H380">
-        <v>0.1652129120471894</v>
+        <v>0.185253947726654</v>
       </c>
       <c r="I380">
-        <v>11.90183419561578</v>
+        <v>12.84874761775116</v>
       </c>
       <c r="J380">
-        <v>0.3490829021921049</v>
+        <v>0.4205009528995372</v>
       </c>
       <c r="K380">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L380">
-        <v>81.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M380">
-        <v>204</v>
+        <v>207.5</v>
       </c>
       <c r="N380">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="O380">
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="381" spans="1:16">
       <c r="A381" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B381" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C381">
-        <v>11.23800505061848</v>
+        <v>-1.02931617171204</v>
       </c>
       <c r="D381" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E381">
-        <v>22.78708795281059</v>
+        <v>-3.367440857122276</v>
       </c>
       <c r="F381">
         <v>1</v>
       </c>
       <c r="G381">
-        <v>0.1543619949493815</v>
+        <v>0.162829316171712</v>
       </c>
       <c r="H381">
-        <v>0.1652129120471894</v>
+        <v>0.1613674408571223</v>
       </c>
       <c r="I381">
-        <v>11.54908290219211</v>
+        <v>-2.338124685410236</v>
       </c>
       <c r="J381">
-        <v>0.3490829021921049</v>
+        <v>0.4381246854102249</v>
       </c>
       <c r="K381">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="L381">
-        <v>82.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="M381">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="N381">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="O381">
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20638,349 +20623,49 @@
         <v>0</v>
       </c>
       <c r="B382" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C382">
-        <v>8.066617110777202</v>
+        <v>-36.89254119687769</v>
       </c>
       <c r="D382" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E382">
-        <v>20.60412942273109</v>
+        <v>-39.42244783429415</v>
       </c>
       <c r="F382">
         <v>1</v>
       </c>
       <c r="G382">
-        <v>0.1631333828892228</v>
+        <v>0.1986925411968777</v>
       </c>
       <c r="H382">
-        <v>0.1673958705772689</v>
+        <v>0.1974224478342941</v>
       </c>
       <c r="I382">
-        <v>12.53751231195389</v>
+        <v>-2.52990663741646</v>
       </c>
       <c r="J382">
-        <v>0.3597836793003378</v>
+        <v>0.6299066374164582</v>
       </c>
       <c r="K382">
-        <v>215.5</v>
+        <v>187</v>
       </c>
       <c r="L382">
-        <v>85.59999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="M382">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="N382">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="O382">
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="383" spans="1:16">
-      <c r="A383" s="1">
-        <v>1</v>
-      </c>
-      <c r="B383" t="s">
-        <v>137</v>
-      </c>
-      <c r="C383">
-        <v>9.044345743430753</v>
-      </c>
-      <c r="D383" t="s">
-        <v>250</v>
-      </c>
-      <c r="E383">
-        <v>20.60412942273109</v>
-      </c>
-      <c r="F383">
-        <v>1</v>
-      </c>
-      <c r="G383">
-        <v>0.1565556542565693</v>
-      </c>
-      <c r="H383">
-        <v>0.1673958705772689</v>
-      </c>
-      <c r="I383">
-        <v>11.55978367930034</v>
-      </c>
-      <c r="J383">
-        <v>0.3597836793003378</v>
-      </c>
-      <c r="K383">
-        <v>205</v>
-      </c>
-      <c r="L383">
-        <v>82.8</v>
-      </c>
-      <c r="M383">
-        <v>204</v>
-      </c>
-      <c r="N383">
-        <v>94</v>
-      </c>
-      <c r="O383">
-        <v>1</v>
-      </c>
-      <c r="P383" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="384" spans="1:16">
-      <c r="A384" s="1">
-        <v>0</v>
-      </c>
-      <c r="B384" t="s">
-        <v>138</v>
-      </c>
-      <c r="C384">
-        <v>-2.124244140274371</v>
-      </c>
-      <c r="D384" t="s">
-        <v>251</v>
-      </c>
-      <c r="E384">
-        <v>10.72424068728326</v>
-      </c>
-      <c r="F384">
-        <v>1</v>
-      </c>
-      <c r="G384">
-        <v>0.1703242441402744</v>
-      </c>
-      <c r="H384">
-        <v>0.1852757593127167</v>
-      </c>
-      <c r="I384">
-        <v>12.84848482755763</v>
-      </c>
-      <c r="J384">
-        <v>0.4206060689769481</v>
-      </c>
-      <c r="K384">
-        <v>205</v>
-      </c>
-      <c r="L384">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="M384">
-        <v>207.5</v>
-      </c>
-      <c r="N384">
-        <v>98</v>
-      </c>
-      <c r="O384">
-        <v>1</v>
-      </c>
-      <c r="P384" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="385" spans="1:16">
-      <c r="A385" s="1">
-        <v>0</v>
-      </c>
-      <c r="B385" t="s">
-        <v>139</v>
-      </c>
-      <c r="C385">
-        <v>13.16161645214643</v>
-      </c>
-      <c r="D385" t="s">
-        <v>252</v>
-      </c>
-      <c r="E385">
-        <v>8.161307255339082</v>
-      </c>
-      <c r="F385">
-        <v>-1</v>
-      </c>
-      <c r="G385">
-        <v>0.1634383835478536</v>
-      </c>
-      <c r="H385">
-        <v>0.1676386927446609</v>
-      </c>
-      <c r="I385">
-        <v>5.000309196807351</v>
-      </c>
-      <c r="J385">
-        <v>0.4381246854102249</v>
-      </c>
-      <c r="K385">
-        <v>171.5</v>
-      </c>
-      <c r="L385">
-        <v>88.3</v>
-      </c>
-      <c r="M385">
-        <v>182</v>
-      </c>
-      <c r="N385">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="O385">
-        <v>1</v>
-      </c>
-      <c r="P385" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="386" spans="1:16">
-      <c r="A386" s="1">
-        <v>0</v>
-      </c>
-      <c r="B386" t="s">
-        <v>140</v>
-      </c>
-      <c r="C386">
-        <v>-21.82338146012957</v>
-      </c>
-      <c r="D386" t="s">
-        <v>252</v>
-      </c>
-      <c r="E386">
-        <v>-26.74300800979539</v>
-      </c>
-      <c r="F386">
-        <v>-1</v>
-      </c>
-      <c r="G386">
-        <v>0.2024233814601296</v>
-      </c>
-      <c r="H386">
-        <v>0.2025430080097954</v>
-      </c>
-      <c r="I386">
-        <v>4.919626549665821</v>
-      </c>
-      <c r="J386">
-        <v>0.6299066374164582</v>
-      </c>
-      <c r="K386">
-        <v>178</v>
-      </c>
-      <c r="L386">
-        <v>90.3</v>
-      </c>
-      <c r="M386">
-        <v>182</v>
-      </c>
-      <c r="N386">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="O386">
-        <v>1</v>
-      </c>
-      <c r="P386" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="387" spans="1:16">
-      <c r="A387" s="1">
-        <v>0</v>
-      </c>
-      <c r="B387" t="s">
-        <v>141</v>
-      </c>
-      <c r="C387">
-        <v>32.20533098261782</v>
-      </c>
-      <c r="D387" t="s">
-        <v>253</v>
-      </c>
-      <c r="E387">
-        <v>28.32229381498548</v>
-      </c>
-      <c r="F387">
-        <v>-1</v>
-      </c>
-      <c r="G387">
-        <v>0.1503946690173822</v>
-      </c>
-      <c r="H387">
-        <v>0.1530777061850145</v>
-      </c>
-      <c r="I387">
-        <v>3.883037167632338</v>
-      </c>
-      <c r="J387">
-        <v>0.3283037167632343</v>
-      </c>
-      <c r="K387">
-        <v>180</v>
-      </c>
-      <c r="L387">
-        <v>91.3</v>
-      </c>
-      <c r="M387">
-        <v>190</v>
-      </c>
-      <c r="N387">
-        <v>90.7</v>
-      </c>
-      <c r="O387">
-        <v>1</v>
-      </c>
-      <c r="P387" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="388" spans="1:16">
-      <c r="A388" s="1">
-        <v>0</v>
-      </c>
-      <c r="B388" t="s">
-        <v>141</v>
-      </c>
-      <c r="C388">
-        <v>30.11806288540985</v>
-      </c>
-      <c r="D388" t="s">
-        <v>253</v>
-      </c>
-      <c r="E388">
-        <v>26.11906637904373</v>
-      </c>
-      <c r="F388">
-        <v>-1</v>
-      </c>
-      <c r="G388">
-        <v>0.1524819371145902</v>
-      </c>
-      <c r="H388">
-        <v>0.1552809336209563</v>
-      </c>
-      <c r="I388">
-        <v>3.998996506366119</v>
-      </c>
-      <c r="J388">
-        <v>0.3398996506366119</v>
-      </c>
-      <c r="K388">
-        <v>180</v>
-      </c>
-      <c r="L388">
-        <v>91.3</v>
-      </c>
-      <c r="M388">
-        <v>190</v>
-      </c>
-      <c r="N388">
-        <v>90.7</v>
-      </c>
-      <c r="O388">
-        <v>1</v>
-      </c>
-      <c r="P388" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-2474-2382-800.xlsx
+++ b/s60_signal/position-2474-2382-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="473">
   <si>
     <t>trade_time</t>
   </si>
@@ -415,999 +415,1002 @@
     <t>2020-12-29</t>
   </si>
   <si>
+    <t>2021-01-19</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>2021-01-21</t>
+  </si>
+  <si>
+    <t>2021-01-28</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>2021-07-26</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
+    <t>2010-10-22</t>
+  </si>
+  <si>
+    <t>2010-10-25</t>
+  </si>
+  <si>
+    <t>2010-10-28</t>
+  </si>
+  <si>
+    <t>2011-05-13</t>
+  </si>
+  <si>
+    <t>2011-05-16</t>
+  </si>
+  <si>
+    <t>2011-05-17</t>
+  </si>
+  <si>
+    <t>2011-05-18</t>
+  </si>
+  <si>
+    <t>2011-05-19</t>
+  </si>
+  <si>
+    <t>2011-05-20</t>
+  </si>
+  <si>
+    <t>2011-05-23</t>
+  </si>
+  <si>
+    <t>2011-05-24</t>
+  </si>
+  <si>
+    <t>2011-05-25</t>
+  </si>
+  <si>
+    <t>2011-05-26</t>
+  </si>
+  <si>
+    <t>2011-05-27</t>
+  </si>
+  <si>
+    <t>2011-05-30</t>
+  </si>
+  <si>
+    <t>2011-05-31</t>
+  </si>
+  <si>
+    <t>2011-06-02</t>
+  </si>
+  <si>
+    <t>2011-06-03</t>
+  </si>
+  <si>
+    <t>2011-07-22</t>
+  </si>
+  <si>
+    <t>2011-07-25</t>
+  </si>
+  <si>
+    <t>2011-07-27</t>
+  </si>
+  <si>
+    <t>2011-07-28</t>
+  </si>
+  <si>
+    <t>2011-07-29</t>
+  </si>
+  <si>
+    <t>2011-10-07</t>
+  </si>
+  <si>
+    <t>2011-10-05</t>
+  </si>
+  <si>
+    <t>2012-02-29</t>
+  </si>
+  <si>
+    <t>2012-07-18</t>
+  </si>
+  <si>
+    <t>2012-05-02</t>
+  </si>
+  <si>
+    <t>2012-05-25</t>
+  </si>
+  <si>
+    <t>2012-11-13</t>
+  </si>
+  <si>
+    <t>2012-11-14</t>
+  </si>
+  <si>
+    <t>2012-12-14</t>
+  </si>
+  <si>
+    <t>2012-08-01</t>
+  </si>
+  <si>
+    <t>2013-06-14</t>
+  </si>
+  <si>
+    <t>2013-06-17</t>
+  </si>
+  <si>
+    <t>2013-06-18</t>
+  </si>
+  <si>
+    <t>2013-05-20</t>
+  </si>
+  <si>
+    <t>2013-08-06</t>
+  </si>
+  <si>
+    <t>2013-05-16</t>
+  </si>
+  <si>
+    <t>2013-11-28</t>
+  </si>
+  <si>
+    <t>2013-12-04</t>
+  </si>
+  <si>
+    <t>2014-02-17</t>
+  </si>
+  <si>
+    <t>2014-02-19</t>
+  </si>
+  <si>
+    <t>2013-08-07</t>
+  </si>
+  <si>
+    <t>2013-08-08</t>
+  </si>
+  <si>
+    <t>2013-08-09</t>
+  </si>
+  <si>
+    <t>2013-09-23</t>
+  </si>
+  <si>
+    <t>2014-04-25</t>
+  </si>
+  <si>
+    <t>2014-04-24</t>
+  </si>
+  <si>
+    <t>2014-09-15</t>
+  </si>
+  <si>
+    <t>2014-12-02</t>
+  </si>
+  <si>
+    <t>2014-09-10</t>
+  </si>
+  <si>
+    <t>2014-09-04</t>
+  </si>
+  <si>
+    <t>2014-11-11</t>
+  </si>
+  <si>
+    <t>2014-09-03</t>
+  </si>
+  <si>
+    <t>2014-11-03</t>
+  </si>
+  <si>
+    <t>2014-11-27</t>
+  </si>
+  <si>
+    <t>2015-03-18</t>
+  </si>
+  <si>
+    <t>2015-08-07</t>
+  </si>
+  <si>
+    <t>2016-03-16</t>
+  </si>
+  <si>
+    <t>2016-03-17</t>
+  </si>
+  <si>
+    <t>2016-02-01</t>
+  </si>
+  <si>
+    <t>2016-02-02</t>
+  </si>
+  <si>
+    <t>2016-07-18</t>
+  </si>
+  <si>
+    <t>2016-06-30</t>
+  </si>
+  <si>
+    <t>2016-08-03</t>
+  </si>
+  <si>
+    <t>2016-07-01</t>
+  </si>
+  <si>
+    <t>2017-02-08</t>
+  </si>
+  <si>
+    <t>2017-06-23</t>
+  </si>
+  <si>
+    <t>2017-03-29</t>
+  </si>
+  <si>
+    <t>2017-11-15</t>
+  </si>
+  <si>
+    <t>2018-03-08</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>2018-04-18</t>
+  </si>
+  <si>
+    <t>2018-04-19</t>
+  </si>
+  <si>
+    <t>2018-04-20</t>
+  </si>
+  <si>
+    <t>2018-04-23</t>
+  </si>
+  <si>
+    <t>2018-05-04</t>
+  </si>
+  <si>
+    <t>2018-05-07</t>
+  </si>
+  <si>
+    <t>2018-05-08</t>
+  </si>
+  <si>
+    <t>2018-04-12</t>
+  </si>
+  <si>
+    <t>2018-11-16</t>
+  </si>
+  <si>
+    <t>2018-11-30</t>
+  </si>
+  <si>
+    <t>2018-12-03</t>
+  </si>
+  <si>
+    <t>2018-12-27</t>
+  </si>
+  <si>
+    <t>2019-01-03</t>
+  </si>
+  <si>
+    <t>2019-02-14</t>
+  </si>
+  <si>
+    <t>2019-02-20</t>
+  </si>
+  <si>
+    <t>2019-09-12</t>
+  </si>
+  <si>
+    <t>2019-09-16</t>
+  </si>
+  <si>
+    <t>2019-09-17</t>
+  </si>
+  <si>
+    <t>2019-09-18</t>
+  </si>
+  <si>
+    <t>2019-09-19</t>
+  </si>
+  <si>
+    <t>2019-09-23</t>
+  </si>
+  <si>
+    <t>2019-10-30</t>
+  </si>
+  <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
+    <t>2019-11-11</t>
+  </si>
+  <si>
+    <t>2019-11-14</t>
+  </si>
+  <si>
+    <t>2019-11-05</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2020-05-29</t>
+  </si>
+  <si>
+    <t>2020-06-03</t>
+  </si>
+  <si>
+    <t>2020-06-04</t>
+  </si>
+  <si>
+    <t>2021-02-17</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>2021-03-23</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>2021-03-29</t>
+  </si>
+  <si>
+    <t>2010-08-03</t>
+  </si>
+  <si>
+    <t>2010-08-19</t>
+  </si>
+  <si>
+    <t>2010-08-26</t>
+  </si>
+  <si>
+    <t>2010-08-27</t>
+  </si>
+  <si>
+    <t>2010-08-30</t>
+  </si>
+  <si>
+    <t>2010-09-17</t>
+  </si>
+  <si>
+    <t>2010-09-20</t>
+  </si>
+  <si>
+    <t>2010-09-21</t>
+  </si>
+  <si>
+    <t>2010-09-23</t>
+  </si>
+  <si>
+    <t>2010-09-24</t>
+  </si>
+  <si>
+    <t>2010-09-27</t>
+  </si>
+  <si>
+    <t>2010-09-28</t>
+  </si>
+  <si>
+    <t>2010-09-29</t>
+  </si>
+  <si>
+    <t>2010-09-30</t>
+  </si>
+  <si>
+    <t>2010-10-01</t>
+  </si>
+  <si>
+    <t>2010-10-04</t>
+  </si>
+  <si>
+    <t>2010-10-05</t>
+  </si>
+  <si>
+    <t>2010-10-06</t>
+  </si>
+  <si>
+    <t>2010-10-07</t>
+  </si>
+  <si>
+    <t>2010-10-08</t>
+  </si>
+  <si>
+    <t>2010-10-11</t>
+  </si>
+  <si>
+    <t>2010-11-24</t>
+  </si>
+  <si>
+    <t>2010-11-25</t>
+  </si>
+  <si>
+    <t>2010-11-26</t>
+  </si>
+  <si>
+    <t>2010-11-29</t>
+  </si>
+  <si>
+    <t>2010-11-30</t>
+  </si>
+  <si>
+    <t>2010-12-01</t>
+  </si>
+  <si>
+    <t>2010-12-02</t>
+  </si>
+  <si>
+    <t>2010-12-03</t>
+  </si>
+  <si>
+    <t>2011-06-24</t>
+  </si>
+  <si>
+    <t>2011-06-27</t>
+  </si>
+  <si>
+    <t>2011-06-30</t>
+  </si>
+  <si>
+    <t>2011-07-07</t>
+  </si>
+  <si>
+    <t>2011-12-02</t>
+  </si>
+  <si>
+    <t>2011-12-05</t>
+  </si>
+  <si>
+    <t>2012-02-24</t>
+  </si>
+  <si>
+    <t>2012-03-02</t>
+  </si>
+  <si>
+    <t>2012-03-06</t>
+  </si>
+  <si>
+    <t>2012-03-07</t>
+  </si>
+  <si>
+    <t>2012-03-12</t>
+  </si>
+  <si>
+    <t>2012-03-13</t>
+  </si>
+  <si>
+    <t>2012-03-29</t>
+  </si>
+  <si>
+    <t>2012-03-30</t>
+  </si>
+  <si>
+    <t>2012-05-03</t>
+  </si>
+  <si>
+    <t>2012-05-15</t>
+  </si>
+  <si>
+    <t>2012-05-16</t>
+  </si>
+  <si>
+    <t>2012-05-17</t>
+  </si>
+  <si>
+    <t>2012-05-18</t>
+  </si>
+  <si>
+    <t>2012-05-21</t>
+  </si>
+  <si>
+    <t>2012-05-22</t>
+  </si>
+  <si>
+    <t>2012-05-23</t>
+  </si>
+  <si>
+    <t>2012-05-24</t>
+  </si>
+  <si>
+    <t>2012-05-28</t>
+  </si>
+  <si>
+    <t>2012-05-29</t>
+  </si>
+  <si>
+    <t>2012-05-30</t>
+  </si>
+  <si>
+    <t>2012-05-31</t>
+  </si>
+  <si>
+    <t>2012-06-01</t>
+  </si>
+  <si>
+    <t>2012-06-04</t>
+  </si>
+  <si>
+    <t>2012-06-05</t>
+  </si>
+  <si>
+    <t>2012-06-06</t>
+  </si>
+  <si>
+    <t>2012-06-07</t>
+  </si>
+  <si>
+    <t>2012-06-08</t>
+  </si>
+  <si>
+    <t>2012-06-11</t>
+  </si>
+  <si>
+    <t>2012-06-12</t>
+  </si>
+  <si>
+    <t>2012-06-13</t>
+  </si>
+  <si>
+    <t>2012-06-14</t>
+  </si>
+  <si>
+    <t>2012-06-15</t>
+  </si>
+  <si>
+    <t>2012-06-19</t>
+  </si>
+  <si>
+    <t>2012-06-20</t>
+  </si>
+  <si>
+    <t>2012-06-22</t>
+  </si>
+  <si>
+    <t>2012-10-18</t>
+  </si>
+  <si>
+    <t>2012-10-19</t>
+  </si>
+  <si>
+    <t>2012-10-22</t>
+  </si>
+  <si>
+    <t>2013-04-08</t>
+  </si>
+  <si>
+    <t>2013-04-12</t>
+  </si>
+  <si>
+    <t>2013-06-25</t>
+  </si>
+  <si>
+    <t>2013-06-27</t>
+  </si>
+  <si>
+    <t>2013-06-28</t>
+  </si>
+  <si>
+    <t>2013-07-01</t>
+  </si>
+  <si>
+    <t>2013-07-02</t>
+  </si>
+  <si>
+    <t>2013-07-03</t>
+  </si>
+  <si>
+    <t>2013-07-04</t>
+  </si>
+  <si>
+    <t>2013-10-28</t>
+  </si>
+  <si>
+    <t>2014-01-22</t>
+  </si>
+  <si>
+    <t>2014-01-23</t>
+  </si>
+  <si>
+    <t>2014-01-24</t>
+  </si>
+  <si>
+    <t>2014-01-27</t>
+  </si>
+  <si>
+    <t>2014-02-06</t>
+  </si>
+  <si>
+    <t>2014-02-07</t>
+  </si>
+  <si>
+    <t>2014-02-10</t>
+  </si>
+  <si>
+    <t>2014-02-11</t>
+  </si>
+  <si>
+    <t>2014-02-18</t>
+  </si>
+  <si>
+    <t>2014-02-20</t>
+  </si>
+  <si>
+    <t>2014-02-21</t>
+  </si>
+  <si>
+    <t>2014-07-08</t>
+  </si>
+  <si>
+    <t>2014-07-10</t>
+  </si>
+  <si>
+    <t>2014-07-11</t>
+  </si>
+  <si>
+    <t>2014-07-16</t>
+  </si>
+  <si>
+    <t>2014-07-17</t>
+  </si>
+  <si>
+    <t>2014-07-18</t>
+  </si>
+  <si>
+    <t>2014-10-15</t>
+  </si>
+  <si>
+    <t>2014-11-04</t>
+  </si>
+  <si>
+    <t>2015-06-11</t>
+  </si>
+  <si>
+    <t>2015-06-12</t>
+  </si>
+  <si>
+    <t>2015-06-15</t>
+  </si>
+  <si>
+    <t>2015-07-22</t>
+  </si>
+  <si>
+    <t>2015-07-23</t>
+  </si>
+  <si>
+    <t>2015-10-15</t>
+  </si>
+  <si>
+    <t>2015-10-16</t>
+  </si>
+  <si>
+    <t>2015-11-19</t>
+  </si>
+  <si>
+    <t>2016-04-01</t>
+  </si>
+  <si>
+    <t>2016-04-07</t>
+  </si>
+  <si>
+    <t>2016-04-08</t>
+  </si>
+  <si>
+    <t>2016-04-15</t>
+  </si>
+  <si>
+    <t>2016-04-18</t>
+  </si>
+  <si>
+    <t>2016-04-19</t>
+  </si>
+  <si>
+    <t>2016-04-21</t>
+  </si>
+  <si>
+    <t>2016-04-22</t>
+  </si>
+  <si>
+    <t>2016-04-27</t>
+  </si>
+  <si>
+    <t>2016-04-28</t>
+  </si>
+  <si>
+    <t>2016-05-03</t>
+  </si>
+  <si>
+    <t>2016-05-05</t>
+  </si>
+  <si>
+    <t>2016-05-10</t>
+  </si>
+  <si>
+    <t>2016-05-11</t>
+  </si>
+  <si>
+    <t>2016-05-12</t>
+  </si>
+  <si>
+    <t>2016-05-13</t>
+  </si>
+  <si>
+    <t>2016-05-16</t>
+  </si>
+  <si>
+    <t>2016-05-17</t>
+  </si>
+  <si>
+    <t>2016-10-27</t>
+  </si>
+  <si>
+    <t>2016-12-15</t>
+  </si>
+  <si>
+    <t>2017-06-26</t>
+  </si>
+  <si>
+    <t>2017-06-27</t>
+  </si>
+  <si>
+    <t>2017-07-11</t>
+  </si>
+  <si>
+    <t>2017-07-12</t>
+  </si>
+  <si>
+    <t>2017-07-13</t>
+  </si>
+  <si>
+    <t>2017-07-14</t>
+  </si>
+  <si>
+    <t>2017-07-17</t>
+  </si>
+  <si>
+    <t>2017-08-21</t>
+  </si>
+  <si>
+    <t>2017-08-22</t>
+  </si>
+  <si>
+    <t>2017-08-23</t>
+  </si>
+  <si>
+    <t>2017-08-24</t>
+  </si>
+  <si>
+    <t>2017-08-25</t>
+  </si>
+  <si>
+    <t>2017-09-06</t>
+  </si>
+  <si>
+    <t>2017-09-07</t>
+  </si>
+  <si>
+    <t>2017-09-08</t>
+  </si>
+  <si>
+    <t>2018-01-12</t>
+  </si>
+  <si>
+    <t>2018-01-15</t>
+  </si>
+  <si>
+    <t>2018-01-16</t>
+  </si>
+  <si>
+    <t>2018-01-17</t>
+  </si>
+  <si>
+    <t>2018-01-30</t>
+  </si>
+  <si>
+    <t>2018-01-31</t>
+  </si>
+  <si>
+    <t>2018-02-06</t>
+  </si>
+  <si>
+    <t>2018-02-22</t>
+  </si>
+  <si>
+    <t>2018-03-30</t>
+  </si>
+  <si>
+    <t>2018-05-16</t>
+  </si>
+  <si>
+    <t>2018-05-21</t>
+  </si>
+  <si>
+    <t>2018-11-20</t>
+  </si>
+  <si>
+    <t>2018-12-28</t>
+  </si>
+  <si>
+    <t>2019-01-09</t>
+  </si>
+  <si>
+    <t>2019-01-10</t>
+  </si>
+  <si>
+    <t>2019-01-15</t>
+  </si>
+  <si>
+    <t>2019-01-16</t>
+  </si>
+  <si>
+    <t>2019-01-17</t>
+  </si>
+  <si>
+    <t>2019-01-18</t>
+  </si>
+  <si>
+    <t>2019-01-22</t>
+  </si>
+  <si>
+    <t>2019-01-23</t>
+  </si>
+  <si>
+    <t>2019-01-24</t>
+  </si>
+  <si>
+    <t>2019-01-25</t>
+  </si>
+  <si>
+    <t>2019-01-29</t>
+  </si>
+  <si>
+    <t>2019-03-11</t>
+  </si>
+  <si>
+    <t>2019-03-12</t>
+  </si>
+  <si>
+    <t>2019-03-13</t>
+  </si>
+  <si>
+    <t>2019-04-09</t>
+  </si>
+  <si>
+    <t>2019-04-10</t>
+  </si>
+  <si>
+    <t>2019-04-18</t>
+  </si>
+  <si>
+    <t>2019-04-19</t>
+  </si>
+  <si>
+    <t>2019-04-25</t>
+  </si>
+  <si>
+    <t>2019-04-26</t>
+  </si>
+  <si>
+    <t>2019-05-02</t>
+  </si>
+  <si>
+    <t>2019-05-07</t>
+  </si>
+  <si>
+    <t>2019-05-08</t>
+  </si>
+  <si>
+    <t>2019-05-09</t>
+  </si>
+  <si>
+    <t>2019-05-10</t>
+  </si>
+  <si>
+    <t>2019-05-13</t>
+  </si>
+  <si>
+    <t>2019-07-29</t>
+  </si>
+  <si>
+    <t>2019-08-29</t>
+  </si>
+  <si>
+    <t>2019-08-30</t>
+  </si>
+  <si>
+    <t>2019-09-02</t>
+  </si>
+  <si>
+    <t>2019-09-03</t>
+  </si>
+  <si>
+    <t>2019-09-04</t>
+  </si>
+  <si>
+    <t>2019-09-05</t>
+  </si>
+  <si>
+    <t>2019-09-06</t>
+  </si>
+  <si>
+    <t>2019-09-10</t>
+  </si>
+  <si>
+    <t>2020-02-20</t>
+  </si>
+  <si>
+    <t>2020-02-21</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>2020-02-27</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-03-04</t>
+  </si>
+  <si>
+    <t>2020-03-05</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2020-03-09</t>
+  </si>
+  <si>
+    <t>2020-03-12</t>
+  </si>
+  <si>
+    <t>2020-11-02</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>2020-12-28</t>
+  </si>
+  <si>
     <t>2020-12-31</t>
   </si>
   <si>
-    <t>2021-01-19</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-14</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>2021-01-21</t>
-  </si>
-  <si>
-    <t>2021-01-28</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-07-26</t>
-  </si>
-  <si>
-    <t>2010-10-22</t>
-  </si>
-  <si>
-    <t>2010-10-25</t>
-  </si>
-  <si>
-    <t>2010-10-28</t>
-  </si>
-  <si>
-    <t>2011-05-13</t>
-  </si>
-  <si>
-    <t>2011-05-16</t>
-  </si>
-  <si>
-    <t>2011-05-17</t>
-  </si>
-  <si>
-    <t>2011-05-18</t>
-  </si>
-  <si>
-    <t>2011-05-19</t>
-  </si>
-  <si>
-    <t>2011-05-20</t>
-  </si>
-  <si>
-    <t>2011-05-23</t>
-  </si>
-  <si>
-    <t>2011-05-24</t>
-  </si>
-  <si>
-    <t>2011-05-25</t>
-  </si>
-  <si>
-    <t>2011-05-26</t>
-  </si>
-  <si>
-    <t>2011-05-27</t>
-  </si>
-  <si>
-    <t>2011-05-30</t>
-  </si>
-  <si>
-    <t>2011-05-31</t>
-  </si>
-  <si>
-    <t>2011-06-02</t>
-  </si>
-  <si>
-    <t>2011-06-03</t>
-  </si>
-  <si>
-    <t>2011-07-22</t>
-  </si>
-  <si>
-    <t>2011-07-25</t>
-  </si>
-  <si>
-    <t>2011-07-27</t>
-  </si>
-  <si>
-    <t>2011-07-28</t>
-  </si>
-  <si>
-    <t>2011-07-29</t>
-  </si>
-  <si>
-    <t>2011-10-07</t>
-  </si>
-  <si>
-    <t>2011-10-05</t>
-  </si>
-  <si>
-    <t>2012-02-29</t>
-  </si>
-  <si>
-    <t>2012-07-18</t>
-  </si>
-  <si>
-    <t>2012-05-02</t>
-  </si>
-  <si>
-    <t>2012-05-25</t>
-  </si>
-  <si>
-    <t>2012-11-13</t>
-  </si>
-  <si>
-    <t>2012-11-14</t>
-  </si>
-  <si>
-    <t>2012-12-14</t>
-  </si>
-  <si>
-    <t>2012-08-01</t>
-  </si>
-  <si>
-    <t>2013-06-14</t>
-  </si>
-  <si>
-    <t>2013-06-17</t>
-  </si>
-  <si>
-    <t>2013-06-18</t>
-  </si>
-  <si>
-    <t>2013-05-20</t>
-  </si>
-  <si>
-    <t>2013-08-06</t>
-  </si>
-  <si>
-    <t>2013-05-16</t>
-  </si>
-  <si>
-    <t>2013-11-28</t>
-  </si>
-  <si>
-    <t>2013-12-04</t>
-  </si>
-  <si>
-    <t>2014-02-17</t>
-  </si>
-  <si>
-    <t>2014-02-19</t>
-  </si>
-  <si>
-    <t>2013-08-07</t>
-  </si>
-  <si>
-    <t>2013-08-08</t>
-  </si>
-  <si>
-    <t>2013-08-09</t>
-  </si>
-  <si>
-    <t>2013-09-23</t>
-  </si>
-  <si>
-    <t>2014-04-25</t>
-  </si>
-  <si>
-    <t>2014-04-24</t>
-  </si>
-  <si>
-    <t>2014-09-15</t>
-  </si>
-  <si>
-    <t>2014-12-02</t>
-  </si>
-  <si>
-    <t>2014-09-10</t>
-  </si>
-  <si>
-    <t>2014-09-04</t>
-  </si>
-  <si>
-    <t>2014-11-11</t>
-  </si>
-  <si>
-    <t>2014-09-03</t>
-  </si>
-  <si>
-    <t>2014-11-03</t>
-  </si>
-  <si>
-    <t>2014-11-27</t>
-  </si>
-  <si>
-    <t>2015-03-18</t>
-  </si>
-  <si>
-    <t>2015-08-07</t>
-  </si>
-  <si>
-    <t>2016-03-16</t>
-  </si>
-  <si>
-    <t>2016-03-17</t>
-  </si>
-  <si>
-    <t>2016-02-01</t>
-  </si>
-  <si>
-    <t>2016-02-02</t>
-  </si>
-  <si>
-    <t>2016-07-18</t>
-  </si>
-  <si>
-    <t>2016-06-30</t>
-  </si>
-  <si>
-    <t>2016-08-03</t>
-  </si>
-  <si>
-    <t>2016-07-01</t>
-  </si>
-  <si>
-    <t>2017-02-08</t>
-  </si>
-  <si>
-    <t>2017-06-23</t>
-  </si>
-  <si>
-    <t>2017-03-29</t>
-  </si>
-  <si>
-    <t>2017-11-15</t>
-  </si>
-  <si>
-    <t>2018-03-08</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>2018-04-18</t>
-  </si>
-  <si>
-    <t>2018-04-19</t>
-  </si>
-  <si>
-    <t>2018-04-20</t>
-  </si>
-  <si>
-    <t>2018-04-23</t>
-  </si>
-  <si>
-    <t>2018-05-04</t>
-  </si>
-  <si>
-    <t>2018-05-07</t>
-  </si>
-  <si>
-    <t>2018-05-08</t>
-  </si>
-  <si>
-    <t>2018-04-12</t>
-  </si>
-  <si>
-    <t>2018-11-16</t>
-  </si>
-  <si>
-    <t>2018-11-30</t>
-  </si>
-  <si>
-    <t>2018-12-03</t>
-  </si>
-  <si>
-    <t>2018-12-27</t>
-  </si>
-  <si>
-    <t>2019-01-03</t>
-  </si>
-  <si>
-    <t>2019-02-14</t>
-  </si>
-  <si>
-    <t>2019-02-20</t>
-  </si>
-  <si>
-    <t>2019-09-12</t>
-  </si>
-  <si>
-    <t>2019-09-16</t>
-  </si>
-  <si>
-    <t>2019-09-17</t>
-  </si>
-  <si>
-    <t>2019-09-18</t>
-  </si>
-  <si>
-    <t>2019-09-19</t>
-  </si>
-  <si>
-    <t>2019-09-23</t>
-  </si>
-  <si>
-    <t>2019-10-30</t>
-  </si>
-  <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
-    <t>2019-11-11</t>
-  </si>
-  <si>
-    <t>2019-11-14</t>
-  </si>
-  <si>
-    <t>2019-11-05</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2020-05-29</t>
-  </si>
-  <si>
-    <t>2020-06-03</t>
-  </si>
-  <si>
-    <t>2020-06-04</t>
-  </si>
-  <si>
-    <t>2021-02-17</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>2021-03-23</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>2021-03-29</t>
-  </si>
-  <si>
-    <t>2021-07-28</t>
-  </si>
-  <si>
-    <t>2010-08-03</t>
-  </si>
-  <si>
-    <t>2010-08-19</t>
-  </si>
-  <si>
-    <t>2010-08-26</t>
-  </si>
-  <si>
-    <t>2010-08-27</t>
-  </si>
-  <si>
-    <t>2010-08-30</t>
-  </si>
-  <si>
-    <t>2010-09-17</t>
-  </si>
-  <si>
-    <t>2010-09-20</t>
-  </si>
-  <si>
-    <t>2010-09-21</t>
-  </si>
-  <si>
-    <t>2010-09-23</t>
-  </si>
-  <si>
-    <t>2010-09-24</t>
-  </si>
-  <si>
-    <t>2010-09-27</t>
-  </si>
-  <si>
-    <t>2010-09-28</t>
-  </si>
-  <si>
-    <t>2010-09-29</t>
-  </si>
-  <si>
-    <t>2010-09-30</t>
-  </si>
-  <si>
-    <t>2010-10-01</t>
-  </si>
-  <si>
-    <t>2010-10-04</t>
-  </si>
-  <si>
-    <t>2010-10-05</t>
-  </si>
-  <si>
-    <t>2010-10-06</t>
-  </si>
-  <si>
-    <t>2010-10-07</t>
-  </si>
-  <si>
-    <t>2010-10-08</t>
-  </si>
-  <si>
-    <t>2010-10-11</t>
-  </si>
-  <si>
-    <t>2010-11-24</t>
-  </si>
-  <si>
-    <t>2010-11-25</t>
-  </si>
-  <si>
-    <t>2010-11-26</t>
-  </si>
-  <si>
-    <t>2010-11-29</t>
-  </si>
-  <si>
-    <t>2010-11-30</t>
-  </si>
-  <si>
-    <t>2010-12-01</t>
-  </si>
-  <si>
-    <t>2010-12-02</t>
-  </si>
-  <si>
-    <t>2010-12-03</t>
-  </si>
-  <si>
-    <t>2011-06-24</t>
-  </si>
-  <si>
-    <t>2011-06-27</t>
-  </si>
-  <si>
-    <t>2011-06-30</t>
-  </si>
-  <si>
-    <t>2011-07-07</t>
-  </si>
-  <si>
-    <t>2011-12-02</t>
-  </si>
-  <si>
-    <t>2011-12-05</t>
-  </si>
-  <si>
-    <t>2012-02-24</t>
-  </si>
-  <si>
-    <t>2012-03-02</t>
-  </si>
-  <si>
-    <t>2012-03-06</t>
-  </si>
-  <si>
-    <t>2012-03-07</t>
-  </si>
-  <si>
-    <t>2012-03-12</t>
-  </si>
-  <si>
-    <t>2012-03-13</t>
-  </si>
-  <si>
-    <t>2012-03-29</t>
-  </si>
-  <si>
-    <t>2012-03-30</t>
-  </si>
-  <si>
-    <t>2012-05-03</t>
-  </si>
-  <si>
-    <t>2012-05-15</t>
-  </si>
-  <si>
-    <t>2012-05-16</t>
-  </si>
-  <si>
-    <t>2012-05-17</t>
-  </si>
-  <si>
-    <t>2012-05-18</t>
-  </si>
-  <si>
-    <t>2012-05-21</t>
-  </si>
-  <si>
-    <t>2012-05-22</t>
-  </si>
-  <si>
-    <t>2012-05-23</t>
-  </si>
-  <si>
-    <t>2012-05-24</t>
-  </si>
-  <si>
-    <t>2012-05-28</t>
-  </si>
-  <si>
-    <t>2012-05-29</t>
-  </si>
-  <si>
-    <t>2012-05-30</t>
-  </si>
-  <si>
-    <t>2012-05-31</t>
-  </si>
-  <si>
-    <t>2012-06-01</t>
-  </si>
-  <si>
-    <t>2012-06-04</t>
-  </si>
-  <si>
-    <t>2012-06-05</t>
-  </si>
-  <si>
-    <t>2012-06-06</t>
-  </si>
-  <si>
-    <t>2012-06-07</t>
-  </si>
-  <si>
-    <t>2012-06-08</t>
-  </si>
-  <si>
-    <t>2012-06-11</t>
-  </si>
-  <si>
-    <t>2012-06-12</t>
-  </si>
-  <si>
-    <t>2012-06-13</t>
-  </si>
-  <si>
-    <t>2012-06-14</t>
-  </si>
-  <si>
-    <t>2012-06-15</t>
-  </si>
-  <si>
-    <t>2012-06-19</t>
-  </si>
-  <si>
-    <t>2012-06-20</t>
-  </si>
-  <si>
-    <t>2012-06-22</t>
-  </si>
-  <si>
-    <t>2012-10-18</t>
-  </si>
-  <si>
-    <t>2012-10-19</t>
-  </si>
-  <si>
-    <t>2012-10-22</t>
-  </si>
-  <si>
-    <t>2013-04-08</t>
-  </si>
-  <si>
-    <t>2013-04-12</t>
-  </si>
-  <si>
-    <t>2013-06-25</t>
-  </si>
-  <si>
-    <t>2013-06-27</t>
-  </si>
-  <si>
-    <t>2013-06-28</t>
-  </si>
-  <si>
-    <t>2013-07-01</t>
-  </si>
-  <si>
-    <t>2013-07-02</t>
-  </si>
-  <si>
-    <t>2013-07-03</t>
-  </si>
-  <si>
-    <t>2013-07-04</t>
-  </si>
-  <si>
-    <t>2013-10-28</t>
-  </si>
-  <si>
-    <t>2014-01-22</t>
-  </si>
-  <si>
-    <t>2014-01-23</t>
-  </si>
-  <si>
-    <t>2014-01-24</t>
-  </si>
-  <si>
-    <t>2014-01-27</t>
-  </si>
-  <si>
-    <t>2014-02-06</t>
-  </si>
-  <si>
-    <t>2014-02-07</t>
-  </si>
-  <si>
-    <t>2014-02-10</t>
-  </si>
-  <si>
-    <t>2014-02-11</t>
-  </si>
-  <si>
-    <t>2014-02-18</t>
-  </si>
-  <si>
-    <t>2014-02-20</t>
-  </si>
-  <si>
-    <t>2014-02-21</t>
-  </si>
-  <si>
-    <t>2014-07-08</t>
-  </si>
-  <si>
-    <t>2014-07-10</t>
-  </si>
-  <si>
-    <t>2014-07-11</t>
-  </si>
-  <si>
-    <t>2014-07-16</t>
-  </si>
-  <si>
-    <t>2014-07-17</t>
-  </si>
-  <si>
-    <t>2014-07-18</t>
-  </si>
-  <si>
-    <t>2014-10-15</t>
-  </si>
-  <si>
-    <t>2014-11-04</t>
-  </si>
-  <si>
-    <t>2015-06-11</t>
-  </si>
-  <si>
-    <t>2015-06-12</t>
-  </si>
-  <si>
-    <t>2015-06-15</t>
-  </si>
-  <si>
-    <t>2015-07-22</t>
-  </si>
-  <si>
-    <t>2015-07-23</t>
-  </si>
-  <si>
-    <t>2015-10-15</t>
-  </si>
-  <si>
-    <t>2015-10-16</t>
-  </si>
-  <si>
-    <t>2015-11-19</t>
-  </si>
-  <si>
-    <t>2016-04-01</t>
-  </si>
-  <si>
-    <t>2016-04-07</t>
-  </si>
-  <si>
-    <t>2016-04-08</t>
-  </si>
-  <si>
-    <t>2016-04-15</t>
-  </si>
-  <si>
-    <t>2016-04-18</t>
-  </si>
-  <si>
-    <t>2016-04-19</t>
-  </si>
-  <si>
-    <t>2016-04-21</t>
-  </si>
-  <si>
-    <t>2016-04-22</t>
-  </si>
-  <si>
-    <t>2016-04-27</t>
-  </si>
-  <si>
-    <t>2016-04-28</t>
-  </si>
-  <si>
-    <t>2016-05-03</t>
-  </si>
-  <si>
-    <t>2016-05-05</t>
-  </si>
-  <si>
-    <t>2016-05-10</t>
-  </si>
-  <si>
-    <t>2016-05-11</t>
-  </si>
-  <si>
-    <t>2016-05-12</t>
-  </si>
-  <si>
-    <t>2016-05-13</t>
-  </si>
-  <si>
-    <t>2016-05-16</t>
-  </si>
-  <si>
-    <t>2016-05-17</t>
-  </si>
-  <si>
-    <t>2016-10-27</t>
-  </si>
-  <si>
-    <t>2016-12-15</t>
-  </si>
-  <si>
-    <t>2017-06-26</t>
-  </si>
-  <si>
-    <t>2017-06-27</t>
-  </si>
-  <si>
-    <t>2017-07-11</t>
-  </si>
-  <si>
-    <t>2017-07-12</t>
-  </si>
-  <si>
-    <t>2017-07-13</t>
-  </si>
-  <si>
-    <t>2017-07-14</t>
-  </si>
-  <si>
-    <t>2017-07-17</t>
-  </si>
-  <si>
-    <t>2017-08-21</t>
-  </si>
-  <si>
-    <t>2017-08-22</t>
-  </si>
-  <si>
-    <t>2017-08-23</t>
-  </si>
-  <si>
-    <t>2017-08-24</t>
-  </si>
-  <si>
-    <t>2017-08-25</t>
-  </si>
-  <si>
-    <t>2017-09-06</t>
-  </si>
-  <si>
-    <t>2017-09-07</t>
-  </si>
-  <si>
-    <t>2017-09-08</t>
-  </si>
-  <si>
-    <t>2018-01-12</t>
-  </si>
-  <si>
-    <t>2018-01-15</t>
-  </si>
-  <si>
-    <t>2018-01-16</t>
-  </si>
-  <si>
-    <t>2018-01-17</t>
-  </si>
-  <si>
-    <t>2018-01-30</t>
-  </si>
-  <si>
-    <t>2018-01-31</t>
-  </si>
-  <si>
-    <t>2018-02-06</t>
-  </si>
-  <si>
-    <t>2018-02-22</t>
-  </si>
-  <si>
-    <t>2018-03-30</t>
-  </si>
-  <si>
-    <t>2018-05-16</t>
-  </si>
-  <si>
-    <t>2018-05-21</t>
-  </si>
-  <si>
-    <t>2018-11-20</t>
-  </si>
-  <si>
-    <t>2018-12-28</t>
-  </si>
-  <si>
-    <t>2019-01-09</t>
-  </si>
-  <si>
-    <t>2019-01-10</t>
-  </si>
-  <si>
-    <t>2019-01-15</t>
-  </si>
-  <si>
-    <t>2019-01-16</t>
-  </si>
-  <si>
-    <t>2019-01-17</t>
-  </si>
-  <si>
-    <t>2019-01-18</t>
-  </si>
-  <si>
-    <t>2019-01-22</t>
-  </si>
-  <si>
-    <t>2019-01-23</t>
-  </si>
-  <si>
-    <t>2019-01-24</t>
-  </si>
-  <si>
-    <t>2019-01-25</t>
-  </si>
-  <si>
-    <t>2019-01-29</t>
-  </si>
-  <si>
-    <t>2019-03-11</t>
-  </si>
-  <si>
-    <t>2019-03-12</t>
-  </si>
-  <si>
-    <t>2019-03-13</t>
-  </si>
-  <si>
-    <t>2019-04-09</t>
-  </si>
-  <si>
-    <t>2019-04-10</t>
-  </si>
-  <si>
-    <t>2019-04-18</t>
-  </si>
-  <si>
-    <t>2019-04-19</t>
-  </si>
-  <si>
-    <t>2019-04-25</t>
-  </si>
-  <si>
-    <t>2019-04-26</t>
-  </si>
-  <si>
-    <t>2019-05-02</t>
-  </si>
-  <si>
-    <t>2019-05-07</t>
-  </si>
-  <si>
-    <t>2019-05-08</t>
-  </si>
-  <si>
-    <t>2019-05-09</t>
-  </si>
-  <si>
-    <t>2019-05-10</t>
-  </si>
-  <si>
-    <t>2019-05-13</t>
-  </si>
-  <si>
-    <t>2019-07-29</t>
-  </si>
-  <si>
-    <t>2019-08-29</t>
-  </si>
-  <si>
-    <t>2019-08-30</t>
-  </si>
-  <si>
-    <t>2019-09-02</t>
-  </si>
-  <si>
-    <t>2019-09-03</t>
-  </si>
-  <si>
-    <t>2019-09-04</t>
-  </si>
-  <si>
-    <t>2019-09-05</t>
-  </si>
-  <si>
-    <t>2019-09-06</t>
-  </si>
-  <si>
-    <t>2019-09-10</t>
-  </si>
-  <si>
-    <t>2020-02-20</t>
-  </si>
-  <si>
-    <t>2020-02-21</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-02-26</t>
-  </si>
-  <si>
-    <t>2020-02-27</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-03-04</t>
-  </si>
-  <si>
-    <t>2020-03-05</t>
-  </si>
-  <si>
-    <t>2020-03-06</t>
-  </si>
-  <si>
-    <t>2020-03-09</t>
-  </si>
-  <si>
-    <t>2020-03-12</t>
-  </si>
-  <si>
-    <t>2020-11-02</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-23</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>2020-12-28</t>
-  </si>
-  <si>
     <t>2021-01-05</t>
   </si>
   <si>
@@ -1417,10 +1420,19 @@
     <t>2021-01-20</t>
   </si>
   <si>
+    <t>2021-01-25</t>
+  </si>
+  <si>
     <t>2021-04-21</t>
   </si>
   <si>
     <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>2021-06-17</t>
+  </si>
+  <si>
+    <t>2021-06-18</t>
   </si>
 </sst>
 </file>
@@ -1839,7 +1851,7 @@
         <v>39.24967816269653</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E2">
         <v>47.58658728904034</v>
@@ -1889,7 +1901,7 @@
         <v>41.7045814878046</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E3">
         <v>51.36624085194781</v>
@@ -1939,7 +1951,7 @@
         <v>47.73273319613877</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E4">
         <v>59.43490802303255</v>
@@ -1989,7 +2001,7 @@
         <v>47.24820828667414</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E5">
         <v>58.87563172501095</v>
@@ -2039,7 +2051,7 @@
         <v>47.16470096247878</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E6">
         <v>58.77924108291729</v>
@@ -2089,7 +2101,7 @@
         <v>-15.1664654510749</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E7">
         <v>-7.294892481790129</v>
@@ -2139,7 +2151,7 @@
         <v>-14.45834344229912</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E8">
         <v>-7.294892481790129</v>
@@ -2189,7 +2201,7 @@
         <v>-13.39336737209288</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E9">
         <v>-7.294892481790129</v>
@@ -2239,7 +2251,7 @@
         <v>-16.33245230627455</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E10">
         <v>-7.294892481790129</v>
@@ -2289,7 +2301,7 @@
         <v>-29.63643996743208</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E11">
         <v>-21.37792699357366</v>
@@ -2339,7 +2351,7 @@
         <v>-29.01030081710592</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E12">
         <v>-21.37792699357366</v>
@@ -2389,7 +2401,7 @@
         <v>-28.60118761449661</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E13">
         <v>-21.37792699357366</v>
@@ -2439,7 +2451,7 @@
         <v>-49.08464630848418</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E14">
         <v>-42.77667080227592</v>
@@ -2489,7 +2501,7 @@
         <v>-48.56869529606767</v>
       </c>
       <c r="D15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E15">
         <v>-42.77667080227592</v>
@@ -2539,7 +2551,7 @@
         <v>-49.0410871967355</v>
       </c>
       <c r="D16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E16">
         <v>-42.77667080227592</v>
@@ -2589,7 +2601,7 @@
         <v>-65.70804604683664</v>
       </c>
       <c r="D17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E17">
         <v>-56.94115587886895</v>
@@ -2639,7 +2651,7 @@
         <v>-65.6116252316011</v>
       </c>
       <c r="D18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E18">
         <v>-56.94115587886895</v>
@@ -2689,7 +2701,7 @@
         <v>-79.57406496333017</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E19">
         <v>-67.54165070713992</v>
@@ -2739,7 +2751,7 @@
         <v>-113.1125372679468</v>
       </c>
       <c r="D20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E20">
         <v>-103.9345101187686</v>
@@ -2789,7 +2801,7 @@
         <v>-150.4700278614179</v>
       </c>
       <c r="D21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E21">
         <v>-141.3269680910878</v>
@@ -2839,7 +2851,7 @@
         <v>-191.2456393652701</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E22">
         <v>-165.2314426418361</v>
@@ -2889,7 +2901,7 @@
         <v>-208.9753900042601</v>
       </c>
       <c r="D23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E23">
         <v>-181.8698454183375</v>
@@ -2939,7 +2951,7 @@
         <v>-222.2487414251906</v>
       </c>
       <c r="D24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E24">
         <v>-206.4607237347662</v>
@@ -2989,7 +3001,7 @@
         <v>-239.7112109310854</v>
       </c>
       <c r="D25" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E25">
         <v>-219.5184020745525</v>
@@ -3039,7 +3051,7 @@
         <v>-263.1154559964206</v>
       </c>
       <c r="D26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E26">
         <v>-240.6747187530921</v>
@@ -3089,7 +3101,7 @@
         <v>-268.6224791106823</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E27">
         <v>-252.6279978948062</v>
@@ -3197,7 +3209,7 @@
         <v>-254.0793405031437</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E30">
         <v>-235.7082244929039</v>
@@ -3247,7 +3259,7 @@
         <v>-238.7059320352077</v>
       </c>
       <c r="D31" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E31">
         <v>-223.7765478327873</v>
@@ -3376,7 +3388,7 @@
         <v>-85.8076603763717</v>
       </c>
       <c r="D34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E34">
         <v>-85.31060902491748</v>
@@ -3426,7 +3438,7 @@
         <v>-78.41701518144652</v>
       </c>
       <c r="D35" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E35">
         <v>-77.28396586589429</v>
@@ -3534,7 +3546,7 @@
         <v>-77.43890142953504</v>
       </c>
       <c r="D38" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E38">
         <v>-86.03210595388953</v>
@@ -3584,7 +3596,7 @@
         <v>-75.24842836769179</v>
       </c>
       <c r="D39" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E39">
         <v>-82.41442691778926</v>
@@ -3634,7 +3646,7 @@
         <v>-75.26941837884658</v>
       </c>
       <c r="D40" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E40">
         <v>-76.41687497573176</v>
@@ -3684,7 +3696,7 @@
         <v>2.405986219478436</v>
       </c>
       <c r="D41" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E41">
         <v>22.3137495724129</v>
@@ -3734,7 +3746,7 @@
         <v>-1.953147134466214</v>
       </c>
       <c r="D42" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E42">
         <v>19.32012787151115</v>
@@ -3784,7 +3796,7 @@
         <v>-16.2502130791469</v>
       </c>
       <c r="D43" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E43">
         <v>8.401660897453333</v>
@@ -3834,7 +3846,7 @@
         <v>-14.74859467309044</v>
       </c>
       <c r="D44" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E44">
         <v>8.401660897453333</v>
@@ -3884,7 +3896,7 @@
         <v>-29.86968571903745</v>
       </c>
       <c r="D45" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E45">
         <v>-0.9514709154835543</v>
@@ -3934,7 +3946,7 @@
         <v>60.63454015125168</v>
       </c>
       <c r="D46" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E46">
         <v>75.91925407409063</v>
@@ -3984,7 +3996,7 @@
         <v>61.36441721922468</v>
       </c>
       <c r="D47" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E47">
         <v>75.91925407409063</v>
@@ -4034,7 +4046,7 @@
         <v>89.12505313226613</v>
       </c>
       <c r="D48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E48">
         <v>73.92461224371841</v>
@@ -4084,7 +4096,7 @@
         <v>60.18080332327113</v>
       </c>
       <c r="D49" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E49">
         <v>75.16419394721952</v>
@@ -4134,7 +4146,7 @@
         <v>60.90367287266527</v>
       </c>
       <c r="D50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E50">
         <v>75.16419394721952</v>
@@ -4184,7 +4196,7 @@
         <v>88.41554187615753</v>
       </c>
       <c r="D51" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E51">
         <v>73.33247692380556</v>
@@ -4234,7 +4246,7 @@
         <v>39.99810912339372</v>
       </c>
       <c r="D52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E52">
         <v>55.15583755182445</v>
@@ -4284,7 +4296,7 @@
         <v>41.30719414984996</v>
       </c>
       <c r="D53" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E53">
         <v>55.15583755182445</v>
@@ -4334,7 +4346,7 @@
         <v>43.08151977105167</v>
       </c>
       <c r="D54" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E54">
         <v>55.9485635535138</v>
@@ -4370,7 +4382,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4384,7 +4396,7 @@
         <v>42.16532004667869</v>
       </c>
       <c r="D55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E55">
         <v>55.9485635535138</v>
@@ -4420,7 +4432,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4434,7 +4446,7 @@
         <v>42.55008107334416</v>
       </c>
       <c r="D56" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E56">
         <v>56.30400099154195</v>
@@ -4484,7 +4496,7 @@
         <v>43.58368103616133</v>
       </c>
       <c r="D57" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E57">
         <v>56.30400099154195</v>
@@ -4534,7 +4546,7 @@
         <v>44.27504780738504</v>
       </c>
       <c r="D58" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E58">
         <v>56.96559598792828</v>
@@ -4584,7 +4596,7 @@
         <v>44.76828997217422</v>
       </c>
       <c r="D59" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E59">
         <v>57.43759805949687</v>
@@ -4634,7 +4646,7 @@
         <v>46.95250922066406</v>
       </c>
       <c r="D60" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E60">
         <v>58.6275946856681</v>
@@ -4684,7 +4696,7 @@
         <v>47.37813227189867</v>
       </c>
       <c r="D61" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E61">
         <v>59.01897220404476</v>
@@ -4734,7 +4746,7 @@
         <v>48.93720072957618</v>
       </c>
       <c r="D62" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E62">
         <v>59.68207127489522</v>
@@ -4784,7 +4796,7 @@
         <v>48.94662890110423</v>
       </c>
       <c r="D63" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E63">
         <v>59.69094484809811</v>
@@ -4834,7 +4846,7 @@
         <v>54.08932335660573</v>
       </c>
       <c r="D64" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E64">
         <v>62.52278850035134</v>
@@ -4884,7 +4896,7 @@
         <v>67.18932335660573</v>
       </c>
       <c r="D65" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E65">
         <v>59.01736085156006</v>
@@ -4934,7 +4946,7 @@
         <v>54.27142458878302</v>
       </c>
       <c r="D66" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E66">
         <v>62.70264156916842</v>
@@ -4984,7 +4996,7 @@
         <v>67.37142458878301</v>
       </c>
       <c r="D67" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E67">
         <v>59.17608118479113</v>
@@ -5034,7 +5046,7 @@
         <v>54.44666418857609</v>
       </c>
       <c r="D68" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E68">
         <v>57.92296041603655</v>
@@ -5084,7 +5096,7 @@
         <v>54.38623819452964</v>
       </c>
       <c r="D69" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E69">
         <v>62.81603772299223</v>
@@ -5134,7 +5146,7 @@
         <v>54.68320045790918</v>
       </c>
       <c r="D70" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E70">
         <v>62.81603772299223</v>
@@ -5184,7 +5196,7 @@
         <v>67.48623819452963</v>
       </c>
       <c r="D71" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E71">
         <v>59.27615329054065</v>
@@ -5234,7 +5246,7 @@
         <v>54.5181037654851</v>
       </c>
       <c r="D72" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E72">
         <v>55.68274527440479</v>
@@ -5284,7 +5296,7 @@
         <v>101.1269386779503</v>
       </c>
       <c r="D73" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E73">
         <v>83.94100067443752</v>
@@ -5334,7 +5346,7 @@
         <v>75.45009517739128</v>
       </c>
       <c r="D74" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E74">
         <v>80.27451240300203</v>
@@ -5384,7 +5396,7 @@
         <v>121.9136696617972</v>
       </c>
       <c r="D75" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E75">
         <v>104.5517569407011</v>
@@ -5434,7 +5446,7 @@
         <v>124.0730248787269</v>
       </c>
       <c r="D76" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E76">
         <v>106.3319083146578</v>
@@ -5484,7 +5496,7 @@
         <v>125.8987716223492</v>
       </c>
       <c r="D77" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E77">
         <v>107.8370361179367</v>
@@ -5534,7 +5546,7 @@
         <v>127.8315078706938</v>
       </c>
       <c r="D78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E78">
         <v>102.3788447068554</v>
@@ -5584,7 +5596,7 @@
         <v>127.8608026942557</v>
       </c>
       <c r="D79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E79">
         <v>102.3788447068554</v>
@@ -5634,7 +5646,7 @@
         <v>126.3344628429377</v>
       </c>
       <c r="D80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E80">
         <v>101.3477167540643</v>
@@ -5684,7 +5696,7 @@
         <v>126.3293867347399</v>
       </c>
       <c r="D81" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E81">
         <v>101.3477167540643</v>
@@ -5734,7 +5746,7 @@
         <v>126.0311094090764</v>
       </c>
       <c r="D82" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E82">
         <v>101.1387743378843</v>
@@ -5784,7 +5796,7 @@
         <v>126.0190685536726</v>
       </c>
       <c r="D83" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E83">
         <v>101.1387743378843</v>
@@ -5834,7 +5846,7 @@
         <v>126.620958855311</v>
       </c>
       <c r="D84" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E84">
         <v>101.5450481911581</v>
@@ -5884,7 +5896,7 @@
         <v>126.6224604616829</v>
       </c>
       <c r="D85" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E85">
         <v>101.5450481911581</v>
@@ -5934,7 +5946,7 @@
         <v>125.7796367080902</v>
       </c>
       <c r="D86" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E86">
         <v>100.9655660999601</v>
@@ -5984,7 +5996,7 @@
         <v>125.7618222447556</v>
       </c>
       <c r="D87" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E87">
         <v>100.9655660999601</v>
@@ -6034,7 +6046,7 @@
         <v>125.0669218669525</v>
       </c>
       <c r="D88" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E88">
         <v>100.4746655716255</v>
@@ -6070,7 +6082,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6084,7 +6096,7 @@
         <v>125.0327440526733</v>
       </c>
       <c r="D89" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E89">
         <v>100.4746655716255</v>
@@ -6120,7 +6132,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6134,7 +6146,7 @@
         <v>123.2289469739378</v>
       </c>
       <c r="D90" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E90">
         <v>99.20871347694691</v>
@@ -6184,7 +6196,7 @@
         <v>123.1525707565027</v>
       </c>
       <c r="D91" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E91">
         <v>99.20871347694691</v>
@@ -6234,7 +6246,7 @@
         <v>122.9583501275863</v>
       </c>
       <c r="D92" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E92">
         <v>99.02233299604161</v>
@@ -6284,7 +6296,7 @@
         <v>122.8757612274544</v>
       </c>
       <c r="D93" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E93">
         <v>99.02233299604161</v>
@@ -6334,7 +6346,7 @@
         <v>124.3519741722009</v>
       </c>
       <c r="D94" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E94">
         <v>99.98222710840369</v>
@@ -6384,7 +6396,7 @@
         <v>124.3013817424811</v>
       </c>
       <c r="D95" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E95">
         <v>99.98222710840369</v>
@@ -6434,7 +6446,7 @@
         <v>124.6891745905705</v>
       </c>
       <c r="D96" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E96">
         <v>100.2144824986073</v>
@@ -6484,7 +6496,7 @@
         <v>124.6463240071908</v>
       </c>
       <c r="D97" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E97">
         <v>100.2144824986073</v>
@@ -6534,7 +6546,7 @@
         <v>124.4800191586875</v>
       </c>
       <c r="D98" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E98">
         <v>100.0704213593001</v>
@@ -6584,7 +6596,7 @@
         <v>124.4323665373309</v>
       </c>
       <c r="D99" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E99">
         <v>100.0704213593001</v>
@@ -6634,7 +6646,7 @@
         <v>123.0108457893896</v>
       </c>
       <c r="D100" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E100">
         <v>99.05849072228368</v>
@@ -6684,7 +6696,7 @@
         <v>122.9294621467991</v>
       </c>
       <c r="D101" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E101">
         <v>99.05849072228368</v>
@@ -6734,7 +6746,7 @@
         <v>121.6453568496303</v>
       </c>
       <c r="D102" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E102">
         <v>98.11797538112289</v>
@@ -6784,7 +6796,7 @@
         <v>121.5326226956677</v>
       </c>
       <c r="D103" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E103">
         <v>98.11797538112289</v>
@@ -6834,7 +6846,7 @@
         <v>121.0299428079651</v>
       </c>
       <c r="D104" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E104">
         <v>97.69409326058823</v>
@@ -6884,7 +6896,7 @@
         <v>120.9030792499847</v>
       </c>
       <c r="D105" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E105">
         <v>97.69409326058823</v>
@@ -6934,7 +6946,7 @@
         <v>120.2680139970007</v>
       </c>
       <c r="D106" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E106">
         <v>97.169295355077</v>
@@ -6984,7 +6996,7 @@
         <v>120.1236571755032</v>
       </c>
       <c r="D107" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E107">
         <v>97.169295355077</v>
@@ -7034,7 +7046,7 @@
         <v>119.3894537106139</v>
       </c>
       <c r="D108" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E108">
         <v>96.56416454557592</v>
@@ -7084,7 +7096,7 @@
         <v>119.2249258621331</v>
       </c>
       <c r="D109" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E109">
         <v>96.56416454557592</v>
@@ -7134,7 +7146,7 @@
         <v>118.0996069245826</v>
       </c>
       <c r="D110" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E110">
         <v>95.67574966744206</v>
@@ -7184,7 +7196,7 @@
         <v>117.9054652468306</v>
       </c>
       <c r="D111" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E111">
         <v>95.67574966744206</v>
@@ -7234,7 +7246,7 @@
         <v>117.1017444652623</v>
       </c>
       <c r="D112" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E112">
         <v>94.98844644291023</v>
@@ -7284,7 +7296,7 @@
         <v>116.8846926800259</v>
       </c>
       <c r="D113" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E113">
         <v>94.98844644291023</v>
@@ -7334,7 +7346,7 @@
         <v>115.7903395541055</v>
       </c>
       <c r="D114" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E114">
         <v>94.08518285614407</v>
@@ -7384,7 +7396,7 @@
         <v>115.5431789826436</v>
       </c>
       <c r="D115" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E115">
         <v>94.08518285614407</v>
@@ -7434,7 +7446,7 @@
         <v>114.3600161010092</v>
       </c>
       <c r="D116" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E116">
         <v>93.10001108998082</v>
@@ -7484,7 +7496,7 @@
         <v>114.0800164706752</v>
       </c>
       <c r="D117" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E117">
         <v>93.10001108998082</v>
@@ -7534,7 +7546,7 @@
         <v>112.9215721869154</v>
       </c>
       <c r="D118" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E118">
         <v>92.10924614915092</v>
@@ -7584,7 +7596,7 @@
         <v>112.6085470585538</v>
       </c>
       <c r="D119" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E119">
         <v>92.10924614915092</v>
@@ -7634,7 +7646,7 @@
         <v>111.0753114680939</v>
       </c>
       <c r="D120" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E120">
         <v>91.07689300844227</v>
@@ -7684,7 +7696,7 @@
         <v>109.3637030177276</v>
       </c>
       <c r="D121" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E121">
         <v>89.92443844086398</v>
@@ -7734,7 +7746,7 @@
         <v>106.6367917601738</v>
       </c>
       <c r="D122" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E122">
         <v>88.08836352929409</v>
@@ -7784,7 +7796,7 @@
         <v>99.96873044828921</v>
       </c>
       <c r="D123" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E123">
         <v>83.59864643650396</v>
@@ -7834,7 +7846,7 @@
         <v>39.91051382546476</v>
       </c>
       <c r="D124" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E124">
         <v>42.55014562583152</v>
@@ -7884,7 +7896,7 @@
         <v>34.76754143004694</v>
       </c>
       <c r="D125" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E125">
         <v>38.11145388461416</v>
@@ -7934,7 +7946,7 @@
         <v>27.87373902743889</v>
       </c>
       <c r="D126" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E126">
         <v>28.73232502982488</v>
@@ -7984,7 +7996,7 @@
         <v>52.34452590842368</v>
       </c>
       <c r="D127" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E127">
         <v>60.02089394070224</v>
@@ -8034,7 +8046,7 @@
         <v>66.2681578761451</v>
       </c>
       <c r="D128" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E128">
         <v>59.00746128062423</v>
@@ -8084,7 +8096,7 @@
         <v>65.90298372726488</v>
       </c>
       <c r="D129" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E129">
         <v>59.00746128062423</v>
@@ -8134,7 +8146,7 @@
         <v>75.19054270184851</v>
       </c>
       <c r="D130" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E130">
         <v>82.88620847856147</v>
@@ -8184,7 +8196,7 @@
         <v>91.01410438583636</v>
       </c>
       <c r="D131" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E131">
         <v>85.34034548895417</v>
@@ -8234,7 +8246,7 @@
         <v>90.69117289103272</v>
       </c>
       <c r="D132" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E132">
         <v>85.34034548895417</v>
@@ -8284,7 +8296,7 @@
         <v>106.425283452306</v>
       </c>
       <c r="D133" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E133">
         <v>102.4841645631825</v>
@@ -8334,7 +8346,7 @@
         <v>106.7743510447031</v>
       </c>
       <c r="D134" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E134">
         <v>102.4841645631825</v>
@@ -8384,7 +8396,7 @@
         <v>64.83381773702186</v>
       </c>
       <c r="D135" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E135">
         <v>61.17785949472258</v>
@@ -8434,7 +8446,7 @@
         <v>53.81062761975522</v>
       </c>
       <c r="D136" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E136">
         <v>45.81713512679965</v>
@@ -8484,7 +8496,7 @@
         <v>53.43128846396477</v>
       </c>
       <c r="D137" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E137">
         <v>47.7894228477703</v>
@@ -8534,7 +8546,7 @@
         <v>48.70129852147022</v>
       </c>
       <c r="D138" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E138">
         <v>39.19252273181839</v>
@@ -8584,7 +8596,7 @@
         <v>44.87334693499027</v>
       </c>
       <c r="D139" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E139">
         <v>34.44403390958535</v>
@@ -8634,7 +8646,7 @@
         <v>40.45906823400685</v>
       </c>
       <c r="D140" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E140">
         <v>29.40254968722779</v>
@@ -8684,7 +8696,7 @@
         <v>37.79538016242914</v>
       </c>
       <c r="D141" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E141">
         <v>25.15160114518396</v>
@@ -8734,7 +8746,7 @@
         <v>37.68076952930594</v>
       </c>
       <c r="D142" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E142">
         <v>25.01802919408082</v>
@@ -8784,7 +8796,7 @@
         <v>63.15408222226404</v>
       </c>
       <c r="D143" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E143">
         <v>53.56243089690908</v>
@@ -8834,7 +8846,7 @@
         <v>31.1030054990203</v>
       </c>
       <c r="D144" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E144">
         <v>14.08734435244297</v>
@@ -8884,7 +8896,7 @@
         <v>25.05484991241799</v>
       </c>
       <c r="D145" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E145">
         <v>6.922187058405115</v>
@@ -8934,7 +8946,7 @@
         <v>18.81638310475921</v>
       </c>
       <c r="D146" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E146">
         <v>-0.4684290245420044</v>
@@ -8984,7 +8996,7 @@
         <v>13.01676813424353</v>
       </c>
       <c r="D147" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E147">
         <v>-7.339144057179965</v>
@@ -9034,7 +9046,7 @@
         <v>8.024396355482963</v>
       </c>
       <c r="D148" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E148">
         <v>-13.25353044372964</v>
@@ -9084,7 +9096,7 @@
         <v>7.720504878426524</v>
       </c>
       <c r="D149" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E149">
         <v>-13.61354602240461</v>
@@ -9134,7 +9146,7 @@
         <v>10.31388326476601</v>
       </c>
       <c r="D150" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E150">
         <v>-10.54121036651594</v>
@@ -9184,7 +9196,7 @@
         <v>11.14758883248732</v>
       </c>
       <c r="D151" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E151">
         <v>-9.553532148900146</v>
@@ -9234,7 +9246,7 @@
         <v>20.84560393192861</v>
       </c>
       <c r="D152" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E152">
         <v>1.935557811248756</v>
@@ -9270,7 +9282,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9284,7 +9296,7 @@
         <v>21.43389351871438</v>
       </c>
       <c r="D153" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E153">
         <v>2.632495474873352</v>
@@ -9334,7 +9346,7 @@
         <v>22.6162561113628</v>
       </c>
       <c r="D154" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E154">
         <v>4.033222330128012</v>
@@ -9370,7 +9382,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9384,7 +9396,7 @@
         <v>23.86897930913528</v>
       </c>
       <c r="D155" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E155">
         <v>5.517304316678292</v>
@@ -9434,7 +9446,7 @@
         <v>24.29022509961407</v>
       </c>
       <c r="D156" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E156">
         <v>6.016347753146405</v>
@@ -9484,7 +9496,7 @@
         <v>80.77258742920839</v>
       </c>
       <c r="D157" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E157">
         <v>71.50140757768273</v>
@@ -9534,7 +9546,7 @@
         <v>80.87119828430862</v>
       </c>
       <c r="D158" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E158">
         <v>71.50140757768273</v>
@@ -9584,7 +9596,7 @@
         <v>82.15331534782203</v>
       </c>
       <c r="D159" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E159">
         <v>71.50140757768273</v>
@@ -9634,7 +9646,7 @@
         <v>76.19581669669289</v>
       </c>
       <c r="D160" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E160">
         <v>66.74547500154564</v>
@@ -9684,7 +9696,7 @@
         <v>75.21863715900577</v>
       </c>
       <c r="D161" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E161">
         <v>66.74547500154564</v>
@@ -9734,7 +9746,7 @@
         <v>77.89414970172665</v>
       </c>
       <c r="D162" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E162">
         <v>66.74547500154564</v>
@@ -9784,7 +9796,7 @@
         <v>60.11863715900578</v>
       </c>
       <c r="D163" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E163">
         <v>68.03744024109169</v>
@@ -9834,7 +9846,7 @@
         <v>72.44565132750211</v>
       </c>
       <c r="D164" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E164">
         <v>62.8485060058029</v>
@@ -9884,7 +9896,7 @@
         <v>71.50850914251097</v>
       </c>
       <c r="D165" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E165">
         <v>62.8485060058029</v>
@@ -9934,7 +9946,7 @@
         <v>74.40422712505978</v>
       </c>
       <c r="D166" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E166">
         <v>62.8485060058029</v>
@@ -9984,7 +9996,7 @@
         <v>56.40850914251097</v>
       </c>
       <c r="D167" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E167">
         <v>64.59422790923679</v>
@@ -10034,7 +10046,7 @@
         <v>67.88820949982238</v>
       </c>
       <c r="D168" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E168">
         <v>60.43722302948107</v>
@@ -10084,7 +10096,7 @@
         <v>70.99880138202717</v>
       </c>
       <c r="D169" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E169">
         <v>60.43722302948107</v>
@@ -10134,7 +10146,7 @@
         <v>52.78820949982239</v>
       </c>
       <c r="D170" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E170">
         <v>61.23438147825242</v>
@@ -10184,7 +10196,7 @@
         <v>64.41272601732022</v>
       </c>
       <c r="D171" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E171">
         <v>56.61794172047242</v>
@@ -10234,7 +10246,7 @@
         <v>49.31272601732023</v>
       </c>
       <c r="D172" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E172">
         <v>58.0089327786641</v>
@@ -10284,7 +10296,7 @@
         <v>61.16879231159055</v>
       </c>
       <c r="D173" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E173">
         <v>53.82441738118666</v>
@@ -10334,7 +10346,7 @@
         <v>46.06879231159056</v>
       </c>
       <c r="D174" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E174">
         <v>54.08446933112747</v>
@@ -10384,7 +10396,7 @@
         <v>58.07192781203269</v>
       </c>
       <c r="D175" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E175">
         <v>50.68812094147531</v>
@@ -10434,7 +10446,7 @@
         <v>42.9719278120327</v>
       </c>
       <c r="D176" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E176">
         <v>51.29394934141796</v>
@@ -10484,7 +10496,7 @@
         <v>72.62623022483724</v>
       </c>
       <c r="D177" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E177">
         <v>78.13274022613687</v>
@@ -10534,7 +10546,7 @@
         <v>72.14377020837516</v>
       </c>
       <c r="D178" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E178">
         <v>78.53925022743653</v>
@@ -10584,7 +10596,7 @@
         <v>83.25643025082999</v>
       </c>
       <c r="D179" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E179">
         <v>77.7759602547289</v>
@@ -10692,7 +10704,7 @@
         <v>66.25534327603719</v>
       </c>
       <c r="D182" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E182">
         <v>53.25789242985769</v>
@@ -10742,7 +10754,7 @@
         <v>66.50153349826817</v>
       </c>
       <c r="D183" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E183">
         <v>53.49926887679366</v>
@@ -10792,7 +10804,7 @@
         <v>65.13958707494101</v>
       </c>
       <c r="D184" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E184">
         <v>53.20617458032149</v>
@@ -10842,7 +10854,7 @@
         <v>65.2660759255686</v>
       </c>
       <c r="D185" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E185">
         <v>53.20617458032149</v>
@@ -10892,7 +10904,7 @@
         <v>63.88275361614285</v>
       </c>
       <c r="D186" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E186">
         <v>51.96525040581191</v>
@@ -10942,7 +10954,7 @@
         <v>82.52792611826956</v>
       </c>
       <c r="D187" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E187">
         <v>99.94767772279653</v>
@@ -10992,7 +11004,7 @@
         <v>80.81507949145069</v>
       </c>
       <c r="D188" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E188">
         <v>99.94767772279653</v>
@@ -11042,7 +11054,7 @@
         <v>82.55697724266327</v>
       </c>
       <c r="D189" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E189">
         <v>99.94767772279653</v>
@@ -11092,7 +11104,7 @@
         <v>80.68386776738032</v>
       </c>
       <c r="D190" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E190">
         <v>99.94767772279653</v>
@@ -11142,7 +11154,7 @@
         <v>83.46212404051099</v>
       </c>
       <c r="D191" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E191">
         <v>101.9293746430213</v>
@@ -11192,7 +11204,7 @@
         <v>81.65627098338047</v>
       </c>
       <c r="D192" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E192">
         <v>101.9293746430213</v>
@@ -11242,7 +11254,7 @@
         <v>83.46017302146748</v>
       </c>
       <c r="D193" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E193">
         <v>101.9293746430213</v>
@@ -11292,7 +11304,7 @@
         <v>81.57259587924717</v>
       </c>
       <c r="D194" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E194">
         <v>101.9293746430213</v>
@@ -11392,7 +11404,7 @@
         <v>33.77481800214022</v>
       </c>
       <c r="D196" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E196">
         <v>39.96346245740297</v>
@@ -11442,7 +11454,7 @@
         <v>24.63764534106641</v>
       </c>
       <c r="D197" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E197">
         <v>34.16939555445761</v>
@@ -11492,7 +11504,7 @@
         <v>43.28817453279771</v>
       </c>
       <c r="D198" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E198">
         <v>46.14425779500065</v>
@@ -11542,7 +11554,7 @@
         <v>24.23598497532834</v>
       </c>
       <c r="D199" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E199">
         <v>33.03819935984974</v>
@@ -11592,7 +11604,7 @@
         <v>24.17071464201896</v>
       </c>
       <c r="D200" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E200">
         <v>33.03819935984974</v>
@@ -11642,7 +11654,7 @@
         <v>23.32366123264667</v>
       </c>
       <c r="D201" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E201">
         <v>32.29172372079252</v>
@@ -11692,7 +11704,7 @@
         <v>22.94912669441385</v>
       </c>
       <c r="D202" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E202">
         <v>31.49029169144093</v>
@@ -11742,7 +11754,7 @@
         <v>22.44844130251504</v>
       </c>
       <c r="D203" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E203">
         <v>30.75050022869873</v>
@@ -11792,7 +11804,7 @@
         <v>22.12056025614258</v>
       </c>
       <c r="D204" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E204">
         <v>30.75050022869873</v>
@@ -11842,7 +11854,7 @@
         <v>21.00936580829927</v>
       </c>
       <c r="D205" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E205">
         <v>29.75836232883863</v>
@@ -11892,7 +11904,7 @@
         <v>22.21712321587968</v>
       </c>
       <c r="D206" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E206">
         <v>29.83950116198865</v>
@@ -11942,7 +11954,7 @@
         <v>22.36605537346383</v>
       </c>
       <c r="D207" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E207">
         <v>29.99532225197207</v>
@@ -11992,7 +12004,7 @@
         <v>21.71901729202467</v>
       </c>
       <c r="D208" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E208">
         <v>28.96097369076485</v>
@@ -12042,7 +12054,7 @@
         <v>21.37743590654157</v>
       </c>
       <c r="D209" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E209">
         <v>28.96097369076485</v>
@@ -12092,7 +12104,7 @@
         <v>21.5505095382167</v>
       </c>
       <c r="D210" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E210">
         <v>29.1420529309536</v>
@@ -12142,7 +12154,7 @@
         <v>21.4477218260166</v>
       </c>
       <c r="D211" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E211">
         <v>29.03451072105261</v>
@@ -12192,7 +12204,7 @@
         <v>21.93200329930192</v>
       </c>
       <c r="D212" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E212">
         <v>29.03451072105261</v>
@@ -12242,7 +12254,7 @@
         <v>21.82005829590757</v>
       </c>
       <c r="D213" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E213">
         <v>29.42406980298699</v>
@@ -12292,7 +12304,7 @@
         <v>22.28137628646834</v>
       </c>
       <c r="D214" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E214">
         <v>29.42406980298699</v>
@@ -12342,7 +12354,7 @@
         <v>25.08434479788652</v>
       </c>
       <c r="D215" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E215">
         <v>32.83934753082841</v>
@@ -12392,7 +12404,7 @@
         <v>25.82576998567276</v>
       </c>
       <c r="D216" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E216">
         <v>32.83934753082841</v>
@@ -12442,7 +12454,7 @@
         <v>25.62576998567276</v>
       </c>
       <c r="D217" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E217">
         <v>32.83934753082841</v>
@@ -12492,7 +12504,7 @@
         <v>39.54291961010028</v>
       </c>
       <c r="D218" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E218">
         <v>32.24005830276027</v>
@@ -12542,7 +12554,7 @@
         <v>27.32311840696546</v>
       </c>
       <c r="D219" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E219">
         <v>35.18167674737576</v>
@@ -12592,7 +12604,7 @@
         <v>27.936331890267</v>
       </c>
       <c r="D220" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E220">
         <v>35.18167674737576</v>
@@ -12642,7 +12654,7 @@
         <v>27.736331890267</v>
       </c>
       <c r="D221" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E221">
         <v>35.18167674737576</v>
@@ -12692,7 +12704,7 @@
         <v>41.90990492366392</v>
       </c>
       <c r="D222" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E222">
         <v>34.44924459541966</v>
@@ -12742,7 +12754,7 @@
         <v>29.32582523799188</v>
       </c>
       <c r="D223" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E223">
         <v>36.94571726179005</v>
@@ -12792,7 +12804,7 @@
         <v>43.69251428559836</v>
       </c>
       <c r="D224" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E224">
         <v>36.11301333322514</v>
@@ -12842,7 +12854,7 @@
         <v>44.11030807122381</v>
       </c>
       <c r="D225" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E225">
         <v>36.50295419980888</v>
@@ -12892,7 +12904,7 @@
         <v>45.39200591893177</v>
       </c>
       <c r="D226" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E226">
         <v>37.69920552433632</v>
@@ -12942,7 +12954,7 @@
         <v>46.2461284866414</v>
       </c>
       <c r="D227" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E227">
         <v>38.49638658753197</v>
@@ -12992,7 +13004,7 @@
         <v>46.90307634880546</v>
       </c>
       <c r="D228" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E228">
         <v>39.10953792555176</v>
@@ -13042,7 +13054,7 @@
         <v>33.83569560835785</v>
       </c>
       <c r="D229" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E229">
         <v>40.9206360962427</v>
@@ -13092,7 +13104,7 @@
         <v>46.73201951087134</v>
       </c>
       <c r="D230" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E230">
         <v>38.94988487681324</v>
@@ -13142,7 +13154,7 @@
         <v>33.22416759327695</v>
       </c>
       <c r="D231" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E231">
         <v>40.34408700115657</v>
@@ -13192,7 +13204,7 @@
         <v>46.15305807647522</v>
       </c>
       <c r="D232" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E232">
         <v>38.40952087137686</v>
@@ -13242,7 +13254,7 @@
         <v>33.50490381338868</v>
       </c>
       <c r="D233" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E233">
         <v>40.17087450822464</v>
@@ -13292,7 +13304,7 @@
         <v>45.97912084507914</v>
       </c>
       <c r="D234" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E234">
         <v>38.24717945540719</v>
@@ -13342,7 +13354,7 @@
         <v>34.16379673036971</v>
       </c>
       <c r="D235" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E235">
         <v>40.85258622752538</v>
@@ -13392,7 +13404,7 @@
         <v>46.66368491466983</v>
       </c>
       <c r="D236" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E236">
         <v>38.8861059203585</v>
@@ -13442,7 +13454,7 @@
         <v>35.00523304555671</v>
       </c>
       <c r="D237" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E237">
         <v>41.72316319432058</v>
@@ -13492,7 +13504,7 @@
         <v>47.53790446291606</v>
       </c>
       <c r="D238" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E238">
         <v>39.70204416538832</v>
@@ -13542,7 +13554,7 @@
         <v>35.77509163864829</v>
       </c>
       <c r="D239" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E239">
         <v>42.51968355686988</v>
@@ -13592,7 +13604,7 @@
         <v>48.33775754664758</v>
       </c>
       <c r="D240" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E240">
         <v>40.4485737102044</v>
@@ -13642,7 +13654,7 @@
         <v>36.40438752667171</v>
       </c>
       <c r="D241" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E241">
         <v>43.17077324188112</v>
@@ -13692,7 +13704,7 @@
         <v>48.9915714562823</v>
       </c>
       <c r="D242" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E242">
         <v>41.05880002586348</v>
@@ -13742,7 +13754,7 @@
         <v>32.86635202836143</v>
       </c>
       <c r="D243" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E243">
         <v>23.40810673803942</v>
@@ -13792,7 +13804,7 @@
         <v>14.22574367387871</v>
       </c>
       <c r="D244" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E244">
         <v>19.5340376774239</v>
@@ -13842,7 +13854,7 @@
         <v>24.88800304387275</v>
       </c>
       <c r="D245" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E245">
         <v>11.91657154564347</v>
@@ -13892,7 +13904,7 @@
         <v>39.44906102636678</v>
       </c>
       <c r="D246" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E246">
         <v>28.36395585832523</v>
@@ -13971,7 +13983,7 @@
         <v>36.85113379578714</v>
       </c>
       <c r="D248" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E248">
         <v>25.5208599983697</v>
@@ -14021,7 +14033,7 @@
         <v>33.94646019309421</v>
       </c>
       <c r="D249" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E249">
         <v>22.34206984707826</v>
@@ -14071,7 +14083,7 @@
         <v>33.30875742504994</v>
       </c>
       <c r="D250" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E250">
         <v>21.64418651979802</v>
@@ -14200,7 +14212,7 @@
         <v>9.926891175013289</v>
       </c>
       <c r="D253" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E253">
         <v>9.938904864210649</v>
@@ -14250,7 +14262,7 @@
         <v>8.61566853605617</v>
       </c>
       <c r="D254" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E254">
         <v>9.007561895624264</v>
@@ -14350,7 +14362,7 @@
         <v>15.27625616990661</v>
       </c>
       <c r="D256" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E256">
         <v>13.96823074035395</v>
@@ -14400,7 +14412,7 @@
         <v>14.49984262437423</v>
       </c>
       <c r="D257" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E257">
         <v>14.19011246930496</v>
@@ -14450,7 +14462,7 @@
         <v>13.68984307357539</v>
       </c>
       <c r="D258" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E258">
         <v>15.44321014679792</v>
@@ -14500,7 +14512,7 @@
         <v>14.26953725404694</v>
       </c>
       <c r="D259" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E259">
         <v>17.46734434330768</v>
@@ -14550,7 +14562,7 @@
         <v>59.06263065139578</v>
       </c>
       <c r="D260" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E260">
         <v>59.07357361272927</v>
@@ -14600,7 +14612,7 @@
         <v>60.66257075424956</v>
       </c>
       <c r="D261" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E261">
         <v>61.38454095582109</v>
@@ -14650,7 +14662,7 @@
         <v>61.58779745865752</v>
       </c>
       <c r="D262" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E262">
         <v>62.08864679971672</v>
@@ -15150,7 +15162,7 @@
         <v>-12.91711279591523</v>
       </c>
       <c r="D272" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E272">
         <v>-24.080705554696</v>
@@ -15200,7 +15212,7 @@
         <v>-13.89288092370901</v>
       </c>
       <c r="D273" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E273">
         <v>-24.64699491908532</v>
@@ -15250,7 +15262,7 @@
         <v>-13.4171424523624</v>
       </c>
       <c r="D274" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E274">
         <v>-24.64699491908532</v>
@@ -15300,7 +15312,7 @@
         <v>-7.909028461817627</v>
       </c>
       <c r="D275" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E275">
         <v>-18.4089921717041</v>
@@ -15350,7 +15362,7 @@
         <v>-3.803879058776658</v>
       </c>
       <c r="D276" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E276">
         <v>-13.75986303266694</v>
@@ -15400,7 +15412,7 @@
         <v>-7.200798160312672</v>
       </c>
       <c r="D277" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E277">
         <v>-16.37029482433257</v>
@@ -15450,7 +15462,7 @@
         <v>1.814674940949821</v>
       </c>
       <c r="D278" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E278">
         <v>-6.106103736501311</v>
@@ -15650,7 +15662,7 @@
         <v>68.89152801060949</v>
       </c>
       <c r="D282" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E282">
         <v>67.76768139345658</v>
@@ -15700,7 +15712,7 @@
         <v>68.93096321131679</v>
       </c>
       <c r="D283" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E283">
         <v>67.76768139345658</v>
@@ -15750,7 +15762,7 @@
         <v>68.53130803182968</v>
       </c>
       <c r="D284" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E284">
         <v>67.76768139345658</v>
@@ -15800,7 +15812,7 @@
         <v>69.00549946949548</v>
       </c>
       <c r="D285" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E285">
         <v>67.76768139345658</v>
@@ -15850,7 +15862,7 @@
         <v>77.0344578684535</v>
       </c>
       <c r="D286" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E286">
         <v>79.16818364992574</v>
@@ -15900,7 +15912,7 @@
         <v>76.35596494832328</v>
       </c>
       <c r="D287" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E287">
         <v>79.16818364992574</v>
@@ -15950,7 +15962,7 @@
         <v>77.32922500711149</v>
       </c>
       <c r="D288" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E288">
         <v>79.16818364992574</v>
@@ -16000,7 +16012,7 @@
         <v>79.78847196430716</v>
       </c>
       <c r="D289" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E289">
         <v>84.66094269739213</v>
@@ -16036,7 +16048,7 @@
         <v>0</v>
       </c>
       <c r="P289" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16050,7 +16062,7 @@
         <v>79.029452316228</v>
       </c>
       <c r="D290" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E290">
         <v>84.66094269739213</v>
@@ -16086,7 +16098,7 @@
         <v>0</v>
       </c>
       <c r="P290" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16100,7 +16112,7 @@
         <v>80.07787065443522</v>
       </c>
       <c r="D291" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E291">
         <v>84.66094269739213</v>
@@ -16136,7 +16148,7 @@
         <v>0</v>
       </c>
       <c r="P291" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16186,7 +16198,7 @@
         <v>0</v>
       </c>
       <c r="P292" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16236,7 +16248,7 @@
         <v>0</v>
       </c>
       <c r="P293" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16286,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="P294" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16300,7 +16312,7 @@
         <v>26.32548638029413</v>
       </c>
       <c r="D295" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E295">
         <v>26.99422663021349</v>
@@ -16350,7 +16362,7 @@
         <v>22.18948293316849</v>
       </c>
       <c r="D296" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E296">
         <v>24.84672272180288</v>
@@ -16400,7 +16412,7 @@
         <v>21.86052377863092</v>
       </c>
       <c r="D297" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E297">
         <v>24.84672272180288</v>
@@ -16450,7 +16462,7 @@
         <v>40.77814878274022</v>
       </c>
       <c r="D298" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E298">
         <v>48.87821615334129</v>
@@ -16500,7 +16512,7 @@
         <v>40.67981251944272</v>
       </c>
       <c r="D299" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E299">
         <v>48.87821615334129</v>
@@ -16550,7 +16562,7 @@
         <v>56.75038402863819</v>
       </c>
       <c r="D300" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E300">
         <v>62.17870887338118</v>
@@ -16600,7 +16612,7 @@
         <v>59.81014784804309</v>
       </c>
       <c r="D301" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E301">
         <v>65.19117101289457</v>
@@ -16650,7 +16662,7 @@
         <v>60.36835189313004</v>
       </c>
       <c r="D302" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E302">
         <v>65.519432176365</v>
@@ -16700,7 +16712,7 @@
         <v>61.49835591209959</v>
       </c>
       <c r="D303" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E303">
         <v>65.45054113973049</v>
@@ -16750,7 +16762,7 @@
         <v>61.74303834428476</v>
       </c>
       <c r="D304" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E304">
         <v>65.59070564276428</v>
@@ -16800,7 +16812,7 @@
         <v>62.08800405152936</v>
       </c>
       <c r="D305" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E305">
         <v>65.70367105582346</v>
@@ -16850,7 +16862,7 @@
         <v>62.52195117925444</v>
       </c>
       <c r="D306" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E306">
         <v>66.54562713332096</v>
@@ -16900,7 +16912,7 @@
         <v>63.12382871565654</v>
       </c>
       <c r="D307" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E307">
         <v>66.7862115872222</v>
@@ -16950,7 +16962,7 @@
         <v>63.43713576842169</v>
       </c>
       <c r="D308" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E308">
         <v>68.73084934526386</v>
@@ -17000,7 +17012,7 @@
         <v>63.67236578705479</v>
       </c>
       <c r="D309" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E309">
         <v>68.98960236576026</v>
@@ -17050,7 +17062,7 @@
         <v>63.92214730715632</v>
       </c>
       <c r="D310" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E310">
         <v>69.26436203787196</v>
@@ -17100,7 +17112,7 @@
         <v>64.84267428552164</v>
       </c>
       <c r="D311" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E311">
         <v>70.2769417140738</v>
@@ -17150,7 +17162,7 @@
         <v>67.02639425410899</v>
       </c>
       <c r="D312" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E312">
         <v>72.67903367951989</v>
@@ -17200,7 +17212,7 @@
         <v>48.8201383647419</v>
       </c>
       <c r="D313" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E313">
         <v>53.28068312873989</v>
@@ -17250,7 +17262,7 @@
         <v>43.78661428769819</v>
       </c>
       <c r="D314" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E314">
         <v>49.20590413019019</v>
@@ -17300,7 +17312,7 @@
         <v>43.50856722084519</v>
       </c>
       <c r="D315" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E315">
         <v>49.20590413019019</v>
@@ -17350,7 +17362,7 @@
         <v>38.43277181447034</v>
       </c>
       <c r="D316" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E316">
         <v>43.81134802598723</v>
@@ -17400,7 +17412,7 @@
         <v>39.10060265112747</v>
       </c>
       <c r="D317" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E317">
         <v>43.81134802598723</v>
@@ -17450,7 +17462,7 @@
         <v>28.12299460113455</v>
       </c>
       <c r="D318" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E318">
         <v>35.22229514558674</v>
@@ -17500,7 +17512,7 @@
         <v>27.81471186440677</v>
       </c>
       <c r="D319" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E319">
         <v>34.92338983050847</v>
@@ -17550,7 +17562,7 @@
         <v>31.34037664954478</v>
       </c>
       <c r="D320" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E320">
         <v>38.34181005944457</v>
@@ -17600,7 +17612,7 @@
         <v>31.06966226989418</v>
       </c>
       <c r="D321" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E321">
         <v>38.07933033773011</v>
@@ -17650,7 +17662,7 @@
         <v>30.73117805425061</v>
       </c>
       <c r="D322" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E322">
         <v>37.75114221990079</v>
@@ -17700,7 +17712,7 @@
         <v>30.23209518986696</v>
       </c>
       <c r="D323" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E323">
         <v>37.26724058333109</v>
@@ -17750,7 +17762,7 @@
         <v>29.66328200930995</v>
       </c>
       <c r="D324" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E324">
         <v>36.71572970484425</v>
@@ -17800,7 +17812,7 @@
         <v>29.90527095369034</v>
       </c>
       <c r="D325" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E325">
         <v>36.95035776878722</v>
@@ -17850,7 +17862,7 @@
         <v>29.61163508265873</v>
       </c>
       <c r="D326" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E326">
         <v>36.66565378736873</v>
@@ -17900,7 +17912,7 @@
         <v>29.60796663375891</v>
       </c>
       <c r="D327" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E327">
         <v>38.73216492329536</v>
@@ -17950,7 +17962,7 @@
         <v>29.99267097270676</v>
       </c>
       <c r="D328" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E328">
         <v>39.11028686861102</v>
@@ -18000,7 +18012,7 @@
         <v>30.47592970891776</v>
       </c>
       <c r="D329" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E329">
         <v>39.58527691922146</v>
@@ -18079,7 +18091,7 @@
         <v>37.15547839433958</v>
       </c>
       <c r="D331" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E331">
         <v>43.97524497646168</v>
@@ -18129,7 +18141,7 @@
         <v>37.01610527202449</v>
       </c>
       <c r="D332" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E332">
         <v>43.97524497646168</v>
@@ -18179,7 +18191,7 @@
         <v>25.78116025897209</v>
       </c>
       <c r="D333" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E333">
         <v>34.97083622412276</v>
@@ -18229,7 +18241,7 @@
         <v>21.78292834045364</v>
       </c>
       <c r="D334" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E334">
         <v>32.11135258573889</v>
@@ -18279,7 +18291,7 @@
         <v>16.20611168178342</v>
       </c>
       <c r="D335" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E335">
         <v>27.00103770079773</v>
@@ -18329,7 +18341,7 @@
         <v>16.50484318653699</v>
       </c>
       <c r="D336" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E336">
         <v>27.00103770079773</v>
@@ -18379,7 +18391,7 @@
         <v>7.513223702566968</v>
       </c>
       <c r="D337" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E337">
         <v>19.03531145368304</v>
@@ -18429,7 +18441,7 @@
         <v>7.993745640345985</v>
       </c>
       <c r="D338" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E338">
         <v>19.03531145368304</v>
@@ -18479,7 +18491,7 @@
         <v>-3.101932223543415</v>
       </c>
       <c r="D339" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E339">
         <v>9.308115338882274</v>
@@ -18529,7 +18541,7 @@
         <v>-2.399420332936991</v>
       </c>
       <c r="D340" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E340">
         <v>9.308115338882274</v>
@@ -18579,7 +18591,7 @@
         <v>-2.646016646848999</v>
       </c>
       <c r="D341" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E341">
         <v>9.308115338882274</v>
@@ -18629,7 +18641,7 @@
         <v>-9.121415898188509</v>
       </c>
       <c r="D342" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E342">
         <v>3.792162618009769</v>
@@ -18679,7 +18691,7 @@
         <v>-8.59683700961601</v>
       </c>
       <c r="D343" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E343">
         <v>3.792162618009769</v>
@@ -18729,7 +18741,7 @@
         <v>-12.89770073310627</v>
       </c>
       <c r="D344" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E344">
         <v>0.3317647274577595</v>
@@ -18779,7 +18791,7 @@
         <v>-14.09288737405897</v>
       </c>
       <c r="D345" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E345">
         <v>-0.7634443237574615</v>
@@ -18829,7 +18841,7 @@
         <v>59.56360813550708</v>
       </c>
       <c r="D346" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E346">
         <v>75.18159673719033</v>
@@ -18879,7 +18891,7 @@
         <v>60.31956868780029</v>
       </c>
       <c r="D347" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E347">
         <v>76.03992694760657</v>
@@ -18929,7 +18941,7 @@
         <v>62.79431714399279</v>
       </c>
       <c r="D348" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E348">
         <v>77.62631903124894</v>
@@ -18979,7 +18991,7 @@
         <v>64.08298118239738</v>
       </c>
       <c r="D349" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E349">
         <v>79.11665728256037</v>
@@ -19029,7 +19041,7 @@
         <v>64.68906100731142</v>
       </c>
       <c r="D350" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E350">
         <v>79.81758779625406</v>
@@ -19079,7 +19091,7 @@
         <v>66.03163316666149</v>
       </c>
       <c r="D351" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E351">
         <v>81.37027071794273</v>
@@ -19129,7 +19141,7 @@
         <v>65.93064756206419</v>
       </c>
       <c r="D352" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E352">
         <v>81.25348100015911</v>
@@ -19179,7 +19191,7 @@
         <v>64.84418812133572</v>
       </c>
       <c r="D353" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E353">
         <v>80.16577874075962</v>
@@ -19229,7 +19241,7 @@
         <v>63.26616721431549</v>
       </c>
       <c r="D354" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E354">
         <v>79.97190339753475</v>
@@ -19279,7 +19291,7 @@
         <v>61.66554474645639</v>
       </c>
       <c r="D355" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E355">
         <v>78.05285470927927</v>
@@ -19329,7 +19341,7 @@
         <v>60.62679073828761</v>
       </c>
       <c r="D356" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E356">
         <v>76.80745202574536</v>
@@ -19379,7 +19391,7 @@
         <v>59.7052486970962</v>
       </c>
       <c r="D357" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E357">
         <v>75.70257933975458</v>
@@ -19429,7 +19441,7 @@
         <v>50.59926427854958</v>
       </c>
       <c r="D358" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E358">
         <v>64.78505955942813</v>
@@ -19479,7 +19491,7 @@
         <v>54.80887863487924</v>
       </c>
       <c r="D359" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E359">
         <v>72.15232554251514</v>
@@ -19529,7 +19541,7 @@
         <v>22.63799956449154</v>
       </c>
       <c r="D360" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E360">
         <v>34.76775640560354</v>
@@ -19579,7 +19591,7 @@
         <v>21.94224021195173</v>
       </c>
       <c r="D361" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E361">
         <v>34.09962025316457</v>
@@ -19620,34 +19632,34 @@
     </row>
     <row r="362" spans="1:16">
       <c r="A362" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B362" t="s">
         <v>131</v>
       </c>
       <c r="C362">
-        <v>22.5492051810421</v>
+        <v>21.49005400241875</v>
       </c>
       <c r="D362" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E362">
-        <v>34.09962025316457</v>
+        <v>33.11192987695436</v>
       </c>
       <c r="F362">
         <v>1</v>
       </c>
       <c r="G362">
-        <v>0.1396507948189579</v>
+        <v>0.1407099459975812</v>
       </c>
       <c r="H362">
-        <v>0.1433003797468354</v>
+        <v>0.1442880701230456</v>
       </c>
       <c r="I362">
-        <v>11.55041507212247</v>
+        <v>11.62187587453561</v>
       </c>
       <c r="J362">
-        <v>0.2821725051516043</v>
+        <v>0.2872768481811144</v>
       </c>
       <c r="K362">
         <v>207.5</v>
@@ -19665,7 +19677,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>461</v>
+        <v>130</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19676,28 +19688,28 @@
         <v>132</v>
       </c>
       <c r="C363">
-        <v>21.6518845469621</v>
+        <v>20.6287291557878</v>
       </c>
       <c r="D363" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E363">
-        <v>33.16829145286381</v>
+        <v>32.1976697125811</v>
       </c>
       <c r="F363">
         <v>1</v>
       </c>
       <c r="G363">
-        <v>0.1391481154530379</v>
+        <v>0.1401712708442122</v>
       </c>
       <c r="H363">
-        <v>0.1446317085471362</v>
+        <v>0.1456023302874189</v>
       </c>
       <c r="I363">
-        <v>11.5164069059017</v>
+        <v>11.56894055679329</v>
       </c>
       <c r="J363">
-        <v>0.2872768481811144</v>
+        <v>0.2922800530279325</v>
       </c>
       <c r="K363">
         <v>204.5</v>
@@ -19715,57 +19727,57 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>130</v>
+        <v>462</v>
       </c>
     </row>
     <row r="364" spans="1:16">
       <c r="A364" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B364" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C364">
-        <v>21.72096927469043</v>
+        <v>18.55332655028487</v>
       </c>
       <c r="D364" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E364">
-        <v>33.16829145286381</v>
+        <v>31.09968346874662</v>
       </c>
       <c r="F364">
         <v>1</v>
       </c>
       <c r="G364">
-        <v>0.1400790307253096</v>
+        <v>0.1422466734497151</v>
       </c>
       <c r="H364">
-        <v>0.1446317085471362</v>
+        <v>0.1557003165312534</v>
       </c>
       <c r="I364">
-        <v>11.44732217817337</v>
+        <v>12.54635691846175</v>
       </c>
       <c r="J364">
-        <v>0.2872768481811144</v>
+        <v>0.3024287210255019</v>
       </c>
       <c r="K364">
+        <v>204.5</v>
+      </c>
+      <c r="L364">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="M364">
         <v>206</v>
       </c>
-      <c r="L364">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="M364">
-        <v>194</v>
-      </c>
       <c r="N364">
-        <v>88.90000000000001</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="O364">
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>130</v>
+        <v>463</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19773,37 +19785,37 @@
         <v>0</v>
       </c>
       <c r="B365" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C365">
-        <v>20.6287291557878</v>
+        <v>15.37197148226591</v>
       </c>
       <c r="D365" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E365">
-        <v>33.1903090762459</v>
+        <v>26.81839483339797</v>
       </c>
       <c r="F365">
         <v>1</v>
       </c>
       <c r="G365">
-        <v>0.1401712708442122</v>
+        <v>0.1498280285177341</v>
       </c>
       <c r="H365">
-        <v>0.1536096909237541</v>
+        <v>0.159981605166602</v>
       </c>
       <c r="I365">
-        <v>12.5615799204581</v>
+        <v>11.44642335113207</v>
       </c>
       <c r="J365">
-        <v>0.2922800530279325</v>
+        <v>0.3232116755660293</v>
       </c>
       <c r="K365">
-        <v>204.5</v>
+        <v>208</v>
       </c>
       <c r="L365">
-        <v>80.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="M365">
         <v>206</v>
@@ -19815,7 +19827,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19823,37 +19835,37 @@
         <v>0</v>
       </c>
       <c r="B366" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C366">
-        <v>18.55332655028487</v>
+        <v>14.44543186753303</v>
       </c>
       <c r="D366" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E366">
-        <v>31.09968346874662</v>
+        <v>25.90076425342215</v>
       </c>
       <c r="F366">
         <v>1</v>
       </c>
       <c r="G366">
-        <v>0.1422466734497151</v>
+        <v>0.150754568132467</v>
       </c>
       <c r="H366">
-        <v>0.1557003165312534</v>
+        <v>0.1608992357465779</v>
       </c>
       <c r="I366">
-        <v>12.54635691846175</v>
+        <v>11.45533238588912</v>
       </c>
       <c r="J366">
-        <v>0.3024287210255019</v>
+        <v>0.3276661929445527</v>
       </c>
       <c r="K366">
-        <v>204.5</v>
+        <v>208</v>
       </c>
       <c r="L366">
-        <v>80.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="M366">
         <v>206</v>
@@ -19865,7 +19877,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>463</v>
+        <v>131</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19876,110 +19888,110 @@
         <v>134</v>
       </c>
       <c r="C367">
-        <v>15.37197148226591</v>
+        <v>13.45577889447236</v>
       </c>
       <c r="D367" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E367">
-        <v>26.81839483339797</v>
+        <v>24.42984924623116</v>
       </c>
       <c r="F367">
         <v>1</v>
       </c>
       <c r="G367">
-        <v>0.1498280285177341</v>
+        <v>0.1543442211055276</v>
       </c>
       <c r="H367">
-        <v>0.159981605166602</v>
+        <v>0.1629701507537689</v>
       </c>
       <c r="I367">
-        <v>11.44642335113207</v>
+        <v>10.9740703517588</v>
       </c>
       <c r="J367">
-        <v>0.3232116755660293</v>
+        <v>0.335448671931084</v>
       </c>
       <c r="K367">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L367">
-        <v>82.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="M367">
-        <v>206</v>
+        <v>206.5</v>
       </c>
       <c r="N367">
-        <v>93.40000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="O367">
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>133</v>
+        <v>465</v>
       </c>
     </row>
     <row r="368" spans="1:16">
       <c r="A368" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B368" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C368">
-        <v>14.44543186753303</v>
+        <v>13.31081119885138</v>
       </c>
       <c r="D368" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E368">
-        <v>25.90076425342215</v>
+        <v>24.42984924623116</v>
       </c>
       <c r="F368">
         <v>1</v>
       </c>
       <c r="G368">
-        <v>0.150754568132467</v>
+        <v>0.1578891888011486</v>
       </c>
       <c r="H368">
-        <v>0.1608992357465779</v>
+        <v>0.1629701507537689</v>
       </c>
       <c r="I368">
-        <v>11.45533238588912</v>
+        <v>11.11903804737977</v>
       </c>
       <c r="J368">
-        <v>0.3276661929445527</v>
+        <v>0.335448671931084</v>
       </c>
       <c r="K368">
-        <v>208</v>
+        <v>215.5</v>
       </c>
       <c r="L368">
-        <v>82.59999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M368">
-        <v>206</v>
+        <v>206.5</v>
       </c>
       <c r="N368">
-        <v>93.40000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="O368">
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>131</v>
+        <v>465</v>
       </c>
     </row>
     <row r="369" spans="1:16">
       <c r="A369" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B369" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C369">
-        <v>13.45577889447236</v>
+        <v>13.42667623833452</v>
       </c>
       <c r="D369" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E369">
         <v>24.42984924623116</v>
@@ -19988,22 +20000,22 @@
         <v>1</v>
       </c>
       <c r="G369">
-        <v>0.1543442211055276</v>
+        <v>0.1529733237616655</v>
       </c>
       <c r="H369">
         <v>0.1629701507537689</v>
       </c>
       <c r="I369">
-        <v>10.9740703517588</v>
+        <v>11.00317300789663</v>
       </c>
       <c r="J369">
         <v>0.335448671931084</v>
       </c>
       <c r="K369">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L369">
-        <v>83.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="M369">
         <v>206.5</v>
@@ -20015,121 +20027,121 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="370" spans="1:16">
       <c r="A370" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B370" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C370">
-        <v>13.31081119885138</v>
+        <v>10.59259053965798</v>
       </c>
       <c r="D370" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E370">
-        <v>24.42984924623116</v>
+        <v>21.96162940390666</v>
       </c>
       <c r="F370">
         <v>1</v>
       </c>
       <c r="G370">
-        <v>0.1578891888011486</v>
+        <v>0.157207409460342</v>
       </c>
       <c r="H370">
-        <v>0.1629701507537689</v>
+        <v>0.1640383705960933</v>
       </c>
       <c r="I370">
-        <v>11.11903804737977</v>
+        <v>11.36903886424868</v>
       </c>
       <c r="J370">
-        <v>0.335448671931084</v>
+        <v>0.3490829021921049</v>
       </c>
       <c r="K370">
-        <v>215.5</v>
+        <v>210</v>
       </c>
       <c r="L370">
-        <v>85.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="M370">
-        <v>206.5</v>
+        <v>203.5</v>
       </c>
       <c r="N370">
-        <v>93.7</v>
+        <v>93</v>
       </c>
       <c r="O370">
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="371" spans="1:16">
       <c r="A371" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B371" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C371">
-        <v>13.42667623833452</v>
+        <v>10.37263457760139</v>
       </c>
       <c r="D371" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E371">
-        <v>24.42984924623116</v>
+        <v>21.96162940390666</v>
       </c>
       <c r="F371">
         <v>1</v>
       </c>
       <c r="G371">
-        <v>0.1529733237616655</v>
+        <v>0.1608273654223986</v>
       </c>
       <c r="H371">
-        <v>0.1629701507537689</v>
+        <v>0.1640383705960933</v>
       </c>
       <c r="I371">
-        <v>11.00317300789663</v>
+        <v>11.58899482630527</v>
       </c>
       <c r="J371">
-        <v>0.335448671931084</v>
+        <v>0.3490829021921049</v>
       </c>
       <c r="K371">
-        <v>208</v>
+        <v>215.5</v>
       </c>
       <c r="L371">
-        <v>83.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M371">
-        <v>206.5</v>
+        <v>203.5</v>
       </c>
       <c r="N371">
-        <v>93.7</v>
+        <v>93</v>
       </c>
       <c r="O371">
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="372" spans="1:16">
       <c r="A372" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B372" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C372">
-        <v>10.59259053965798</v>
+        <v>10.59075634404218</v>
       </c>
       <c r="D372" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E372">
         <v>21.96162940390666</v>
@@ -20138,22 +20150,22 @@
         <v>1</v>
       </c>
       <c r="G372">
-        <v>0.157207409460342</v>
+        <v>0.1558092436559578</v>
       </c>
       <c r="H372">
         <v>0.1640383705960933</v>
       </c>
       <c r="I372">
-        <v>11.36903886424868</v>
+        <v>11.37087305986448</v>
       </c>
       <c r="J372">
         <v>0.3490829021921049</v>
       </c>
       <c r="K372">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L372">
-        <v>83.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="M372">
         <v>203.5</v>
@@ -20165,39 +20177,39 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="373" spans="1:16">
       <c r="A373" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B373" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C373">
-        <v>10.37263457760139</v>
+        <v>8.066617110777202</v>
       </c>
       <c r="D373" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E373">
-        <v>21.96162940390666</v>
+        <v>20.60412942273109</v>
       </c>
       <c r="F373">
         <v>1</v>
       </c>
       <c r="G373">
-        <v>0.1608273654223986</v>
+        <v>0.1631333828892228</v>
       </c>
       <c r="H373">
-        <v>0.1640383705960933</v>
+        <v>0.1673958705772689</v>
       </c>
       <c r="I373">
-        <v>11.58899482630527</v>
+        <v>12.53751231195389</v>
       </c>
       <c r="J373">
-        <v>0.3490829021921049</v>
+        <v>0.3597836793003378</v>
       </c>
       <c r="K373">
         <v>215.5</v>
@@ -20206,48 +20218,48 @@
         <v>85.59999999999999</v>
       </c>
       <c r="M373">
-        <v>203.5</v>
+        <v>204</v>
       </c>
       <c r="N373">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O373">
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>465</v>
+        <v>134</v>
       </c>
     </row>
     <row r="374" spans="1:16">
       <c r="A374" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B374" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C374">
-        <v>10.59075634404218</v>
+        <v>8.364994705529739</v>
       </c>
       <c r="D374" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E374">
-        <v>21.96162940390666</v>
+        <v>20.60412942273109</v>
       </c>
       <c r="F374">
         <v>1</v>
       </c>
       <c r="G374">
-        <v>0.1558092436559578</v>
+        <v>0.1580350052944703</v>
       </c>
       <c r="H374">
-        <v>0.1640383705960933</v>
+        <v>0.1673958705772689</v>
       </c>
       <c r="I374">
-        <v>11.37087305986448</v>
+        <v>12.23913471720135</v>
       </c>
       <c r="J374">
-        <v>0.3490829021921049</v>
+        <v>0.3597836793003378</v>
       </c>
       <c r="K374">
         <v>208</v>
@@ -20256,48 +20268,48 @@
         <v>83.2</v>
       </c>
       <c r="M374">
-        <v>203.5</v>
+        <v>204</v>
       </c>
       <c r="N374">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O374">
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>465</v>
+        <v>134</v>
       </c>
     </row>
     <row r="375" spans="1:16">
       <c r="A375" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B375" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C375">
-        <v>10.88525375719482</v>
+        <v>8.723696781331768</v>
       </c>
       <c r="D375" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E375">
-        <v>21.96162940390666</v>
+        <v>20.60412942273109</v>
       </c>
       <c r="F375">
         <v>1</v>
       </c>
       <c r="G375">
-        <v>0.1519147462428052</v>
+        <v>0.1540763032186682</v>
       </c>
       <c r="H375">
-        <v>0.1640383705960933</v>
+        <v>0.1673958705772689</v>
       </c>
       <c r="I375">
-        <v>11.07637564671184</v>
+        <v>11.88043264139932</v>
       </c>
       <c r="J375">
-        <v>0.3490829021921049</v>
+        <v>0.3597836793003378</v>
       </c>
       <c r="K375">
         <v>202</v>
@@ -20306,16 +20318,16 @@
         <v>81.40000000000001</v>
       </c>
       <c r="M375">
-        <v>203.5</v>
+        <v>204</v>
       </c>
       <c r="N375">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O375">
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>465</v>
+        <v>134</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20323,43 +20335,43 @@
         <v>0</v>
       </c>
       <c r="B376" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C376">
-        <v>8.066617110777202</v>
+        <v>-3.424244140274368</v>
       </c>
       <c r="D376" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E376">
-        <v>20.60412942273109</v>
+        <v>10.72424068728326</v>
       </c>
       <c r="F376">
         <v>1</v>
       </c>
       <c r="G376">
-        <v>0.1631333828892228</v>
+        <v>0.1690242441402744</v>
       </c>
       <c r="H376">
-        <v>0.1673958705772689</v>
+        <v>0.1852757593127167</v>
       </c>
       <c r="I376">
-        <v>12.53751231195389</v>
+        <v>14.14848482755762</v>
       </c>
       <c r="J376">
-        <v>0.3597836793003378</v>
+        <v>0.4206060689769481</v>
       </c>
       <c r="K376">
-        <v>215.5</v>
+        <v>205</v>
       </c>
       <c r="L376">
-        <v>85.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="M376">
-        <v>204</v>
+        <v>207.5</v>
       </c>
       <c r="N376">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="O376">
         <v>1</v>
@@ -20370,102 +20382,81 @@
     </row>
     <row r="377" spans="1:16">
       <c r="A377" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B377" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C377">
-        <v>8.364994705529739</v>
+        <v>-2.10269534440512</v>
       </c>
       <c r="D377" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E377">
-        <v>20.60412942273109</v>
+        <v>10.74605227334604</v>
       </c>
       <c r="F377">
         <v>1</v>
       </c>
       <c r="G377">
-        <v>0.1580350052944703</v>
+        <v>0.1703026953444051</v>
       </c>
       <c r="H377">
-        <v>0.1673958705772689</v>
+        <v>0.185253947726654</v>
       </c>
       <c r="I377">
-        <v>12.23913471720135</v>
+        <v>12.84874761775116</v>
       </c>
       <c r="J377">
-        <v>0.3597836793003378</v>
+        <v>0.4205009528995372</v>
       </c>
       <c r="K377">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L377">
-        <v>83.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M377">
-        <v>204</v>
+        <v>207.5</v>
       </c>
       <c r="N377">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="O377">
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>135</v>
+        <v>467</v>
       </c>
     </row>
     <row r="378" spans="1:16">
       <c r="A378" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B378" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C378">
-        <v>8.723696781331768</v>
-      </c>
-      <c r="D378" t="s">
-        <v>250</v>
-      </c>
-      <c r="E378">
-        <v>20.60412942273109</v>
+        <v>-1.224428027264494</v>
       </c>
       <c r="F378">
         <v>1</v>
       </c>
       <c r="G378">
-        <v>0.1540763032186682</v>
-      </c>
-      <c r="H378">
-        <v>0.1673958705772689</v>
-      </c>
-      <c r="I378">
-        <v>11.88043264139932</v>
+        <v>0.1558244280272645</v>
       </c>
       <c r="J378">
-        <v>0.3597836793003378</v>
+        <v>0.4244563677149432</v>
       </c>
       <c r="K378">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="L378">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="M378">
-        <v>204</v>
-      </c>
-      <c r="N378">
-        <v>94</v>
-      </c>
-      <c r="O378">
-        <v>1</v>
+        <v>77.3</v>
       </c>
       <c r="P378" t="s">
-        <v>135</v>
+        <v>468</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20473,49 +20464,49 @@
         <v>0</v>
       </c>
       <c r="B379" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C379">
-        <v>-3.424244140274368</v>
+        <v>-1.02931617171204</v>
       </c>
       <c r="D379" t="s">
-        <v>251</v>
+        <v>140</v>
       </c>
       <c r="E379">
-        <v>10.72424068728326</v>
+        <v>-3.753066800891602</v>
       </c>
       <c r="F379">
         <v>1</v>
       </c>
       <c r="G379">
-        <v>0.1690242441402744</v>
+        <v>0.162829316171712</v>
       </c>
       <c r="H379">
-        <v>0.1852757593127167</v>
+        <v>0.1583530668008916</v>
       </c>
       <c r="I379">
-        <v>14.14848482755762</v>
+        <v>-2.723750629179563</v>
       </c>
       <c r="J379">
-        <v>0.4206060689769481</v>
+        <v>0.4381246854102249</v>
       </c>
       <c r="K379">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="L379">
-        <v>82.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="M379">
-        <v>207.5</v>
+        <v>185</v>
       </c>
       <c r="N379">
-        <v>98</v>
+        <v>77.3</v>
       </c>
       <c r="O379">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P379" t="s">
-        <v>136</v>
+        <v>469</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20523,49 +20514,49 @@
         <v>0</v>
       </c>
       <c r="B380" t="s">
+        <v>141</v>
+      </c>
+      <c r="C380">
+        <v>-36.89254119687769</v>
+      </c>
+      <c r="D380" t="s">
         <v>140</v>
       </c>
-      <c r="C380">
-        <v>-2.10269534440512</v>
-      </c>
-      <c r="D380" t="s">
-        <v>251</v>
-      </c>
       <c r="E380">
-        <v>10.74605227334604</v>
+        <v>-39.23272792204477</v>
       </c>
       <c r="F380">
         <v>1</v>
       </c>
       <c r="G380">
-        <v>0.1703026953444051</v>
+        <v>0.1986925411968777</v>
       </c>
       <c r="H380">
-        <v>0.185253947726654</v>
+        <v>0.1938327279220448</v>
       </c>
       <c r="I380">
-        <v>12.84874761775116</v>
+        <v>-2.340186725167086</v>
       </c>
       <c r="J380">
-        <v>0.4205009528995372</v>
+        <v>0.6299066374164582</v>
       </c>
       <c r="K380">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="L380">
-        <v>84.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="M380">
-        <v>207.5</v>
+        <v>185</v>
       </c>
       <c r="N380">
-        <v>98</v>
+        <v>77.3</v>
       </c>
       <c r="O380">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P380" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20573,49 +20564,49 @@
         <v>0</v>
       </c>
       <c r="B381" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C381">
-        <v>-1.02931617171204</v>
+        <v>18.35059753174872</v>
       </c>
       <c r="D381" t="s">
-        <v>252</v>
+        <v>140</v>
       </c>
       <c r="E381">
-        <v>-3.367440857122276</v>
+        <v>16.56381239880164</v>
       </c>
       <c r="F381">
         <v>1</v>
       </c>
       <c r="G381">
-        <v>0.162829316171712</v>
+        <v>0.1424494024682513</v>
       </c>
       <c r="H381">
-        <v>0.1613674408571223</v>
+        <v>0.1380361876011983</v>
       </c>
       <c r="I381">
-        <v>-2.338124685410236</v>
+        <v>-1.786785132947074</v>
       </c>
       <c r="J381">
-        <v>0.4381246854102249</v>
+        <v>0.3283037167632343</v>
       </c>
       <c r="K381">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L381">
-        <v>80.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="M381">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="N381">
-        <v>79</v>
+        <v>77.3</v>
       </c>
       <c r="O381">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P381" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20623,49 +20614,49 @@
         <v>0</v>
       </c>
       <c r="B382" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C382">
-        <v>-36.89254119687769</v>
+        <v>16.15896602968036</v>
       </c>
       <c r="D382" t="s">
-        <v>252</v>
+        <v>140</v>
       </c>
       <c r="E382">
-        <v>-39.42244783429415</v>
+        <v>14.41856463222679</v>
       </c>
       <c r="F382">
         <v>1</v>
       </c>
       <c r="G382">
-        <v>0.1986925411968777</v>
+        <v>0.1446410339703197</v>
       </c>
       <c r="H382">
-        <v>0.1974224478342941</v>
+        <v>0.1401814353677732</v>
       </c>
       <c r="I382">
-        <v>-2.52990663741646</v>
+        <v>-1.740401397453567</v>
       </c>
       <c r="J382">
-        <v>0.6299066374164582</v>
+        <v>0.3398996506366119</v>
       </c>
       <c r="K382">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L382">
-        <v>80.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="M382">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="N382">
-        <v>79</v>
+        <v>77.3</v>
       </c>
       <c r="O382">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P382" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-2474-2382-800.xlsx
+++ b/s60_signal/position-2474-2382-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="469">
   <si>
     <t>trade_time</t>
   </si>
@@ -418,1003 +418,991 @@
     <t>2021-01-19</t>
   </si>
   <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>2021-01-28</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>2021-07-26</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>2010-10-22</t>
+  </si>
+  <si>
+    <t>2010-10-25</t>
+  </si>
+  <si>
+    <t>2010-10-28</t>
+  </si>
+  <si>
+    <t>2011-05-13</t>
+  </si>
+  <si>
+    <t>2011-05-16</t>
+  </si>
+  <si>
+    <t>2011-05-17</t>
+  </si>
+  <si>
+    <t>2011-05-18</t>
+  </si>
+  <si>
+    <t>2011-05-19</t>
+  </si>
+  <si>
+    <t>2011-05-20</t>
+  </si>
+  <si>
+    <t>2011-05-23</t>
+  </si>
+  <si>
+    <t>2011-05-24</t>
+  </si>
+  <si>
+    <t>2011-05-25</t>
+  </si>
+  <si>
+    <t>2011-05-26</t>
+  </si>
+  <si>
+    <t>2011-05-27</t>
+  </si>
+  <si>
+    <t>2011-05-30</t>
+  </si>
+  <si>
+    <t>2011-05-31</t>
+  </si>
+  <si>
+    <t>2011-06-02</t>
+  </si>
+  <si>
+    <t>2011-06-03</t>
+  </si>
+  <si>
+    <t>2011-07-22</t>
+  </si>
+  <si>
+    <t>2011-07-25</t>
+  </si>
+  <si>
+    <t>2011-07-27</t>
+  </si>
+  <si>
+    <t>2011-07-28</t>
+  </si>
+  <si>
+    <t>2011-07-29</t>
+  </si>
+  <si>
+    <t>2011-10-07</t>
+  </si>
+  <si>
+    <t>2011-10-05</t>
+  </si>
+  <si>
+    <t>2012-02-29</t>
+  </si>
+  <si>
+    <t>2012-07-18</t>
+  </si>
+  <si>
+    <t>2012-05-02</t>
+  </si>
+  <si>
+    <t>2012-05-25</t>
+  </si>
+  <si>
+    <t>2012-11-13</t>
+  </si>
+  <si>
+    <t>2012-11-14</t>
+  </si>
+  <si>
+    <t>2012-12-14</t>
+  </si>
+  <si>
+    <t>2012-08-01</t>
+  </si>
+  <si>
+    <t>2013-06-14</t>
+  </si>
+  <si>
+    <t>2013-06-17</t>
+  </si>
+  <si>
+    <t>2013-06-18</t>
+  </si>
+  <si>
+    <t>2013-05-20</t>
+  </si>
+  <si>
+    <t>2013-08-06</t>
+  </si>
+  <si>
+    <t>2013-05-16</t>
+  </si>
+  <si>
+    <t>2013-11-28</t>
+  </si>
+  <si>
+    <t>2013-12-04</t>
+  </si>
+  <si>
+    <t>2014-02-17</t>
+  </si>
+  <si>
+    <t>2014-02-19</t>
+  </si>
+  <si>
+    <t>2013-08-07</t>
+  </si>
+  <si>
+    <t>2013-08-08</t>
+  </si>
+  <si>
+    <t>2013-08-09</t>
+  </si>
+  <si>
+    <t>2013-09-23</t>
+  </si>
+  <si>
+    <t>2014-04-25</t>
+  </si>
+  <si>
+    <t>2014-04-24</t>
+  </si>
+  <si>
+    <t>2014-09-15</t>
+  </si>
+  <si>
+    <t>2014-12-02</t>
+  </si>
+  <si>
+    <t>2014-09-10</t>
+  </si>
+  <si>
+    <t>2014-09-04</t>
+  </si>
+  <si>
+    <t>2014-11-11</t>
+  </si>
+  <si>
+    <t>2014-09-03</t>
+  </si>
+  <si>
+    <t>2014-11-03</t>
+  </si>
+  <si>
+    <t>2014-11-27</t>
+  </si>
+  <si>
+    <t>2015-03-18</t>
+  </si>
+  <si>
+    <t>2015-08-07</t>
+  </si>
+  <si>
+    <t>2016-03-16</t>
+  </si>
+  <si>
+    <t>2016-03-17</t>
+  </si>
+  <si>
+    <t>2016-02-01</t>
+  </si>
+  <si>
+    <t>2016-02-02</t>
+  </si>
+  <si>
+    <t>2016-07-18</t>
+  </si>
+  <si>
+    <t>2016-06-30</t>
+  </si>
+  <si>
+    <t>2016-08-03</t>
+  </si>
+  <si>
+    <t>2016-07-01</t>
+  </si>
+  <si>
+    <t>2017-02-08</t>
+  </si>
+  <si>
+    <t>2017-06-23</t>
+  </si>
+  <si>
+    <t>2017-03-29</t>
+  </si>
+  <si>
+    <t>2017-11-15</t>
+  </si>
+  <si>
+    <t>2018-03-08</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>2018-04-18</t>
+  </si>
+  <si>
+    <t>2018-04-19</t>
+  </si>
+  <si>
+    <t>2018-04-20</t>
+  </si>
+  <si>
+    <t>2018-04-23</t>
+  </si>
+  <si>
+    <t>2018-05-04</t>
+  </si>
+  <si>
+    <t>2018-05-07</t>
+  </si>
+  <si>
+    <t>2018-05-08</t>
+  </si>
+  <si>
+    <t>2018-04-12</t>
+  </si>
+  <si>
+    <t>2018-11-16</t>
+  </si>
+  <si>
+    <t>2018-11-30</t>
+  </si>
+  <si>
+    <t>2018-12-03</t>
+  </si>
+  <si>
+    <t>2018-12-27</t>
+  </si>
+  <si>
+    <t>2019-01-03</t>
+  </si>
+  <si>
+    <t>2019-02-14</t>
+  </si>
+  <si>
+    <t>2019-02-20</t>
+  </si>
+  <si>
+    <t>2019-09-12</t>
+  </si>
+  <si>
+    <t>2019-09-16</t>
+  </si>
+  <si>
+    <t>2019-09-17</t>
+  </si>
+  <si>
+    <t>2019-09-18</t>
+  </si>
+  <si>
+    <t>2019-09-19</t>
+  </si>
+  <si>
+    <t>2019-09-23</t>
+  </si>
+  <si>
+    <t>2019-10-30</t>
+  </si>
+  <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
+    <t>2019-11-11</t>
+  </si>
+  <si>
+    <t>2019-11-14</t>
+  </si>
+  <si>
+    <t>2019-11-05</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2020-05-29</t>
+  </si>
+  <si>
+    <t>2020-06-03</t>
+  </si>
+  <si>
+    <t>2020-06-04</t>
+  </si>
+  <si>
+    <t>2021-02-17</t>
+  </si>
+  <si>
+    <t>2021-03-23</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>2021-03-29</t>
+  </si>
+  <si>
+    <t>2010-08-03</t>
+  </si>
+  <si>
+    <t>2010-08-19</t>
+  </si>
+  <si>
+    <t>2010-08-26</t>
+  </si>
+  <si>
+    <t>2010-08-27</t>
+  </si>
+  <si>
+    <t>2010-08-30</t>
+  </si>
+  <si>
+    <t>2010-09-17</t>
+  </si>
+  <si>
+    <t>2010-09-20</t>
+  </si>
+  <si>
+    <t>2010-09-21</t>
+  </si>
+  <si>
+    <t>2010-09-23</t>
+  </si>
+  <si>
+    <t>2010-09-24</t>
+  </si>
+  <si>
+    <t>2010-09-27</t>
+  </si>
+  <si>
+    <t>2010-09-28</t>
+  </si>
+  <si>
+    <t>2010-09-29</t>
+  </si>
+  <si>
+    <t>2010-09-30</t>
+  </si>
+  <si>
+    <t>2010-10-01</t>
+  </si>
+  <si>
+    <t>2010-10-04</t>
+  </si>
+  <si>
+    <t>2010-10-05</t>
+  </si>
+  <si>
+    <t>2010-10-06</t>
+  </si>
+  <si>
+    <t>2010-10-07</t>
+  </si>
+  <si>
+    <t>2010-10-08</t>
+  </si>
+  <si>
+    <t>2010-10-11</t>
+  </si>
+  <si>
+    <t>2010-11-24</t>
+  </si>
+  <si>
+    <t>2010-11-25</t>
+  </si>
+  <si>
+    <t>2010-11-26</t>
+  </si>
+  <si>
+    <t>2010-11-29</t>
+  </si>
+  <si>
+    <t>2010-11-30</t>
+  </si>
+  <si>
+    <t>2010-12-01</t>
+  </si>
+  <si>
+    <t>2010-12-02</t>
+  </si>
+  <si>
+    <t>2010-12-03</t>
+  </si>
+  <si>
+    <t>2011-06-24</t>
+  </si>
+  <si>
+    <t>2011-06-27</t>
+  </si>
+  <si>
+    <t>2011-06-30</t>
+  </si>
+  <si>
+    <t>2011-07-07</t>
+  </si>
+  <si>
+    <t>2011-12-02</t>
+  </si>
+  <si>
+    <t>2011-12-05</t>
+  </si>
+  <si>
+    <t>2012-02-24</t>
+  </si>
+  <si>
+    <t>2012-03-02</t>
+  </si>
+  <si>
+    <t>2012-03-06</t>
+  </si>
+  <si>
+    <t>2012-03-07</t>
+  </si>
+  <si>
+    <t>2012-03-12</t>
+  </si>
+  <si>
+    <t>2012-03-13</t>
+  </si>
+  <si>
+    <t>2012-03-29</t>
+  </si>
+  <si>
+    <t>2012-03-30</t>
+  </si>
+  <si>
+    <t>2012-05-03</t>
+  </si>
+  <si>
+    <t>2012-05-15</t>
+  </si>
+  <si>
+    <t>2012-05-16</t>
+  </si>
+  <si>
+    <t>2012-05-17</t>
+  </si>
+  <si>
+    <t>2012-05-18</t>
+  </si>
+  <si>
+    <t>2012-05-21</t>
+  </si>
+  <si>
+    <t>2012-05-22</t>
+  </si>
+  <si>
+    <t>2012-05-23</t>
+  </si>
+  <si>
+    <t>2012-05-24</t>
+  </si>
+  <si>
+    <t>2012-05-28</t>
+  </si>
+  <si>
+    <t>2012-05-29</t>
+  </si>
+  <si>
+    <t>2012-05-30</t>
+  </si>
+  <si>
+    <t>2012-05-31</t>
+  </si>
+  <si>
+    <t>2012-06-01</t>
+  </si>
+  <si>
+    <t>2012-06-04</t>
+  </si>
+  <si>
+    <t>2012-06-05</t>
+  </si>
+  <si>
+    <t>2012-06-06</t>
+  </si>
+  <si>
+    <t>2012-06-07</t>
+  </si>
+  <si>
+    <t>2012-06-08</t>
+  </si>
+  <si>
+    <t>2012-06-11</t>
+  </si>
+  <si>
+    <t>2012-06-12</t>
+  </si>
+  <si>
+    <t>2012-06-13</t>
+  </si>
+  <si>
+    <t>2012-06-14</t>
+  </si>
+  <si>
+    <t>2012-06-15</t>
+  </si>
+  <si>
+    <t>2012-06-19</t>
+  </si>
+  <si>
+    <t>2012-06-20</t>
+  </si>
+  <si>
+    <t>2012-06-22</t>
+  </si>
+  <si>
+    <t>2012-10-18</t>
+  </si>
+  <si>
+    <t>2012-10-19</t>
+  </si>
+  <si>
+    <t>2012-10-22</t>
+  </si>
+  <si>
+    <t>2013-04-08</t>
+  </si>
+  <si>
+    <t>2013-04-12</t>
+  </si>
+  <si>
+    <t>2013-06-25</t>
+  </si>
+  <si>
+    <t>2013-06-27</t>
+  </si>
+  <si>
+    <t>2013-06-28</t>
+  </si>
+  <si>
+    <t>2013-07-01</t>
+  </si>
+  <si>
+    <t>2013-07-02</t>
+  </si>
+  <si>
+    <t>2013-07-03</t>
+  </si>
+  <si>
+    <t>2013-07-04</t>
+  </si>
+  <si>
+    <t>2013-10-28</t>
+  </si>
+  <si>
+    <t>2014-01-22</t>
+  </si>
+  <si>
+    <t>2014-01-23</t>
+  </si>
+  <si>
+    <t>2014-01-24</t>
+  </si>
+  <si>
+    <t>2014-01-27</t>
+  </si>
+  <si>
+    <t>2014-02-06</t>
+  </si>
+  <si>
+    <t>2014-02-07</t>
+  </si>
+  <si>
+    <t>2014-02-10</t>
+  </si>
+  <si>
+    <t>2014-02-11</t>
+  </si>
+  <si>
+    <t>2014-02-18</t>
+  </si>
+  <si>
+    <t>2014-02-20</t>
+  </si>
+  <si>
+    <t>2014-02-21</t>
+  </si>
+  <si>
+    <t>2014-07-08</t>
+  </si>
+  <si>
+    <t>2014-07-10</t>
+  </si>
+  <si>
+    <t>2014-07-11</t>
+  </si>
+  <si>
+    <t>2014-07-16</t>
+  </si>
+  <si>
+    <t>2014-07-17</t>
+  </si>
+  <si>
+    <t>2014-07-18</t>
+  </si>
+  <si>
+    <t>2014-10-15</t>
+  </si>
+  <si>
+    <t>2014-11-04</t>
+  </si>
+  <si>
+    <t>2015-06-11</t>
+  </si>
+  <si>
+    <t>2015-06-12</t>
+  </si>
+  <si>
+    <t>2015-06-15</t>
+  </si>
+  <si>
+    <t>2015-07-22</t>
+  </si>
+  <si>
+    <t>2015-07-23</t>
+  </si>
+  <si>
+    <t>2015-10-15</t>
+  </si>
+  <si>
+    <t>2015-10-16</t>
+  </si>
+  <si>
+    <t>2015-11-19</t>
+  </si>
+  <si>
+    <t>2016-04-01</t>
+  </si>
+  <si>
+    <t>2016-04-07</t>
+  </si>
+  <si>
+    <t>2016-04-08</t>
+  </si>
+  <si>
+    <t>2016-04-15</t>
+  </si>
+  <si>
+    <t>2016-04-18</t>
+  </si>
+  <si>
+    <t>2016-04-19</t>
+  </si>
+  <si>
+    <t>2016-04-21</t>
+  </si>
+  <si>
+    <t>2016-04-22</t>
+  </si>
+  <si>
+    <t>2016-04-27</t>
+  </si>
+  <si>
+    <t>2016-04-28</t>
+  </si>
+  <si>
+    <t>2016-05-03</t>
+  </si>
+  <si>
+    <t>2016-05-05</t>
+  </si>
+  <si>
+    <t>2016-05-10</t>
+  </si>
+  <si>
+    <t>2016-05-11</t>
+  </si>
+  <si>
+    <t>2016-05-12</t>
+  </si>
+  <si>
+    <t>2016-05-13</t>
+  </si>
+  <si>
+    <t>2016-05-16</t>
+  </si>
+  <si>
+    <t>2016-05-17</t>
+  </si>
+  <si>
+    <t>2016-10-27</t>
+  </si>
+  <si>
+    <t>2016-12-15</t>
+  </si>
+  <si>
+    <t>2017-06-26</t>
+  </si>
+  <si>
+    <t>2017-06-27</t>
+  </si>
+  <si>
+    <t>2017-07-11</t>
+  </si>
+  <si>
+    <t>2017-07-12</t>
+  </si>
+  <si>
+    <t>2017-07-13</t>
+  </si>
+  <si>
+    <t>2017-07-14</t>
+  </si>
+  <si>
+    <t>2017-07-17</t>
+  </si>
+  <si>
+    <t>2017-08-21</t>
+  </si>
+  <si>
+    <t>2017-08-22</t>
+  </si>
+  <si>
+    <t>2017-08-23</t>
+  </si>
+  <si>
+    <t>2017-08-24</t>
+  </si>
+  <si>
+    <t>2017-08-25</t>
+  </si>
+  <si>
+    <t>2017-09-06</t>
+  </si>
+  <si>
+    <t>2017-09-07</t>
+  </si>
+  <si>
+    <t>2017-09-08</t>
+  </si>
+  <si>
+    <t>2018-01-12</t>
+  </si>
+  <si>
+    <t>2018-01-15</t>
+  </si>
+  <si>
+    <t>2018-01-16</t>
+  </si>
+  <si>
+    <t>2018-01-17</t>
+  </si>
+  <si>
+    <t>2018-01-30</t>
+  </si>
+  <si>
+    <t>2018-01-31</t>
+  </si>
+  <si>
+    <t>2018-02-06</t>
+  </si>
+  <si>
+    <t>2018-02-22</t>
+  </si>
+  <si>
+    <t>2018-03-30</t>
+  </si>
+  <si>
+    <t>2018-05-16</t>
+  </si>
+  <si>
+    <t>2018-05-21</t>
+  </si>
+  <si>
+    <t>2018-11-20</t>
+  </si>
+  <si>
+    <t>2018-12-28</t>
+  </si>
+  <si>
+    <t>2019-01-09</t>
+  </si>
+  <si>
+    <t>2019-01-10</t>
+  </si>
+  <si>
+    <t>2019-01-15</t>
+  </si>
+  <si>
+    <t>2019-01-16</t>
+  </si>
+  <si>
+    <t>2019-01-17</t>
+  </si>
+  <si>
+    <t>2019-01-18</t>
+  </si>
+  <si>
+    <t>2019-01-22</t>
+  </si>
+  <si>
+    <t>2019-01-23</t>
+  </si>
+  <si>
+    <t>2019-01-24</t>
+  </si>
+  <si>
+    <t>2019-01-25</t>
+  </si>
+  <si>
+    <t>2019-01-29</t>
+  </si>
+  <si>
+    <t>2019-03-11</t>
+  </si>
+  <si>
+    <t>2019-03-12</t>
+  </si>
+  <si>
+    <t>2019-03-13</t>
+  </si>
+  <si>
+    <t>2019-04-09</t>
+  </si>
+  <si>
+    <t>2019-04-10</t>
+  </si>
+  <si>
+    <t>2019-04-18</t>
+  </si>
+  <si>
+    <t>2019-04-19</t>
+  </si>
+  <si>
+    <t>2019-04-25</t>
+  </si>
+  <si>
+    <t>2019-04-26</t>
+  </si>
+  <si>
+    <t>2019-05-02</t>
+  </si>
+  <si>
+    <t>2019-05-07</t>
+  </si>
+  <si>
+    <t>2019-05-08</t>
+  </si>
+  <si>
+    <t>2019-05-09</t>
+  </si>
+  <si>
+    <t>2019-05-10</t>
+  </si>
+  <si>
+    <t>2019-05-13</t>
+  </si>
+  <si>
+    <t>2019-07-29</t>
+  </si>
+  <si>
+    <t>2019-08-29</t>
+  </si>
+  <si>
+    <t>2019-08-30</t>
+  </si>
+  <si>
+    <t>2019-09-02</t>
+  </si>
+  <si>
+    <t>2019-09-03</t>
+  </si>
+  <si>
+    <t>2019-09-04</t>
+  </si>
+  <si>
+    <t>2019-09-05</t>
+  </si>
+  <si>
+    <t>2019-09-06</t>
+  </si>
+  <si>
+    <t>2019-09-10</t>
+  </si>
+  <si>
+    <t>2020-02-20</t>
+  </si>
+  <si>
+    <t>2020-02-21</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>2020-02-27</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-03-04</t>
+  </si>
+  <si>
+    <t>2020-03-05</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2020-03-09</t>
+  </si>
+  <si>
+    <t>2020-03-12</t>
+  </si>
+  <si>
+    <t>2020-11-02</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>2020-12-28</t>
+  </si>
+  <si>
+    <t>2021-01-05</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
     <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-14</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>2021-01-21</t>
-  </si>
-  <si>
-    <t>2021-01-28</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>2021-07-26</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
-    <t>2010-10-22</t>
-  </si>
-  <si>
-    <t>2010-10-25</t>
-  </si>
-  <si>
-    <t>2010-10-28</t>
-  </si>
-  <si>
-    <t>2011-05-13</t>
-  </si>
-  <si>
-    <t>2011-05-16</t>
-  </si>
-  <si>
-    <t>2011-05-17</t>
-  </si>
-  <si>
-    <t>2011-05-18</t>
-  </si>
-  <si>
-    <t>2011-05-19</t>
-  </si>
-  <si>
-    <t>2011-05-20</t>
-  </si>
-  <si>
-    <t>2011-05-23</t>
-  </si>
-  <si>
-    <t>2011-05-24</t>
-  </si>
-  <si>
-    <t>2011-05-25</t>
-  </si>
-  <si>
-    <t>2011-05-26</t>
-  </si>
-  <si>
-    <t>2011-05-27</t>
-  </si>
-  <si>
-    <t>2011-05-30</t>
-  </si>
-  <si>
-    <t>2011-05-31</t>
-  </si>
-  <si>
-    <t>2011-06-02</t>
-  </si>
-  <si>
-    <t>2011-06-03</t>
-  </si>
-  <si>
-    <t>2011-07-22</t>
-  </si>
-  <si>
-    <t>2011-07-25</t>
-  </si>
-  <si>
-    <t>2011-07-27</t>
-  </si>
-  <si>
-    <t>2011-07-28</t>
-  </si>
-  <si>
-    <t>2011-07-29</t>
-  </si>
-  <si>
-    <t>2011-10-07</t>
-  </si>
-  <si>
-    <t>2011-10-05</t>
-  </si>
-  <si>
-    <t>2012-02-29</t>
-  </si>
-  <si>
-    <t>2012-07-18</t>
-  </si>
-  <si>
-    <t>2012-05-02</t>
-  </si>
-  <si>
-    <t>2012-05-25</t>
-  </si>
-  <si>
-    <t>2012-11-13</t>
-  </si>
-  <si>
-    <t>2012-11-14</t>
-  </si>
-  <si>
-    <t>2012-12-14</t>
-  </si>
-  <si>
-    <t>2012-08-01</t>
-  </si>
-  <si>
-    <t>2013-06-14</t>
-  </si>
-  <si>
-    <t>2013-06-17</t>
-  </si>
-  <si>
-    <t>2013-06-18</t>
-  </si>
-  <si>
-    <t>2013-05-20</t>
-  </si>
-  <si>
-    <t>2013-08-06</t>
-  </si>
-  <si>
-    <t>2013-05-16</t>
-  </si>
-  <si>
-    <t>2013-11-28</t>
-  </si>
-  <si>
-    <t>2013-12-04</t>
-  </si>
-  <si>
-    <t>2014-02-17</t>
-  </si>
-  <si>
-    <t>2014-02-19</t>
-  </si>
-  <si>
-    <t>2013-08-07</t>
-  </si>
-  <si>
-    <t>2013-08-08</t>
-  </si>
-  <si>
-    <t>2013-08-09</t>
-  </si>
-  <si>
-    <t>2013-09-23</t>
-  </si>
-  <si>
-    <t>2014-04-25</t>
-  </si>
-  <si>
-    <t>2014-04-24</t>
-  </si>
-  <si>
-    <t>2014-09-15</t>
-  </si>
-  <si>
-    <t>2014-12-02</t>
-  </si>
-  <si>
-    <t>2014-09-10</t>
-  </si>
-  <si>
-    <t>2014-09-04</t>
-  </si>
-  <si>
-    <t>2014-11-11</t>
-  </si>
-  <si>
-    <t>2014-09-03</t>
-  </si>
-  <si>
-    <t>2014-11-03</t>
-  </si>
-  <si>
-    <t>2014-11-27</t>
-  </si>
-  <si>
-    <t>2015-03-18</t>
-  </si>
-  <si>
-    <t>2015-08-07</t>
-  </si>
-  <si>
-    <t>2016-03-16</t>
-  </si>
-  <si>
-    <t>2016-03-17</t>
-  </si>
-  <si>
-    <t>2016-02-01</t>
-  </si>
-  <si>
-    <t>2016-02-02</t>
-  </si>
-  <si>
-    <t>2016-07-18</t>
-  </si>
-  <si>
-    <t>2016-06-30</t>
-  </si>
-  <si>
-    <t>2016-08-03</t>
-  </si>
-  <si>
-    <t>2016-07-01</t>
-  </si>
-  <si>
-    <t>2017-02-08</t>
-  </si>
-  <si>
-    <t>2017-06-23</t>
-  </si>
-  <si>
-    <t>2017-03-29</t>
-  </si>
-  <si>
-    <t>2017-11-15</t>
-  </si>
-  <si>
-    <t>2018-03-08</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>2018-04-18</t>
-  </si>
-  <si>
-    <t>2018-04-19</t>
-  </si>
-  <si>
-    <t>2018-04-20</t>
-  </si>
-  <si>
-    <t>2018-04-23</t>
-  </si>
-  <si>
-    <t>2018-05-04</t>
-  </si>
-  <si>
-    <t>2018-05-07</t>
-  </si>
-  <si>
-    <t>2018-05-08</t>
-  </si>
-  <si>
-    <t>2018-04-12</t>
-  </si>
-  <si>
-    <t>2018-11-16</t>
-  </si>
-  <si>
-    <t>2018-11-30</t>
-  </si>
-  <si>
-    <t>2018-12-03</t>
-  </si>
-  <si>
-    <t>2018-12-27</t>
-  </si>
-  <si>
-    <t>2019-01-03</t>
-  </si>
-  <si>
-    <t>2019-02-14</t>
-  </si>
-  <si>
-    <t>2019-02-20</t>
-  </si>
-  <si>
-    <t>2019-09-12</t>
-  </si>
-  <si>
-    <t>2019-09-16</t>
-  </si>
-  <si>
-    <t>2019-09-17</t>
-  </si>
-  <si>
-    <t>2019-09-18</t>
-  </si>
-  <si>
-    <t>2019-09-19</t>
-  </si>
-  <si>
-    <t>2019-09-23</t>
-  </si>
-  <si>
-    <t>2019-10-30</t>
-  </si>
-  <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
-    <t>2019-11-11</t>
-  </si>
-  <si>
-    <t>2019-11-14</t>
-  </si>
-  <si>
-    <t>2019-11-05</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2020-05-29</t>
-  </si>
-  <si>
-    <t>2020-06-03</t>
-  </si>
-  <si>
-    <t>2020-06-04</t>
-  </si>
-  <si>
-    <t>2021-02-17</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>2021-03-23</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>2021-03-29</t>
-  </si>
-  <si>
-    <t>2010-08-03</t>
-  </si>
-  <si>
-    <t>2010-08-19</t>
-  </si>
-  <si>
-    <t>2010-08-26</t>
-  </si>
-  <si>
-    <t>2010-08-27</t>
-  </si>
-  <si>
-    <t>2010-08-30</t>
-  </si>
-  <si>
-    <t>2010-09-17</t>
-  </si>
-  <si>
-    <t>2010-09-20</t>
-  </si>
-  <si>
-    <t>2010-09-21</t>
-  </si>
-  <si>
-    <t>2010-09-23</t>
-  </si>
-  <si>
-    <t>2010-09-24</t>
-  </si>
-  <si>
-    <t>2010-09-27</t>
-  </si>
-  <si>
-    <t>2010-09-28</t>
-  </si>
-  <si>
-    <t>2010-09-29</t>
-  </si>
-  <si>
-    <t>2010-09-30</t>
-  </si>
-  <si>
-    <t>2010-10-01</t>
-  </si>
-  <si>
-    <t>2010-10-04</t>
-  </si>
-  <si>
-    <t>2010-10-05</t>
-  </si>
-  <si>
-    <t>2010-10-06</t>
-  </si>
-  <si>
-    <t>2010-10-07</t>
-  </si>
-  <si>
-    <t>2010-10-08</t>
-  </si>
-  <si>
-    <t>2010-10-11</t>
-  </si>
-  <si>
-    <t>2010-11-24</t>
-  </si>
-  <si>
-    <t>2010-11-25</t>
-  </si>
-  <si>
-    <t>2010-11-26</t>
-  </si>
-  <si>
-    <t>2010-11-29</t>
-  </si>
-  <si>
-    <t>2010-11-30</t>
-  </si>
-  <si>
-    <t>2010-12-01</t>
-  </si>
-  <si>
-    <t>2010-12-02</t>
-  </si>
-  <si>
-    <t>2010-12-03</t>
-  </si>
-  <si>
-    <t>2011-06-24</t>
-  </si>
-  <si>
-    <t>2011-06-27</t>
-  </si>
-  <si>
-    <t>2011-06-30</t>
-  </si>
-  <si>
-    <t>2011-07-07</t>
-  </si>
-  <si>
-    <t>2011-12-02</t>
-  </si>
-  <si>
-    <t>2011-12-05</t>
-  </si>
-  <si>
-    <t>2012-02-24</t>
-  </si>
-  <si>
-    <t>2012-03-02</t>
-  </si>
-  <si>
-    <t>2012-03-06</t>
-  </si>
-  <si>
-    <t>2012-03-07</t>
-  </si>
-  <si>
-    <t>2012-03-12</t>
-  </si>
-  <si>
-    <t>2012-03-13</t>
-  </si>
-  <si>
-    <t>2012-03-29</t>
-  </si>
-  <si>
-    <t>2012-03-30</t>
-  </si>
-  <si>
-    <t>2012-05-03</t>
-  </si>
-  <si>
-    <t>2012-05-15</t>
-  </si>
-  <si>
-    <t>2012-05-16</t>
-  </si>
-  <si>
-    <t>2012-05-17</t>
-  </si>
-  <si>
-    <t>2012-05-18</t>
-  </si>
-  <si>
-    <t>2012-05-21</t>
-  </si>
-  <si>
-    <t>2012-05-22</t>
-  </si>
-  <si>
-    <t>2012-05-23</t>
-  </si>
-  <si>
-    <t>2012-05-24</t>
-  </si>
-  <si>
-    <t>2012-05-28</t>
-  </si>
-  <si>
-    <t>2012-05-29</t>
-  </si>
-  <si>
-    <t>2012-05-30</t>
-  </si>
-  <si>
-    <t>2012-05-31</t>
-  </si>
-  <si>
-    <t>2012-06-01</t>
-  </si>
-  <si>
-    <t>2012-06-04</t>
-  </si>
-  <si>
-    <t>2012-06-05</t>
-  </si>
-  <si>
-    <t>2012-06-06</t>
-  </si>
-  <si>
-    <t>2012-06-07</t>
-  </si>
-  <si>
-    <t>2012-06-08</t>
-  </si>
-  <si>
-    <t>2012-06-11</t>
-  </si>
-  <si>
-    <t>2012-06-12</t>
-  </si>
-  <si>
-    <t>2012-06-13</t>
-  </si>
-  <si>
-    <t>2012-06-14</t>
-  </si>
-  <si>
-    <t>2012-06-15</t>
-  </si>
-  <si>
-    <t>2012-06-19</t>
-  </si>
-  <si>
-    <t>2012-06-20</t>
-  </si>
-  <si>
-    <t>2012-06-22</t>
-  </si>
-  <si>
-    <t>2012-10-18</t>
-  </si>
-  <si>
-    <t>2012-10-19</t>
-  </si>
-  <si>
-    <t>2012-10-22</t>
-  </si>
-  <si>
-    <t>2013-04-08</t>
-  </si>
-  <si>
-    <t>2013-04-12</t>
-  </si>
-  <si>
-    <t>2013-06-25</t>
-  </si>
-  <si>
-    <t>2013-06-27</t>
-  </si>
-  <si>
-    <t>2013-06-28</t>
-  </si>
-  <si>
-    <t>2013-07-01</t>
-  </si>
-  <si>
-    <t>2013-07-02</t>
-  </si>
-  <si>
-    <t>2013-07-03</t>
-  </si>
-  <si>
-    <t>2013-07-04</t>
-  </si>
-  <si>
-    <t>2013-10-28</t>
-  </si>
-  <si>
-    <t>2014-01-22</t>
-  </si>
-  <si>
-    <t>2014-01-23</t>
-  </si>
-  <si>
-    <t>2014-01-24</t>
-  </si>
-  <si>
-    <t>2014-01-27</t>
-  </si>
-  <si>
-    <t>2014-02-06</t>
-  </si>
-  <si>
-    <t>2014-02-07</t>
-  </si>
-  <si>
-    <t>2014-02-10</t>
-  </si>
-  <si>
-    <t>2014-02-11</t>
-  </si>
-  <si>
-    <t>2014-02-18</t>
-  </si>
-  <si>
-    <t>2014-02-20</t>
-  </si>
-  <si>
-    <t>2014-02-21</t>
-  </si>
-  <si>
-    <t>2014-07-08</t>
-  </si>
-  <si>
-    <t>2014-07-10</t>
-  </si>
-  <si>
-    <t>2014-07-11</t>
-  </si>
-  <si>
-    <t>2014-07-16</t>
-  </si>
-  <si>
-    <t>2014-07-17</t>
-  </si>
-  <si>
-    <t>2014-07-18</t>
-  </si>
-  <si>
-    <t>2014-10-15</t>
-  </si>
-  <si>
-    <t>2014-11-04</t>
-  </si>
-  <si>
-    <t>2015-06-11</t>
-  </si>
-  <si>
-    <t>2015-06-12</t>
-  </si>
-  <si>
-    <t>2015-06-15</t>
-  </si>
-  <si>
-    <t>2015-07-22</t>
-  </si>
-  <si>
-    <t>2015-07-23</t>
-  </si>
-  <si>
-    <t>2015-10-15</t>
-  </si>
-  <si>
-    <t>2015-10-16</t>
-  </si>
-  <si>
-    <t>2015-11-19</t>
-  </si>
-  <si>
-    <t>2016-04-01</t>
-  </si>
-  <si>
-    <t>2016-04-07</t>
-  </si>
-  <si>
-    <t>2016-04-08</t>
-  </si>
-  <si>
-    <t>2016-04-15</t>
-  </si>
-  <si>
-    <t>2016-04-18</t>
-  </si>
-  <si>
-    <t>2016-04-19</t>
-  </si>
-  <si>
-    <t>2016-04-21</t>
-  </si>
-  <si>
-    <t>2016-04-22</t>
-  </si>
-  <si>
-    <t>2016-04-27</t>
-  </si>
-  <si>
-    <t>2016-04-28</t>
-  </si>
-  <si>
-    <t>2016-05-03</t>
-  </si>
-  <si>
-    <t>2016-05-05</t>
-  </si>
-  <si>
-    <t>2016-05-10</t>
-  </si>
-  <si>
-    <t>2016-05-11</t>
-  </si>
-  <si>
-    <t>2016-05-12</t>
-  </si>
-  <si>
-    <t>2016-05-13</t>
-  </si>
-  <si>
-    <t>2016-05-16</t>
-  </si>
-  <si>
-    <t>2016-05-17</t>
-  </si>
-  <si>
-    <t>2016-10-27</t>
-  </si>
-  <si>
-    <t>2016-12-15</t>
-  </si>
-  <si>
-    <t>2017-06-26</t>
-  </si>
-  <si>
-    <t>2017-06-27</t>
-  </si>
-  <si>
-    <t>2017-07-11</t>
-  </si>
-  <si>
-    <t>2017-07-12</t>
-  </si>
-  <si>
-    <t>2017-07-13</t>
-  </si>
-  <si>
-    <t>2017-07-14</t>
-  </si>
-  <si>
-    <t>2017-07-17</t>
-  </si>
-  <si>
-    <t>2017-08-21</t>
-  </si>
-  <si>
-    <t>2017-08-22</t>
-  </si>
-  <si>
-    <t>2017-08-23</t>
-  </si>
-  <si>
-    <t>2017-08-24</t>
-  </si>
-  <si>
-    <t>2017-08-25</t>
-  </si>
-  <si>
-    <t>2017-09-06</t>
-  </si>
-  <si>
-    <t>2017-09-07</t>
-  </si>
-  <si>
-    <t>2017-09-08</t>
-  </si>
-  <si>
-    <t>2018-01-12</t>
-  </si>
-  <si>
-    <t>2018-01-15</t>
-  </si>
-  <si>
-    <t>2018-01-16</t>
-  </si>
-  <si>
-    <t>2018-01-17</t>
-  </si>
-  <si>
-    <t>2018-01-30</t>
-  </si>
-  <si>
-    <t>2018-01-31</t>
-  </si>
-  <si>
-    <t>2018-02-06</t>
-  </si>
-  <si>
-    <t>2018-02-22</t>
-  </si>
-  <si>
-    <t>2018-03-30</t>
-  </si>
-  <si>
-    <t>2018-05-16</t>
-  </si>
-  <si>
-    <t>2018-05-21</t>
-  </si>
-  <si>
-    <t>2018-11-20</t>
-  </si>
-  <si>
-    <t>2018-12-28</t>
-  </si>
-  <si>
-    <t>2019-01-09</t>
-  </si>
-  <si>
-    <t>2019-01-10</t>
-  </si>
-  <si>
-    <t>2019-01-15</t>
-  </si>
-  <si>
-    <t>2019-01-16</t>
-  </si>
-  <si>
-    <t>2019-01-17</t>
-  </si>
-  <si>
-    <t>2019-01-18</t>
-  </si>
-  <si>
-    <t>2019-01-22</t>
-  </si>
-  <si>
-    <t>2019-01-23</t>
-  </si>
-  <si>
-    <t>2019-01-24</t>
-  </si>
-  <si>
-    <t>2019-01-25</t>
-  </si>
-  <si>
-    <t>2019-01-29</t>
-  </si>
-  <si>
-    <t>2019-03-11</t>
-  </si>
-  <si>
-    <t>2019-03-12</t>
-  </si>
-  <si>
-    <t>2019-03-13</t>
-  </si>
-  <si>
-    <t>2019-04-09</t>
-  </si>
-  <si>
-    <t>2019-04-10</t>
-  </si>
-  <si>
-    <t>2019-04-18</t>
-  </si>
-  <si>
-    <t>2019-04-19</t>
-  </si>
-  <si>
-    <t>2019-04-25</t>
-  </si>
-  <si>
-    <t>2019-04-26</t>
-  </si>
-  <si>
-    <t>2019-05-02</t>
-  </si>
-  <si>
-    <t>2019-05-07</t>
-  </si>
-  <si>
-    <t>2019-05-08</t>
-  </si>
-  <si>
-    <t>2019-05-09</t>
-  </si>
-  <si>
-    <t>2019-05-10</t>
-  </si>
-  <si>
-    <t>2019-05-13</t>
-  </si>
-  <si>
-    <t>2019-07-29</t>
-  </si>
-  <si>
-    <t>2019-08-29</t>
-  </si>
-  <si>
-    <t>2019-08-30</t>
-  </si>
-  <si>
-    <t>2019-09-02</t>
-  </si>
-  <si>
-    <t>2019-09-03</t>
-  </si>
-  <si>
-    <t>2019-09-04</t>
-  </si>
-  <si>
-    <t>2019-09-05</t>
-  </si>
-  <si>
-    <t>2019-09-06</t>
-  </si>
-  <si>
-    <t>2019-09-10</t>
-  </si>
-  <si>
-    <t>2020-02-20</t>
-  </si>
-  <si>
-    <t>2020-02-21</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-02-26</t>
-  </si>
-  <si>
-    <t>2020-02-27</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-03-04</t>
-  </si>
-  <si>
-    <t>2020-03-05</t>
-  </si>
-  <si>
-    <t>2020-03-06</t>
-  </si>
-  <si>
-    <t>2020-03-09</t>
-  </si>
-  <si>
-    <t>2020-03-12</t>
-  </si>
-  <si>
-    <t>2020-11-02</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-23</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>2020-12-28</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-05</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
   </si>
   <si>
     <t>2021-01-20</t>
@@ -1790,7 +1778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P382"/>
+  <dimension ref="A1:P378"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1851,7 +1839,7 @@
         <v>39.24967816269653</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E2">
         <v>47.58658728904034</v>
@@ -1887,7 +1875,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1901,7 +1889,7 @@
         <v>41.7045814878046</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E3">
         <v>51.36624085194781</v>
@@ -1937,7 +1925,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1951,7 +1939,7 @@
         <v>47.73273319613877</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E4">
         <v>59.43490802303255</v>
@@ -1987,7 +1975,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2001,7 +1989,7 @@
         <v>47.24820828667414</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5">
         <v>58.87563172501095</v>
@@ -2037,7 +2025,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2051,7 +2039,7 @@
         <v>47.16470096247878</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E6">
         <v>58.77924108291729</v>
@@ -2087,7 +2075,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2101,7 +2089,7 @@
         <v>-15.1664654510749</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E7">
         <v>-7.294892481790129</v>
@@ -2137,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2151,7 +2139,7 @@
         <v>-14.45834344229912</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E8">
         <v>-7.294892481790129</v>
@@ -2187,7 +2175,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2201,7 +2189,7 @@
         <v>-13.39336737209288</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E9">
         <v>-7.294892481790129</v>
@@ -2237,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2251,7 +2239,7 @@
         <v>-16.33245230627455</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E10">
         <v>-7.294892481790129</v>
@@ -2287,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2301,7 +2289,7 @@
         <v>-29.63643996743208</v>
       </c>
       <c r="D11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E11">
         <v>-21.37792699357366</v>
@@ -2337,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2351,7 +2339,7 @@
         <v>-29.01030081710592</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E12">
         <v>-21.37792699357366</v>
@@ -2387,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2401,7 +2389,7 @@
         <v>-28.60118761449661</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E13">
         <v>-21.37792699357366</v>
@@ -2437,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2451,7 +2439,7 @@
         <v>-49.08464630848418</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E14">
         <v>-42.77667080227592</v>
@@ -2487,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2501,7 +2489,7 @@
         <v>-48.56869529606767</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E15">
         <v>-42.77667080227592</v>
@@ -2537,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2551,7 +2539,7 @@
         <v>-49.0410871967355</v>
       </c>
       <c r="D16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E16">
         <v>-42.77667080227592</v>
@@ -2587,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2601,7 +2589,7 @@
         <v>-65.70804604683664</v>
       </c>
       <c r="D17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E17">
         <v>-56.94115587886895</v>
@@ -2637,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2651,7 +2639,7 @@
         <v>-65.6116252316011</v>
       </c>
       <c r="D18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E18">
         <v>-56.94115587886895</v>
@@ -2687,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2701,7 +2689,7 @@
         <v>-79.57406496333017</v>
       </c>
       <c r="D19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E19">
         <v>-67.54165070713992</v>
@@ -2737,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2751,7 +2739,7 @@
         <v>-113.1125372679468</v>
       </c>
       <c r="D20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E20">
         <v>-103.9345101187686</v>
@@ -2787,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2801,7 +2789,7 @@
         <v>-150.4700278614179</v>
       </c>
       <c r="D21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E21">
         <v>-141.3269680910878</v>
@@ -2837,7 +2825,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2851,7 +2839,7 @@
         <v>-191.2456393652701</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E22">
         <v>-165.2314426418361</v>
@@ -2887,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2901,7 +2889,7 @@
         <v>-208.9753900042601</v>
       </c>
       <c r="D23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E23">
         <v>-181.8698454183375</v>
@@ -2937,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2951,7 +2939,7 @@
         <v>-222.2487414251906</v>
       </c>
       <c r="D24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E24">
         <v>-206.4607237347662</v>
@@ -2987,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3001,7 +2989,7 @@
         <v>-239.7112109310854</v>
       </c>
       <c r="D25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E25">
         <v>-219.5184020745525</v>
@@ -3037,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3051,7 +3039,7 @@
         <v>-263.1154559964206</v>
       </c>
       <c r="D26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E26">
         <v>-240.6747187530921</v>
@@ -3087,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3101,7 +3089,7 @@
         <v>-268.6224791106823</v>
       </c>
       <c r="D27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E27">
         <v>-252.6279978948062</v>
@@ -3137,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3166,7 +3154,7 @@
         <v>59.3</v>
       </c>
       <c r="P28" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3195,7 +3183,7 @@
         <v>65.5</v>
       </c>
       <c r="P29" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3209,7 +3197,7 @@
         <v>-254.0793405031437</v>
       </c>
       <c r="D30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E30">
         <v>-235.7082244929039</v>
@@ -3245,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3259,7 +3247,7 @@
         <v>-238.7059320352077</v>
       </c>
       <c r="D31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E31">
         <v>-223.7765478327873</v>
@@ -3295,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3324,7 +3312,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="P32" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3374,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3388,7 +3376,7 @@
         <v>-85.8076603763717</v>
       </c>
       <c r="D34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E34">
         <v>-85.31060902491748</v>
@@ -3424,7 +3412,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3438,7 +3426,7 @@
         <v>-78.41701518144652</v>
       </c>
       <c r="D35" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E35">
         <v>-77.28396586589429</v>
@@ -3474,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3503,7 +3491,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="P36" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3532,7 +3520,7 @@
         <v>70.09999999999999</v>
       </c>
       <c r="P37" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3546,7 +3534,7 @@
         <v>-77.43890142953504</v>
       </c>
       <c r="D38" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E38">
         <v>-86.03210595388953</v>
@@ -3582,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3596,7 +3584,7 @@
         <v>-75.24842836769179</v>
       </c>
       <c r="D39" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E39">
         <v>-82.41442691778926</v>
@@ -3632,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3646,7 +3634,7 @@
         <v>-75.26941837884658</v>
       </c>
       <c r="D40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E40">
         <v>-76.41687497573176</v>
@@ -3682,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3696,7 +3684,7 @@
         <v>2.405986219478436</v>
       </c>
       <c r="D41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E41">
         <v>22.3137495724129</v>
@@ -3732,7 +3720,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3746,7 +3734,7 @@
         <v>-1.953147134466214</v>
       </c>
       <c r="D42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E42">
         <v>19.32012787151115</v>
@@ -3782,7 +3770,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3796,7 +3784,7 @@
         <v>-16.2502130791469</v>
       </c>
       <c r="D43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E43">
         <v>8.401660897453333</v>
@@ -3832,7 +3820,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3846,7 +3834,7 @@
         <v>-14.74859467309044</v>
       </c>
       <c r="D44" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E44">
         <v>8.401660897453333</v>
@@ -3882,7 +3870,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3896,7 +3884,7 @@
         <v>-29.86968571903745</v>
       </c>
       <c r="D45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E45">
         <v>-0.9514709154835543</v>
@@ -3932,7 +3920,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3946,7 +3934,7 @@
         <v>60.63454015125168</v>
       </c>
       <c r="D46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E46">
         <v>75.91925407409063</v>
@@ -3982,7 +3970,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3996,7 +3984,7 @@
         <v>61.36441721922468</v>
       </c>
       <c r="D47" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E47">
         <v>75.91925407409063</v>
@@ -4032,7 +4020,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4046,7 +4034,7 @@
         <v>89.12505313226613</v>
       </c>
       <c r="D48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E48">
         <v>73.92461224371841</v>
@@ -4082,7 +4070,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4096,7 +4084,7 @@
         <v>60.18080332327113</v>
       </c>
       <c r="D49" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E49">
         <v>75.16419394721952</v>
@@ -4132,7 +4120,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4146,7 +4134,7 @@
         <v>60.90367287266527</v>
       </c>
       <c r="D50" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E50">
         <v>75.16419394721952</v>
@@ -4182,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4196,7 +4184,7 @@
         <v>88.41554187615753</v>
       </c>
       <c r="D51" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E51">
         <v>73.33247692380556</v>
@@ -4232,7 +4220,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4246,7 +4234,7 @@
         <v>39.99810912339372</v>
       </c>
       <c r="D52" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E52">
         <v>55.15583755182445</v>
@@ -4282,7 +4270,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4296,7 +4284,7 @@
         <v>41.30719414984996</v>
       </c>
       <c r="D53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E53">
         <v>55.15583755182445</v>
@@ -4332,7 +4320,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4346,7 +4334,7 @@
         <v>43.08151977105167</v>
       </c>
       <c r="D54" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E54">
         <v>55.9485635535138</v>
@@ -4382,7 +4370,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4396,7 +4384,7 @@
         <v>42.16532004667869</v>
       </c>
       <c r="D55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E55">
         <v>55.9485635535138</v>
@@ -4432,7 +4420,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4446,7 +4434,7 @@
         <v>42.55008107334416</v>
       </c>
       <c r="D56" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E56">
         <v>56.30400099154195</v>
@@ -4496,7 +4484,7 @@
         <v>43.58368103616133</v>
       </c>
       <c r="D57" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E57">
         <v>56.30400099154195</v>
@@ -4546,7 +4534,7 @@
         <v>44.27504780738504</v>
       </c>
       <c r="D58" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E58">
         <v>56.96559598792828</v>
@@ -4582,7 +4570,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4596,7 +4584,7 @@
         <v>44.76828997217422</v>
       </c>
       <c r="D59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E59">
         <v>57.43759805949687</v>
@@ -4646,7 +4634,7 @@
         <v>46.95250922066406</v>
       </c>
       <c r="D60" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E60">
         <v>58.6275946856681</v>
@@ -4682,7 +4670,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4696,7 +4684,7 @@
         <v>47.37813227189867</v>
       </c>
       <c r="D61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E61">
         <v>59.01897220404476</v>
@@ -4732,7 +4720,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4746,7 +4734,7 @@
         <v>48.93720072957618</v>
       </c>
       <c r="D62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E62">
         <v>59.68207127489522</v>
@@ -4782,7 +4770,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4796,7 +4784,7 @@
         <v>48.94662890110423</v>
       </c>
       <c r="D63" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E63">
         <v>59.69094484809811</v>
@@ -4832,7 +4820,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4846,7 +4834,7 @@
         <v>54.08932335660573</v>
       </c>
       <c r="D64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E64">
         <v>62.52278850035134</v>
@@ -4896,7 +4884,7 @@
         <v>67.18932335660573</v>
       </c>
       <c r="D65" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E65">
         <v>59.01736085156006</v>
@@ -4946,7 +4934,7 @@
         <v>54.27142458878302</v>
       </c>
       <c r="D66" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E66">
         <v>62.70264156916842</v>
@@ -4982,7 +4970,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4996,7 +4984,7 @@
         <v>67.37142458878301</v>
       </c>
       <c r="D67" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E67">
         <v>59.17608118479113</v>
@@ -5032,7 +5020,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5046,7 +5034,7 @@
         <v>54.44666418857609</v>
       </c>
       <c r="D68" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E68">
         <v>57.92296041603655</v>
@@ -5082,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="P68" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5096,7 +5084,7 @@
         <v>54.38623819452964</v>
       </c>
       <c r="D69" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E69">
         <v>62.81603772299223</v>
@@ -5132,7 +5120,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5146,7 +5134,7 @@
         <v>54.68320045790918</v>
       </c>
       <c r="D70" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E70">
         <v>62.81603772299223</v>
@@ -5182,7 +5170,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5196,7 +5184,7 @@
         <v>67.48623819452963</v>
       </c>
       <c r="D71" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E71">
         <v>59.27615329054065</v>
@@ -5232,7 +5220,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5246,7 +5234,7 @@
         <v>54.5181037654851</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E72">
         <v>55.68274527440479</v>
@@ -5282,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="P72" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5296,7 +5284,7 @@
         <v>101.1269386779503</v>
       </c>
       <c r="D73" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E73">
         <v>83.94100067443752</v>
@@ -5332,7 +5320,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5346,7 +5334,7 @@
         <v>75.45009517739128</v>
       </c>
       <c r="D74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E74">
         <v>80.27451240300203</v>
@@ -5382,7 +5370,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5396,7 +5384,7 @@
         <v>121.9136696617972</v>
       </c>
       <c r="D75" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E75">
         <v>104.5517569407011</v>
@@ -5432,7 +5420,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5446,7 +5434,7 @@
         <v>124.0730248787269</v>
       </c>
       <c r="D76" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E76">
         <v>106.3319083146578</v>
@@ -5482,7 +5470,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5496,7 +5484,7 @@
         <v>125.8987716223492</v>
       </c>
       <c r="D77" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E77">
         <v>107.8370361179367</v>
@@ -5532,7 +5520,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5546,7 +5534,7 @@
         <v>127.8315078706938</v>
       </c>
       <c r="D78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E78">
         <v>102.3788447068554</v>
@@ -5582,7 +5570,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5596,7 +5584,7 @@
         <v>127.8608026942557</v>
       </c>
       <c r="D79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E79">
         <v>102.3788447068554</v>
@@ -5632,7 +5620,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5646,7 +5634,7 @@
         <v>126.3344628429377</v>
       </c>
       <c r="D80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E80">
         <v>101.3477167540643</v>
@@ -5682,7 +5670,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5696,7 +5684,7 @@
         <v>126.3293867347399</v>
       </c>
       <c r="D81" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E81">
         <v>101.3477167540643</v>
@@ -5732,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5746,7 +5734,7 @@
         <v>126.0311094090764</v>
       </c>
       <c r="D82" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E82">
         <v>101.1387743378843</v>
@@ -5782,7 +5770,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5796,7 +5784,7 @@
         <v>126.0190685536726</v>
       </c>
       <c r="D83" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E83">
         <v>101.1387743378843</v>
@@ -5832,7 +5820,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5846,7 +5834,7 @@
         <v>126.620958855311</v>
       </c>
       <c r="D84" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E84">
         <v>101.5450481911581</v>
@@ -5882,7 +5870,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5896,7 +5884,7 @@
         <v>126.6224604616829</v>
       </c>
       <c r="D85" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E85">
         <v>101.5450481911581</v>
@@ -5932,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5946,7 +5934,7 @@
         <v>125.7796367080902</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E86">
         <v>100.9655660999601</v>
@@ -5982,7 +5970,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5996,7 +5984,7 @@
         <v>125.7618222447556</v>
       </c>
       <c r="D87" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E87">
         <v>100.9655660999601</v>
@@ -6032,7 +6020,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6046,7 +6034,7 @@
         <v>125.0669218669525</v>
       </c>
       <c r="D88" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E88">
         <v>100.4746655716255</v>
@@ -6082,7 +6070,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6096,7 +6084,7 @@
         <v>125.0327440526733</v>
       </c>
       <c r="D89" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E89">
         <v>100.4746655716255</v>
@@ -6132,7 +6120,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6146,7 +6134,7 @@
         <v>123.2289469739378</v>
       </c>
       <c r="D90" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E90">
         <v>99.20871347694691</v>
@@ -6182,7 +6170,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6196,7 +6184,7 @@
         <v>123.1525707565027</v>
       </c>
       <c r="D91" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E91">
         <v>99.20871347694691</v>
@@ -6232,7 +6220,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6246,7 +6234,7 @@
         <v>122.9583501275863</v>
       </c>
       <c r="D92" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E92">
         <v>99.02233299604161</v>
@@ -6282,7 +6270,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6296,7 +6284,7 @@
         <v>122.8757612274544</v>
       </c>
       <c r="D93" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E93">
         <v>99.02233299604161</v>
@@ -6332,7 +6320,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6346,7 +6334,7 @@
         <v>124.3519741722009</v>
       </c>
       <c r="D94" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E94">
         <v>99.98222710840369</v>
@@ -6382,7 +6370,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6396,7 +6384,7 @@
         <v>124.3013817424811</v>
       </c>
       <c r="D95" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E95">
         <v>99.98222710840369</v>
@@ -6432,7 +6420,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6446,7 +6434,7 @@
         <v>124.6891745905705</v>
       </c>
       <c r="D96" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E96">
         <v>100.2144824986073</v>
@@ -6482,7 +6470,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6496,7 +6484,7 @@
         <v>124.6463240071908</v>
       </c>
       <c r="D97" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E97">
         <v>100.2144824986073</v>
@@ -6532,7 +6520,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6546,7 +6534,7 @@
         <v>124.4800191586875</v>
       </c>
       <c r="D98" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E98">
         <v>100.0704213593001</v>
@@ -6582,7 +6570,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6596,7 +6584,7 @@
         <v>124.4323665373309</v>
       </c>
       <c r="D99" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E99">
         <v>100.0704213593001</v>
@@ -6632,7 +6620,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6646,7 +6634,7 @@
         <v>123.0108457893896</v>
       </c>
       <c r="D100" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E100">
         <v>99.05849072228368</v>
@@ -6682,7 +6670,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6696,7 +6684,7 @@
         <v>122.9294621467991</v>
       </c>
       <c r="D101" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E101">
         <v>99.05849072228368</v>
@@ -6732,7 +6720,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6746,7 +6734,7 @@
         <v>121.6453568496303</v>
       </c>
       <c r="D102" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E102">
         <v>98.11797538112289</v>
@@ -6782,7 +6770,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6796,7 +6784,7 @@
         <v>121.5326226956677</v>
       </c>
       <c r="D103" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E103">
         <v>98.11797538112289</v>
@@ -6832,7 +6820,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6846,7 +6834,7 @@
         <v>121.0299428079651</v>
       </c>
       <c r="D104" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E104">
         <v>97.69409326058823</v>
@@ -6882,7 +6870,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6896,7 +6884,7 @@
         <v>120.9030792499847</v>
       </c>
       <c r="D105" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E105">
         <v>97.69409326058823</v>
@@ -6932,7 +6920,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6946,7 +6934,7 @@
         <v>120.2680139970007</v>
       </c>
       <c r="D106" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E106">
         <v>97.169295355077</v>
@@ -6982,7 +6970,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6996,7 +6984,7 @@
         <v>120.1236571755032</v>
       </c>
       <c r="D107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E107">
         <v>97.169295355077</v>
@@ -7032,7 +7020,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7046,7 +7034,7 @@
         <v>119.3894537106139</v>
       </c>
       <c r="D108" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E108">
         <v>96.56416454557592</v>
@@ -7082,7 +7070,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7096,7 +7084,7 @@
         <v>119.2249258621331</v>
       </c>
       <c r="D109" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E109">
         <v>96.56416454557592</v>
@@ -7132,7 +7120,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7146,7 +7134,7 @@
         <v>118.0996069245826</v>
       </c>
       <c r="D110" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E110">
         <v>95.67574966744206</v>
@@ -7182,7 +7170,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7196,7 +7184,7 @@
         <v>117.9054652468306</v>
       </c>
       <c r="D111" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E111">
         <v>95.67574966744206</v>
@@ -7232,7 +7220,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7246,7 +7234,7 @@
         <v>117.1017444652623</v>
       </c>
       <c r="D112" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E112">
         <v>94.98844644291023</v>
@@ -7282,7 +7270,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7296,7 +7284,7 @@
         <v>116.8846926800259</v>
       </c>
       <c r="D113" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E113">
         <v>94.98844644291023</v>
@@ -7332,7 +7320,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7346,7 +7334,7 @@
         <v>115.7903395541055</v>
       </c>
       <c r="D114" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E114">
         <v>94.08518285614407</v>
@@ -7382,7 +7370,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7396,7 +7384,7 @@
         <v>115.5431789826436</v>
       </c>
       <c r="D115" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E115">
         <v>94.08518285614407</v>
@@ -7432,7 +7420,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7446,7 +7434,7 @@
         <v>114.3600161010092</v>
       </c>
       <c r="D116" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E116">
         <v>93.10001108998082</v>
@@ -7482,7 +7470,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7496,7 +7484,7 @@
         <v>114.0800164706752</v>
       </c>
       <c r="D117" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E117">
         <v>93.10001108998082</v>
@@ -7532,7 +7520,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7546,7 +7534,7 @@
         <v>112.9215721869154</v>
       </c>
       <c r="D118" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E118">
         <v>92.10924614915092</v>
@@ -7582,7 +7570,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7596,7 +7584,7 @@
         <v>112.6085470585538</v>
       </c>
       <c r="D119" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E119">
         <v>92.10924614915092</v>
@@ -7632,7 +7620,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7646,7 +7634,7 @@
         <v>111.0753114680939</v>
       </c>
       <c r="D120" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E120">
         <v>91.07689300844227</v>
@@ -7696,7 +7684,7 @@
         <v>109.3637030177276</v>
       </c>
       <c r="D121" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E121">
         <v>89.92443844086398</v>
@@ -7732,7 +7720,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7746,7 +7734,7 @@
         <v>106.6367917601738</v>
       </c>
       <c r="D122" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E122">
         <v>88.08836352929409</v>
@@ -7782,7 +7770,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7796,7 +7784,7 @@
         <v>99.96873044828921</v>
       </c>
       <c r="D123" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E123">
         <v>83.59864643650396</v>
@@ -7832,7 +7820,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7846,7 +7834,7 @@
         <v>39.91051382546476</v>
       </c>
       <c r="D124" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E124">
         <v>42.55014562583152</v>
@@ -7882,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7896,7 +7884,7 @@
         <v>34.76754143004694</v>
       </c>
       <c r="D125" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E125">
         <v>38.11145388461416</v>
@@ -7932,7 +7920,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7946,7 +7934,7 @@
         <v>27.87373902743889</v>
       </c>
       <c r="D126" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E126">
         <v>28.73232502982488</v>
@@ -7982,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7996,7 +7984,7 @@
         <v>52.34452590842368</v>
       </c>
       <c r="D127" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E127">
         <v>60.02089394070224</v>
@@ -8032,7 +8020,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8046,7 +8034,7 @@
         <v>66.2681578761451</v>
       </c>
       <c r="D128" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E128">
         <v>59.00746128062423</v>
@@ -8082,7 +8070,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8096,7 +8084,7 @@
         <v>65.90298372726488</v>
       </c>
       <c r="D129" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E129">
         <v>59.00746128062423</v>
@@ -8132,7 +8120,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8146,7 +8134,7 @@
         <v>75.19054270184851</v>
       </c>
       <c r="D130" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E130">
         <v>82.88620847856147</v>
@@ -8182,7 +8170,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8196,7 +8184,7 @@
         <v>91.01410438583636</v>
       </c>
       <c r="D131" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E131">
         <v>85.34034548895417</v>
@@ -8232,7 +8220,7 @@
         <v>0</v>
       </c>
       <c r="P131" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8246,7 +8234,7 @@
         <v>90.69117289103272</v>
       </c>
       <c r="D132" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E132">
         <v>85.34034548895417</v>
@@ -8282,7 +8270,7 @@
         <v>0</v>
       </c>
       <c r="P132" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8296,7 +8284,7 @@
         <v>106.425283452306</v>
       </c>
       <c r="D133" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E133">
         <v>102.4841645631825</v>
@@ -8346,7 +8334,7 @@
         <v>106.7743510447031</v>
       </c>
       <c r="D134" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E134">
         <v>102.4841645631825</v>
@@ -8396,7 +8384,7 @@
         <v>64.83381773702186</v>
       </c>
       <c r="D135" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E135">
         <v>61.17785949472258</v>
@@ -8432,7 +8420,7 @@
         <v>0</v>
       </c>
       <c r="P135" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8446,7 +8434,7 @@
         <v>53.81062761975522</v>
       </c>
       <c r="D136" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E136">
         <v>45.81713512679965</v>
@@ -8482,7 +8470,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8496,7 +8484,7 @@
         <v>53.43128846396477</v>
       </c>
       <c r="D137" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E137">
         <v>47.7894228477703</v>
@@ -8532,7 +8520,7 @@
         <v>0</v>
       </c>
       <c r="P137" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8546,7 +8534,7 @@
         <v>48.70129852147022</v>
       </c>
       <c r="D138" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E138">
         <v>39.19252273181839</v>
@@ -8582,7 +8570,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8596,7 +8584,7 @@
         <v>44.87334693499027</v>
       </c>
       <c r="D139" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E139">
         <v>34.44403390958535</v>
@@ -8632,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8646,7 +8634,7 @@
         <v>40.45906823400685</v>
       </c>
       <c r="D140" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E140">
         <v>29.40254968722779</v>
@@ -8682,7 +8670,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8696,7 +8684,7 @@
         <v>37.79538016242914</v>
       </c>
       <c r="D141" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E141">
         <v>25.15160114518396</v>
@@ -8732,7 +8720,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8746,7 +8734,7 @@
         <v>37.68076952930594</v>
       </c>
       <c r="D142" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E142">
         <v>25.01802919408082</v>
@@ -8782,7 +8770,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8796,7 +8784,7 @@
         <v>63.15408222226404</v>
       </c>
       <c r="D143" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E143">
         <v>53.56243089690908</v>
@@ -8832,7 +8820,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8846,7 +8834,7 @@
         <v>31.1030054990203</v>
       </c>
       <c r="D144" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E144">
         <v>14.08734435244297</v>
@@ -8882,7 +8870,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8896,7 +8884,7 @@
         <v>25.05484991241799</v>
       </c>
       <c r="D145" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E145">
         <v>6.922187058405115</v>
@@ -8932,7 +8920,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8946,7 +8934,7 @@
         <v>18.81638310475921</v>
       </c>
       <c r="D146" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E146">
         <v>-0.4684290245420044</v>
@@ -8982,7 +8970,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8996,7 +8984,7 @@
         <v>13.01676813424353</v>
       </c>
       <c r="D147" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E147">
         <v>-7.339144057179965</v>
@@ -9032,7 +9020,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9046,7 +9034,7 @@
         <v>8.024396355482963</v>
       </c>
       <c r="D148" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E148">
         <v>-13.25353044372964</v>
@@ -9082,7 +9070,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9096,7 +9084,7 @@
         <v>7.720504878426524</v>
       </c>
       <c r="D149" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E149">
         <v>-13.61354602240461</v>
@@ -9132,7 +9120,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9146,7 +9134,7 @@
         <v>10.31388326476601</v>
       </c>
       <c r="D150" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E150">
         <v>-10.54121036651594</v>
@@ -9182,7 +9170,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9196,7 +9184,7 @@
         <v>11.14758883248732</v>
       </c>
       <c r="D151" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E151">
         <v>-9.553532148900146</v>
@@ -9232,7 +9220,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9246,7 +9234,7 @@
         <v>20.84560393192861</v>
       </c>
       <c r="D152" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E152">
         <v>1.935557811248756</v>
@@ -9282,7 +9270,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9296,7 +9284,7 @@
         <v>21.43389351871438</v>
       </c>
       <c r="D153" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E153">
         <v>2.632495474873352</v>
@@ -9332,7 +9320,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9346,7 +9334,7 @@
         <v>22.6162561113628</v>
       </c>
       <c r="D154" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E154">
         <v>4.033222330128012</v>
@@ -9382,7 +9370,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9396,7 +9384,7 @@
         <v>23.86897930913528</v>
       </c>
       <c r="D155" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E155">
         <v>5.517304316678292</v>
@@ -9432,7 +9420,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9446,7 +9434,7 @@
         <v>24.29022509961407</v>
       </c>
       <c r="D156" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E156">
         <v>6.016347753146405</v>
@@ -9482,7 +9470,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9496,7 +9484,7 @@
         <v>80.77258742920839</v>
       </c>
       <c r="D157" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E157">
         <v>71.50140757768273</v>
@@ -9532,7 +9520,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9546,7 +9534,7 @@
         <v>80.87119828430862</v>
       </c>
       <c r="D158" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E158">
         <v>71.50140757768273</v>
@@ -9582,7 +9570,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9596,7 +9584,7 @@
         <v>82.15331534782203</v>
       </c>
       <c r="D159" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E159">
         <v>71.50140757768273</v>
@@ -9632,7 +9620,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9646,7 +9634,7 @@
         <v>76.19581669669289</v>
       </c>
       <c r="D160" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E160">
         <v>66.74547500154564</v>
@@ -9682,7 +9670,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9696,7 +9684,7 @@
         <v>75.21863715900577</v>
       </c>
       <c r="D161" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E161">
         <v>66.74547500154564</v>
@@ -9732,7 +9720,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9746,7 +9734,7 @@
         <v>77.89414970172665</v>
       </c>
       <c r="D162" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E162">
         <v>66.74547500154564</v>
@@ -9782,7 +9770,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9796,7 +9784,7 @@
         <v>60.11863715900578</v>
       </c>
       <c r="D163" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E163">
         <v>68.03744024109169</v>
@@ -9832,7 +9820,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9846,7 +9834,7 @@
         <v>72.44565132750211</v>
       </c>
       <c r="D164" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E164">
         <v>62.8485060058029</v>
@@ -9882,7 +9870,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9896,7 +9884,7 @@
         <v>71.50850914251097</v>
       </c>
       <c r="D165" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E165">
         <v>62.8485060058029</v>
@@ -9932,7 +9920,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9946,7 +9934,7 @@
         <v>74.40422712505978</v>
       </c>
       <c r="D166" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E166">
         <v>62.8485060058029</v>
@@ -9982,7 +9970,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9996,7 +9984,7 @@
         <v>56.40850914251097</v>
       </c>
       <c r="D167" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E167">
         <v>64.59422790923679</v>
@@ -10032,7 +10020,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10046,7 +10034,7 @@
         <v>67.88820949982238</v>
       </c>
       <c r="D168" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E168">
         <v>60.43722302948107</v>
@@ -10096,7 +10084,7 @@
         <v>70.99880138202717</v>
       </c>
       <c r="D169" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E169">
         <v>60.43722302948107</v>
@@ -10146,7 +10134,7 @@
         <v>52.78820949982239</v>
       </c>
       <c r="D170" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E170">
         <v>61.23438147825242</v>
@@ -10196,7 +10184,7 @@
         <v>64.41272601732022</v>
       </c>
       <c r="D171" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E171">
         <v>56.61794172047242</v>
@@ -10232,7 +10220,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10246,7 +10234,7 @@
         <v>49.31272601732023</v>
       </c>
       <c r="D172" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E172">
         <v>58.0089327786641</v>
@@ -10282,7 +10270,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10296,7 +10284,7 @@
         <v>61.16879231159055</v>
       </c>
       <c r="D173" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E173">
         <v>53.82441738118666</v>
@@ -10332,7 +10320,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10346,7 +10334,7 @@
         <v>46.06879231159056</v>
       </c>
       <c r="D174" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E174">
         <v>54.08446933112747</v>
@@ -10382,7 +10370,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10396,7 +10384,7 @@
         <v>58.07192781203269</v>
       </c>
       <c r="D175" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E175">
         <v>50.68812094147531</v>
@@ -10432,7 +10420,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10446,7 +10434,7 @@
         <v>42.9719278120327</v>
       </c>
       <c r="D176" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E176">
         <v>51.29394934141796</v>
@@ -10482,7 +10470,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10496,7 +10484,7 @@
         <v>72.62623022483724</v>
       </c>
       <c r="D177" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E177">
         <v>78.13274022613687</v>
@@ -10532,7 +10520,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10546,7 +10534,7 @@
         <v>72.14377020837516</v>
       </c>
       <c r="D178" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E178">
         <v>78.53925022743653</v>
@@ -10582,7 +10570,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10596,7 +10584,7 @@
         <v>83.25643025082999</v>
       </c>
       <c r="D179" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E179">
         <v>77.7759602547289</v>
@@ -10632,7 +10620,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10661,7 +10649,7 @@
         <v>71.40000000000001</v>
       </c>
       <c r="P180" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10690,7 +10678,7 @@
         <v>72.09999999999999</v>
       </c>
       <c r="P181" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10704,7 +10692,7 @@
         <v>66.25534327603719</v>
       </c>
       <c r="D182" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E182">
         <v>53.25789242985769</v>
@@ -10754,7 +10742,7 @@
         <v>66.50153349826817</v>
       </c>
       <c r="D183" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E183">
         <v>53.49926887679366</v>
@@ -10790,7 +10778,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10804,7 +10792,7 @@
         <v>65.13958707494101</v>
       </c>
       <c r="D184" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E184">
         <v>53.20617458032149</v>
@@ -10840,7 +10828,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10854,7 +10842,7 @@
         <v>65.2660759255686</v>
       </c>
       <c r="D185" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E185">
         <v>53.20617458032149</v>
@@ -10890,7 +10878,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10904,7 +10892,7 @@
         <v>63.88275361614285</v>
       </c>
       <c r="D186" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E186">
         <v>51.96525040581191</v>
@@ -10940,7 +10928,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10954,7 +10942,7 @@
         <v>82.52792611826956</v>
       </c>
       <c r="D187" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E187">
         <v>99.94767772279653</v>
@@ -10990,7 +10978,7 @@
         <v>0</v>
       </c>
       <c r="P187" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11004,7 +10992,7 @@
         <v>80.81507949145069</v>
       </c>
       <c r="D188" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E188">
         <v>99.94767772279653</v>
@@ -11040,7 +11028,7 @@
         <v>0</v>
       </c>
       <c r="P188" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11054,7 +11042,7 @@
         <v>82.55697724266327</v>
       </c>
       <c r="D189" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E189">
         <v>99.94767772279653</v>
@@ -11090,7 +11078,7 @@
         <v>0</v>
       </c>
       <c r="P189" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11104,7 +11092,7 @@
         <v>80.68386776738032</v>
       </c>
       <c r="D190" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E190">
         <v>99.94767772279653</v>
@@ -11140,7 +11128,7 @@
         <v>0</v>
       </c>
       <c r="P190" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11154,7 +11142,7 @@
         <v>83.46212404051099</v>
       </c>
       <c r="D191" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E191">
         <v>101.9293746430213</v>
@@ -11190,7 +11178,7 @@
         <v>0</v>
       </c>
       <c r="P191" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11204,7 +11192,7 @@
         <v>81.65627098338047</v>
       </c>
       <c r="D192" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E192">
         <v>101.9293746430213</v>
@@ -11240,7 +11228,7 @@
         <v>0</v>
       </c>
       <c r="P192" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11254,7 +11242,7 @@
         <v>83.46017302146748</v>
       </c>
       <c r="D193" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E193">
         <v>101.9293746430213</v>
@@ -11290,7 +11278,7 @@
         <v>0</v>
       </c>
       <c r="P193" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11304,7 +11292,7 @@
         <v>81.57259587924717</v>
       </c>
       <c r="D194" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E194">
         <v>101.9293746430213</v>
@@ -11340,7 +11328,7 @@
         <v>0</v>
       </c>
       <c r="P194" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11390,7 +11378,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11404,7 +11392,7 @@
         <v>33.77481800214022</v>
       </c>
       <c r="D196" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E196">
         <v>39.96346245740297</v>
@@ -11440,7 +11428,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11454,7 +11442,7 @@
         <v>24.63764534106641</v>
       </c>
       <c r="D197" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E197">
         <v>34.16939555445761</v>
@@ -11490,7 +11478,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11504,7 +11492,7 @@
         <v>43.28817453279771</v>
       </c>
       <c r="D198" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E198">
         <v>46.14425779500065</v>
@@ -11540,7 +11528,7 @@
         <v>0</v>
       </c>
       <c r="P198" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11554,7 +11542,7 @@
         <v>24.23598497532834</v>
       </c>
       <c r="D199" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E199">
         <v>33.03819935984974</v>
@@ -11590,7 +11578,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11604,7 +11592,7 @@
         <v>24.17071464201896</v>
       </c>
       <c r="D200" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E200">
         <v>33.03819935984974</v>
@@ -11640,7 +11628,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11654,7 +11642,7 @@
         <v>23.32366123264667</v>
       </c>
       <c r="D201" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E201">
         <v>32.29172372079252</v>
@@ -11704,7 +11692,7 @@
         <v>22.94912669441385</v>
       </c>
       <c r="D202" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E202">
         <v>31.49029169144093</v>
@@ -11740,7 +11728,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11754,7 +11742,7 @@
         <v>22.44844130251504</v>
       </c>
       <c r="D203" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E203">
         <v>30.75050022869873</v>
@@ -11790,7 +11778,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11804,7 +11792,7 @@
         <v>22.12056025614258</v>
       </c>
       <c r="D204" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E204">
         <v>30.75050022869873</v>
@@ -11840,7 +11828,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11854,7 +11842,7 @@
         <v>21.00936580829927</v>
       </c>
       <c r="D205" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E205">
         <v>29.75836232883863</v>
@@ -11904,7 +11892,7 @@
         <v>22.21712321587968</v>
       </c>
       <c r="D206" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E206">
         <v>29.83950116198865</v>
@@ -11940,7 +11928,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11954,7 +11942,7 @@
         <v>22.36605537346383</v>
       </c>
       <c r="D207" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E207">
         <v>29.99532225197207</v>
@@ -11990,7 +11978,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12004,7 +11992,7 @@
         <v>21.71901729202467</v>
       </c>
       <c r="D208" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E208">
         <v>28.96097369076485</v>
@@ -12040,7 +12028,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12054,7 +12042,7 @@
         <v>21.37743590654157</v>
       </c>
       <c r="D209" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E209">
         <v>28.96097369076485</v>
@@ -12090,7 +12078,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12104,7 +12092,7 @@
         <v>21.5505095382167</v>
       </c>
       <c r="D210" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E210">
         <v>29.1420529309536</v>
@@ -12154,7 +12142,7 @@
         <v>21.4477218260166</v>
       </c>
       <c r="D211" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E211">
         <v>29.03451072105261</v>
@@ -12190,7 +12178,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12204,7 +12192,7 @@
         <v>21.93200329930192</v>
       </c>
       <c r="D212" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E212">
         <v>29.03451072105261</v>
@@ -12240,7 +12228,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12254,7 +12242,7 @@
         <v>21.82005829590757</v>
       </c>
       <c r="D213" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E213">
         <v>29.42406980298699</v>
@@ -12290,7 +12278,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12304,7 +12292,7 @@
         <v>22.28137628646834</v>
       </c>
       <c r="D214" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E214">
         <v>29.42406980298699</v>
@@ -12340,7 +12328,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12354,7 +12342,7 @@
         <v>25.08434479788652</v>
       </c>
       <c r="D215" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E215">
         <v>32.83934753082841</v>
@@ -12390,7 +12378,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12404,7 +12392,7 @@
         <v>25.82576998567276</v>
       </c>
       <c r="D216" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E216">
         <v>32.83934753082841</v>
@@ -12440,7 +12428,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12454,7 +12442,7 @@
         <v>25.62576998567276</v>
       </c>
       <c r="D217" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E217">
         <v>32.83934753082841</v>
@@ -12490,7 +12478,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12504,7 +12492,7 @@
         <v>39.54291961010028</v>
       </c>
       <c r="D218" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E218">
         <v>32.24005830276027</v>
@@ -12540,7 +12528,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12554,7 +12542,7 @@
         <v>27.32311840696546</v>
       </c>
       <c r="D219" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E219">
         <v>35.18167674737576</v>
@@ -12590,7 +12578,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12604,7 +12592,7 @@
         <v>27.936331890267</v>
       </c>
       <c r="D220" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E220">
         <v>35.18167674737576</v>
@@ -12640,7 +12628,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12654,7 +12642,7 @@
         <v>27.736331890267</v>
       </c>
       <c r="D221" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E221">
         <v>35.18167674737576</v>
@@ -12690,7 +12678,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12704,7 +12692,7 @@
         <v>41.90990492366392</v>
       </c>
       <c r="D222" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E222">
         <v>34.44924459541966</v>
@@ -12740,7 +12728,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12754,7 +12742,7 @@
         <v>29.32582523799188</v>
       </c>
       <c r="D223" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E223">
         <v>36.94571726179005</v>
@@ -12804,7 +12792,7 @@
         <v>43.69251428559836</v>
       </c>
       <c r="D224" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E224">
         <v>36.11301333322514</v>
@@ -12854,7 +12842,7 @@
         <v>44.11030807122381</v>
       </c>
       <c r="D225" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E225">
         <v>36.50295419980888</v>
@@ -12890,7 +12878,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12904,7 +12892,7 @@
         <v>45.39200591893177</v>
       </c>
       <c r="D226" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E226">
         <v>37.69920552433632</v>
@@ -12954,7 +12942,7 @@
         <v>46.2461284866414</v>
       </c>
       <c r="D227" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E227">
         <v>38.49638658753197</v>
@@ -12990,7 +12978,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13004,7 +12992,7 @@
         <v>46.90307634880546</v>
       </c>
       <c r="D228" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E228">
         <v>39.10953792555176</v>
@@ -13054,7 +13042,7 @@
         <v>33.83569560835785</v>
       </c>
       <c r="D229" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E229">
         <v>40.9206360962427</v>
@@ -13104,7 +13092,7 @@
         <v>46.73201951087134</v>
       </c>
       <c r="D230" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E230">
         <v>38.94988487681324</v>
@@ -13154,7 +13142,7 @@
         <v>33.22416759327695</v>
       </c>
       <c r="D231" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E231">
         <v>40.34408700115657</v>
@@ -13190,7 +13178,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13204,7 +13192,7 @@
         <v>46.15305807647522</v>
       </c>
       <c r="D232" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E232">
         <v>38.40952087137686</v>
@@ -13240,7 +13228,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13254,7 +13242,7 @@
         <v>33.50490381338868</v>
       </c>
       <c r="D233" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E233">
         <v>40.17087450822464</v>
@@ -13290,7 +13278,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13304,7 +13292,7 @@
         <v>45.97912084507914</v>
       </c>
       <c r="D234" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E234">
         <v>38.24717945540719</v>
@@ -13340,7 +13328,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13354,7 +13342,7 @@
         <v>34.16379673036971</v>
       </c>
       <c r="D235" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E235">
         <v>40.85258622752538</v>
@@ -13390,7 +13378,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13404,7 +13392,7 @@
         <v>46.66368491466983</v>
       </c>
       <c r="D236" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E236">
         <v>38.8861059203585</v>
@@ -13440,7 +13428,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13454,7 +13442,7 @@
         <v>35.00523304555671</v>
       </c>
       <c r="D237" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E237">
         <v>41.72316319432058</v>
@@ -13490,7 +13478,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13504,7 +13492,7 @@
         <v>47.53790446291606</v>
       </c>
       <c r="D238" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E238">
         <v>39.70204416538832</v>
@@ -13540,7 +13528,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13554,7 +13542,7 @@
         <v>35.77509163864829</v>
       </c>
       <c r="D239" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E239">
         <v>42.51968355686988</v>
@@ -13590,7 +13578,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13604,7 +13592,7 @@
         <v>48.33775754664758</v>
       </c>
       <c r="D240" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E240">
         <v>40.4485737102044</v>
@@ -13640,7 +13628,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13654,7 +13642,7 @@
         <v>36.40438752667171</v>
       </c>
       <c r="D241" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E241">
         <v>43.17077324188112</v>
@@ -13690,7 +13678,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13704,7 +13692,7 @@
         <v>48.9915714562823</v>
       </c>
       <c r="D242" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E242">
         <v>41.05880002586348</v>
@@ -13740,7 +13728,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13754,7 +13742,7 @@
         <v>32.86635202836143</v>
       </c>
       <c r="D243" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E243">
         <v>23.40810673803942</v>
@@ -13790,7 +13778,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13804,7 +13792,7 @@
         <v>14.22574367387871</v>
       </c>
       <c r="D244" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E244">
         <v>19.5340376774239</v>
@@ -13840,7 +13828,7 @@
         <v>0</v>
       </c>
       <c r="P244" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13854,7 +13842,7 @@
         <v>24.88800304387275</v>
       </c>
       <c r="D245" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E245">
         <v>11.91657154564347</v>
@@ -13890,7 +13878,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13904,7 +13892,7 @@
         <v>39.44906102636678</v>
       </c>
       <c r="D246" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E246">
         <v>28.36395585832523</v>
@@ -13940,7 +13928,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13969,7 +13957,7 @@
         <v>59.4</v>
       </c>
       <c r="P247" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13983,7 +13971,7 @@
         <v>36.85113379578714</v>
       </c>
       <c r="D248" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E248">
         <v>25.5208599983697</v>
@@ -14019,7 +14007,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14033,7 +14021,7 @@
         <v>33.94646019309421</v>
       </c>
       <c r="D249" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E249">
         <v>22.34206984707826</v>
@@ -14069,7 +14057,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14083,7 +14071,7 @@
         <v>33.30875742504994</v>
       </c>
       <c r="D250" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E250">
         <v>21.64418651979802</v>
@@ -14119,7 +14107,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14148,7 +14136,7 @@
         <v>59.5</v>
       </c>
       <c r="P251" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14198,7 +14186,7 @@
         <v>0</v>
       </c>
       <c r="P252" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14212,7 +14200,7 @@
         <v>9.926891175013289</v>
       </c>
       <c r="D253" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E253">
         <v>9.938904864210649</v>
@@ -14248,7 +14236,7 @@
         <v>0</v>
       </c>
       <c r="P253" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14262,7 +14250,7 @@
         <v>8.61566853605617</v>
       </c>
       <c r="D254" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E254">
         <v>9.007561895624264</v>
@@ -14298,7 +14286,7 @@
         <v>0</v>
       </c>
       <c r="P254" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14348,7 +14336,7 @@
         <v>0</v>
       </c>
       <c r="P255" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14362,7 +14350,7 @@
         <v>15.27625616990661</v>
       </c>
       <c r="D256" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E256">
         <v>13.96823074035395</v>
@@ -14398,7 +14386,7 @@
         <v>0</v>
       </c>
       <c r="P256" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14412,7 +14400,7 @@
         <v>14.49984262437423</v>
       </c>
       <c r="D257" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E257">
         <v>14.19011246930496</v>
@@ -14448,7 +14436,7 @@
         <v>0</v>
       </c>
       <c r="P257" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14462,7 +14450,7 @@
         <v>13.68984307357539</v>
       </c>
       <c r="D258" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E258">
         <v>15.44321014679792</v>
@@ -14498,7 +14486,7 @@
         <v>0</v>
       </c>
       <c r="P258" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14512,7 +14500,7 @@
         <v>14.26953725404694</v>
       </c>
       <c r="D259" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E259">
         <v>17.46734434330768</v>
@@ -14548,7 +14536,7 @@
         <v>0</v>
       </c>
       <c r="P259" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14562,7 +14550,7 @@
         <v>59.06263065139578</v>
       </c>
       <c r="D260" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E260">
         <v>59.07357361272927</v>
@@ -14598,7 +14586,7 @@
         <v>0</v>
       </c>
       <c r="P260" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14612,7 +14600,7 @@
         <v>60.66257075424956</v>
       </c>
       <c r="D261" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E261">
         <v>61.38454095582109</v>
@@ -14648,7 +14636,7 @@
         <v>0</v>
       </c>
       <c r="P261" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14662,7 +14650,7 @@
         <v>61.58779745865752</v>
       </c>
       <c r="D262" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E262">
         <v>62.08864679971672</v>
@@ -14698,7 +14686,7 @@
         <v>0</v>
       </c>
       <c r="P262" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14748,7 +14736,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14798,7 +14786,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14848,7 +14836,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14898,7 +14886,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14948,7 +14936,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14998,7 +14986,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15048,7 +15036,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15098,7 +15086,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15148,7 +15136,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15162,7 +15150,7 @@
         <v>-12.91711279591523</v>
       </c>
       <c r="D272" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E272">
         <v>-24.080705554696</v>
@@ -15212,7 +15200,7 @@
         <v>-13.89288092370901</v>
       </c>
       <c r="D273" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E273">
         <v>-24.64699491908532</v>
@@ -15248,7 +15236,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15262,7 +15250,7 @@
         <v>-13.4171424523624</v>
       </c>
       <c r="D274" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E274">
         <v>-24.64699491908532</v>
@@ -15298,7 +15286,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15312,7 +15300,7 @@
         <v>-7.909028461817627</v>
       </c>
       <c r="D275" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E275">
         <v>-18.4089921717041</v>
@@ -15348,7 +15336,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15362,7 +15350,7 @@
         <v>-3.803879058776658</v>
       </c>
       <c r="D276" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E276">
         <v>-13.75986303266694</v>
@@ -15412,7 +15400,7 @@
         <v>-7.200798160312672</v>
       </c>
       <c r="D277" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E277">
         <v>-16.37029482433257</v>
@@ -15462,7 +15450,7 @@
         <v>1.814674940949821</v>
       </c>
       <c r="D278" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E278">
         <v>-6.106103736501311</v>
@@ -15548,7 +15536,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15648,7 +15636,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15662,7 +15650,7 @@
         <v>68.89152801060949</v>
       </c>
       <c r="D282" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E282">
         <v>67.76768139345658</v>
@@ -15698,7 +15686,7 @@
         <v>0</v>
       </c>
       <c r="P282" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15712,7 +15700,7 @@
         <v>68.93096321131679</v>
       </c>
       <c r="D283" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E283">
         <v>67.76768139345658</v>
@@ -15748,7 +15736,7 @@
         <v>0</v>
       </c>
       <c r="P283" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15762,7 +15750,7 @@
         <v>68.53130803182968</v>
       </c>
       <c r="D284" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E284">
         <v>67.76768139345658</v>
@@ -15798,7 +15786,7 @@
         <v>0</v>
       </c>
       <c r="P284" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15812,7 +15800,7 @@
         <v>69.00549946949548</v>
       </c>
       <c r="D285" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E285">
         <v>67.76768139345658</v>
@@ -15848,7 +15836,7 @@
         <v>0</v>
       </c>
       <c r="P285" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15862,7 +15850,7 @@
         <v>77.0344578684535</v>
       </c>
       <c r="D286" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E286">
         <v>79.16818364992574</v>
@@ -15912,7 +15900,7 @@
         <v>76.35596494832328</v>
       </c>
       <c r="D287" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E287">
         <v>79.16818364992574</v>
@@ -15962,7 +15950,7 @@
         <v>77.32922500711149</v>
       </c>
       <c r="D288" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E288">
         <v>79.16818364992574</v>
@@ -16012,7 +16000,7 @@
         <v>79.78847196430716</v>
       </c>
       <c r="D289" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E289">
         <v>84.66094269739213</v>
@@ -16048,7 +16036,7 @@
         <v>0</v>
       </c>
       <c r="P289" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16062,7 +16050,7 @@
         <v>79.029452316228</v>
       </c>
       <c r="D290" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E290">
         <v>84.66094269739213</v>
@@ -16098,7 +16086,7 @@
         <v>0</v>
       </c>
       <c r="P290" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16112,7 +16100,7 @@
         <v>80.07787065443522</v>
       </c>
       <c r="D291" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E291">
         <v>84.66094269739213</v>
@@ -16148,7 +16136,7 @@
         <v>0</v>
       </c>
       <c r="P291" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16198,7 +16186,7 @@
         <v>0</v>
       </c>
       <c r="P292" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16248,7 +16236,7 @@
         <v>0</v>
       </c>
       <c r="P293" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16298,7 +16286,7 @@
         <v>0</v>
       </c>
       <c r="P294" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16312,7 +16300,7 @@
         <v>26.32548638029413</v>
       </c>
       <c r="D295" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E295">
         <v>26.99422663021349</v>
@@ -16348,7 +16336,7 @@
         <v>0</v>
       </c>
       <c r="P295" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16362,7 +16350,7 @@
         <v>22.18948293316849</v>
       </c>
       <c r="D296" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E296">
         <v>24.84672272180288</v>
@@ -16398,7 +16386,7 @@
         <v>0</v>
       </c>
       <c r="P296" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16412,7 +16400,7 @@
         <v>21.86052377863092</v>
       </c>
       <c r="D297" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E297">
         <v>24.84672272180288</v>
@@ -16448,7 +16436,7 @@
         <v>0</v>
       </c>
       <c r="P297" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16462,7 +16450,7 @@
         <v>40.77814878274022</v>
       </c>
       <c r="D298" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E298">
         <v>48.87821615334129</v>
@@ -16498,7 +16486,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16512,7 +16500,7 @@
         <v>40.67981251944272</v>
       </c>
       <c r="D299" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E299">
         <v>48.87821615334129</v>
@@ -16548,7 +16536,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16562,7 +16550,7 @@
         <v>56.75038402863819</v>
       </c>
       <c r="D300" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E300">
         <v>62.17870887338118</v>
@@ -16598,7 +16586,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16612,7 +16600,7 @@
         <v>59.81014784804309</v>
       </c>
       <c r="D301" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E301">
         <v>65.19117101289457</v>
@@ -16648,7 +16636,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16662,7 +16650,7 @@
         <v>60.36835189313004</v>
       </c>
       <c r="D302" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E302">
         <v>65.519432176365</v>
@@ -16698,7 +16686,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16712,7 +16700,7 @@
         <v>61.49835591209959</v>
       </c>
       <c r="D303" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E303">
         <v>65.45054113973049</v>
@@ -16762,7 +16750,7 @@
         <v>61.74303834428476</v>
       </c>
       <c r="D304" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E304">
         <v>65.59070564276428</v>
@@ -16798,7 +16786,7 @@
         <v>0</v>
       </c>
       <c r="P304" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16812,7 +16800,7 @@
         <v>62.08800405152936</v>
       </c>
       <c r="D305" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E305">
         <v>65.70367105582346</v>
@@ -16848,7 +16836,7 @@
         <v>0</v>
       </c>
       <c r="P305" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16862,7 +16850,7 @@
         <v>62.52195117925444</v>
       </c>
       <c r="D306" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E306">
         <v>66.54562713332096</v>
@@ -16898,7 +16886,7 @@
         <v>0</v>
       </c>
       <c r="P306" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16912,7 +16900,7 @@
         <v>63.12382871565654</v>
       </c>
       <c r="D307" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E307">
         <v>66.7862115872222</v>
@@ -16948,7 +16936,7 @@
         <v>0</v>
       </c>
       <c r="P307" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16962,7 +16950,7 @@
         <v>63.43713576842169</v>
       </c>
       <c r="D308" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E308">
         <v>68.73084934526386</v>
@@ -16998,7 +16986,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17012,7 +17000,7 @@
         <v>63.67236578705479</v>
       </c>
       <c r="D309" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E309">
         <v>68.98960236576026</v>
@@ -17048,7 +17036,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17062,7 +17050,7 @@
         <v>63.92214730715632</v>
       </c>
       <c r="D310" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E310">
         <v>69.26436203787196</v>
@@ -17098,7 +17086,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17112,7 +17100,7 @@
         <v>64.84267428552164</v>
       </c>
       <c r="D311" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E311">
         <v>70.2769417140738</v>
@@ -17148,7 +17136,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17162,7 +17150,7 @@
         <v>67.02639425410899</v>
       </c>
       <c r="D312" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E312">
         <v>72.67903367951989</v>
@@ -17198,7 +17186,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17212,7 +17200,7 @@
         <v>48.8201383647419</v>
       </c>
       <c r="D313" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E313">
         <v>53.28068312873989</v>
@@ -17248,7 +17236,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17262,7 +17250,7 @@
         <v>43.78661428769819</v>
       </c>
       <c r="D314" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E314">
         <v>49.20590413019019</v>
@@ -17298,7 +17286,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17312,7 +17300,7 @@
         <v>43.50856722084519</v>
       </c>
       <c r="D315" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E315">
         <v>49.20590413019019</v>
@@ -17348,7 +17336,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17362,7 +17350,7 @@
         <v>38.43277181447034</v>
       </c>
       <c r="D316" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E316">
         <v>43.81134802598723</v>
@@ -17398,7 +17386,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17412,7 +17400,7 @@
         <v>39.10060265112747</v>
       </c>
       <c r="D317" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E317">
         <v>43.81134802598723</v>
@@ -17448,7 +17436,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17462,7 +17450,7 @@
         <v>28.12299460113455</v>
       </c>
       <c r="D318" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E318">
         <v>35.22229514558674</v>
@@ -17498,7 +17486,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17512,7 +17500,7 @@
         <v>27.81471186440677</v>
       </c>
       <c r="D319" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E319">
         <v>34.92338983050847</v>
@@ -17548,7 +17536,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17562,7 +17550,7 @@
         <v>31.34037664954478</v>
       </c>
       <c r="D320" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E320">
         <v>38.34181005944457</v>
@@ -17598,7 +17586,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17612,7 +17600,7 @@
         <v>31.06966226989418</v>
       </c>
       <c r="D321" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E321">
         <v>38.07933033773011</v>
@@ -17648,7 +17636,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17662,7 +17650,7 @@
         <v>30.73117805425061</v>
       </c>
       <c r="D322" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E322">
         <v>37.75114221990079</v>
@@ -17698,7 +17686,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17712,7 +17700,7 @@
         <v>30.23209518986696</v>
       </c>
       <c r="D323" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E323">
         <v>37.26724058333109</v>
@@ -17748,7 +17736,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17762,7 +17750,7 @@
         <v>29.66328200930995</v>
       </c>
       <c r="D324" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E324">
         <v>36.71572970484425</v>
@@ -17798,7 +17786,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17812,7 +17800,7 @@
         <v>29.90527095369034</v>
       </c>
       <c r="D325" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E325">
         <v>36.95035776878722</v>
@@ -17848,7 +17836,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17862,7 +17850,7 @@
         <v>29.61163508265873</v>
       </c>
       <c r="D326" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E326">
         <v>36.66565378736873</v>
@@ -17898,7 +17886,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17912,7 +17900,7 @@
         <v>29.60796663375891</v>
       </c>
       <c r="D327" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E327">
         <v>38.73216492329536</v>
@@ -17948,7 +17936,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17962,7 +17950,7 @@
         <v>29.99267097270676</v>
       </c>
       <c r="D328" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E328">
         <v>39.11028686861102</v>
@@ -17998,7 +17986,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18012,7 +18000,7 @@
         <v>30.47592970891776</v>
       </c>
       <c r="D329" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E329">
         <v>39.58527691922146</v>
@@ -18048,7 +18036,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18077,7 +18065,7 @@
         <v>64.5</v>
       </c>
       <c r="P330" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18091,7 +18079,7 @@
         <v>37.15547839433958</v>
       </c>
       <c r="D331" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E331">
         <v>43.97524497646168</v>
@@ -18127,7 +18115,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18141,7 +18129,7 @@
         <v>37.01610527202449</v>
       </c>
       <c r="D332" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E332">
         <v>43.97524497646168</v>
@@ -18177,7 +18165,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18191,7 +18179,7 @@
         <v>25.78116025897209</v>
       </c>
       <c r="D333" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E333">
         <v>34.97083622412276</v>
@@ -18227,7 +18215,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18241,7 +18229,7 @@
         <v>21.78292834045364</v>
       </c>
       <c r="D334" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E334">
         <v>32.11135258573889</v>
@@ -18277,7 +18265,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18291,7 +18279,7 @@
         <v>16.20611168178342</v>
       </c>
       <c r="D335" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E335">
         <v>27.00103770079773</v>
@@ -18327,7 +18315,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18341,7 +18329,7 @@
         <v>16.50484318653699</v>
       </c>
       <c r="D336" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E336">
         <v>27.00103770079773</v>
@@ -18377,7 +18365,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18391,7 +18379,7 @@
         <v>7.513223702566968</v>
       </c>
       <c r="D337" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E337">
         <v>19.03531145368304</v>
@@ -18427,7 +18415,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18441,7 +18429,7 @@
         <v>7.993745640345985</v>
       </c>
       <c r="D338" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E338">
         <v>19.03531145368304</v>
@@ -18477,7 +18465,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18491,7 +18479,7 @@
         <v>-3.101932223543415</v>
       </c>
       <c r="D339" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E339">
         <v>9.308115338882274</v>
@@ -18527,7 +18515,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18541,7 +18529,7 @@
         <v>-2.399420332936991</v>
       </c>
       <c r="D340" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E340">
         <v>9.308115338882274</v>
@@ -18577,7 +18565,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18591,7 +18579,7 @@
         <v>-2.646016646848999</v>
       </c>
       <c r="D341" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E341">
         <v>9.308115338882274</v>
@@ -18627,7 +18615,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18641,7 +18629,7 @@
         <v>-9.121415898188509</v>
       </c>
       <c r="D342" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E342">
         <v>3.792162618009769</v>
@@ -18677,7 +18665,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18691,7 +18679,7 @@
         <v>-8.59683700961601</v>
       </c>
       <c r="D343" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E343">
         <v>3.792162618009769</v>
@@ -18727,7 +18715,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18741,7 +18729,7 @@
         <v>-12.89770073310627</v>
       </c>
       <c r="D344" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E344">
         <v>0.3317647274577595</v>
@@ -18777,7 +18765,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18791,7 +18779,7 @@
         <v>-14.09288737405897</v>
       </c>
       <c r="D345" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E345">
         <v>-0.7634443237574615</v>
@@ -18827,7 +18815,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18841,7 +18829,7 @@
         <v>59.56360813550708</v>
       </c>
       <c r="D346" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E346">
         <v>75.18159673719033</v>
@@ -18877,7 +18865,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18891,7 +18879,7 @@
         <v>60.31956868780029</v>
       </c>
       <c r="D347" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E347">
         <v>76.03992694760657</v>
@@ -18927,7 +18915,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18941,7 +18929,7 @@
         <v>62.79431714399279</v>
       </c>
       <c r="D348" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E348">
         <v>77.62631903124894</v>
@@ -18977,7 +18965,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18991,7 +18979,7 @@
         <v>64.08298118239738</v>
       </c>
       <c r="D349" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E349">
         <v>79.11665728256037</v>
@@ -19027,7 +19015,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19041,7 +19029,7 @@
         <v>64.68906100731142</v>
       </c>
       <c r="D350" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E350">
         <v>79.81758779625406</v>
@@ -19077,7 +19065,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19091,7 +19079,7 @@
         <v>66.03163316666149</v>
       </c>
       <c r="D351" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E351">
         <v>81.37027071794273</v>
@@ -19127,7 +19115,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19141,7 +19129,7 @@
         <v>65.93064756206419</v>
       </c>
       <c r="D352" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E352">
         <v>81.25348100015911</v>
@@ -19177,7 +19165,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19191,7 +19179,7 @@
         <v>64.84418812133572</v>
       </c>
       <c r="D353" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E353">
         <v>80.16577874075962</v>
@@ -19227,7 +19215,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19241,7 +19229,7 @@
         <v>63.26616721431549</v>
       </c>
       <c r="D354" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E354">
         <v>79.97190339753475</v>
@@ -19277,7 +19265,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19291,7 +19279,7 @@
         <v>61.66554474645639</v>
       </c>
       <c r="D355" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E355">
         <v>78.05285470927927</v>
@@ -19327,7 +19315,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19341,7 +19329,7 @@
         <v>60.62679073828761</v>
       </c>
       <c r="D356" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E356">
         <v>76.80745202574536</v>
@@ -19377,7 +19365,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19391,7 +19379,7 @@
         <v>59.7052486970962</v>
       </c>
       <c r="D357" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E357">
         <v>75.70257933975458</v>
@@ -19427,7 +19415,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19441,7 +19429,7 @@
         <v>50.59926427854958</v>
       </c>
       <c r="D358" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E358">
         <v>64.78505955942813</v>
@@ -19477,7 +19465,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19491,7 +19479,7 @@
         <v>54.80887863487924</v>
       </c>
       <c r="D359" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E359">
         <v>72.15232554251514</v>
@@ -19527,7 +19515,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19541,7 +19529,7 @@
         <v>22.63799956449154</v>
       </c>
       <c r="D360" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E360">
         <v>34.76775640560354</v>
@@ -19577,7 +19565,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19591,7 +19579,7 @@
         <v>21.94224021195173</v>
       </c>
       <c r="D361" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E361">
         <v>34.09962025316457</v>
@@ -19627,7 +19615,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19638,28 +19626,28 @@
         <v>131</v>
       </c>
       <c r="C362">
-        <v>21.49005400241875</v>
+        <v>20.45188899670399</v>
       </c>
       <c r="D362" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E362">
-        <v>33.11192987695436</v>
+        <v>32.14380973909506</v>
       </c>
       <c r="F362">
         <v>1</v>
       </c>
       <c r="G362">
-        <v>0.1407099459975812</v>
+        <v>0.141748111003296</v>
       </c>
       <c r="H362">
-        <v>0.1442880701230456</v>
+        <v>0.1452561902609049</v>
       </c>
       <c r="I362">
-        <v>11.62187587453561</v>
+        <v>11.69192074239107</v>
       </c>
       <c r="J362">
-        <v>0.2872768481811144</v>
+        <v>0.2922800530279325</v>
       </c>
       <c r="K362">
         <v>207.5</v>
@@ -19677,7 +19665,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>130</v>
+        <v>458</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19688,28 +19676,28 @@
         <v>132</v>
       </c>
       <c r="C363">
-        <v>20.6287291557878</v>
+        <v>18.55332655028487</v>
       </c>
       <c r="D363" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E363">
-        <v>32.1976697125811</v>
+        <v>30.18004248156539</v>
       </c>
       <c r="F363">
         <v>1</v>
       </c>
       <c r="G363">
-        <v>0.1401712708442122</v>
+        <v>0.1422466734497151</v>
       </c>
       <c r="H363">
-        <v>0.1456023302874189</v>
+        <v>0.1472199575184346</v>
       </c>
       <c r="I363">
-        <v>11.56894055679329</v>
+        <v>11.62671593128051</v>
       </c>
       <c r="J363">
-        <v>0.2922800530279325</v>
+        <v>0.3024287210255019</v>
       </c>
       <c r="K363">
         <v>204.5</v>
@@ -19718,16 +19706,16 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M363">
-        <v>194</v>
+        <v>193.5</v>
       </c>
       <c r="N363">
-        <v>88.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="O363">
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19735,37 +19723,37 @@
         <v>0</v>
       </c>
       <c r="B364" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C364">
-        <v>18.55332655028487</v>
+        <v>14.44543186753303</v>
       </c>
       <c r="D364" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E364">
-        <v>31.09968346874662</v>
+        <v>25.90076425342215</v>
       </c>
       <c r="F364">
         <v>1</v>
       </c>
       <c r="G364">
-        <v>0.1422466734497151</v>
+        <v>0.150754568132467</v>
       </c>
       <c r="H364">
-        <v>0.1557003165312534</v>
+        <v>0.1608992357465779</v>
       </c>
       <c r="I364">
-        <v>12.54635691846175</v>
+        <v>11.45533238588912</v>
       </c>
       <c r="J364">
-        <v>0.3024287210255019</v>
+        <v>0.3276661929445527</v>
       </c>
       <c r="K364">
-        <v>204.5</v>
+        <v>208</v>
       </c>
       <c r="L364">
-        <v>80.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="M364">
         <v>206</v>
@@ -19777,7 +19765,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>463</v>
+        <v>131</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19788,28 +19776,28 @@
         <v>133</v>
       </c>
       <c r="C365">
-        <v>15.37197148226591</v>
+        <v>12.82667623833451</v>
       </c>
       <c r="D365" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E365">
-        <v>26.81839483339797</v>
+        <v>24.29757358219669</v>
       </c>
       <c r="F365">
         <v>1</v>
       </c>
       <c r="G365">
-        <v>0.1498280285177341</v>
+        <v>0.1523733237616655</v>
       </c>
       <c r="H365">
-        <v>0.159981605166602</v>
+        <v>0.1625024264178033</v>
       </c>
       <c r="I365">
-        <v>11.44642335113207</v>
+        <v>11.47089734386218</v>
       </c>
       <c r="J365">
-        <v>0.3232116755660293</v>
+        <v>0.335448671931084</v>
       </c>
       <c r="K365">
         <v>208</v>
@@ -19827,7 +19815,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19835,131 +19823,131 @@
         <v>0</v>
       </c>
       <c r="B366" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C366">
-        <v>14.44543186753303</v>
+        <v>10.37263457760139</v>
       </c>
       <c r="D366" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E366">
-        <v>25.90076425342215</v>
+        <v>21.96162940390666</v>
       </c>
       <c r="F366">
         <v>1</v>
       </c>
       <c r="G366">
-        <v>0.150754568132467</v>
+        <v>0.1608273654223986</v>
       </c>
       <c r="H366">
-        <v>0.1608992357465779</v>
+        <v>0.1640383705960933</v>
       </c>
       <c r="I366">
-        <v>11.45533238588912</v>
+        <v>11.58899482630527</v>
       </c>
       <c r="J366">
-        <v>0.3276661929445527</v>
+        <v>0.3490829021921049</v>
       </c>
       <c r="K366">
-        <v>208</v>
+        <v>215.5</v>
       </c>
       <c r="L366">
-        <v>82.59999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M366">
-        <v>206</v>
+        <v>203.5</v>
       </c>
       <c r="N366">
-        <v>93.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="O366">
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>131</v>
+        <v>461</v>
       </c>
     </row>
     <row r="367" spans="1:16">
       <c r="A367" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B367" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C367">
-        <v>13.45577889447236</v>
+        <v>9.990756344042168</v>
       </c>
       <c r="D367" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E367">
-        <v>24.42984924623116</v>
+        <v>21.96162940390666</v>
       </c>
       <c r="F367">
         <v>1</v>
       </c>
       <c r="G367">
-        <v>0.1543442211055276</v>
+        <v>0.1552092436559578</v>
       </c>
       <c r="H367">
-        <v>0.1629701507537689</v>
+        <v>0.1640383705960933</v>
       </c>
       <c r="I367">
-        <v>10.9740703517588</v>
+        <v>11.97087305986449</v>
       </c>
       <c r="J367">
-        <v>0.335448671931084</v>
+        <v>0.3490829021921049</v>
       </c>
       <c r="K367">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L367">
-        <v>83.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="M367">
-        <v>206.5</v>
+        <v>203.5</v>
       </c>
       <c r="N367">
-        <v>93.7</v>
+        <v>93</v>
       </c>
       <c r="O367">
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="368" spans="1:16">
       <c r="A368" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B368" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C368">
-        <v>13.31081119885138</v>
+        <v>8.066617110777202</v>
       </c>
       <c r="D368" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E368">
-        <v>24.42984924623116</v>
+        <v>19.78402126238126</v>
       </c>
       <c r="F368">
         <v>1</v>
       </c>
       <c r="G368">
-        <v>0.1578891888011486</v>
+        <v>0.1631333828892228</v>
       </c>
       <c r="H368">
-        <v>0.1629701507537689</v>
+        <v>0.1662159787376188</v>
       </c>
       <c r="I368">
-        <v>11.11903804737977</v>
+        <v>11.71740415160406</v>
       </c>
       <c r="J368">
-        <v>0.335448671931084</v>
+        <v>0.3597836793003378</v>
       </c>
       <c r="K368">
         <v>215.5</v>
@@ -19968,48 +19956,48 @@
         <v>85.59999999999999</v>
       </c>
       <c r="M368">
-        <v>206.5</v>
+        <v>203.5</v>
       </c>
       <c r="N368">
-        <v>93.7</v>
+        <v>93</v>
       </c>
       <c r="O368">
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="369" spans="1:16">
       <c r="A369" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B369" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C369">
-        <v>13.42667623833452</v>
+        <v>8.364994705529739</v>
       </c>
       <c r="D369" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E369">
-        <v>24.42984924623116</v>
+        <v>19.78402126238126</v>
       </c>
       <c r="F369">
         <v>1</v>
       </c>
       <c r="G369">
-        <v>0.1529733237616655</v>
+        <v>0.1580350052944703</v>
       </c>
       <c r="H369">
-        <v>0.1629701507537689</v>
+        <v>0.1662159787376188</v>
       </c>
       <c r="I369">
-        <v>11.00317300789663</v>
+        <v>11.41902655685152</v>
       </c>
       <c r="J369">
-        <v>0.335448671931084</v>
+        <v>0.3597836793003378</v>
       </c>
       <c r="K369">
         <v>208</v>
@@ -20018,16 +20006,16 @@
         <v>83.2</v>
       </c>
       <c r="M369">
-        <v>206.5</v>
+        <v>203.5</v>
       </c>
       <c r="N369">
-        <v>93.7</v>
+        <v>93</v>
       </c>
       <c r="O369">
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20035,149 +20023,128 @@
         <v>0</v>
       </c>
       <c r="B370" t="s">
+        <v>136</v>
+      </c>
+      <c r="C370">
+        <v>-3.424244140274368</v>
+      </c>
+      <c r="D370" t="s">
+        <v>248</v>
+      </c>
+      <c r="E370">
+        <v>10.72424068728326</v>
+      </c>
+      <c r="F370">
+        <v>1</v>
+      </c>
+      <c r="G370">
+        <v>0.1690242441402744</v>
+      </c>
+      <c r="H370">
+        <v>0.1852757593127167</v>
+      </c>
+      <c r="I370">
+        <v>14.14848482755762</v>
+      </c>
+      <c r="J370">
+        <v>0.4206060689769481</v>
+      </c>
+      <c r="K370">
+        <v>205</v>
+      </c>
+      <c r="L370">
+        <v>82.8</v>
+      </c>
+      <c r="M370">
+        <v>207.5</v>
+      </c>
+      <c r="N370">
+        <v>98</v>
+      </c>
+      <c r="O370">
+        <v>1</v>
+      </c>
+      <c r="P370" t="s">
         <v>134</v>
-      </c>
-      <c r="C370">
-        <v>10.59259053965798</v>
-      </c>
-      <c r="D370" t="s">
-        <v>250</v>
-      </c>
-      <c r="E370">
-        <v>21.96162940390666</v>
-      </c>
-      <c r="F370">
-        <v>1</v>
-      </c>
-      <c r="G370">
-        <v>0.157207409460342</v>
-      </c>
-      <c r="H370">
-        <v>0.1640383705960933</v>
-      </c>
-      <c r="I370">
-        <v>11.36903886424868</v>
-      </c>
-      <c r="J370">
-        <v>0.3490829021921049</v>
-      </c>
-      <c r="K370">
-        <v>210</v>
-      </c>
-      <c r="L370">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="M370">
-        <v>203.5</v>
-      </c>
-      <c r="N370">
-        <v>93</v>
-      </c>
-      <c r="O370">
-        <v>1</v>
-      </c>
-      <c r="P370" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="371" spans="1:16">
       <c r="A371" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B371" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C371">
-        <v>10.37263457760139</v>
+        <v>-2.10269534440512</v>
       </c>
       <c r="D371" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E371">
-        <v>21.96162940390666</v>
+        <v>10.74605227334604</v>
       </c>
       <c r="F371">
         <v>1</v>
       </c>
       <c r="G371">
-        <v>0.1608273654223986</v>
+        <v>0.1703026953444051</v>
       </c>
       <c r="H371">
-        <v>0.1640383705960933</v>
+        <v>0.185253947726654</v>
       </c>
       <c r="I371">
-        <v>11.58899482630527</v>
+        <v>12.84874761775116</v>
       </c>
       <c r="J371">
-        <v>0.3490829021921049</v>
+        <v>0.4205009528995372</v>
       </c>
       <c r="K371">
-        <v>215.5</v>
+        <v>205</v>
       </c>
       <c r="L371">
-        <v>85.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M371">
-        <v>203.5</v>
+        <v>207.5</v>
       </c>
       <c r="N371">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="O371">
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="372" spans="1:16">
       <c r="A372" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B372" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C372">
-        <v>10.59075634404218</v>
-      </c>
-      <c r="D372" t="s">
-        <v>250</v>
-      </c>
-      <c r="E372">
-        <v>21.96162940390666</v>
+        <v>-1.654179145112977</v>
       </c>
       <c r="F372">
         <v>1</v>
       </c>
       <c r="G372">
-        <v>0.1558092436559578</v>
-      </c>
-      <c r="H372">
-        <v>0.1640383705960933</v>
-      </c>
-      <c r="I372">
-        <v>11.37087305986448</v>
+        <v>0.156454179145113</v>
       </c>
       <c r="J372">
-        <v>0.3490829021921049</v>
+        <v>0.4205009528995372</v>
       </c>
       <c r="K372">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="L372">
-        <v>83.2</v>
-      </c>
-      <c r="M372">
-        <v>203.5</v>
-      </c>
-      <c r="N372">
-        <v>93</v>
-      </c>
-      <c r="O372">
-        <v>1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="P372" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20185,49 +20152,49 @@
         <v>0</v>
       </c>
       <c r="B373" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C373">
-        <v>8.066617110777202</v>
+        <v>-2.91355538156337</v>
       </c>
       <c r="D373" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E373">
-        <v>20.60412942273109</v>
+        <v>9.925303699149282</v>
       </c>
       <c r="F373">
         <v>1</v>
       </c>
       <c r="G373">
-        <v>0.1631333828892228</v>
+        <v>0.1711135553815633</v>
       </c>
       <c r="H373">
-        <v>0.1673958705772689</v>
+        <v>0.1860746963008507</v>
       </c>
       <c r="I373">
-        <v>12.53751231195389</v>
+        <v>12.83885908071265</v>
       </c>
       <c r="J373">
-        <v>0.3597836793003378</v>
+        <v>0.4244563677149432</v>
       </c>
       <c r="K373">
-        <v>215.5</v>
+        <v>205</v>
       </c>
       <c r="L373">
-        <v>85.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M373">
-        <v>204</v>
+        <v>207.5</v>
       </c>
       <c r="N373">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="O373">
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>134</v>
+        <v>464</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20235,99 +20202,99 @@
         <v>1</v>
       </c>
       <c r="B374" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C374">
-        <v>8.364994705529739</v>
+        <v>-1.797797130409322</v>
       </c>
       <c r="D374" t="s">
-        <v>251</v>
+        <v>138</v>
       </c>
       <c r="E374">
-        <v>20.60412942273109</v>
+        <v>-2.397797130409316</v>
       </c>
       <c r="F374">
         <v>1</v>
       </c>
       <c r="G374">
-        <v>0.1580350052944703</v>
+        <v>0.1577977971304093</v>
       </c>
       <c r="H374">
-        <v>0.1673958705772689</v>
+        <v>0.1571977971304093</v>
       </c>
       <c r="I374">
-        <v>12.23913471720135</v>
+        <v>-0.5999999999999943</v>
       </c>
       <c r="J374">
-        <v>0.3597836793003378</v>
+        <v>0.4244563677149432</v>
       </c>
       <c r="K374">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="L374">
-        <v>83.2</v>
+        <v>78</v>
       </c>
       <c r="M374">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="N374">
-        <v>94</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O374">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P374" t="s">
-        <v>134</v>
+        <v>464</v>
       </c>
     </row>
     <row r="375" spans="1:16">
       <c r="A375" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B375" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C375">
-        <v>8.723696781331768</v>
+        <v>-1.02931617171204</v>
       </c>
       <c r="D375" t="s">
-        <v>251</v>
+        <v>138</v>
       </c>
       <c r="E375">
-        <v>20.60412942273109</v>
+        <v>-4.96744085712227</v>
       </c>
       <c r="F375">
         <v>1</v>
       </c>
       <c r="G375">
-        <v>0.1540763032186682</v>
+        <v>0.162829316171712</v>
       </c>
       <c r="H375">
-        <v>0.1673958705772689</v>
+        <v>0.1597674408571223</v>
       </c>
       <c r="I375">
-        <v>11.88043264139932</v>
+        <v>-3.93812468541023</v>
       </c>
       <c r="J375">
-        <v>0.3597836793003378</v>
+        <v>0.4381246854102249</v>
       </c>
       <c r="K375">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="L375">
-        <v>81.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="M375">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="N375">
-        <v>94</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O375">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P375" t="s">
-        <v>134</v>
+        <v>465</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20335,49 +20302,49 @@
         <v>0</v>
       </c>
       <c r="B376" t="s">
+        <v>140</v>
+      </c>
+      <c r="C376">
+        <v>-36.89254119687769</v>
+      </c>
+      <c r="D376" t="s">
         <v>138</v>
       </c>
-      <c r="C376">
-        <v>-3.424244140274368</v>
-      </c>
-      <c r="D376" t="s">
-        <v>252</v>
-      </c>
       <c r="E376">
-        <v>10.72424068728326</v>
+        <v>-41.02244783429414</v>
       </c>
       <c r="F376">
         <v>1</v>
       </c>
       <c r="G376">
-        <v>0.1690242441402744</v>
+        <v>0.1986925411968777</v>
       </c>
       <c r="H376">
-        <v>0.1852757593127167</v>
+        <v>0.1958224478342942</v>
       </c>
       <c r="I376">
-        <v>14.14848482755762</v>
+        <v>-4.129906637416454</v>
       </c>
       <c r="J376">
-        <v>0.4206060689769481</v>
+        <v>0.6299066374164582</v>
       </c>
       <c r="K376">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="L376">
-        <v>82.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="M376">
-        <v>207.5</v>
+        <v>188</v>
       </c>
       <c r="N376">
-        <v>98</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O376">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P376" t="s">
-        <v>135</v>
+        <v>466</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20385,46 +20352,46 @@
         <v>0</v>
       </c>
       <c r="B377" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C377">
-        <v>-2.10269534440512</v>
+        <v>16.56381239880164</v>
       </c>
       <c r="D377" t="s">
-        <v>252</v>
+        <v>138</v>
       </c>
       <c r="E377">
-        <v>10.74605227334604</v>
+        <v>15.67890124851195</v>
       </c>
       <c r="F377">
         <v>1</v>
       </c>
       <c r="G377">
-        <v>0.1703026953444051</v>
+        <v>0.1380361876011983</v>
       </c>
       <c r="H377">
-        <v>0.185253947726654</v>
+        <v>0.1391210987514881</v>
       </c>
       <c r="I377">
-        <v>12.84874761775116</v>
+        <v>-0.884911150289696</v>
       </c>
       <c r="J377">
-        <v>0.4205009528995372</v>
+        <v>0.3283037167632343</v>
       </c>
       <c r="K377">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="L377">
-        <v>84.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="M377">
-        <v>207.5</v>
+        <v>188</v>
       </c>
       <c r="N377">
-        <v>98</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O377">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P377" t="s">
         <v>467</v>
@@ -20435,228 +20402,49 @@
         <v>0</v>
       </c>
       <c r="B378" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C378">
-        <v>-1.224428027264494</v>
+        <v>14.09886568031695</v>
+      </c>
+      <c r="D378" t="s">
+        <v>138</v>
+      </c>
+      <c r="E378">
+        <v>13.49886568031696</v>
       </c>
       <c r="F378">
         <v>1</v>
       </c>
       <c r="G378">
-        <v>0.1558244280272645</v>
+        <v>0.141901134319683</v>
+      </c>
+      <c r="H378">
+        <v>0.1413011343196831</v>
+      </c>
+      <c r="I378">
+        <v>-0.5999999999999943</v>
       </c>
       <c r="J378">
-        <v>0.4244563677149432</v>
+        <v>0.3398996506366119</v>
       </c>
       <c r="K378">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L378">
-        <v>77.3</v>
+        <v>78</v>
+      </c>
+      <c r="M378">
+        <v>188</v>
+      </c>
+      <c r="N378">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="O378">
+        <v>0</v>
       </c>
       <c r="P378" t="s">
         <v>468</v>
-      </c>
-    </row>
-    <row r="379" spans="1:16">
-      <c r="A379" s="1">
-        <v>0</v>
-      </c>
-      <c r="B379" t="s">
-        <v>141</v>
-      </c>
-      <c r="C379">
-        <v>-1.02931617171204</v>
-      </c>
-      <c r="D379" t="s">
-        <v>140</v>
-      </c>
-      <c r="E379">
-        <v>-3.753066800891602</v>
-      </c>
-      <c r="F379">
-        <v>1</v>
-      </c>
-      <c r="G379">
-        <v>0.162829316171712</v>
-      </c>
-      <c r="H379">
-        <v>0.1583530668008916</v>
-      </c>
-      <c r="I379">
-        <v>-2.723750629179563</v>
-      </c>
-      <c r="J379">
-        <v>0.4381246854102249</v>
-      </c>
-      <c r="K379">
-        <v>187</v>
-      </c>
-      <c r="L379">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="M379">
-        <v>185</v>
-      </c>
-      <c r="N379">
-        <v>77.3</v>
-      </c>
-      <c r="O379">
-        <v>0</v>
-      </c>
-      <c r="P379" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="380" spans="1:16">
-      <c r="A380" s="1">
-        <v>0</v>
-      </c>
-      <c r="B380" t="s">
-        <v>141</v>
-      </c>
-      <c r="C380">
-        <v>-36.89254119687769</v>
-      </c>
-      <c r="D380" t="s">
-        <v>140</v>
-      </c>
-      <c r="E380">
-        <v>-39.23272792204477</v>
-      </c>
-      <c r="F380">
-        <v>1</v>
-      </c>
-      <c r="G380">
-        <v>0.1986925411968777</v>
-      </c>
-      <c r="H380">
-        <v>0.1938327279220448</v>
-      </c>
-      <c r="I380">
-        <v>-2.340186725167086</v>
-      </c>
-      <c r="J380">
-        <v>0.6299066374164582</v>
-      </c>
-      <c r="K380">
-        <v>187</v>
-      </c>
-      <c r="L380">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="M380">
-        <v>185</v>
-      </c>
-      <c r="N380">
-        <v>77.3</v>
-      </c>
-      <c r="O380">
-        <v>0</v>
-      </c>
-      <c r="P380" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="381" spans="1:16">
-      <c r="A381" s="1">
-        <v>0</v>
-      </c>
-      <c r="B381" t="s">
-        <v>142</v>
-      </c>
-      <c r="C381">
-        <v>18.35059753174872</v>
-      </c>
-      <c r="D381" t="s">
-        <v>140</v>
-      </c>
-      <c r="E381">
-        <v>16.56381239880164</v>
-      </c>
-      <c r="F381">
-        <v>1</v>
-      </c>
-      <c r="G381">
-        <v>0.1424494024682513</v>
-      </c>
-      <c r="H381">
-        <v>0.1380361876011983</v>
-      </c>
-      <c r="I381">
-        <v>-1.786785132947074</v>
-      </c>
-      <c r="J381">
-        <v>0.3283037167632343</v>
-      </c>
-      <c r="K381">
-        <v>189</v>
-      </c>
-      <c r="L381">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="M381">
-        <v>185</v>
-      </c>
-      <c r="N381">
-        <v>77.3</v>
-      </c>
-      <c r="O381">
-        <v>0</v>
-      </c>
-      <c r="P381" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="382" spans="1:16">
-      <c r="A382" s="1">
-        <v>0</v>
-      </c>
-      <c r="B382" t="s">
-        <v>142</v>
-      </c>
-      <c r="C382">
-        <v>16.15896602968036</v>
-      </c>
-      <c r="D382" t="s">
-        <v>140</v>
-      </c>
-      <c r="E382">
-        <v>14.41856463222679</v>
-      </c>
-      <c r="F382">
-        <v>1</v>
-      </c>
-      <c r="G382">
-        <v>0.1446410339703197</v>
-      </c>
-      <c r="H382">
-        <v>0.1401814353677732</v>
-      </c>
-      <c r="I382">
-        <v>-1.740401397453567</v>
-      </c>
-      <c r="J382">
-        <v>0.3398996506366119</v>
-      </c>
-      <c r="K382">
-        <v>189</v>
-      </c>
-      <c r="L382">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="M382">
-        <v>185</v>
-      </c>
-      <c r="N382">
-        <v>77.3</v>
-      </c>
-      <c r="O382">
-        <v>0</v>
-      </c>
-      <c r="P382" t="s">
-        <v>472</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-2474-2382-800.xlsx
+++ b/s60_signal/position-2474-2382-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="468">
   <si>
     <t>trade_time</t>
   </si>
@@ -406,999 +406,993 @@
     <t>2020-11-12</t>
   </si>
   <si>
-    <t>2020-12-24</t>
-  </si>
-  <si>
     <t>2021-01-04</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2021-01-19</t>
+  </si>
+  <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>2021-01-21</t>
+  </si>
+  <si>
+    <t>2021-01-28</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
+    <t>2010-10-22</t>
+  </si>
+  <si>
+    <t>2010-10-25</t>
+  </si>
+  <si>
+    <t>2010-10-28</t>
+  </si>
+  <si>
+    <t>2011-05-13</t>
+  </si>
+  <si>
+    <t>2011-05-16</t>
+  </si>
+  <si>
+    <t>2011-05-17</t>
+  </si>
+  <si>
+    <t>2011-05-18</t>
+  </si>
+  <si>
+    <t>2011-05-19</t>
+  </si>
+  <si>
+    <t>2011-05-20</t>
+  </si>
+  <si>
+    <t>2011-05-23</t>
+  </si>
+  <si>
+    <t>2011-05-24</t>
+  </si>
+  <si>
+    <t>2011-05-25</t>
+  </si>
+  <si>
+    <t>2011-05-26</t>
+  </si>
+  <si>
+    <t>2011-05-27</t>
+  </si>
+  <si>
+    <t>2011-05-30</t>
+  </si>
+  <si>
+    <t>2011-05-31</t>
+  </si>
+  <si>
+    <t>2011-06-02</t>
+  </si>
+  <si>
+    <t>2011-06-03</t>
+  </si>
+  <si>
+    <t>2011-07-22</t>
+  </si>
+  <si>
+    <t>2011-07-25</t>
+  </si>
+  <si>
+    <t>2011-07-27</t>
+  </si>
+  <si>
+    <t>2011-07-28</t>
+  </si>
+  <si>
+    <t>2011-07-29</t>
+  </si>
+  <si>
+    <t>2011-10-07</t>
+  </si>
+  <si>
+    <t>2011-10-05</t>
+  </si>
+  <si>
+    <t>2012-02-29</t>
+  </si>
+  <si>
+    <t>2012-07-18</t>
+  </si>
+  <si>
+    <t>2012-05-02</t>
+  </si>
+  <si>
+    <t>2012-05-25</t>
+  </si>
+  <si>
+    <t>2012-11-13</t>
+  </si>
+  <si>
+    <t>2012-11-14</t>
+  </si>
+  <si>
+    <t>2012-12-14</t>
+  </si>
+  <si>
+    <t>2012-08-01</t>
+  </si>
+  <si>
+    <t>2013-06-14</t>
+  </si>
+  <si>
+    <t>2013-06-17</t>
+  </si>
+  <si>
+    <t>2013-06-18</t>
+  </si>
+  <si>
+    <t>2013-05-20</t>
+  </si>
+  <si>
+    <t>2013-08-06</t>
+  </si>
+  <si>
+    <t>2013-05-16</t>
+  </si>
+  <si>
+    <t>2013-11-28</t>
+  </si>
+  <si>
+    <t>2013-12-04</t>
+  </si>
+  <si>
+    <t>2014-02-17</t>
+  </si>
+  <si>
+    <t>2014-02-19</t>
+  </si>
+  <si>
+    <t>2013-08-07</t>
+  </si>
+  <si>
+    <t>2013-08-08</t>
+  </si>
+  <si>
+    <t>2013-08-09</t>
+  </si>
+  <si>
+    <t>2013-09-23</t>
+  </si>
+  <si>
+    <t>2014-04-25</t>
+  </si>
+  <si>
+    <t>2014-04-24</t>
+  </si>
+  <si>
+    <t>2014-09-15</t>
+  </si>
+  <si>
+    <t>2014-12-02</t>
+  </si>
+  <si>
+    <t>2014-09-10</t>
+  </si>
+  <si>
+    <t>2014-09-04</t>
+  </si>
+  <si>
+    <t>2014-11-11</t>
+  </si>
+  <si>
+    <t>2014-09-03</t>
+  </si>
+  <si>
+    <t>2014-11-03</t>
+  </si>
+  <si>
+    <t>2014-11-27</t>
+  </si>
+  <si>
+    <t>2015-03-18</t>
+  </si>
+  <si>
+    <t>2015-08-07</t>
+  </si>
+  <si>
+    <t>2016-03-16</t>
+  </si>
+  <si>
+    <t>2016-03-17</t>
+  </si>
+  <si>
+    <t>2016-02-01</t>
+  </si>
+  <si>
+    <t>2016-02-02</t>
+  </si>
+  <si>
+    <t>2016-07-18</t>
+  </si>
+  <si>
+    <t>2016-06-30</t>
+  </si>
+  <si>
+    <t>2016-08-03</t>
+  </si>
+  <si>
+    <t>2016-07-01</t>
+  </si>
+  <si>
+    <t>2017-02-08</t>
+  </si>
+  <si>
+    <t>2017-06-23</t>
+  </si>
+  <si>
+    <t>2017-03-29</t>
+  </si>
+  <si>
+    <t>2017-11-15</t>
+  </si>
+  <si>
+    <t>2018-03-08</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>2018-04-18</t>
+  </si>
+  <si>
+    <t>2018-04-19</t>
+  </si>
+  <si>
+    <t>2018-04-20</t>
+  </si>
+  <si>
+    <t>2018-04-23</t>
+  </si>
+  <si>
+    <t>2018-05-04</t>
+  </si>
+  <si>
+    <t>2018-05-07</t>
+  </si>
+  <si>
+    <t>2018-05-08</t>
+  </si>
+  <si>
+    <t>2018-04-12</t>
+  </si>
+  <si>
+    <t>2018-11-16</t>
+  </si>
+  <si>
+    <t>2018-11-30</t>
+  </si>
+  <si>
+    <t>2018-12-03</t>
+  </si>
+  <si>
+    <t>2018-12-27</t>
+  </si>
+  <si>
+    <t>2019-01-03</t>
+  </si>
+  <si>
+    <t>2019-02-14</t>
+  </si>
+  <si>
+    <t>2019-02-20</t>
+  </si>
+  <si>
+    <t>2019-09-12</t>
+  </si>
+  <si>
+    <t>2019-09-16</t>
+  </si>
+  <si>
+    <t>2019-09-17</t>
+  </si>
+  <si>
+    <t>2019-09-18</t>
+  </si>
+  <si>
+    <t>2019-09-19</t>
+  </si>
+  <si>
+    <t>2019-09-23</t>
+  </si>
+  <si>
+    <t>2019-10-30</t>
+  </si>
+  <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
+    <t>2019-11-11</t>
+  </si>
+  <si>
+    <t>2019-11-14</t>
+  </si>
+  <si>
+    <t>2019-11-05</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2020-05-29</t>
+  </si>
+  <si>
+    <t>2020-06-03</t>
+  </si>
+  <si>
+    <t>2020-06-04</t>
+  </si>
+  <si>
+    <t>2021-02-17</t>
+  </si>
+  <si>
+    <t>2021-03-23</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>2021-03-29</t>
+  </si>
+  <si>
+    <t>2021-08-05</t>
+  </si>
+  <si>
+    <t>2010-08-03</t>
+  </si>
+  <si>
+    <t>2010-08-19</t>
+  </si>
+  <si>
+    <t>2010-08-26</t>
+  </si>
+  <si>
+    <t>2010-08-27</t>
+  </si>
+  <si>
+    <t>2010-08-30</t>
+  </si>
+  <si>
+    <t>2010-09-17</t>
+  </si>
+  <si>
+    <t>2010-09-20</t>
+  </si>
+  <si>
+    <t>2010-09-21</t>
+  </si>
+  <si>
+    <t>2010-09-23</t>
+  </si>
+  <si>
+    <t>2010-09-24</t>
+  </si>
+  <si>
+    <t>2010-09-27</t>
+  </si>
+  <si>
+    <t>2010-09-28</t>
+  </si>
+  <si>
+    <t>2010-09-29</t>
+  </si>
+  <si>
+    <t>2010-09-30</t>
+  </si>
+  <si>
+    <t>2010-10-01</t>
+  </si>
+  <si>
+    <t>2010-10-04</t>
+  </si>
+  <si>
+    <t>2010-10-05</t>
+  </si>
+  <si>
+    <t>2010-10-06</t>
+  </si>
+  <si>
+    <t>2010-10-07</t>
+  </si>
+  <si>
+    <t>2010-10-08</t>
+  </si>
+  <si>
+    <t>2010-10-11</t>
+  </si>
+  <si>
+    <t>2010-11-24</t>
+  </si>
+  <si>
+    <t>2010-11-25</t>
+  </si>
+  <si>
+    <t>2010-11-26</t>
+  </si>
+  <si>
+    <t>2010-11-29</t>
+  </si>
+  <si>
+    <t>2010-11-30</t>
+  </si>
+  <si>
+    <t>2010-12-01</t>
+  </si>
+  <si>
+    <t>2010-12-02</t>
+  </si>
+  <si>
+    <t>2010-12-03</t>
+  </si>
+  <si>
+    <t>2011-06-24</t>
+  </si>
+  <si>
+    <t>2011-06-27</t>
+  </si>
+  <si>
+    <t>2011-06-30</t>
+  </si>
+  <si>
+    <t>2011-07-07</t>
+  </si>
+  <si>
+    <t>2011-12-02</t>
+  </si>
+  <si>
+    <t>2011-12-05</t>
+  </si>
+  <si>
+    <t>2012-02-24</t>
+  </si>
+  <si>
+    <t>2012-03-02</t>
+  </si>
+  <si>
+    <t>2012-03-06</t>
+  </si>
+  <si>
+    <t>2012-03-07</t>
+  </si>
+  <si>
+    <t>2012-03-12</t>
+  </si>
+  <si>
+    <t>2012-03-13</t>
+  </si>
+  <si>
+    <t>2012-03-29</t>
+  </si>
+  <si>
+    <t>2012-03-30</t>
+  </si>
+  <si>
+    <t>2012-05-03</t>
+  </si>
+  <si>
+    <t>2012-05-15</t>
+  </si>
+  <si>
+    <t>2012-05-16</t>
+  </si>
+  <si>
+    <t>2012-05-17</t>
+  </si>
+  <si>
+    <t>2012-05-18</t>
+  </si>
+  <si>
+    <t>2012-05-21</t>
+  </si>
+  <si>
+    <t>2012-05-22</t>
+  </si>
+  <si>
+    <t>2012-05-23</t>
+  </si>
+  <si>
+    <t>2012-05-24</t>
+  </si>
+  <si>
+    <t>2012-05-28</t>
+  </si>
+  <si>
+    <t>2012-05-29</t>
+  </si>
+  <si>
+    <t>2012-05-30</t>
+  </si>
+  <si>
+    <t>2012-05-31</t>
+  </si>
+  <si>
+    <t>2012-06-01</t>
+  </si>
+  <si>
+    <t>2012-06-04</t>
+  </si>
+  <si>
+    <t>2012-06-05</t>
+  </si>
+  <si>
+    <t>2012-06-06</t>
+  </si>
+  <si>
+    <t>2012-06-07</t>
+  </si>
+  <si>
+    <t>2012-06-08</t>
+  </si>
+  <si>
+    <t>2012-06-11</t>
+  </si>
+  <si>
+    <t>2012-06-12</t>
+  </si>
+  <si>
+    <t>2012-06-13</t>
+  </si>
+  <si>
+    <t>2012-06-14</t>
+  </si>
+  <si>
+    <t>2012-06-15</t>
+  </si>
+  <si>
+    <t>2012-06-19</t>
+  </si>
+  <si>
+    <t>2012-06-20</t>
+  </si>
+  <si>
+    <t>2012-06-22</t>
+  </si>
+  <si>
+    <t>2012-10-18</t>
+  </si>
+  <si>
+    <t>2012-10-19</t>
+  </si>
+  <si>
+    <t>2012-10-22</t>
+  </si>
+  <si>
+    <t>2013-04-08</t>
+  </si>
+  <si>
+    <t>2013-04-12</t>
+  </si>
+  <si>
+    <t>2013-06-25</t>
+  </si>
+  <si>
+    <t>2013-06-27</t>
+  </si>
+  <si>
+    <t>2013-06-28</t>
+  </si>
+  <si>
+    <t>2013-07-01</t>
+  </si>
+  <si>
+    <t>2013-07-02</t>
+  </si>
+  <si>
+    <t>2013-07-03</t>
+  </si>
+  <si>
+    <t>2013-07-04</t>
+  </si>
+  <si>
+    <t>2013-10-28</t>
+  </si>
+  <si>
+    <t>2014-01-22</t>
+  </si>
+  <si>
+    <t>2014-01-23</t>
+  </si>
+  <si>
+    <t>2014-01-24</t>
+  </si>
+  <si>
+    <t>2014-01-27</t>
+  </si>
+  <si>
+    <t>2014-02-06</t>
+  </si>
+  <si>
+    <t>2014-02-07</t>
+  </si>
+  <si>
+    <t>2014-02-10</t>
+  </si>
+  <si>
+    <t>2014-02-11</t>
+  </si>
+  <si>
+    <t>2014-02-18</t>
+  </si>
+  <si>
+    <t>2014-02-20</t>
+  </si>
+  <si>
+    <t>2014-02-21</t>
+  </si>
+  <si>
+    <t>2014-07-08</t>
+  </si>
+  <si>
+    <t>2014-07-10</t>
+  </si>
+  <si>
+    <t>2014-07-11</t>
+  </si>
+  <si>
+    <t>2014-07-16</t>
+  </si>
+  <si>
+    <t>2014-07-17</t>
+  </si>
+  <si>
+    <t>2014-07-18</t>
+  </si>
+  <si>
+    <t>2014-10-15</t>
+  </si>
+  <si>
+    <t>2014-11-04</t>
+  </si>
+  <si>
+    <t>2015-06-11</t>
+  </si>
+  <si>
+    <t>2015-06-12</t>
+  </si>
+  <si>
+    <t>2015-06-15</t>
+  </si>
+  <si>
+    <t>2015-07-22</t>
+  </si>
+  <si>
+    <t>2015-07-23</t>
+  </si>
+  <si>
+    <t>2015-10-15</t>
+  </si>
+  <si>
+    <t>2015-10-16</t>
+  </si>
+  <si>
+    <t>2015-11-19</t>
+  </si>
+  <si>
+    <t>2016-04-01</t>
+  </si>
+  <si>
+    <t>2016-04-07</t>
+  </si>
+  <si>
+    <t>2016-04-08</t>
+  </si>
+  <si>
+    <t>2016-04-15</t>
+  </si>
+  <si>
+    <t>2016-04-18</t>
+  </si>
+  <si>
+    <t>2016-04-19</t>
+  </si>
+  <si>
+    <t>2016-04-21</t>
+  </si>
+  <si>
+    <t>2016-04-22</t>
+  </si>
+  <si>
+    <t>2016-04-27</t>
+  </si>
+  <si>
+    <t>2016-04-28</t>
+  </si>
+  <si>
+    <t>2016-05-03</t>
+  </si>
+  <si>
+    <t>2016-05-05</t>
+  </si>
+  <si>
+    <t>2016-05-10</t>
+  </si>
+  <si>
+    <t>2016-05-11</t>
+  </si>
+  <si>
+    <t>2016-05-12</t>
+  </si>
+  <si>
+    <t>2016-05-13</t>
+  </si>
+  <si>
+    <t>2016-05-16</t>
+  </si>
+  <si>
+    <t>2016-05-17</t>
+  </si>
+  <si>
+    <t>2016-10-27</t>
+  </si>
+  <si>
+    <t>2016-12-15</t>
+  </si>
+  <si>
+    <t>2017-06-26</t>
+  </si>
+  <si>
+    <t>2017-06-27</t>
+  </si>
+  <si>
+    <t>2017-07-11</t>
+  </si>
+  <si>
+    <t>2017-07-12</t>
+  </si>
+  <si>
+    <t>2017-07-13</t>
+  </si>
+  <si>
+    <t>2017-07-14</t>
+  </si>
+  <si>
+    <t>2017-07-17</t>
+  </si>
+  <si>
+    <t>2017-08-21</t>
+  </si>
+  <si>
+    <t>2017-08-22</t>
+  </si>
+  <si>
+    <t>2017-08-23</t>
+  </si>
+  <si>
+    <t>2017-08-24</t>
+  </si>
+  <si>
+    <t>2017-08-25</t>
+  </si>
+  <si>
+    <t>2017-09-06</t>
+  </si>
+  <si>
+    <t>2017-09-07</t>
+  </si>
+  <si>
+    <t>2017-09-08</t>
+  </si>
+  <si>
+    <t>2018-01-12</t>
+  </si>
+  <si>
+    <t>2018-01-15</t>
+  </si>
+  <si>
+    <t>2018-01-16</t>
+  </si>
+  <si>
+    <t>2018-01-17</t>
+  </si>
+  <si>
+    <t>2018-01-30</t>
+  </si>
+  <si>
+    <t>2018-01-31</t>
+  </si>
+  <si>
+    <t>2018-02-06</t>
+  </si>
+  <si>
+    <t>2018-02-22</t>
+  </si>
+  <si>
+    <t>2018-03-30</t>
+  </si>
+  <si>
+    <t>2018-05-16</t>
+  </si>
+  <si>
+    <t>2018-05-21</t>
+  </si>
+  <si>
+    <t>2018-11-20</t>
+  </si>
+  <si>
+    <t>2018-12-28</t>
+  </si>
+  <si>
+    <t>2019-01-09</t>
+  </si>
+  <si>
+    <t>2019-01-10</t>
+  </si>
+  <si>
+    <t>2019-01-15</t>
+  </si>
+  <si>
+    <t>2019-01-16</t>
+  </si>
+  <si>
+    <t>2019-01-17</t>
+  </si>
+  <si>
+    <t>2019-01-18</t>
+  </si>
+  <si>
+    <t>2019-01-22</t>
+  </si>
+  <si>
+    <t>2019-01-23</t>
+  </si>
+  <si>
+    <t>2019-01-24</t>
+  </si>
+  <si>
+    <t>2019-01-25</t>
+  </si>
+  <si>
+    <t>2019-01-29</t>
+  </si>
+  <si>
+    <t>2019-03-11</t>
+  </si>
+  <si>
+    <t>2019-03-12</t>
+  </si>
+  <si>
+    <t>2019-03-13</t>
+  </si>
+  <si>
+    <t>2019-04-09</t>
+  </si>
+  <si>
+    <t>2019-04-10</t>
+  </si>
+  <si>
+    <t>2019-04-18</t>
+  </si>
+  <si>
+    <t>2019-04-19</t>
+  </si>
+  <si>
+    <t>2019-04-25</t>
+  </si>
+  <si>
+    <t>2019-04-26</t>
+  </si>
+  <si>
+    <t>2019-05-02</t>
+  </si>
+  <si>
+    <t>2019-05-07</t>
+  </si>
+  <si>
+    <t>2019-05-08</t>
+  </si>
+  <si>
+    <t>2019-05-09</t>
+  </si>
+  <si>
+    <t>2019-05-10</t>
+  </si>
+  <si>
+    <t>2019-05-13</t>
+  </si>
+  <si>
+    <t>2019-07-29</t>
+  </si>
+  <si>
+    <t>2019-08-29</t>
+  </si>
+  <si>
+    <t>2019-08-30</t>
+  </si>
+  <si>
+    <t>2019-09-02</t>
+  </si>
+  <si>
+    <t>2019-09-03</t>
+  </si>
+  <si>
+    <t>2019-09-04</t>
+  </si>
+  <si>
+    <t>2019-09-05</t>
+  </si>
+  <si>
+    <t>2019-09-06</t>
+  </si>
+  <si>
+    <t>2019-09-10</t>
+  </si>
+  <si>
+    <t>2020-02-20</t>
+  </si>
+  <si>
+    <t>2020-02-21</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>2020-02-27</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-03-04</t>
+  </si>
+  <si>
+    <t>2020-03-05</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2020-03-09</t>
+  </si>
+  <si>
+    <t>2020-03-12</t>
+  </si>
+  <si>
+    <t>2020-11-02</t>
+  </si>
+  <si>
+    <t>2020-12-28</t>
+  </si>
+  <si>
     <t>2020-12-29</t>
   </si>
   <si>
-    <t>2021-01-19</t>
-  </si>
-  <si>
-    <t>2021-01-14</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>2021-01-28</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>2021-07-26</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>2010-10-22</t>
-  </si>
-  <si>
-    <t>2010-10-25</t>
-  </si>
-  <si>
-    <t>2010-10-28</t>
-  </si>
-  <si>
-    <t>2011-05-13</t>
-  </si>
-  <si>
-    <t>2011-05-16</t>
-  </si>
-  <si>
-    <t>2011-05-17</t>
-  </si>
-  <si>
-    <t>2011-05-18</t>
-  </si>
-  <si>
-    <t>2011-05-19</t>
-  </si>
-  <si>
-    <t>2011-05-20</t>
-  </si>
-  <si>
-    <t>2011-05-23</t>
-  </si>
-  <si>
-    <t>2011-05-24</t>
-  </si>
-  <si>
-    <t>2011-05-25</t>
-  </si>
-  <si>
-    <t>2011-05-26</t>
-  </si>
-  <si>
-    <t>2011-05-27</t>
-  </si>
-  <si>
-    <t>2011-05-30</t>
-  </si>
-  <si>
-    <t>2011-05-31</t>
-  </si>
-  <si>
-    <t>2011-06-02</t>
-  </si>
-  <si>
-    <t>2011-06-03</t>
-  </si>
-  <si>
-    <t>2011-07-22</t>
-  </si>
-  <si>
-    <t>2011-07-25</t>
-  </si>
-  <si>
-    <t>2011-07-27</t>
-  </si>
-  <si>
-    <t>2011-07-28</t>
-  </si>
-  <si>
-    <t>2011-07-29</t>
-  </si>
-  <si>
-    <t>2011-10-07</t>
-  </si>
-  <si>
-    <t>2011-10-05</t>
-  </si>
-  <si>
-    <t>2012-02-29</t>
-  </si>
-  <si>
-    <t>2012-07-18</t>
-  </si>
-  <si>
-    <t>2012-05-02</t>
-  </si>
-  <si>
-    <t>2012-05-25</t>
-  </si>
-  <si>
-    <t>2012-11-13</t>
-  </si>
-  <si>
-    <t>2012-11-14</t>
-  </si>
-  <si>
-    <t>2012-12-14</t>
-  </si>
-  <si>
-    <t>2012-08-01</t>
-  </si>
-  <si>
-    <t>2013-06-14</t>
-  </si>
-  <si>
-    <t>2013-06-17</t>
-  </si>
-  <si>
-    <t>2013-06-18</t>
-  </si>
-  <si>
-    <t>2013-05-20</t>
-  </si>
-  <si>
-    <t>2013-08-06</t>
-  </si>
-  <si>
-    <t>2013-05-16</t>
-  </si>
-  <si>
-    <t>2013-11-28</t>
-  </si>
-  <si>
-    <t>2013-12-04</t>
-  </si>
-  <si>
-    <t>2014-02-17</t>
-  </si>
-  <si>
-    <t>2014-02-19</t>
-  </si>
-  <si>
-    <t>2013-08-07</t>
-  </si>
-  <si>
-    <t>2013-08-08</t>
-  </si>
-  <si>
-    <t>2013-08-09</t>
-  </si>
-  <si>
-    <t>2013-09-23</t>
-  </si>
-  <si>
-    <t>2014-04-25</t>
-  </si>
-  <si>
-    <t>2014-04-24</t>
-  </si>
-  <si>
-    <t>2014-09-15</t>
-  </si>
-  <si>
-    <t>2014-12-02</t>
-  </si>
-  <si>
-    <t>2014-09-10</t>
-  </si>
-  <si>
-    <t>2014-09-04</t>
-  </si>
-  <si>
-    <t>2014-11-11</t>
-  </si>
-  <si>
-    <t>2014-09-03</t>
-  </si>
-  <si>
-    <t>2014-11-03</t>
-  </si>
-  <si>
-    <t>2014-11-27</t>
-  </si>
-  <si>
-    <t>2015-03-18</t>
-  </si>
-  <si>
-    <t>2015-08-07</t>
-  </si>
-  <si>
-    <t>2016-03-16</t>
-  </si>
-  <si>
-    <t>2016-03-17</t>
-  </si>
-  <si>
-    <t>2016-02-01</t>
-  </si>
-  <si>
-    <t>2016-02-02</t>
-  </si>
-  <si>
-    <t>2016-07-18</t>
-  </si>
-  <si>
-    <t>2016-06-30</t>
-  </si>
-  <si>
-    <t>2016-08-03</t>
-  </si>
-  <si>
-    <t>2016-07-01</t>
-  </si>
-  <si>
-    <t>2017-02-08</t>
-  </si>
-  <si>
-    <t>2017-06-23</t>
-  </si>
-  <si>
-    <t>2017-03-29</t>
-  </si>
-  <si>
-    <t>2017-11-15</t>
-  </si>
-  <si>
-    <t>2018-03-08</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>2018-04-18</t>
-  </si>
-  <si>
-    <t>2018-04-19</t>
-  </si>
-  <si>
-    <t>2018-04-20</t>
-  </si>
-  <si>
-    <t>2018-04-23</t>
-  </si>
-  <si>
-    <t>2018-05-04</t>
-  </si>
-  <si>
-    <t>2018-05-07</t>
-  </si>
-  <si>
-    <t>2018-05-08</t>
-  </si>
-  <si>
-    <t>2018-04-12</t>
-  </si>
-  <si>
-    <t>2018-11-16</t>
-  </si>
-  <si>
-    <t>2018-11-30</t>
-  </si>
-  <si>
-    <t>2018-12-03</t>
-  </si>
-  <si>
-    <t>2018-12-27</t>
-  </si>
-  <si>
-    <t>2019-01-03</t>
-  </si>
-  <si>
-    <t>2019-02-14</t>
-  </si>
-  <si>
-    <t>2019-02-20</t>
-  </si>
-  <si>
-    <t>2019-09-12</t>
-  </si>
-  <si>
-    <t>2019-09-16</t>
-  </si>
-  <si>
-    <t>2019-09-17</t>
-  </si>
-  <si>
-    <t>2019-09-18</t>
-  </si>
-  <si>
-    <t>2019-09-19</t>
-  </si>
-  <si>
-    <t>2019-09-23</t>
-  </si>
-  <si>
-    <t>2019-10-30</t>
-  </si>
-  <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
-    <t>2019-11-11</t>
-  </si>
-  <si>
-    <t>2019-11-14</t>
-  </si>
-  <si>
-    <t>2019-11-05</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2020-05-29</t>
-  </si>
-  <si>
-    <t>2020-06-03</t>
-  </si>
-  <si>
-    <t>2020-06-04</t>
-  </si>
-  <si>
-    <t>2021-02-17</t>
-  </si>
-  <si>
-    <t>2021-03-23</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>2021-03-29</t>
-  </si>
-  <si>
-    <t>2010-08-03</t>
-  </si>
-  <si>
-    <t>2010-08-19</t>
-  </si>
-  <si>
-    <t>2010-08-26</t>
-  </si>
-  <si>
-    <t>2010-08-27</t>
-  </si>
-  <si>
-    <t>2010-08-30</t>
-  </si>
-  <si>
-    <t>2010-09-17</t>
-  </si>
-  <si>
-    <t>2010-09-20</t>
-  </si>
-  <si>
-    <t>2010-09-21</t>
-  </si>
-  <si>
-    <t>2010-09-23</t>
-  </si>
-  <si>
-    <t>2010-09-24</t>
-  </si>
-  <si>
-    <t>2010-09-27</t>
-  </si>
-  <si>
-    <t>2010-09-28</t>
-  </si>
-  <si>
-    <t>2010-09-29</t>
-  </si>
-  <si>
-    <t>2010-09-30</t>
-  </si>
-  <si>
-    <t>2010-10-01</t>
-  </si>
-  <si>
-    <t>2010-10-04</t>
-  </si>
-  <si>
-    <t>2010-10-05</t>
-  </si>
-  <si>
-    <t>2010-10-06</t>
-  </si>
-  <si>
-    <t>2010-10-07</t>
-  </si>
-  <si>
-    <t>2010-10-08</t>
-  </si>
-  <si>
-    <t>2010-10-11</t>
-  </si>
-  <si>
-    <t>2010-11-24</t>
-  </si>
-  <si>
-    <t>2010-11-25</t>
-  </si>
-  <si>
-    <t>2010-11-26</t>
-  </si>
-  <si>
-    <t>2010-11-29</t>
-  </si>
-  <si>
-    <t>2010-11-30</t>
-  </si>
-  <si>
-    <t>2010-12-01</t>
-  </si>
-  <si>
-    <t>2010-12-02</t>
-  </si>
-  <si>
-    <t>2010-12-03</t>
-  </si>
-  <si>
-    <t>2011-06-24</t>
-  </si>
-  <si>
-    <t>2011-06-27</t>
-  </si>
-  <si>
-    <t>2011-06-30</t>
-  </si>
-  <si>
-    <t>2011-07-07</t>
-  </si>
-  <si>
-    <t>2011-12-02</t>
-  </si>
-  <si>
-    <t>2011-12-05</t>
-  </si>
-  <si>
-    <t>2012-02-24</t>
-  </si>
-  <si>
-    <t>2012-03-02</t>
-  </si>
-  <si>
-    <t>2012-03-06</t>
-  </si>
-  <si>
-    <t>2012-03-07</t>
-  </si>
-  <si>
-    <t>2012-03-12</t>
-  </si>
-  <si>
-    <t>2012-03-13</t>
-  </si>
-  <si>
-    <t>2012-03-29</t>
-  </si>
-  <si>
-    <t>2012-03-30</t>
-  </si>
-  <si>
-    <t>2012-05-03</t>
-  </si>
-  <si>
-    <t>2012-05-15</t>
-  </si>
-  <si>
-    <t>2012-05-16</t>
-  </si>
-  <si>
-    <t>2012-05-17</t>
-  </si>
-  <si>
-    <t>2012-05-18</t>
-  </si>
-  <si>
-    <t>2012-05-21</t>
-  </si>
-  <si>
-    <t>2012-05-22</t>
-  </si>
-  <si>
-    <t>2012-05-23</t>
-  </si>
-  <si>
-    <t>2012-05-24</t>
-  </si>
-  <si>
-    <t>2012-05-28</t>
-  </si>
-  <si>
-    <t>2012-05-29</t>
-  </si>
-  <si>
-    <t>2012-05-30</t>
-  </si>
-  <si>
-    <t>2012-05-31</t>
-  </si>
-  <si>
-    <t>2012-06-01</t>
-  </si>
-  <si>
-    <t>2012-06-04</t>
-  </si>
-  <si>
-    <t>2012-06-05</t>
-  </si>
-  <si>
-    <t>2012-06-06</t>
-  </si>
-  <si>
-    <t>2012-06-07</t>
-  </si>
-  <si>
-    <t>2012-06-08</t>
-  </si>
-  <si>
-    <t>2012-06-11</t>
-  </si>
-  <si>
-    <t>2012-06-12</t>
-  </si>
-  <si>
-    <t>2012-06-13</t>
-  </si>
-  <si>
-    <t>2012-06-14</t>
-  </si>
-  <si>
-    <t>2012-06-15</t>
-  </si>
-  <si>
-    <t>2012-06-19</t>
-  </si>
-  <si>
-    <t>2012-06-20</t>
-  </si>
-  <si>
-    <t>2012-06-22</t>
-  </si>
-  <si>
-    <t>2012-10-18</t>
-  </si>
-  <si>
-    <t>2012-10-19</t>
-  </si>
-  <si>
-    <t>2012-10-22</t>
-  </si>
-  <si>
-    <t>2013-04-08</t>
-  </si>
-  <si>
-    <t>2013-04-12</t>
-  </si>
-  <si>
-    <t>2013-06-25</t>
-  </si>
-  <si>
-    <t>2013-06-27</t>
-  </si>
-  <si>
-    <t>2013-06-28</t>
-  </si>
-  <si>
-    <t>2013-07-01</t>
-  </si>
-  <si>
-    <t>2013-07-02</t>
-  </si>
-  <si>
-    <t>2013-07-03</t>
-  </si>
-  <si>
-    <t>2013-07-04</t>
-  </si>
-  <si>
-    <t>2013-10-28</t>
-  </si>
-  <si>
-    <t>2014-01-22</t>
-  </si>
-  <si>
-    <t>2014-01-23</t>
-  </si>
-  <si>
-    <t>2014-01-24</t>
-  </si>
-  <si>
-    <t>2014-01-27</t>
-  </si>
-  <si>
-    <t>2014-02-06</t>
-  </si>
-  <si>
-    <t>2014-02-07</t>
-  </si>
-  <si>
-    <t>2014-02-10</t>
-  </si>
-  <si>
-    <t>2014-02-11</t>
-  </si>
-  <si>
-    <t>2014-02-18</t>
-  </si>
-  <si>
-    <t>2014-02-20</t>
-  </si>
-  <si>
-    <t>2014-02-21</t>
-  </si>
-  <si>
-    <t>2014-07-08</t>
-  </si>
-  <si>
-    <t>2014-07-10</t>
-  </si>
-  <si>
-    <t>2014-07-11</t>
-  </si>
-  <si>
-    <t>2014-07-16</t>
-  </si>
-  <si>
-    <t>2014-07-17</t>
-  </si>
-  <si>
-    <t>2014-07-18</t>
-  </si>
-  <si>
-    <t>2014-10-15</t>
-  </si>
-  <si>
-    <t>2014-11-04</t>
-  </si>
-  <si>
-    <t>2015-06-11</t>
-  </si>
-  <si>
-    <t>2015-06-12</t>
-  </si>
-  <si>
-    <t>2015-06-15</t>
-  </si>
-  <si>
-    <t>2015-07-22</t>
-  </si>
-  <si>
-    <t>2015-07-23</t>
-  </si>
-  <si>
-    <t>2015-10-15</t>
-  </si>
-  <si>
-    <t>2015-10-16</t>
-  </si>
-  <si>
-    <t>2015-11-19</t>
-  </si>
-  <si>
-    <t>2016-04-01</t>
-  </si>
-  <si>
-    <t>2016-04-07</t>
-  </si>
-  <si>
-    <t>2016-04-08</t>
-  </si>
-  <si>
-    <t>2016-04-15</t>
-  </si>
-  <si>
-    <t>2016-04-18</t>
-  </si>
-  <si>
-    <t>2016-04-19</t>
-  </si>
-  <si>
-    <t>2016-04-21</t>
-  </si>
-  <si>
-    <t>2016-04-22</t>
-  </si>
-  <si>
-    <t>2016-04-27</t>
-  </si>
-  <si>
-    <t>2016-04-28</t>
-  </si>
-  <si>
-    <t>2016-05-03</t>
-  </si>
-  <si>
-    <t>2016-05-05</t>
-  </si>
-  <si>
-    <t>2016-05-10</t>
-  </si>
-  <si>
-    <t>2016-05-11</t>
-  </si>
-  <si>
-    <t>2016-05-12</t>
-  </si>
-  <si>
-    <t>2016-05-13</t>
-  </si>
-  <si>
-    <t>2016-05-16</t>
-  </si>
-  <si>
-    <t>2016-05-17</t>
-  </si>
-  <si>
-    <t>2016-10-27</t>
-  </si>
-  <si>
-    <t>2016-12-15</t>
-  </si>
-  <si>
-    <t>2017-06-26</t>
-  </si>
-  <si>
-    <t>2017-06-27</t>
-  </si>
-  <si>
-    <t>2017-07-11</t>
-  </si>
-  <si>
-    <t>2017-07-12</t>
-  </si>
-  <si>
-    <t>2017-07-13</t>
-  </si>
-  <si>
-    <t>2017-07-14</t>
-  </si>
-  <si>
-    <t>2017-07-17</t>
-  </si>
-  <si>
-    <t>2017-08-21</t>
-  </si>
-  <si>
-    <t>2017-08-22</t>
-  </si>
-  <si>
-    <t>2017-08-23</t>
-  </si>
-  <si>
-    <t>2017-08-24</t>
-  </si>
-  <si>
-    <t>2017-08-25</t>
-  </si>
-  <si>
-    <t>2017-09-06</t>
-  </si>
-  <si>
-    <t>2017-09-07</t>
-  </si>
-  <si>
-    <t>2017-09-08</t>
-  </si>
-  <si>
-    <t>2018-01-12</t>
-  </si>
-  <si>
-    <t>2018-01-15</t>
-  </si>
-  <si>
-    <t>2018-01-16</t>
-  </si>
-  <si>
-    <t>2018-01-17</t>
-  </si>
-  <si>
-    <t>2018-01-30</t>
-  </si>
-  <si>
-    <t>2018-01-31</t>
-  </si>
-  <si>
-    <t>2018-02-06</t>
-  </si>
-  <si>
-    <t>2018-02-22</t>
-  </si>
-  <si>
-    <t>2018-03-30</t>
-  </si>
-  <si>
-    <t>2018-05-16</t>
-  </si>
-  <si>
-    <t>2018-05-21</t>
-  </si>
-  <si>
-    <t>2018-11-20</t>
-  </si>
-  <si>
-    <t>2018-12-28</t>
-  </si>
-  <si>
-    <t>2019-01-09</t>
-  </si>
-  <si>
-    <t>2019-01-10</t>
-  </si>
-  <si>
-    <t>2019-01-15</t>
-  </si>
-  <si>
-    <t>2019-01-16</t>
-  </si>
-  <si>
-    <t>2019-01-17</t>
-  </si>
-  <si>
-    <t>2019-01-18</t>
-  </si>
-  <si>
-    <t>2019-01-22</t>
-  </si>
-  <si>
-    <t>2019-01-23</t>
-  </si>
-  <si>
-    <t>2019-01-24</t>
-  </si>
-  <si>
-    <t>2019-01-25</t>
-  </si>
-  <si>
-    <t>2019-01-29</t>
-  </si>
-  <si>
-    <t>2019-03-11</t>
-  </si>
-  <si>
-    <t>2019-03-12</t>
-  </si>
-  <si>
-    <t>2019-03-13</t>
-  </si>
-  <si>
-    <t>2019-04-09</t>
-  </si>
-  <si>
-    <t>2019-04-10</t>
-  </si>
-  <si>
-    <t>2019-04-18</t>
-  </si>
-  <si>
-    <t>2019-04-19</t>
-  </si>
-  <si>
-    <t>2019-04-25</t>
-  </si>
-  <si>
-    <t>2019-04-26</t>
-  </si>
-  <si>
-    <t>2019-05-02</t>
-  </si>
-  <si>
-    <t>2019-05-07</t>
-  </si>
-  <si>
-    <t>2019-05-08</t>
-  </si>
-  <si>
-    <t>2019-05-09</t>
-  </si>
-  <si>
-    <t>2019-05-10</t>
-  </si>
-  <si>
-    <t>2019-05-13</t>
-  </si>
-  <si>
-    <t>2019-07-29</t>
-  </si>
-  <si>
-    <t>2019-08-29</t>
-  </si>
-  <si>
-    <t>2019-08-30</t>
-  </si>
-  <si>
-    <t>2019-09-02</t>
-  </si>
-  <si>
-    <t>2019-09-03</t>
-  </si>
-  <si>
-    <t>2019-09-04</t>
-  </si>
-  <si>
-    <t>2019-09-05</t>
-  </si>
-  <si>
-    <t>2019-09-06</t>
-  </si>
-  <si>
-    <t>2019-09-10</t>
-  </si>
-  <si>
-    <t>2020-02-20</t>
-  </si>
-  <si>
-    <t>2020-02-21</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-02-26</t>
-  </si>
-  <si>
-    <t>2020-02-27</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-03-04</t>
-  </si>
-  <si>
-    <t>2020-03-05</t>
-  </si>
-  <si>
-    <t>2020-03-06</t>
-  </si>
-  <si>
-    <t>2020-03-09</t>
-  </si>
-  <si>
-    <t>2020-03-12</t>
-  </si>
-  <si>
-    <t>2020-11-02</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-23</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>2020-12-28</t>
-  </si>
-  <si>
-    <t>2021-01-05</t>
-  </si>
-  <si>
     <t>2021-01-06</t>
   </si>
   <si>
@@ -1421,6 +1415,9 @@
   </si>
   <si>
     <t>2021-06-18</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
   </si>
 </sst>
 </file>
@@ -1778,7 +1775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P378"/>
+  <dimension ref="A1:P375"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1839,7 +1836,7 @@
         <v>39.24967816269653</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E2">
         <v>47.58658728904034</v>
@@ -1875,7 +1872,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1889,7 +1886,7 @@
         <v>41.7045814878046</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E3">
         <v>51.36624085194781</v>
@@ -1925,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1939,7 +1936,7 @@
         <v>47.73273319613877</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E4">
         <v>59.43490802303255</v>
@@ -1975,7 +1972,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1989,7 +1986,7 @@
         <v>47.24820828667414</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E5">
         <v>58.87563172501095</v>
@@ -2025,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2039,7 +2036,7 @@
         <v>47.16470096247878</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E6">
         <v>58.77924108291729</v>
@@ -2075,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2089,7 +2086,7 @@
         <v>-15.1664654510749</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E7">
         <v>-7.294892481790129</v>
@@ -2125,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2139,7 +2136,7 @@
         <v>-14.45834344229912</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E8">
         <v>-7.294892481790129</v>
@@ -2175,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2189,7 +2186,7 @@
         <v>-13.39336737209288</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E9">
         <v>-7.294892481790129</v>
@@ -2225,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2239,7 +2236,7 @@
         <v>-16.33245230627455</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E10">
         <v>-7.294892481790129</v>
@@ -2275,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2289,7 +2286,7 @@
         <v>-29.63643996743208</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E11">
         <v>-21.37792699357366</v>
@@ -2325,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2339,7 +2336,7 @@
         <v>-29.01030081710592</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E12">
         <v>-21.37792699357366</v>
@@ -2375,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2389,7 +2386,7 @@
         <v>-28.60118761449661</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E13">
         <v>-21.37792699357366</v>
@@ -2425,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2439,7 +2436,7 @@
         <v>-49.08464630848418</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E14">
         <v>-42.77667080227592</v>
@@ -2475,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2489,7 +2486,7 @@
         <v>-48.56869529606767</v>
       </c>
       <c r="D15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E15">
         <v>-42.77667080227592</v>
@@ -2525,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2539,7 +2536,7 @@
         <v>-49.0410871967355</v>
       </c>
       <c r="D16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E16">
         <v>-42.77667080227592</v>
@@ -2575,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2589,7 +2586,7 @@
         <v>-65.70804604683664</v>
       </c>
       <c r="D17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E17">
         <v>-56.94115587886895</v>
@@ -2625,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2639,7 +2636,7 @@
         <v>-65.6116252316011</v>
       </c>
       <c r="D18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E18">
         <v>-56.94115587886895</v>
@@ -2675,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2689,7 +2686,7 @@
         <v>-79.57406496333017</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E19">
         <v>-67.54165070713992</v>
@@ -2725,7 +2722,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2739,7 +2736,7 @@
         <v>-113.1125372679468</v>
       </c>
       <c r="D20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E20">
         <v>-103.9345101187686</v>
@@ -2775,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2789,7 +2786,7 @@
         <v>-150.4700278614179</v>
       </c>
       <c r="D21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E21">
         <v>-141.3269680910878</v>
@@ -2825,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2839,7 +2836,7 @@
         <v>-191.2456393652701</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E22">
         <v>-165.2314426418361</v>
@@ -2875,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2889,7 +2886,7 @@
         <v>-208.9753900042601</v>
       </c>
       <c r="D23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E23">
         <v>-181.8698454183375</v>
@@ -2925,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2939,7 +2936,7 @@
         <v>-222.2487414251906</v>
       </c>
       <c r="D24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E24">
         <v>-206.4607237347662</v>
@@ -2975,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2989,7 +2986,7 @@
         <v>-239.7112109310854</v>
       </c>
       <c r="D25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E25">
         <v>-219.5184020745525</v>
@@ -3025,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3039,7 +3036,7 @@
         <v>-263.1154559964206</v>
       </c>
       <c r="D26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E26">
         <v>-240.6747187530921</v>
@@ -3075,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3089,7 +3086,7 @@
         <v>-268.6224791106823</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E27">
         <v>-252.6279978948062</v>
@@ -3125,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3154,7 +3151,7 @@
         <v>59.3</v>
       </c>
       <c r="P28" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3183,7 +3180,7 @@
         <v>65.5</v>
       </c>
       <c r="P29" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3197,7 +3194,7 @@
         <v>-254.0793405031437</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E30">
         <v>-235.7082244929039</v>
@@ -3233,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3247,7 +3244,7 @@
         <v>-238.7059320352077</v>
       </c>
       <c r="D31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E31">
         <v>-223.7765478327873</v>
@@ -3283,7 +3280,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3312,7 +3309,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="P32" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3362,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3376,7 +3373,7 @@
         <v>-85.8076603763717</v>
       </c>
       <c r="D34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E34">
         <v>-85.31060902491748</v>
@@ -3412,7 +3409,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3426,7 +3423,7 @@
         <v>-78.41701518144652</v>
       </c>
       <c r="D35" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E35">
         <v>-77.28396586589429</v>
@@ -3462,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3491,7 +3488,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="P36" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3520,7 +3517,7 @@
         <v>70.09999999999999</v>
       </c>
       <c r="P37" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3534,7 +3531,7 @@
         <v>-77.43890142953504</v>
       </c>
       <c r="D38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E38">
         <v>-86.03210595388953</v>
@@ -3570,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3584,7 +3581,7 @@
         <v>-75.24842836769179</v>
       </c>
       <c r="D39" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E39">
         <v>-82.41442691778926</v>
@@ -3620,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3634,7 +3631,7 @@
         <v>-75.26941837884658</v>
       </c>
       <c r="D40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E40">
         <v>-76.41687497573176</v>
@@ -3670,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3684,7 +3681,7 @@
         <v>2.405986219478436</v>
       </c>
       <c r="D41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E41">
         <v>22.3137495724129</v>
@@ -3720,7 +3717,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3734,7 +3731,7 @@
         <v>-1.953147134466214</v>
       </c>
       <c r="D42" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E42">
         <v>19.32012787151115</v>
@@ -3770,7 +3767,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3784,7 +3781,7 @@
         <v>-16.2502130791469</v>
       </c>
       <c r="D43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E43">
         <v>8.401660897453333</v>
@@ -3820,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3834,7 +3831,7 @@
         <v>-14.74859467309044</v>
       </c>
       <c r="D44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E44">
         <v>8.401660897453333</v>
@@ -3870,7 +3867,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3884,7 +3881,7 @@
         <v>-29.86968571903745</v>
       </c>
       <c r="D45" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E45">
         <v>-0.9514709154835543</v>
@@ -3920,7 +3917,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3934,7 +3931,7 @@
         <v>60.63454015125168</v>
       </c>
       <c r="D46" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E46">
         <v>75.91925407409063</v>
@@ -3970,7 +3967,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3984,7 +3981,7 @@
         <v>61.36441721922468</v>
       </c>
       <c r="D47" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E47">
         <v>75.91925407409063</v>
@@ -4020,7 +4017,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4034,7 +4031,7 @@
         <v>89.12505313226613</v>
       </c>
       <c r="D48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E48">
         <v>73.92461224371841</v>
@@ -4070,7 +4067,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4084,7 +4081,7 @@
         <v>60.18080332327113</v>
       </c>
       <c r="D49" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E49">
         <v>75.16419394721952</v>
@@ -4120,7 +4117,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4134,7 +4131,7 @@
         <v>60.90367287266527</v>
       </c>
       <c r="D50" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E50">
         <v>75.16419394721952</v>
@@ -4170,7 +4167,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4184,7 +4181,7 @@
         <v>88.41554187615753</v>
       </c>
       <c r="D51" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E51">
         <v>73.33247692380556</v>
@@ -4220,7 +4217,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4234,7 +4231,7 @@
         <v>39.99810912339372</v>
       </c>
       <c r="D52" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E52">
         <v>55.15583755182445</v>
@@ -4270,7 +4267,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4284,7 +4281,7 @@
         <v>41.30719414984996</v>
       </c>
       <c r="D53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E53">
         <v>55.15583755182445</v>
@@ -4320,7 +4317,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4334,7 +4331,7 @@
         <v>43.08151977105167</v>
       </c>
       <c r="D54" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E54">
         <v>55.9485635535138</v>
@@ -4370,7 +4367,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4384,7 +4381,7 @@
         <v>42.16532004667869</v>
       </c>
       <c r="D55" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E55">
         <v>55.9485635535138</v>
@@ -4420,7 +4417,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4434,7 +4431,7 @@
         <v>42.55008107334416</v>
       </c>
       <c r="D56" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E56">
         <v>56.30400099154195</v>
@@ -4484,7 +4481,7 @@
         <v>43.58368103616133</v>
       </c>
       <c r="D57" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E57">
         <v>56.30400099154195</v>
@@ -4534,7 +4531,7 @@
         <v>44.27504780738504</v>
       </c>
       <c r="D58" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E58">
         <v>56.96559598792828</v>
@@ -4570,7 +4567,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4584,7 +4581,7 @@
         <v>44.76828997217422</v>
       </c>
       <c r="D59" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E59">
         <v>57.43759805949687</v>
@@ -4634,7 +4631,7 @@
         <v>46.95250922066406</v>
       </c>
       <c r="D60" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E60">
         <v>58.6275946856681</v>
@@ -4670,7 +4667,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4684,7 +4681,7 @@
         <v>47.37813227189867</v>
       </c>
       <c r="D61" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E61">
         <v>59.01897220404476</v>
@@ -4720,7 +4717,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4734,7 +4731,7 @@
         <v>48.93720072957618</v>
       </c>
       <c r="D62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E62">
         <v>59.68207127489522</v>
@@ -4770,7 +4767,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4784,7 +4781,7 @@
         <v>48.94662890110423</v>
       </c>
       <c r="D63" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E63">
         <v>59.69094484809811</v>
@@ -4820,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4834,7 +4831,7 @@
         <v>54.08932335660573</v>
       </c>
       <c r="D64" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E64">
         <v>62.52278850035134</v>
@@ -4884,7 +4881,7 @@
         <v>67.18932335660573</v>
       </c>
       <c r="D65" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E65">
         <v>59.01736085156006</v>
@@ -4934,7 +4931,7 @@
         <v>54.27142458878302</v>
       </c>
       <c r="D66" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E66">
         <v>62.70264156916842</v>
@@ -4970,7 +4967,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4984,7 +4981,7 @@
         <v>67.37142458878301</v>
       </c>
       <c r="D67" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E67">
         <v>59.17608118479113</v>
@@ -5020,7 +5017,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5034,7 +5031,7 @@
         <v>54.44666418857609</v>
       </c>
       <c r="D68" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E68">
         <v>57.92296041603655</v>
@@ -5070,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="P68" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5084,7 +5081,7 @@
         <v>54.38623819452964</v>
       </c>
       <c r="D69" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E69">
         <v>62.81603772299223</v>
@@ -5120,7 +5117,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5134,7 +5131,7 @@
         <v>54.68320045790918</v>
       </c>
       <c r="D70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E70">
         <v>62.81603772299223</v>
@@ -5170,7 +5167,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5184,7 +5181,7 @@
         <v>67.48623819452963</v>
       </c>
       <c r="D71" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E71">
         <v>59.27615329054065</v>
@@ -5220,7 +5217,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5234,7 +5231,7 @@
         <v>54.5181037654851</v>
       </c>
       <c r="D72" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E72">
         <v>55.68274527440479</v>
@@ -5270,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="P72" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5284,7 +5281,7 @@
         <v>101.1269386779503</v>
       </c>
       <c r="D73" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E73">
         <v>83.94100067443752</v>
@@ -5320,7 +5317,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5334,7 +5331,7 @@
         <v>75.45009517739128</v>
       </c>
       <c r="D74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E74">
         <v>80.27451240300203</v>
@@ -5370,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5384,7 +5381,7 @@
         <v>121.9136696617972</v>
       </c>
       <c r="D75" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E75">
         <v>104.5517569407011</v>
@@ -5420,7 +5417,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5434,7 +5431,7 @@
         <v>124.0730248787269</v>
       </c>
       <c r="D76" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E76">
         <v>106.3319083146578</v>
@@ -5470,7 +5467,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5484,7 +5481,7 @@
         <v>125.8987716223492</v>
       </c>
       <c r="D77" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E77">
         <v>107.8370361179367</v>
@@ -5520,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5534,7 +5531,7 @@
         <v>127.8315078706938</v>
       </c>
       <c r="D78" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E78">
         <v>102.3788447068554</v>
@@ -5570,7 +5567,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5584,7 +5581,7 @@
         <v>127.8608026942557</v>
       </c>
       <c r="D79" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E79">
         <v>102.3788447068554</v>
@@ -5620,7 +5617,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5634,7 +5631,7 @@
         <v>126.3344628429377</v>
       </c>
       <c r="D80" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E80">
         <v>101.3477167540643</v>
@@ -5670,7 +5667,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5684,7 +5681,7 @@
         <v>126.3293867347399</v>
       </c>
       <c r="D81" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E81">
         <v>101.3477167540643</v>
@@ -5720,7 +5717,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5734,7 +5731,7 @@
         <v>126.0311094090764</v>
       </c>
       <c r="D82" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E82">
         <v>101.1387743378843</v>
@@ -5770,7 +5767,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5784,7 +5781,7 @@
         <v>126.0190685536726</v>
       </c>
       <c r="D83" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E83">
         <v>101.1387743378843</v>
@@ -5820,7 +5817,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5834,7 +5831,7 @@
         <v>126.620958855311</v>
       </c>
       <c r="D84" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E84">
         <v>101.5450481911581</v>
@@ -5870,7 +5867,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5884,7 +5881,7 @@
         <v>126.6224604616829</v>
       </c>
       <c r="D85" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E85">
         <v>101.5450481911581</v>
@@ -5920,7 +5917,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5934,7 +5931,7 @@
         <v>125.7796367080902</v>
       </c>
       <c r="D86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E86">
         <v>100.9655660999601</v>
@@ -5970,7 +5967,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5984,7 +5981,7 @@
         <v>125.7618222447556</v>
       </c>
       <c r="D87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E87">
         <v>100.9655660999601</v>
@@ -6020,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6034,7 +6031,7 @@
         <v>125.0669218669525</v>
       </c>
       <c r="D88" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E88">
         <v>100.4746655716255</v>
@@ -6070,7 +6067,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6084,7 +6081,7 @@
         <v>125.0327440526733</v>
       </c>
       <c r="D89" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E89">
         <v>100.4746655716255</v>
@@ -6120,7 +6117,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6134,7 +6131,7 @@
         <v>123.2289469739378</v>
       </c>
       <c r="D90" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E90">
         <v>99.20871347694691</v>
@@ -6170,7 +6167,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6184,7 +6181,7 @@
         <v>123.1525707565027</v>
       </c>
       <c r="D91" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E91">
         <v>99.20871347694691</v>
@@ -6220,7 +6217,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6234,7 +6231,7 @@
         <v>122.9583501275863</v>
       </c>
       <c r="D92" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E92">
         <v>99.02233299604161</v>
@@ -6270,7 +6267,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6284,7 +6281,7 @@
         <v>122.8757612274544</v>
       </c>
       <c r="D93" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E93">
         <v>99.02233299604161</v>
@@ -6320,7 +6317,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6334,7 +6331,7 @@
         <v>124.3519741722009</v>
       </c>
       <c r="D94" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E94">
         <v>99.98222710840369</v>
@@ -6370,7 +6367,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6384,7 +6381,7 @@
         <v>124.3013817424811</v>
       </c>
       <c r="D95" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E95">
         <v>99.98222710840369</v>
@@ -6420,7 +6417,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6434,7 +6431,7 @@
         <v>124.6891745905705</v>
       </c>
       <c r="D96" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E96">
         <v>100.2144824986073</v>
@@ -6470,7 +6467,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6484,7 +6481,7 @@
         <v>124.6463240071908</v>
       </c>
       <c r="D97" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E97">
         <v>100.2144824986073</v>
@@ -6520,7 +6517,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6534,7 +6531,7 @@
         <v>124.4800191586875</v>
       </c>
       <c r="D98" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E98">
         <v>100.0704213593001</v>
@@ -6570,7 +6567,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6584,7 +6581,7 @@
         <v>124.4323665373309</v>
       </c>
       <c r="D99" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E99">
         <v>100.0704213593001</v>
@@ -6620,7 +6617,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6634,7 +6631,7 @@
         <v>123.0108457893896</v>
       </c>
       <c r="D100" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E100">
         <v>99.05849072228368</v>
@@ -6670,7 +6667,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6684,7 +6681,7 @@
         <v>122.9294621467991</v>
       </c>
       <c r="D101" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E101">
         <v>99.05849072228368</v>
@@ -6720,7 +6717,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6734,7 +6731,7 @@
         <v>121.6453568496303</v>
       </c>
       <c r="D102" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E102">
         <v>98.11797538112289</v>
@@ -6770,7 +6767,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6784,7 +6781,7 @@
         <v>121.5326226956677</v>
       </c>
       <c r="D103" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E103">
         <v>98.11797538112289</v>
@@ -6820,7 +6817,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6834,7 +6831,7 @@
         <v>121.0299428079651</v>
       </c>
       <c r="D104" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E104">
         <v>97.69409326058823</v>
@@ -6870,7 +6867,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6884,7 +6881,7 @@
         <v>120.9030792499847</v>
       </c>
       <c r="D105" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E105">
         <v>97.69409326058823</v>
@@ -6920,7 +6917,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6934,7 +6931,7 @@
         <v>120.2680139970007</v>
       </c>
       <c r="D106" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E106">
         <v>97.169295355077</v>
@@ -6970,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6984,7 +6981,7 @@
         <v>120.1236571755032</v>
       </c>
       <c r="D107" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E107">
         <v>97.169295355077</v>
@@ -7020,7 +7017,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7034,7 +7031,7 @@
         <v>119.3894537106139</v>
       </c>
       <c r="D108" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E108">
         <v>96.56416454557592</v>
@@ -7070,7 +7067,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7084,7 +7081,7 @@
         <v>119.2249258621331</v>
       </c>
       <c r="D109" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E109">
         <v>96.56416454557592</v>
@@ -7120,7 +7117,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7134,7 +7131,7 @@
         <v>118.0996069245826</v>
       </c>
       <c r="D110" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E110">
         <v>95.67574966744206</v>
@@ -7170,7 +7167,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7184,7 +7181,7 @@
         <v>117.9054652468306</v>
       </c>
       <c r="D111" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E111">
         <v>95.67574966744206</v>
@@ -7220,7 +7217,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7234,7 +7231,7 @@
         <v>117.1017444652623</v>
       </c>
       <c r="D112" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E112">
         <v>94.98844644291023</v>
@@ -7270,7 +7267,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7284,7 +7281,7 @@
         <v>116.8846926800259</v>
       </c>
       <c r="D113" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E113">
         <v>94.98844644291023</v>
@@ -7320,7 +7317,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7334,7 +7331,7 @@
         <v>115.7903395541055</v>
       </c>
       <c r="D114" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E114">
         <v>94.08518285614407</v>
@@ -7370,7 +7367,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7384,7 +7381,7 @@
         <v>115.5431789826436</v>
       </c>
       <c r="D115" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E115">
         <v>94.08518285614407</v>
@@ -7420,7 +7417,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7434,7 +7431,7 @@
         <v>114.3600161010092</v>
       </c>
       <c r="D116" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E116">
         <v>93.10001108998082</v>
@@ -7470,7 +7467,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7484,7 +7481,7 @@
         <v>114.0800164706752</v>
       </c>
       <c r="D117" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E117">
         <v>93.10001108998082</v>
@@ -7520,7 +7517,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7534,7 +7531,7 @@
         <v>112.9215721869154</v>
       </c>
       <c r="D118" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E118">
         <v>92.10924614915092</v>
@@ -7570,7 +7567,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7584,7 +7581,7 @@
         <v>112.6085470585538</v>
       </c>
       <c r="D119" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E119">
         <v>92.10924614915092</v>
@@ -7620,7 +7617,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7634,7 +7631,7 @@
         <v>111.0753114680939</v>
       </c>
       <c r="D120" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E120">
         <v>91.07689300844227</v>
@@ -7684,7 +7681,7 @@
         <v>109.3637030177276</v>
       </c>
       <c r="D121" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E121">
         <v>89.92443844086398</v>
@@ -7720,7 +7717,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7734,7 +7731,7 @@
         <v>106.6367917601738</v>
       </c>
       <c r="D122" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E122">
         <v>88.08836352929409</v>
@@ -7770,7 +7767,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7784,7 +7781,7 @@
         <v>99.96873044828921</v>
       </c>
       <c r="D123" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E123">
         <v>83.59864643650396</v>
@@ -7820,7 +7817,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7834,7 +7831,7 @@
         <v>39.91051382546476</v>
       </c>
       <c r="D124" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E124">
         <v>42.55014562583152</v>
@@ -7870,7 +7867,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7884,7 +7881,7 @@
         <v>34.76754143004694</v>
       </c>
       <c r="D125" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E125">
         <v>38.11145388461416</v>
@@ -7920,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7934,7 +7931,7 @@
         <v>27.87373902743889</v>
       </c>
       <c r="D126" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E126">
         <v>28.73232502982488</v>
@@ -7970,7 +7967,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7984,7 +7981,7 @@
         <v>52.34452590842368</v>
       </c>
       <c r="D127" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E127">
         <v>60.02089394070224</v>
@@ -8020,7 +8017,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8034,7 +8031,7 @@
         <v>66.2681578761451</v>
       </c>
       <c r="D128" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E128">
         <v>59.00746128062423</v>
@@ -8070,7 +8067,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8084,7 +8081,7 @@
         <v>65.90298372726488</v>
       </c>
       <c r="D129" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E129">
         <v>59.00746128062423</v>
@@ -8120,7 +8117,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8134,7 +8131,7 @@
         <v>75.19054270184851</v>
       </c>
       <c r="D130" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E130">
         <v>82.88620847856147</v>
@@ -8170,7 +8167,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8184,7 +8181,7 @@
         <v>91.01410438583636</v>
       </c>
       <c r="D131" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E131">
         <v>85.34034548895417</v>
@@ -8220,7 +8217,7 @@
         <v>0</v>
       </c>
       <c r="P131" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8234,7 +8231,7 @@
         <v>90.69117289103272</v>
       </c>
       <c r="D132" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E132">
         <v>85.34034548895417</v>
@@ -8270,7 +8267,7 @@
         <v>0</v>
       </c>
       <c r="P132" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8284,7 +8281,7 @@
         <v>106.425283452306</v>
       </c>
       <c r="D133" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E133">
         <v>102.4841645631825</v>
@@ -8334,7 +8331,7 @@
         <v>106.7743510447031</v>
       </c>
       <c r="D134" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E134">
         <v>102.4841645631825</v>
@@ -8384,7 +8381,7 @@
         <v>64.83381773702186</v>
       </c>
       <c r="D135" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E135">
         <v>61.17785949472258</v>
@@ -8420,7 +8417,7 @@
         <v>0</v>
       </c>
       <c r="P135" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8434,7 +8431,7 @@
         <v>53.81062761975522</v>
       </c>
       <c r="D136" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E136">
         <v>45.81713512679965</v>
@@ -8470,7 +8467,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8484,7 +8481,7 @@
         <v>53.43128846396477</v>
       </c>
       <c r="D137" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E137">
         <v>47.7894228477703</v>
@@ -8520,7 +8517,7 @@
         <v>0</v>
       </c>
       <c r="P137" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8534,7 +8531,7 @@
         <v>48.70129852147022</v>
       </c>
       <c r="D138" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E138">
         <v>39.19252273181839</v>
@@ -8570,7 +8567,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8584,7 +8581,7 @@
         <v>44.87334693499027</v>
       </c>
       <c r="D139" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E139">
         <v>34.44403390958535</v>
@@ -8620,7 +8617,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8634,7 +8631,7 @@
         <v>40.45906823400685</v>
       </c>
       <c r="D140" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E140">
         <v>29.40254968722779</v>
@@ -8670,7 +8667,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8684,7 +8681,7 @@
         <v>37.79538016242914</v>
       </c>
       <c r="D141" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E141">
         <v>25.15160114518396</v>
@@ -8720,7 +8717,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8734,7 +8731,7 @@
         <v>37.68076952930594</v>
       </c>
       <c r="D142" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E142">
         <v>25.01802919408082</v>
@@ -8770,7 +8767,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8784,7 +8781,7 @@
         <v>63.15408222226404</v>
       </c>
       <c r="D143" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E143">
         <v>53.56243089690908</v>
@@ -8820,7 +8817,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8834,7 +8831,7 @@
         <v>31.1030054990203</v>
       </c>
       <c r="D144" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E144">
         <v>14.08734435244297</v>
@@ -8870,7 +8867,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8884,7 +8881,7 @@
         <v>25.05484991241799</v>
       </c>
       <c r="D145" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E145">
         <v>6.922187058405115</v>
@@ -8920,7 +8917,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8934,7 +8931,7 @@
         <v>18.81638310475921</v>
       </c>
       <c r="D146" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E146">
         <v>-0.4684290245420044</v>
@@ -8970,7 +8967,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8984,7 +8981,7 @@
         <v>13.01676813424353</v>
       </c>
       <c r="D147" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E147">
         <v>-7.339144057179965</v>
@@ -9020,7 +9017,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9034,7 +9031,7 @@
         <v>8.024396355482963</v>
       </c>
       <c r="D148" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E148">
         <v>-13.25353044372964</v>
@@ -9070,7 +9067,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9084,7 +9081,7 @@
         <v>7.720504878426524</v>
       </c>
       <c r="D149" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E149">
         <v>-13.61354602240461</v>
@@ -9120,7 +9117,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9134,7 +9131,7 @@
         <v>10.31388326476601</v>
       </c>
       <c r="D150" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E150">
         <v>-10.54121036651594</v>
@@ -9170,7 +9167,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9184,7 +9181,7 @@
         <v>11.14758883248732</v>
       </c>
       <c r="D151" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E151">
         <v>-9.553532148900146</v>
@@ -9220,7 +9217,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9234,7 +9231,7 @@
         <v>20.84560393192861</v>
       </c>
       <c r="D152" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E152">
         <v>1.935557811248756</v>
@@ -9270,7 +9267,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9284,7 +9281,7 @@
         <v>21.43389351871438</v>
       </c>
       <c r="D153" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E153">
         <v>2.632495474873352</v>
@@ -9320,7 +9317,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9334,7 +9331,7 @@
         <v>22.6162561113628</v>
       </c>
       <c r="D154" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E154">
         <v>4.033222330128012</v>
@@ -9370,7 +9367,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9384,7 +9381,7 @@
         <v>23.86897930913528</v>
       </c>
       <c r="D155" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E155">
         <v>5.517304316678292</v>
@@ -9420,7 +9417,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9434,7 +9431,7 @@
         <v>24.29022509961407</v>
       </c>
       <c r="D156" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E156">
         <v>6.016347753146405</v>
@@ -9470,7 +9467,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9484,7 +9481,7 @@
         <v>80.77258742920839</v>
       </c>
       <c r="D157" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E157">
         <v>71.50140757768273</v>
@@ -9520,7 +9517,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9534,7 +9531,7 @@
         <v>80.87119828430862</v>
       </c>
       <c r="D158" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E158">
         <v>71.50140757768273</v>
@@ -9570,7 +9567,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9584,7 +9581,7 @@
         <v>82.15331534782203</v>
       </c>
       <c r="D159" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E159">
         <v>71.50140757768273</v>
@@ -9620,7 +9617,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9634,7 +9631,7 @@
         <v>76.19581669669289</v>
       </c>
       <c r="D160" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E160">
         <v>66.74547500154564</v>
@@ -9670,7 +9667,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9684,7 +9681,7 @@
         <v>75.21863715900577</v>
       </c>
       <c r="D161" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E161">
         <v>66.74547500154564</v>
@@ -9720,7 +9717,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9734,7 +9731,7 @@
         <v>77.89414970172665</v>
       </c>
       <c r="D162" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E162">
         <v>66.74547500154564</v>
@@ -9770,7 +9767,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9784,7 +9781,7 @@
         <v>60.11863715900578</v>
       </c>
       <c r="D163" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E163">
         <v>68.03744024109169</v>
@@ -9820,7 +9817,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9834,7 +9831,7 @@
         <v>72.44565132750211</v>
       </c>
       <c r="D164" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E164">
         <v>62.8485060058029</v>
@@ -9870,7 +9867,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9884,7 +9881,7 @@
         <v>71.50850914251097</v>
       </c>
       <c r="D165" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E165">
         <v>62.8485060058029</v>
@@ -9920,7 +9917,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9934,7 +9931,7 @@
         <v>74.40422712505978</v>
       </c>
       <c r="D166" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E166">
         <v>62.8485060058029</v>
@@ -9970,7 +9967,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9984,7 +9981,7 @@
         <v>56.40850914251097</v>
       </c>
       <c r="D167" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E167">
         <v>64.59422790923679</v>
@@ -10020,7 +10017,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10034,7 +10031,7 @@
         <v>67.88820949982238</v>
       </c>
       <c r="D168" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E168">
         <v>60.43722302948107</v>
@@ -10084,7 +10081,7 @@
         <v>70.99880138202717</v>
       </c>
       <c r="D169" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E169">
         <v>60.43722302948107</v>
@@ -10134,7 +10131,7 @@
         <v>52.78820949982239</v>
       </c>
       <c r="D170" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E170">
         <v>61.23438147825242</v>
@@ -10184,7 +10181,7 @@
         <v>64.41272601732022</v>
       </c>
       <c r="D171" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E171">
         <v>56.61794172047242</v>
@@ -10220,7 +10217,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10234,7 +10231,7 @@
         <v>49.31272601732023</v>
       </c>
       <c r="D172" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E172">
         <v>58.0089327786641</v>
@@ -10270,7 +10267,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10284,7 +10281,7 @@
         <v>61.16879231159055</v>
       </c>
       <c r="D173" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E173">
         <v>53.82441738118666</v>
@@ -10320,7 +10317,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10334,7 +10331,7 @@
         <v>46.06879231159056</v>
       </c>
       <c r="D174" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E174">
         <v>54.08446933112747</v>
@@ -10370,7 +10367,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10384,7 +10381,7 @@
         <v>58.07192781203269</v>
       </c>
       <c r="D175" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E175">
         <v>50.68812094147531</v>
@@ -10420,7 +10417,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10434,7 +10431,7 @@
         <v>42.9719278120327</v>
       </c>
       <c r="D176" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E176">
         <v>51.29394934141796</v>
@@ -10470,7 +10467,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10484,7 +10481,7 @@
         <v>72.62623022483724</v>
       </c>
       <c r="D177" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E177">
         <v>78.13274022613687</v>
@@ -10520,7 +10517,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10534,7 +10531,7 @@
         <v>72.14377020837516</v>
       </c>
       <c r="D178" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E178">
         <v>78.53925022743653</v>
@@ -10570,7 +10567,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10584,7 +10581,7 @@
         <v>83.25643025082999</v>
       </c>
       <c r="D179" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E179">
         <v>77.7759602547289</v>
@@ -10620,7 +10617,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10649,7 +10646,7 @@
         <v>71.40000000000001</v>
       </c>
       <c r="P180" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10678,7 +10675,7 @@
         <v>72.09999999999999</v>
       </c>
       <c r="P181" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10692,7 +10689,7 @@
         <v>66.25534327603719</v>
       </c>
       <c r="D182" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E182">
         <v>53.25789242985769</v>
@@ -10742,7 +10739,7 @@
         <v>66.50153349826817</v>
       </c>
       <c r="D183" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E183">
         <v>53.49926887679366</v>
@@ -10778,7 +10775,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10792,7 +10789,7 @@
         <v>65.13958707494101</v>
       </c>
       <c r="D184" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E184">
         <v>53.20617458032149</v>
@@ -10828,7 +10825,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10842,7 +10839,7 @@
         <v>65.2660759255686</v>
       </c>
       <c r="D185" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E185">
         <v>53.20617458032149</v>
@@ -10878,7 +10875,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10892,7 +10889,7 @@
         <v>63.88275361614285</v>
       </c>
       <c r="D186" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E186">
         <v>51.96525040581191</v>
@@ -10928,7 +10925,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10942,7 +10939,7 @@
         <v>82.52792611826956</v>
       </c>
       <c r="D187" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E187">
         <v>99.94767772279653</v>
@@ -10978,7 +10975,7 @@
         <v>0</v>
       </c>
       <c r="P187" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10992,7 +10989,7 @@
         <v>80.81507949145069</v>
       </c>
       <c r="D188" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E188">
         <v>99.94767772279653</v>
@@ -11028,7 +11025,7 @@
         <v>0</v>
       </c>
       <c r="P188" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11042,7 +11039,7 @@
         <v>82.55697724266327</v>
       </c>
       <c r="D189" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E189">
         <v>99.94767772279653</v>
@@ -11078,7 +11075,7 @@
         <v>0</v>
       </c>
       <c r="P189" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11092,7 +11089,7 @@
         <v>80.68386776738032</v>
       </c>
       <c r="D190" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E190">
         <v>99.94767772279653</v>
@@ -11128,7 +11125,7 @@
         <v>0</v>
       </c>
       <c r="P190" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11142,7 +11139,7 @@
         <v>83.46212404051099</v>
       </c>
       <c r="D191" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E191">
         <v>101.9293746430213</v>
@@ -11178,7 +11175,7 @@
         <v>0</v>
       </c>
       <c r="P191" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11192,7 +11189,7 @@
         <v>81.65627098338047</v>
       </c>
       <c r="D192" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E192">
         <v>101.9293746430213</v>
@@ -11228,7 +11225,7 @@
         <v>0</v>
       </c>
       <c r="P192" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11242,7 +11239,7 @@
         <v>83.46017302146748</v>
       </c>
       <c r="D193" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E193">
         <v>101.9293746430213</v>
@@ -11278,7 +11275,7 @@
         <v>0</v>
       </c>
       <c r="P193" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11292,7 +11289,7 @@
         <v>81.57259587924717</v>
       </c>
       <c r="D194" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E194">
         <v>101.9293746430213</v>
@@ -11328,7 +11325,7 @@
         <v>0</v>
       </c>
       <c r="P194" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11378,7 +11375,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11392,7 +11389,7 @@
         <v>33.77481800214022</v>
       </c>
       <c r="D196" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E196">
         <v>39.96346245740297</v>
@@ -11428,7 +11425,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11442,7 +11439,7 @@
         <v>24.63764534106641</v>
       </c>
       <c r="D197" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E197">
         <v>34.16939555445761</v>
@@ -11478,7 +11475,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11492,7 +11489,7 @@
         <v>43.28817453279771</v>
       </c>
       <c r="D198" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E198">
         <v>46.14425779500065</v>
@@ -11528,7 +11525,7 @@
         <v>0</v>
       </c>
       <c r="P198" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11542,7 +11539,7 @@
         <v>24.23598497532834</v>
       </c>
       <c r="D199" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E199">
         <v>33.03819935984974</v>
@@ -11578,7 +11575,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11592,7 +11589,7 @@
         <v>24.17071464201896</v>
       </c>
       <c r="D200" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E200">
         <v>33.03819935984974</v>
@@ -11628,7 +11625,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11642,7 +11639,7 @@
         <v>23.32366123264667</v>
       </c>
       <c r="D201" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E201">
         <v>32.29172372079252</v>
@@ -11692,7 +11689,7 @@
         <v>22.94912669441385</v>
       </c>
       <c r="D202" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E202">
         <v>31.49029169144093</v>
@@ -11728,7 +11725,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11742,7 +11739,7 @@
         <v>22.44844130251504</v>
       </c>
       <c r="D203" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E203">
         <v>30.75050022869873</v>
@@ -11778,7 +11775,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11792,7 +11789,7 @@
         <v>22.12056025614258</v>
       </c>
       <c r="D204" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E204">
         <v>30.75050022869873</v>
@@ -11828,7 +11825,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11842,7 +11839,7 @@
         <v>21.00936580829927</v>
       </c>
       <c r="D205" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E205">
         <v>29.75836232883863</v>
@@ -11892,7 +11889,7 @@
         <v>22.21712321587968</v>
       </c>
       <c r="D206" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E206">
         <v>29.83950116198865</v>
@@ -11928,7 +11925,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11942,7 +11939,7 @@
         <v>22.36605537346383</v>
       </c>
       <c r="D207" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E207">
         <v>29.99532225197207</v>
@@ -11978,7 +11975,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11992,7 +11989,7 @@
         <v>21.71901729202467</v>
       </c>
       <c r="D208" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E208">
         <v>28.96097369076485</v>
@@ -12028,7 +12025,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12042,7 +12039,7 @@
         <v>21.37743590654157</v>
       </c>
       <c r="D209" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E209">
         <v>28.96097369076485</v>
@@ -12078,7 +12075,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12092,7 +12089,7 @@
         <v>21.5505095382167</v>
       </c>
       <c r="D210" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E210">
         <v>29.1420529309536</v>
@@ -12142,7 +12139,7 @@
         <v>21.4477218260166</v>
       </c>
       <c r="D211" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E211">
         <v>29.03451072105261</v>
@@ -12178,7 +12175,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12192,7 +12189,7 @@
         <v>21.93200329930192</v>
       </c>
       <c r="D212" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E212">
         <v>29.03451072105261</v>
@@ -12228,7 +12225,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12242,7 +12239,7 @@
         <v>21.82005829590757</v>
       </c>
       <c r="D213" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E213">
         <v>29.42406980298699</v>
@@ -12278,7 +12275,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12292,7 +12289,7 @@
         <v>22.28137628646834</v>
       </c>
       <c r="D214" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E214">
         <v>29.42406980298699</v>
@@ -12328,7 +12325,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12342,7 +12339,7 @@
         <v>25.08434479788652</v>
       </c>
       <c r="D215" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E215">
         <v>32.83934753082841</v>
@@ -12378,7 +12375,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12392,7 +12389,7 @@
         <v>25.82576998567276</v>
       </c>
       <c r="D216" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E216">
         <v>32.83934753082841</v>
@@ -12428,7 +12425,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12442,7 +12439,7 @@
         <v>25.62576998567276</v>
       </c>
       <c r="D217" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E217">
         <v>32.83934753082841</v>
@@ -12478,7 +12475,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12492,7 +12489,7 @@
         <v>39.54291961010028</v>
       </c>
       <c r="D218" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E218">
         <v>32.24005830276027</v>
@@ -12528,7 +12525,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12542,7 +12539,7 @@
         <v>27.32311840696546</v>
       </c>
       <c r="D219" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E219">
         <v>35.18167674737576</v>
@@ -12578,7 +12575,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12592,7 +12589,7 @@
         <v>27.936331890267</v>
       </c>
       <c r="D220" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E220">
         <v>35.18167674737576</v>
@@ -12628,7 +12625,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12642,7 +12639,7 @@
         <v>27.736331890267</v>
       </c>
       <c r="D221" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E221">
         <v>35.18167674737576</v>
@@ -12678,7 +12675,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12692,7 +12689,7 @@
         <v>41.90990492366392</v>
       </c>
       <c r="D222" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E222">
         <v>34.44924459541966</v>
@@ -12728,7 +12725,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12742,7 +12739,7 @@
         <v>29.32582523799188</v>
       </c>
       <c r="D223" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E223">
         <v>36.94571726179005</v>
@@ -12792,7 +12789,7 @@
         <v>43.69251428559836</v>
       </c>
       <c r="D224" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E224">
         <v>36.11301333322514</v>
@@ -12842,7 +12839,7 @@
         <v>44.11030807122381</v>
       </c>
       <c r="D225" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E225">
         <v>36.50295419980888</v>
@@ -12878,7 +12875,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12892,7 +12889,7 @@
         <v>45.39200591893177</v>
       </c>
       <c r="D226" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E226">
         <v>37.69920552433632</v>
@@ -12942,7 +12939,7 @@
         <v>46.2461284866414</v>
       </c>
       <c r="D227" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E227">
         <v>38.49638658753197</v>
@@ -12978,7 +12975,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12992,7 +12989,7 @@
         <v>46.90307634880546</v>
       </c>
       <c r="D228" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E228">
         <v>39.10953792555176</v>
@@ -13042,7 +13039,7 @@
         <v>33.83569560835785</v>
       </c>
       <c r="D229" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E229">
         <v>40.9206360962427</v>
@@ -13092,7 +13089,7 @@
         <v>46.73201951087134</v>
       </c>
       <c r="D230" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E230">
         <v>38.94988487681324</v>
@@ -13142,7 +13139,7 @@
         <v>33.22416759327695</v>
       </c>
       <c r="D231" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E231">
         <v>40.34408700115657</v>
@@ -13178,7 +13175,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13192,7 +13189,7 @@
         <v>46.15305807647522</v>
       </c>
       <c r="D232" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E232">
         <v>38.40952087137686</v>
@@ -13228,7 +13225,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13242,7 +13239,7 @@
         <v>33.50490381338868</v>
       </c>
       <c r="D233" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E233">
         <v>40.17087450822464</v>
@@ -13278,7 +13275,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13292,7 +13289,7 @@
         <v>45.97912084507914</v>
       </c>
       <c r="D234" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E234">
         <v>38.24717945540719</v>
@@ -13328,7 +13325,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13342,7 +13339,7 @@
         <v>34.16379673036971</v>
       </c>
       <c r="D235" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E235">
         <v>40.85258622752538</v>
@@ -13378,7 +13375,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13392,7 +13389,7 @@
         <v>46.66368491466983</v>
       </c>
       <c r="D236" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E236">
         <v>38.8861059203585</v>
@@ -13428,7 +13425,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13442,7 +13439,7 @@
         <v>35.00523304555671</v>
       </c>
       <c r="D237" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E237">
         <v>41.72316319432058</v>
@@ -13478,7 +13475,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13492,7 +13489,7 @@
         <v>47.53790446291606</v>
       </c>
       <c r="D238" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E238">
         <v>39.70204416538832</v>
@@ -13528,7 +13525,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13542,7 +13539,7 @@
         <v>35.77509163864829</v>
       </c>
       <c r="D239" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E239">
         <v>42.51968355686988</v>
@@ -13578,7 +13575,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13592,7 +13589,7 @@
         <v>48.33775754664758</v>
       </c>
       <c r="D240" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E240">
         <v>40.4485737102044</v>
@@ -13628,7 +13625,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13642,7 +13639,7 @@
         <v>36.40438752667171</v>
       </c>
       <c r="D241" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E241">
         <v>43.17077324188112</v>
@@ -13678,7 +13675,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13692,7 +13689,7 @@
         <v>48.9915714562823</v>
       </c>
       <c r="D242" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E242">
         <v>41.05880002586348</v>
@@ -13728,7 +13725,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13742,7 +13739,7 @@
         <v>32.86635202836143</v>
       </c>
       <c r="D243" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E243">
         <v>23.40810673803942</v>
@@ -13778,7 +13775,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13792,7 +13789,7 @@
         <v>14.22574367387871</v>
       </c>
       <c r="D244" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E244">
         <v>19.5340376774239</v>
@@ -13828,7 +13825,7 @@
         <v>0</v>
       </c>
       <c r="P244" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13842,7 +13839,7 @@
         <v>24.88800304387275</v>
       </c>
       <c r="D245" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E245">
         <v>11.91657154564347</v>
@@ -13878,7 +13875,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13892,7 +13889,7 @@
         <v>39.44906102636678</v>
       </c>
       <c r="D246" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E246">
         <v>28.36395585832523</v>
@@ -13928,7 +13925,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13957,7 +13954,7 @@
         <v>59.4</v>
       </c>
       <c r="P247" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13971,7 +13968,7 @@
         <v>36.85113379578714</v>
       </c>
       <c r="D248" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E248">
         <v>25.5208599983697</v>
@@ -14007,7 +14004,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14021,7 +14018,7 @@
         <v>33.94646019309421</v>
       </c>
       <c r="D249" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E249">
         <v>22.34206984707826</v>
@@ -14057,7 +14054,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14071,7 +14068,7 @@
         <v>33.30875742504994</v>
       </c>
       <c r="D250" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E250">
         <v>21.64418651979802</v>
@@ -14107,7 +14104,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14136,7 +14133,7 @@
         <v>59.5</v>
       </c>
       <c r="P251" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14186,7 +14183,7 @@
         <v>0</v>
       </c>
       <c r="P252" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14200,7 +14197,7 @@
         <v>9.926891175013289</v>
       </c>
       <c r="D253" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E253">
         <v>9.938904864210649</v>
@@ -14236,7 +14233,7 @@
         <v>0</v>
       </c>
       <c r="P253" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14250,7 +14247,7 @@
         <v>8.61566853605617</v>
       </c>
       <c r="D254" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E254">
         <v>9.007561895624264</v>
@@ -14286,7 +14283,7 @@
         <v>0</v>
       </c>
       <c r="P254" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14336,7 +14333,7 @@
         <v>0</v>
       </c>
       <c r="P255" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14350,7 +14347,7 @@
         <v>15.27625616990661</v>
       </c>
       <c r="D256" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E256">
         <v>13.96823074035395</v>
@@ -14386,7 +14383,7 @@
         <v>0</v>
       </c>
       <c r="P256" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14400,7 +14397,7 @@
         <v>14.49984262437423</v>
       </c>
       <c r="D257" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E257">
         <v>14.19011246930496</v>
@@ -14436,7 +14433,7 @@
         <v>0</v>
       </c>
       <c r="P257" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14450,7 +14447,7 @@
         <v>13.68984307357539</v>
       </c>
       <c r="D258" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E258">
         <v>15.44321014679792</v>
@@ -14486,7 +14483,7 @@
         <v>0</v>
       </c>
       <c r="P258" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14500,7 +14497,7 @@
         <v>14.26953725404694</v>
       </c>
       <c r="D259" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E259">
         <v>17.46734434330768</v>
@@ -14536,7 +14533,7 @@
         <v>0</v>
       </c>
       <c r="P259" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14550,7 +14547,7 @@
         <v>59.06263065139578</v>
       </c>
       <c r="D260" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E260">
         <v>59.07357361272927</v>
@@ -14586,7 +14583,7 @@
         <v>0</v>
       </c>
       <c r="P260" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14600,7 +14597,7 @@
         <v>60.66257075424956</v>
       </c>
       <c r="D261" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E261">
         <v>61.38454095582109</v>
@@ -14636,7 +14633,7 @@
         <v>0</v>
       </c>
       <c r="P261" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14650,7 +14647,7 @@
         <v>61.58779745865752</v>
       </c>
       <c r="D262" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E262">
         <v>62.08864679971672</v>
@@ -14686,7 +14683,7 @@
         <v>0</v>
       </c>
       <c r="P262" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14736,7 +14733,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14786,7 +14783,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14836,7 +14833,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14886,7 +14883,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14936,7 +14933,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14986,7 +14983,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15036,7 +15033,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15086,7 +15083,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15136,7 +15133,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15150,7 +15147,7 @@
         <v>-12.91711279591523</v>
       </c>
       <c r="D272" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E272">
         <v>-24.080705554696</v>
@@ -15200,7 +15197,7 @@
         <v>-13.89288092370901</v>
       </c>
       <c r="D273" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E273">
         <v>-24.64699491908532</v>
@@ -15236,7 +15233,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15250,7 +15247,7 @@
         <v>-13.4171424523624</v>
       </c>
       <c r="D274" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E274">
         <v>-24.64699491908532</v>
@@ -15286,7 +15283,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15300,7 +15297,7 @@
         <v>-7.909028461817627</v>
       </c>
       <c r="D275" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E275">
         <v>-18.4089921717041</v>
@@ -15336,7 +15333,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15350,7 +15347,7 @@
         <v>-3.803879058776658</v>
       </c>
       <c r="D276" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E276">
         <v>-13.75986303266694</v>
@@ -15400,7 +15397,7 @@
         <v>-7.200798160312672</v>
       </c>
       <c r="D277" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E277">
         <v>-16.37029482433257</v>
@@ -15450,7 +15447,7 @@
         <v>1.814674940949821</v>
       </c>
       <c r="D278" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E278">
         <v>-6.106103736501311</v>
@@ -15536,7 +15533,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15636,7 +15633,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15650,7 +15647,7 @@
         <v>68.89152801060949</v>
       </c>
       <c r="D282" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E282">
         <v>67.76768139345658</v>
@@ -15686,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="P282" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15700,7 +15697,7 @@
         <v>68.93096321131679</v>
       </c>
       <c r="D283" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E283">
         <v>67.76768139345658</v>
@@ -15736,7 +15733,7 @@
         <v>0</v>
       </c>
       <c r="P283" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15750,7 +15747,7 @@
         <v>68.53130803182968</v>
       </c>
       <c r="D284" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E284">
         <v>67.76768139345658</v>
@@ -15786,7 +15783,7 @@
         <v>0</v>
       </c>
       <c r="P284" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15800,7 +15797,7 @@
         <v>69.00549946949548</v>
       </c>
       <c r="D285" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E285">
         <v>67.76768139345658</v>
@@ -15836,7 +15833,7 @@
         <v>0</v>
       </c>
       <c r="P285" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15850,7 +15847,7 @@
         <v>77.0344578684535</v>
       </c>
       <c r="D286" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E286">
         <v>79.16818364992574</v>
@@ -15900,7 +15897,7 @@
         <v>76.35596494832328</v>
       </c>
       <c r="D287" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E287">
         <v>79.16818364992574</v>
@@ -15950,7 +15947,7 @@
         <v>77.32922500711149</v>
       </c>
       <c r="D288" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E288">
         <v>79.16818364992574</v>
@@ -16000,7 +15997,7 @@
         <v>79.78847196430716</v>
       </c>
       <c r="D289" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E289">
         <v>84.66094269739213</v>
@@ -16036,7 +16033,7 @@
         <v>0</v>
       </c>
       <c r="P289" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16050,7 +16047,7 @@
         <v>79.029452316228</v>
       </c>
       <c r="D290" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E290">
         <v>84.66094269739213</v>
@@ -16086,7 +16083,7 @@
         <v>0</v>
       </c>
       <c r="P290" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16100,7 +16097,7 @@
         <v>80.07787065443522</v>
       </c>
       <c r="D291" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E291">
         <v>84.66094269739213</v>
@@ -16136,7 +16133,7 @@
         <v>0</v>
       </c>
       <c r="P291" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16186,7 +16183,7 @@
         <v>0</v>
       </c>
       <c r="P292" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16236,7 +16233,7 @@
         <v>0</v>
       </c>
       <c r="P293" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16286,7 +16283,7 @@
         <v>0</v>
       </c>
       <c r="P294" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16300,7 +16297,7 @@
         <v>26.32548638029413</v>
       </c>
       <c r="D295" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E295">
         <v>26.99422663021349</v>
@@ -16336,7 +16333,7 @@
         <v>0</v>
       </c>
       <c r="P295" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16350,7 +16347,7 @@
         <v>22.18948293316849</v>
       </c>
       <c r="D296" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E296">
         <v>24.84672272180288</v>
@@ -16386,7 +16383,7 @@
         <v>0</v>
       </c>
       <c r="P296" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16400,7 +16397,7 @@
         <v>21.86052377863092</v>
       </c>
       <c r="D297" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E297">
         <v>24.84672272180288</v>
@@ -16436,7 +16433,7 @@
         <v>0</v>
       </c>
       <c r="P297" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16450,7 +16447,7 @@
         <v>40.77814878274022</v>
       </c>
       <c r="D298" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E298">
         <v>48.87821615334129</v>
@@ -16486,7 +16483,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16500,7 +16497,7 @@
         <v>40.67981251944272</v>
       </c>
       <c r="D299" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E299">
         <v>48.87821615334129</v>
@@ -16536,7 +16533,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16550,7 +16547,7 @@
         <v>56.75038402863819</v>
       </c>
       <c r="D300" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E300">
         <v>62.17870887338118</v>
@@ -16586,7 +16583,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16600,7 +16597,7 @@
         <v>59.81014784804309</v>
       </c>
       <c r="D301" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E301">
         <v>65.19117101289457</v>
@@ -16636,7 +16633,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16650,7 +16647,7 @@
         <v>60.36835189313004</v>
       </c>
       <c r="D302" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E302">
         <v>65.519432176365</v>
@@ -16686,7 +16683,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16700,7 +16697,7 @@
         <v>61.49835591209959</v>
       </c>
       <c r="D303" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E303">
         <v>65.45054113973049</v>
@@ -16750,7 +16747,7 @@
         <v>61.74303834428476</v>
       </c>
       <c r="D304" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E304">
         <v>65.59070564276428</v>
@@ -16786,7 +16783,7 @@
         <v>0</v>
       </c>
       <c r="P304" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16800,7 +16797,7 @@
         <v>62.08800405152936</v>
       </c>
       <c r="D305" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E305">
         <v>65.70367105582346</v>
@@ -16836,7 +16833,7 @@
         <v>0</v>
       </c>
       <c r="P305" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16850,7 +16847,7 @@
         <v>62.52195117925444</v>
       </c>
       <c r="D306" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E306">
         <v>66.54562713332096</v>
@@ -16886,7 +16883,7 @@
         <v>0</v>
       </c>
       <c r="P306" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16900,7 +16897,7 @@
         <v>63.12382871565654</v>
       </c>
       <c r="D307" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E307">
         <v>66.7862115872222</v>
@@ -16936,7 +16933,7 @@
         <v>0</v>
       </c>
       <c r="P307" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16950,7 +16947,7 @@
         <v>63.43713576842169</v>
       </c>
       <c r="D308" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E308">
         <v>68.73084934526386</v>
@@ -16986,7 +16983,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17000,7 +16997,7 @@
         <v>63.67236578705479</v>
       </c>
       <c r="D309" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E309">
         <v>68.98960236576026</v>
@@ -17036,7 +17033,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17050,7 +17047,7 @@
         <v>63.92214730715632</v>
       </c>
       <c r="D310" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E310">
         <v>69.26436203787196</v>
@@ -17086,7 +17083,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17100,7 +17097,7 @@
         <v>64.84267428552164</v>
       </c>
       <c r="D311" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E311">
         <v>70.2769417140738</v>
@@ -17136,7 +17133,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17150,7 +17147,7 @@
         <v>67.02639425410899</v>
       </c>
       <c r="D312" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E312">
         <v>72.67903367951989</v>
@@ -17186,7 +17183,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17200,7 +17197,7 @@
         <v>48.8201383647419</v>
       </c>
       <c r="D313" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E313">
         <v>53.28068312873989</v>
@@ -17236,7 +17233,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17250,7 +17247,7 @@
         <v>43.78661428769819</v>
       </c>
       <c r="D314" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E314">
         <v>49.20590413019019</v>
@@ -17286,7 +17283,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17300,7 +17297,7 @@
         <v>43.50856722084519</v>
       </c>
       <c r="D315" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E315">
         <v>49.20590413019019</v>
@@ -17336,7 +17333,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17350,7 +17347,7 @@
         <v>38.43277181447034</v>
       </c>
       <c r="D316" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E316">
         <v>43.81134802598723</v>
@@ -17386,7 +17383,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17400,7 +17397,7 @@
         <v>39.10060265112747</v>
       </c>
       <c r="D317" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E317">
         <v>43.81134802598723</v>
@@ -17436,7 +17433,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17450,7 +17447,7 @@
         <v>28.12299460113455</v>
       </c>
       <c r="D318" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E318">
         <v>35.22229514558674</v>
@@ -17486,7 +17483,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17500,7 +17497,7 @@
         <v>27.81471186440677</v>
       </c>
       <c r="D319" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E319">
         <v>34.92338983050847</v>
@@ -17536,7 +17533,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17550,7 +17547,7 @@
         <v>31.34037664954478</v>
       </c>
       <c r="D320" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E320">
         <v>38.34181005944457</v>
@@ -17586,7 +17583,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17600,7 +17597,7 @@
         <v>31.06966226989418</v>
       </c>
       <c r="D321" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E321">
         <v>38.07933033773011</v>
@@ -17636,7 +17633,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17650,7 +17647,7 @@
         <v>30.73117805425061</v>
       </c>
       <c r="D322" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E322">
         <v>37.75114221990079</v>
@@ -17686,7 +17683,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17700,7 +17697,7 @@
         <v>30.23209518986696</v>
       </c>
       <c r="D323" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E323">
         <v>37.26724058333109</v>
@@ -17736,7 +17733,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17750,7 +17747,7 @@
         <v>29.66328200930995</v>
       </c>
       <c r="D324" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E324">
         <v>36.71572970484425</v>
@@ -17786,7 +17783,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17800,7 +17797,7 @@
         <v>29.90527095369034</v>
       </c>
       <c r="D325" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E325">
         <v>36.95035776878722</v>
@@ -17836,7 +17833,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17850,7 +17847,7 @@
         <v>29.61163508265873</v>
       </c>
       <c r="D326" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E326">
         <v>36.66565378736873</v>
@@ -17886,7 +17883,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17900,7 +17897,7 @@
         <v>29.60796663375891</v>
       </c>
       <c r="D327" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E327">
         <v>38.73216492329536</v>
@@ -17936,7 +17933,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17950,7 +17947,7 @@
         <v>29.99267097270676</v>
       </c>
       <c r="D328" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E328">
         <v>39.11028686861102</v>
@@ -17986,7 +17983,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18000,7 +17997,7 @@
         <v>30.47592970891776</v>
       </c>
       <c r="D329" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E329">
         <v>39.58527691922146</v>
@@ -18036,7 +18033,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18065,7 +18062,7 @@
         <v>64.5</v>
       </c>
       <c r="P330" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18079,7 +18076,7 @@
         <v>37.15547839433958</v>
       </c>
       <c r="D331" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E331">
         <v>43.97524497646168</v>
@@ -18115,7 +18112,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18129,7 +18126,7 @@
         <v>37.01610527202449</v>
       </c>
       <c r="D332" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E332">
         <v>43.97524497646168</v>
@@ -18165,7 +18162,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18179,7 +18176,7 @@
         <v>25.78116025897209</v>
       </c>
       <c r="D333" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E333">
         <v>34.97083622412276</v>
@@ -18215,7 +18212,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18229,7 +18226,7 @@
         <v>21.78292834045364</v>
       </c>
       <c r="D334" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E334">
         <v>32.11135258573889</v>
@@ -18265,7 +18262,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18279,7 +18276,7 @@
         <v>16.20611168178342</v>
       </c>
       <c r="D335" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E335">
         <v>27.00103770079773</v>
@@ -18315,7 +18312,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18329,7 +18326,7 @@
         <v>16.50484318653699</v>
       </c>
       <c r="D336" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E336">
         <v>27.00103770079773</v>
@@ -18365,7 +18362,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18379,7 +18376,7 @@
         <v>7.513223702566968</v>
       </c>
       <c r="D337" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E337">
         <v>19.03531145368304</v>
@@ -18415,7 +18412,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18429,7 +18426,7 @@
         <v>7.993745640345985</v>
       </c>
       <c r="D338" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E338">
         <v>19.03531145368304</v>
@@ -18465,7 +18462,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18479,7 +18476,7 @@
         <v>-3.101932223543415</v>
       </c>
       <c r="D339" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E339">
         <v>9.308115338882274</v>
@@ -18515,7 +18512,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18529,7 +18526,7 @@
         <v>-2.399420332936991</v>
       </c>
       <c r="D340" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E340">
         <v>9.308115338882274</v>
@@ -18565,7 +18562,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18579,7 +18576,7 @@
         <v>-2.646016646848999</v>
       </c>
       <c r="D341" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E341">
         <v>9.308115338882274</v>
@@ -18615,7 +18612,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18629,7 +18626,7 @@
         <v>-9.121415898188509</v>
       </c>
       <c r="D342" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E342">
         <v>3.792162618009769</v>
@@ -18665,7 +18662,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18679,7 +18676,7 @@
         <v>-8.59683700961601</v>
       </c>
       <c r="D343" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E343">
         <v>3.792162618009769</v>
@@ -18715,7 +18712,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18729,7 +18726,7 @@
         <v>-12.89770073310627</v>
       </c>
       <c r="D344" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E344">
         <v>0.3317647274577595</v>
@@ -18765,7 +18762,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18779,7 +18776,7 @@
         <v>-14.09288737405897</v>
       </c>
       <c r="D345" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E345">
         <v>-0.7634443237574615</v>
@@ -18815,7 +18812,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18829,7 +18826,7 @@
         <v>59.56360813550708</v>
       </c>
       <c r="D346" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E346">
         <v>75.18159673719033</v>
@@ -18865,7 +18862,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18879,7 +18876,7 @@
         <v>60.31956868780029</v>
       </c>
       <c r="D347" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E347">
         <v>76.03992694760657</v>
@@ -18915,7 +18912,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18929,7 +18926,7 @@
         <v>62.79431714399279</v>
       </c>
       <c r="D348" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E348">
         <v>77.62631903124894</v>
@@ -18965,7 +18962,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18979,7 +18976,7 @@
         <v>64.08298118239738</v>
       </c>
       <c r="D349" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E349">
         <v>79.11665728256037</v>
@@ -19015,7 +19012,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19029,7 +19026,7 @@
         <v>64.68906100731142</v>
       </c>
       <c r="D350" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E350">
         <v>79.81758779625406</v>
@@ -19065,7 +19062,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19079,7 +19076,7 @@
         <v>66.03163316666149</v>
       </c>
       <c r="D351" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E351">
         <v>81.37027071794273</v>
@@ -19115,7 +19112,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19129,7 +19126,7 @@
         <v>65.93064756206419</v>
       </c>
       <c r="D352" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E352">
         <v>81.25348100015911</v>
@@ -19165,7 +19162,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19179,7 +19176,7 @@
         <v>64.84418812133572</v>
       </c>
       <c r="D353" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E353">
         <v>80.16577874075962</v>
@@ -19215,7 +19212,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19229,7 +19226,7 @@
         <v>63.26616721431549</v>
       </c>
       <c r="D354" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E354">
         <v>79.97190339753475</v>
@@ -19265,7 +19262,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19279,7 +19276,7 @@
         <v>61.66554474645639</v>
       </c>
       <c r="D355" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E355">
         <v>78.05285470927927</v>
@@ -19315,7 +19312,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19329,7 +19326,7 @@
         <v>60.62679073828761</v>
       </c>
       <c r="D356" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E356">
         <v>76.80745202574536</v>
@@ -19365,7 +19362,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19379,7 +19376,7 @@
         <v>59.7052486970962</v>
       </c>
       <c r="D357" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E357">
         <v>75.70257933975458</v>
@@ -19415,7 +19412,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19429,7 +19426,7 @@
         <v>50.59926427854958</v>
       </c>
       <c r="D358" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E358">
         <v>64.78505955942813</v>
@@ -19465,7 +19462,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19479,7 +19476,7 @@
         <v>54.80887863487924</v>
       </c>
       <c r="D359" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E359">
         <v>72.15232554251514</v>
@@ -19515,7 +19512,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19526,34 +19523,34 @@
         <v>130</v>
       </c>
       <c r="C360">
-        <v>22.63799956449154</v>
+        <v>18.34604038720835</v>
       </c>
       <c r="D360" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E360">
-        <v>34.76775640560354</v>
+        <v>30.18004248156539</v>
       </c>
       <c r="F360">
         <v>1</v>
       </c>
       <c r="G360">
-        <v>0.1349620004355085</v>
+        <v>0.1438539596127917</v>
       </c>
       <c r="H360">
-        <v>0.1426322435943965</v>
+        <v>0.1472199575184346</v>
       </c>
       <c r="I360">
-        <v>12.12975684111201</v>
+        <v>11.83400209435703</v>
       </c>
       <c r="J360">
-        <v>0.2787196051389998</v>
+        <v>0.3024287210255019</v>
       </c>
       <c r="K360">
-        <v>201.5</v>
+        <v>207.5</v>
       </c>
       <c r="L360">
-        <v>78.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="M360">
         <v>193.5</v>
@@ -19565,7 +19562,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19573,37 +19570,37 @@
         <v>0</v>
       </c>
       <c r="B361" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C361">
-        <v>21.94224021195173</v>
+        <v>16.86218987799047</v>
       </c>
       <c r="D361" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E361">
-        <v>34.09962025316457</v>
+        <v>28.54797932714153</v>
       </c>
       <c r="F361">
         <v>1</v>
       </c>
       <c r="G361">
-        <v>0.1356577597880483</v>
+        <v>0.1449378101220095</v>
       </c>
       <c r="H361">
-        <v>0.1433003797468354</v>
+        <v>0.1488520206728585</v>
       </c>
       <c r="I361">
-        <v>12.15738004121285</v>
+        <v>11.68578944915105</v>
       </c>
       <c r="J361">
-        <v>0.2821725051516043</v>
+        <v>0.3108631559320851</v>
       </c>
       <c r="K361">
-        <v>201.5</v>
+        <v>206</v>
       </c>
       <c r="L361">
-        <v>78.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="M361">
         <v>193.5</v>
@@ -19615,7 +19612,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19623,49 +19620,49 @@
         <v>0</v>
       </c>
       <c r="B362" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C362">
-        <v>20.45188899670399</v>
+        <v>9.990756344042168</v>
       </c>
       <c r="D362" t="s">
         <v>245</v>
       </c>
       <c r="E362">
-        <v>32.14380973909506</v>
+        <v>21.4889221484264</v>
       </c>
       <c r="F362">
         <v>1</v>
       </c>
       <c r="G362">
-        <v>0.141748111003296</v>
+        <v>0.1552092436559578</v>
       </c>
       <c r="H362">
-        <v>0.1452561902609049</v>
+        <v>0.1653110778515736</v>
       </c>
       <c r="I362">
-        <v>11.69192074239107</v>
+        <v>11.49816580438423</v>
       </c>
       <c r="J362">
-        <v>0.2922800530279325</v>
+        <v>0.3490829021921049</v>
       </c>
       <c r="K362">
-        <v>207.5</v>
+        <v>208</v>
       </c>
       <c r="L362">
-        <v>81.09999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="M362">
-        <v>193.5</v>
+        <v>206</v>
       </c>
       <c r="N362">
-        <v>88.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="O362">
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19673,81 +19670,81 @@
         <v>0</v>
       </c>
       <c r="B363" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C363">
-        <v>18.55332655028487</v>
+        <v>8.066617110777202</v>
       </c>
       <c r="D363" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E363">
-        <v>30.18004248156539</v>
+        <v>19.78402126238126</v>
       </c>
       <c r="F363">
         <v>1</v>
       </c>
       <c r="G363">
-        <v>0.1422466734497151</v>
+        <v>0.1631333828892228</v>
       </c>
       <c r="H363">
-        <v>0.1472199575184346</v>
+        <v>0.1662159787376188</v>
       </c>
       <c r="I363">
-        <v>11.62671593128051</v>
+        <v>11.71740415160406</v>
       </c>
       <c r="J363">
-        <v>0.3024287210255019</v>
+        <v>0.3597836793003378</v>
       </c>
       <c r="K363">
-        <v>204.5</v>
+        <v>215.5</v>
       </c>
       <c r="L363">
-        <v>80.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M363">
-        <v>193.5</v>
+        <v>203.5</v>
       </c>
       <c r="N363">
-        <v>88.7</v>
+        <v>93</v>
       </c>
       <c r="O363">
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="364" spans="1:16">
       <c r="A364" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B364" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C364">
-        <v>14.44543186753303</v>
+        <v>7.76499470552973</v>
       </c>
       <c r="D364" t="s">
         <v>246</v>
       </c>
       <c r="E364">
-        <v>25.90076425342215</v>
+        <v>19.78402126238126</v>
       </c>
       <c r="F364">
         <v>1</v>
       </c>
       <c r="G364">
-        <v>0.150754568132467</v>
+        <v>0.1574350052944703</v>
       </c>
       <c r="H364">
-        <v>0.1608992357465779</v>
+        <v>0.1662159787376188</v>
       </c>
       <c r="I364">
-        <v>11.45533238588912</v>
+        <v>12.01902655685153</v>
       </c>
       <c r="J364">
-        <v>0.3276661929445527</v>
+        <v>0.3597836793003378</v>
       </c>
       <c r="K364">
         <v>208</v>
@@ -19756,16 +19753,16 @@
         <v>82.59999999999999</v>
       </c>
       <c r="M364">
-        <v>206</v>
+        <v>203.5</v>
       </c>
       <c r="N364">
-        <v>93.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="O364">
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>131</v>
+        <v>460</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19773,143 +19770,143 @@
         <v>0</v>
       </c>
       <c r="B365" t="s">
+        <v>134</v>
+      </c>
+      <c r="C365">
+        <v>-3.562425933343519</v>
+      </c>
+      <c r="D365" t="s">
+        <v>247</v>
+      </c>
+      <c r="E365">
+        <v>8.196361928702586</v>
+      </c>
+      <c r="F365">
+        <v>1</v>
+      </c>
+      <c r="G365">
+        <v>0.1663624259333435</v>
+      </c>
+      <c r="H365">
+        <v>0.1798036380712974</v>
+      </c>
+      <c r="I365">
+        <v>11.75878786204611</v>
+      </c>
+      <c r="J365">
+        <v>0.4206060689769481</v>
+      </c>
+      <c r="K365">
+        <v>202</v>
+      </c>
+      <c r="L365">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="M365">
+        <v>204</v>
+      </c>
+      <c r="N365">
+        <v>94</v>
+      </c>
+      <c r="O365">
+        <v>1</v>
+      </c>
+      <c r="P365" t="s">
         <v>133</v>
-      </c>
-      <c r="C365">
-        <v>12.82667623833451</v>
-      </c>
-      <c r="D365" t="s">
-        <v>246</v>
-      </c>
-      <c r="E365">
-        <v>24.29757358219669</v>
-      </c>
-      <c r="F365">
-        <v>1</v>
-      </c>
-      <c r="G365">
-        <v>0.1523733237616655</v>
-      </c>
-      <c r="H365">
-        <v>0.1625024264178033</v>
-      </c>
-      <c r="I365">
-        <v>11.47089734386218</v>
-      </c>
-      <c r="J365">
-        <v>0.335448671931084</v>
-      </c>
-      <c r="K365">
-        <v>208</v>
-      </c>
-      <c r="L365">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="M365">
-        <v>206</v>
-      </c>
-      <c r="N365">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="O365">
-        <v>1</v>
-      </c>
-      <c r="P365" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="366" spans="1:16">
       <c r="A366" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B366" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C366">
-        <v>10.37263457760139</v>
+        <v>-3.424244140274368</v>
       </c>
       <c r="D366" t="s">
         <v>247</v>
       </c>
       <c r="E366">
-        <v>21.96162940390666</v>
+        <v>8.196361928702586</v>
       </c>
       <c r="F366">
         <v>1</v>
       </c>
       <c r="G366">
-        <v>0.1608273654223986</v>
+        <v>0.1690242441402744</v>
       </c>
       <c r="H366">
-        <v>0.1640383705960933</v>
+        <v>0.1798036380712974</v>
       </c>
       <c r="I366">
-        <v>11.58899482630527</v>
+        <v>11.62060606897695</v>
       </c>
       <c r="J366">
-        <v>0.3490829021921049</v>
+        <v>0.4206060689769481</v>
       </c>
       <c r="K366">
-        <v>215.5</v>
+        <v>205</v>
       </c>
       <c r="L366">
-        <v>85.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="M366">
-        <v>203.5</v>
+        <v>204</v>
       </c>
       <c r="N366">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O366">
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>461</v>
+        <v>133</v>
       </c>
     </row>
     <row r="367" spans="1:16">
       <c r="A367" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B367" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C367">
-        <v>9.990756344042168</v>
+        <v>-2.10269534440512</v>
       </c>
       <c r="D367" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E367">
-        <v>21.96162940390666</v>
+        <v>10.74605227334604</v>
       </c>
       <c r="F367">
         <v>1</v>
       </c>
       <c r="G367">
-        <v>0.1552092436559578</v>
+        <v>0.1703026953444051</v>
       </c>
       <c r="H367">
-        <v>0.1640383705960933</v>
+        <v>0.185253947726654</v>
       </c>
       <c r="I367">
-        <v>11.97087305986449</v>
+        <v>12.84874761775116</v>
       </c>
       <c r="J367">
-        <v>0.3490829021921049</v>
+        <v>0.4205009528995372</v>
       </c>
       <c r="K367">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L367">
-        <v>82.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M367">
-        <v>203.5</v>
+        <v>207.5</v>
       </c>
       <c r="N367">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="O367">
         <v>1</v>
@@ -19920,96 +19917,96 @@
     </row>
     <row r="368" spans="1:16">
       <c r="A368" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B368" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C368">
-        <v>8.066617110777202</v>
+        <v>-2.85417914511298</v>
       </c>
       <c r="D368" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E368">
-        <v>19.78402126238126</v>
+        <v>-2.443928668663204</v>
       </c>
       <c r="F368">
         <v>1</v>
       </c>
       <c r="G368">
-        <v>0.1631333828892228</v>
+        <v>0.155254179145113</v>
       </c>
       <c r="H368">
-        <v>0.1662159787376188</v>
+        <v>0.1552439286686632</v>
       </c>
       <c r="I368">
-        <v>11.71740415160406</v>
+        <v>0.4102504764497752</v>
       </c>
       <c r="J368">
-        <v>0.3597836793003378</v>
+        <v>0.4205009528995372</v>
       </c>
       <c r="K368">
-        <v>215.5</v>
+        <v>188</v>
       </c>
       <c r="L368">
-        <v>85.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="M368">
-        <v>203.5</v>
+        <v>187.5</v>
       </c>
       <c r="N368">
-        <v>93</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="O368">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P368" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="369" spans="1:16">
       <c r="A369" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B369" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C369">
-        <v>8.364994705529739</v>
+        <v>-2.91355538156337</v>
       </c>
       <c r="D369" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E369">
-        <v>19.78402126238126</v>
+        <v>9.925303699149282</v>
       </c>
       <c r="F369">
         <v>1</v>
       </c>
       <c r="G369">
-        <v>0.1580350052944703</v>
+        <v>0.1711135553815633</v>
       </c>
       <c r="H369">
-        <v>0.1662159787376188</v>
+        <v>0.1860746963008507</v>
       </c>
       <c r="I369">
-        <v>11.41902655685152</v>
+        <v>12.83885908071265</v>
       </c>
       <c r="J369">
-        <v>0.3597836793003378</v>
+        <v>0.4244563677149432</v>
       </c>
       <c r="K369">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L369">
-        <v>83.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M369">
-        <v>203.5</v>
+        <v>207.5</v>
       </c>
       <c r="N369">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="O369">
         <v>1</v>
@@ -20020,52 +20017,52 @@
     </row>
     <row r="370" spans="1:16">
       <c r="A370" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B370" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C370">
-        <v>-3.424244140274368</v>
+        <v>-2.397797130409316</v>
       </c>
       <c r="D370" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E370">
-        <v>10.72424068728326</v>
+        <v>-3.185568946551854</v>
       </c>
       <c r="F370">
         <v>1</v>
       </c>
       <c r="G370">
-        <v>0.1690242441402744</v>
+        <v>0.1571977971304093</v>
       </c>
       <c r="H370">
-        <v>0.1852757593127167</v>
+        <v>0.1559855689465519</v>
       </c>
       <c r="I370">
-        <v>14.14848482755762</v>
+        <v>-0.7877718161425378</v>
       </c>
       <c r="J370">
-        <v>0.4206060689769481</v>
+        <v>0.4244563677149432</v>
       </c>
       <c r="K370">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="L370">
-        <v>82.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="M370">
-        <v>207.5</v>
+        <v>187.5</v>
       </c>
       <c r="N370">
-        <v>98</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="O370">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P370" t="s">
-        <v>134</v>
+        <v>462</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20073,46 +20070,46 @@
         <v>0</v>
       </c>
       <c r="B371" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C371">
-        <v>-2.10269534440512</v>
+        <v>-2.4055655425325</v>
       </c>
       <c r="D371" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E371">
-        <v>10.74605227334604</v>
+        <v>-5.748378514417155</v>
       </c>
       <c r="F371">
         <v>1</v>
       </c>
       <c r="G371">
-        <v>0.1703026953444051</v>
+        <v>0.1632055655425325</v>
       </c>
       <c r="H371">
-        <v>0.185253947726654</v>
+        <v>0.1585483785144172</v>
       </c>
       <c r="I371">
-        <v>12.84874761775116</v>
+        <v>-3.342812971884655</v>
       </c>
       <c r="J371">
-        <v>0.4205009528995372</v>
+        <v>0.4381246854102249</v>
       </c>
       <c r="K371">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="L371">
-        <v>84.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="M371">
-        <v>207.5</v>
+        <v>187.5</v>
       </c>
       <c r="N371">
-        <v>98</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="O371">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P371" t="s">
         <v>463</v>
@@ -20120,31 +20117,52 @@
     </row>
     <row r="372" spans="1:16">
       <c r="A372" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B372" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C372">
-        <v>-1.654179145112977</v>
+        <v>-38.65235447171061</v>
+      </c>
+      <c r="D372" t="s">
+        <v>249</v>
+      </c>
+      <c r="E372">
+        <v>-41.70749451558592</v>
       </c>
       <c r="F372">
         <v>1</v>
       </c>
       <c r="G372">
-        <v>0.156454179145113</v>
+        <v>0.1994523544717106</v>
+      </c>
+      <c r="H372">
+        <v>0.1945074945155859</v>
+      </c>
+      <c r="I372">
+        <v>-3.055140043875312</v>
       </c>
       <c r="J372">
-        <v>0.4205009528995372</v>
+        <v>0.6299066374164582</v>
       </c>
       <c r="K372">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L372">
-        <v>77.40000000000001</v>
+        <v>80.40000000000001</v>
+      </c>
+      <c r="M372">
+        <v>187.5</v>
+      </c>
+      <c r="N372">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="O372">
+        <v>0</v>
       </c>
       <c r="P372" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20155,96 +20173,96 @@
         <v>137</v>
       </c>
       <c r="C373">
-        <v>-2.91355538156337</v>
+        <v>14.47890124851195</v>
       </c>
       <c r="D373" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E373">
-        <v>9.925303699149282</v>
+        <v>14.84305310689357</v>
       </c>
       <c r="F373">
         <v>1</v>
       </c>
       <c r="G373">
-        <v>0.1711135553815633</v>
+        <v>0.1379210987514881</v>
       </c>
       <c r="H373">
-        <v>0.1860746963008507</v>
+        <v>0.1379569468931064</v>
       </c>
       <c r="I373">
-        <v>12.83885908071265</v>
+        <v>0.364151858381625</v>
       </c>
       <c r="J373">
-        <v>0.4244563677149432</v>
+        <v>0.3283037167632343</v>
       </c>
       <c r="K373">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="L373">
-        <v>84.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="M373">
-        <v>207.5</v>
+        <v>187.5</v>
       </c>
       <c r="N373">
-        <v>98</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="O373">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P373" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="374" spans="1:16">
       <c r="A374" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B374" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C374">
-        <v>-1.797797130409322</v>
+        <v>12.29886568031696</v>
       </c>
       <c r="D374" t="s">
-        <v>138</v>
+        <v>249</v>
       </c>
       <c r="E374">
-        <v>-2.397797130409316</v>
+        <v>12.66881550563527</v>
       </c>
       <c r="F374">
         <v>1</v>
       </c>
       <c r="G374">
-        <v>0.1577977971304093</v>
+        <v>0.140101134319683</v>
       </c>
       <c r="H374">
-        <v>0.1571977971304093</v>
+        <v>0.1401311844943647</v>
       </c>
       <c r="I374">
-        <v>-0.5999999999999943</v>
+        <v>0.3699498253183151</v>
       </c>
       <c r="J374">
-        <v>0.4244563677149432</v>
+        <v>0.3398996506366119</v>
       </c>
       <c r="K374">
         <v>188</v>
       </c>
       <c r="L374">
-        <v>78</v>
+        <v>76.2</v>
       </c>
       <c r="M374">
-        <v>188</v>
+        <v>187.5</v>
       </c>
       <c r="N374">
-        <v>77.40000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="O374">
         <v>0</v>
       </c>
       <c r="P374" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20255,196 +20273,46 @@
         <v>140</v>
       </c>
       <c r="C375">
-        <v>-1.02931617171204</v>
+        <v>0.7748127541194236</v>
       </c>
       <c r="D375" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E375">
-        <v>-4.96744085712227</v>
+        <v>-9.173050211077154</v>
       </c>
       <c r="F375">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G375">
-        <v>0.162829316171712</v>
+        <v>0.1780251872458806</v>
       </c>
       <c r="H375">
-        <v>0.1597674408571223</v>
+        <v>0.1699730502110772</v>
       </c>
       <c r="I375">
-        <v>-3.93812468541023</v>
+        <v>9.947862965196578</v>
       </c>
       <c r="J375">
-        <v>0.4381246854102249</v>
+        <v>0.4739314825982919</v>
       </c>
       <c r="K375">
         <v>187</v>
       </c>
       <c r="L375">
-        <v>80.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="M375">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N375">
-        <v>77.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="O375">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="376" spans="1:16">
-      <c r="A376" s="1">
-        <v>0</v>
-      </c>
-      <c r="B376" t="s">
-        <v>140</v>
-      </c>
-      <c r="C376">
-        <v>-36.89254119687769</v>
-      </c>
-      <c r="D376" t="s">
-        <v>138</v>
-      </c>
-      <c r="E376">
-        <v>-41.02244783429414</v>
-      </c>
-      <c r="F376">
-        <v>1</v>
-      </c>
-      <c r="G376">
-        <v>0.1986925411968777</v>
-      </c>
-      <c r="H376">
-        <v>0.1958224478342942</v>
-      </c>
-      <c r="I376">
-        <v>-4.129906637416454</v>
-      </c>
-      <c r="J376">
-        <v>0.6299066374164582</v>
-      </c>
-      <c r="K376">
-        <v>187</v>
-      </c>
-      <c r="L376">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="M376">
-        <v>188</v>
-      </c>
-      <c r="N376">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="O376">
-        <v>0</v>
-      </c>
-      <c r="P376" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="377" spans="1:16">
-      <c r="A377" s="1">
-        <v>0</v>
-      </c>
-      <c r="B377" t="s">
-        <v>141</v>
-      </c>
-      <c r="C377">
-        <v>16.56381239880164</v>
-      </c>
-      <c r="D377" t="s">
-        <v>138</v>
-      </c>
-      <c r="E377">
-        <v>15.67890124851195</v>
-      </c>
-      <c r="F377">
-        <v>1</v>
-      </c>
-      <c r="G377">
-        <v>0.1380361876011983</v>
-      </c>
-      <c r="H377">
-        <v>0.1391210987514881</v>
-      </c>
-      <c r="I377">
-        <v>-0.884911150289696</v>
-      </c>
-      <c r="J377">
-        <v>0.3283037167632343</v>
-      </c>
-      <c r="K377">
-        <v>185</v>
-      </c>
-      <c r="L377">
-        <v>77.3</v>
-      </c>
-      <c r="M377">
-        <v>188</v>
-      </c>
-      <c r="N377">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="O377">
-        <v>0</v>
-      </c>
-      <c r="P377" t="s">
         <v>467</v>
-      </c>
-    </row>
-    <row r="378" spans="1:16">
-      <c r="A378" s="1">
-        <v>0</v>
-      </c>
-      <c r="B378" t="s">
-        <v>139</v>
-      </c>
-      <c r="C378">
-        <v>14.09886568031695</v>
-      </c>
-      <c r="D378" t="s">
-        <v>138</v>
-      </c>
-      <c r="E378">
-        <v>13.49886568031696</v>
-      </c>
-      <c r="F378">
-        <v>1</v>
-      </c>
-      <c r="G378">
-        <v>0.141901134319683</v>
-      </c>
-      <c r="H378">
-        <v>0.1413011343196831</v>
-      </c>
-      <c r="I378">
-        <v>-0.5999999999999943</v>
-      </c>
-      <c r="J378">
-        <v>0.3398996506366119</v>
-      </c>
-      <c r="K378">
-        <v>188</v>
-      </c>
-      <c r="L378">
-        <v>78</v>
-      </c>
-      <c r="M378">
-        <v>188</v>
-      </c>
-      <c r="N378">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="O378">
-        <v>0</v>
-      </c>
-      <c r="P378" t="s">
-        <v>468</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-2474-2382-800.xlsx
+++ b/s60_signal/position-2474-2382-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="469">
   <si>
     <t>trade_time</t>
   </si>
@@ -406,10 +406,13 @@
     <t>2020-11-12</t>
   </si>
   <si>
+    <t>2020-12-24</t>
+  </si>
+  <si>
     <t>2021-01-04</t>
   </si>
   <si>
-    <t>2020-12-31</t>
+    <t>2020-12-29</t>
   </si>
   <si>
     <t>2021-01-19</t>
@@ -418,7 +421,7 @@
     <t>2021-01-14</t>
   </si>
   <si>
-    <t>2021-01-21</t>
+    <t>2021-01-18</t>
   </si>
   <si>
     <t>2021-01-28</t>
@@ -427,16 +430,16 @@
     <t>2021-01-27</t>
   </si>
   <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
     <t>2021-08-03</t>
   </si>
   <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
-    <t>2021-07-23</t>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>2021-07-26</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
   </si>
   <si>
     <t>2010-10-22</t>
@@ -757,15 +760,9 @@
     <t>2021-03-25</t>
   </si>
   <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
     <t>2021-03-29</t>
   </si>
   <si>
-    <t>2021-08-05</t>
-  </si>
-  <si>
     <t>2010-08-03</t>
   </si>
   <si>
@@ -1387,10 +1384,19 @@
     <t>2020-11-02</t>
   </si>
   <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
     <t>2020-12-28</t>
   </si>
   <si>
-    <t>2020-12-29</t>
+    <t>2021-01-05</t>
   </si>
   <si>
     <t>2021-01-06</t>
@@ -1415,9 +1421,6 @@
   </si>
   <si>
     <t>2021-06-18</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
   </si>
 </sst>
 </file>
@@ -1775,7 +1778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P375"/>
+  <dimension ref="A1:P378"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1836,7 +1839,7 @@
         <v>39.24967816269653</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E2">
         <v>47.58658728904034</v>
@@ -1872,7 +1875,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1886,7 +1889,7 @@
         <v>41.7045814878046</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E3">
         <v>51.36624085194781</v>
@@ -1922,7 +1925,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1936,7 +1939,7 @@
         <v>47.73273319613877</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E4">
         <v>59.43490802303255</v>
@@ -1972,7 +1975,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1986,7 +1989,7 @@
         <v>47.24820828667414</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E5">
         <v>58.87563172501095</v>
@@ -2022,7 +2025,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2036,7 +2039,7 @@
         <v>47.16470096247878</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E6">
         <v>58.77924108291729</v>
@@ -2072,7 +2075,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2086,7 +2089,7 @@
         <v>-15.1664654510749</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E7">
         <v>-7.294892481790129</v>
@@ -2122,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2136,7 +2139,7 @@
         <v>-14.45834344229912</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E8">
         <v>-7.294892481790129</v>
@@ -2172,7 +2175,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2186,7 +2189,7 @@
         <v>-13.39336737209288</v>
       </c>
       <c r="D9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E9">
         <v>-7.294892481790129</v>
@@ -2222,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2236,7 +2239,7 @@
         <v>-16.33245230627455</v>
       </c>
       <c r="D10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E10">
         <v>-7.294892481790129</v>
@@ -2272,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2286,7 +2289,7 @@
         <v>-29.63643996743208</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E11">
         <v>-21.37792699357366</v>
@@ -2322,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2336,7 +2339,7 @@
         <v>-29.01030081710592</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E12">
         <v>-21.37792699357366</v>
@@ -2372,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2386,7 +2389,7 @@
         <v>-28.60118761449661</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E13">
         <v>-21.37792699357366</v>
@@ -2422,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2436,7 +2439,7 @@
         <v>-49.08464630848418</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E14">
         <v>-42.77667080227592</v>
@@ -2472,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2486,7 +2489,7 @@
         <v>-48.56869529606767</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E15">
         <v>-42.77667080227592</v>
@@ -2522,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2536,7 +2539,7 @@
         <v>-49.0410871967355</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E16">
         <v>-42.77667080227592</v>
@@ -2572,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2586,7 +2589,7 @@
         <v>-65.70804604683664</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E17">
         <v>-56.94115587886895</v>
@@ -2622,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2636,7 +2639,7 @@
         <v>-65.6116252316011</v>
       </c>
       <c r="D18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E18">
         <v>-56.94115587886895</v>
@@ -2672,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2686,7 +2689,7 @@
         <v>-79.57406496333017</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E19">
         <v>-67.54165070713992</v>
@@ -2722,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2736,7 +2739,7 @@
         <v>-113.1125372679468</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E20">
         <v>-103.9345101187686</v>
@@ -2772,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2786,7 +2789,7 @@
         <v>-150.4700278614179</v>
       </c>
       <c r="D21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E21">
         <v>-141.3269680910878</v>
@@ -2822,7 +2825,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2836,7 +2839,7 @@
         <v>-191.2456393652701</v>
       </c>
       <c r="D22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E22">
         <v>-165.2314426418361</v>
@@ -2872,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2886,7 +2889,7 @@
         <v>-208.9753900042601</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E23">
         <v>-181.8698454183375</v>
@@ -2922,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2936,7 +2939,7 @@
         <v>-222.2487414251906</v>
       </c>
       <c r="D24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E24">
         <v>-206.4607237347662</v>
@@ -2972,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2986,7 +2989,7 @@
         <v>-239.7112109310854</v>
       </c>
       <c r="D25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E25">
         <v>-219.5184020745525</v>
@@ -3022,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3036,7 +3039,7 @@
         <v>-263.1154559964206</v>
       </c>
       <c r="D26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E26">
         <v>-240.6747187530921</v>
@@ -3072,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3086,7 +3089,7 @@
         <v>-268.6224791106823</v>
       </c>
       <c r="D27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E27">
         <v>-252.6279978948062</v>
@@ -3122,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3151,7 +3154,7 @@
         <v>59.3</v>
       </c>
       <c r="P28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3180,7 +3183,7 @@
         <v>65.5</v>
       </c>
       <c r="P29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3194,7 +3197,7 @@
         <v>-254.0793405031437</v>
       </c>
       <c r="D30" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E30">
         <v>-235.7082244929039</v>
@@ -3230,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3244,7 +3247,7 @@
         <v>-238.7059320352077</v>
       </c>
       <c r="D31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E31">
         <v>-223.7765478327873</v>
@@ -3280,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3309,7 +3312,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="P32" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3359,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3373,7 +3376,7 @@
         <v>-85.8076603763717</v>
       </c>
       <c r="D34" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E34">
         <v>-85.31060902491748</v>
@@ -3409,7 +3412,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3423,7 +3426,7 @@
         <v>-78.41701518144652</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E35">
         <v>-77.28396586589429</v>
@@ -3459,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3488,7 +3491,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="P36" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3517,7 +3520,7 @@
         <v>70.09999999999999</v>
       </c>
       <c r="P37" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3531,7 +3534,7 @@
         <v>-77.43890142953504</v>
       </c>
       <c r="D38" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E38">
         <v>-86.03210595388953</v>
@@ -3567,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3581,7 +3584,7 @@
         <v>-75.24842836769179</v>
       </c>
       <c r="D39" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E39">
         <v>-82.41442691778926</v>
@@ -3617,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3631,7 +3634,7 @@
         <v>-75.26941837884658</v>
       </c>
       <c r="D40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E40">
         <v>-76.41687497573176</v>
@@ -3667,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3681,7 +3684,7 @@
         <v>2.405986219478436</v>
       </c>
       <c r="D41" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E41">
         <v>22.3137495724129</v>
@@ -3717,7 +3720,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3731,7 +3734,7 @@
         <v>-1.953147134466214</v>
       </c>
       <c r="D42" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E42">
         <v>19.32012787151115</v>
@@ -3767,7 +3770,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3781,7 +3784,7 @@
         <v>-16.2502130791469</v>
       </c>
       <c r="D43" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E43">
         <v>8.401660897453333</v>
@@ -3817,7 +3820,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3831,7 +3834,7 @@
         <v>-14.74859467309044</v>
       </c>
       <c r="D44" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E44">
         <v>8.401660897453333</v>
@@ -3867,7 +3870,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3881,7 +3884,7 @@
         <v>-29.86968571903745</v>
       </c>
       <c r="D45" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E45">
         <v>-0.9514709154835543</v>
@@ -3917,7 +3920,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3931,7 +3934,7 @@
         <v>60.63454015125168</v>
       </c>
       <c r="D46" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E46">
         <v>75.91925407409063</v>
@@ -3967,7 +3970,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3981,7 +3984,7 @@
         <v>61.36441721922468</v>
       </c>
       <c r="D47" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E47">
         <v>75.91925407409063</v>
@@ -4017,7 +4020,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4031,7 +4034,7 @@
         <v>89.12505313226613</v>
       </c>
       <c r="D48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E48">
         <v>73.92461224371841</v>
@@ -4067,7 +4070,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4081,7 +4084,7 @@
         <v>60.18080332327113</v>
       </c>
       <c r="D49" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E49">
         <v>75.16419394721952</v>
@@ -4117,7 +4120,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4131,7 +4134,7 @@
         <v>60.90367287266527</v>
       </c>
       <c r="D50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E50">
         <v>75.16419394721952</v>
@@ -4167,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4181,7 +4184,7 @@
         <v>88.41554187615753</v>
       </c>
       <c r="D51" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E51">
         <v>73.33247692380556</v>
@@ -4217,7 +4220,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4231,7 +4234,7 @@
         <v>39.99810912339372</v>
       </c>
       <c r="D52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E52">
         <v>55.15583755182445</v>
@@ -4267,7 +4270,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4281,7 +4284,7 @@
         <v>41.30719414984996</v>
       </c>
       <c r="D53" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E53">
         <v>55.15583755182445</v>
@@ -4317,7 +4320,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4331,7 +4334,7 @@
         <v>43.08151977105167</v>
       </c>
       <c r="D54" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E54">
         <v>55.9485635535138</v>
@@ -4367,7 +4370,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4381,7 +4384,7 @@
         <v>42.16532004667869</v>
       </c>
       <c r="D55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E55">
         <v>55.9485635535138</v>
@@ -4417,7 +4420,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4431,7 +4434,7 @@
         <v>42.55008107334416</v>
       </c>
       <c r="D56" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E56">
         <v>56.30400099154195</v>
@@ -4481,7 +4484,7 @@
         <v>43.58368103616133</v>
       </c>
       <c r="D57" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E57">
         <v>56.30400099154195</v>
@@ -4531,7 +4534,7 @@
         <v>44.27504780738504</v>
       </c>
       <c r="D58" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E58">
         <v>56.96559598792828</v>
@@ -4567,7 +4570,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4581,7 +4584,7 @@
         <v>44.76828997217422</v>
       </c>
       <c r="D59" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E59">
         <v>57.43759805949687</v>
@@ -4631,7 +4634,7 @@
         <v>46.95250922066406</v>
       </c>
       <c r="D60" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E60">
         <v>58.6275946856681</v>
@@ -4667,7 +4670,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4681,7 +4684,7 @@
         <v>47.37813227189867</v>
       </c>
       <c r="D61" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E61">
         <v>59.01897220404476</v>
@@ -4717,7 +4720,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4731,7 +4734,7 @@
         <v>48.93720072957618</v>
       </c>
       <c r="D62" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E62">
         <v>59.68207127489522</v>
@@ -4767,7 +4770,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4781,7 +4784,7 @@
         <v>48.94662890110423</v>
       </c>
       <c r="D63" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E63">
         <v>59.69094484809811</v>
@@ -4817,7 +4820,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4831,7 +4834,7 @@
         <v>54.08932335660573</v>
       </c>
       <c r="D64" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E64">
         <v>62.52278850035134</v>
@@ -4881,7 +4884,7 @@
         <v>67.18932335660573</v>
       </c>
       <c r="D65" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E65">
         <v>59.01736085156006</v>
@@ -4931,7 +4934,7 @@
         <v>54.27142458878302</v>
       </c>
       <c r="D66" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E66">
         <v>62.70264156916842</v>
@@ -4967,7 +4970,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4981,7 +4984,7 @@
         <v>67.37142458878301</v>
       </c>
       <c r="D67" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E67">
         <v>59.17608118479113</v>
@@ -5017,7 +5020,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5031,7 +5034,7 @@
         <v>54.44666418857609</v>
       </c>
       <c r="D68" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E68">
         <v>57.92296041603655</v>
@@ -5067,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="P68" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5081,7 +5084,7 @@
         <v>54.38623819452964</v>
       </c>
       <c r="D69" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E69">
         <v>62.81603772299223</v>
@@ -5117,7 +5120,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5131,7 +5134,7 @@
         <v>54.68320045790918</v>
       </c>
       <c r="D70" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E70">
         <v>62.81603772299223</v>
@@ -5167,7 +5170,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5181,7 +5184,7 @@
         <v>67.48623819452963</v>
       </c>
       <c r="D71" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E71">
         <v>59.27615329054065</v>
@@ -5217,7 +5220,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5231,7 +5234,7 @@
         <v>54.5181037654851</v>
       </c>
       <c r="D72" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E72">
         <v>55.68274527440479</v>
@@ -5267,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="P72" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5281,7 +5284,7 @@
         <v>101.1269386779503</v>
       </c>
       <c r="D73" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E73">
         <v>83.94100067443752</v>
@@ -5317,7 +5320,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5331,7 +5334,7 @@
         <v>75.45009517739128</v>
       </c>
       <c r="D74" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E74">
         <v>80.27451240300203</v>
@@ -5367,7 +5370,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5381,7 +5384,7 @@
         <v>121.9136696617972</v>
       </c>
       <c r="D75" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E75">
         <v>104.5517569407011</v>
@@ -5417,7 +5420,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5431,7 +5434,7 @@
         <v>124.0730248787269</v>
       </c>
       <c r="D76" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E76">
         <v>106.3319083146578</v>
@@ -5467,7 +5470,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5481,7 +5484,7 @@
         <v>125.8987716223492</v>
       </c>
       <c r="D77" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E77">
         <v>107.8370361179367</v>
@@ -5517,7 +5520,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5531,7 +5534,7 @@
         <v>127.8315078706938</v>
       </c>
       <c r="D78" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E78">
         <v>102.3788447068554</v>
@@ -5567,7 +5570,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5581,7 +5584,7 @@
         <v>127.8608026942557</v>
       </c>
       <c r="D79" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E79">
         <v>102.3788447068554</v>
@@ -5617,7 +5620,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5631,7 +5634,7 @@
         <v>126.3344628429377</v>
       </c>
       <c r="D80" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E80">
         <v>101.3477167540643</v>
@@ -5667,7 +5670,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5681,7 +5684,7 @@
         <v>126.3293867347399</v>
       </c>
       <c r="D81" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E81">
         <v>101.3477167540643</v>
@@ -5717,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5731,7 +5734,7 @@
         <v>126.0311094090764</v>
       </c>
       <c r="D82" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E82">
         <v>101.1387743378843</v>
@@ -5767,7 +5770,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5781,7 +5784,7 @@
         <v>126.0190685536726</v>
       </c>
       <c r="D83" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E83">
         <v>101.1387743378843</v>
@@ -5817,7 +5820,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5831,7 +5834,7 @@
         <v>126.620958855311</v>
       </c>
       <c r="D84" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E84">
         <v>101.5450481911581</v>
@@ -5867,7 +5870,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5881,7 +5884,7 @@
         <v>126.6224604616829</v>
       </c>
       <c r="D85" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E85">
         <v>101.5450481911581</v>
@@ -5917,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5931,7 +5934,7 @@
         <v>125.7796367080902</v>
       </c>
       <c r="D86" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E86">
         <v>100.9655660999601</v>
@@ -5967,7 +5970,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5981,7 +5984,7 @@
         <v>125.7618222447556</v>
       </c>
       <c r="D87" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E87">
         <v>100.9655660999601</v>
@@ -6017,7 +6020,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6031,7 +6034,7 @@
         <v>125.0669218669525</v>
       </c>
       <c r="D88" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E88">
         <v>100.4746655716255</v>
@@ -6067,7 +6070,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6081,7 +6084,7 @@
         <v>125.0327440526733</v>
       </c>
       <c r="D89" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E89">
         <v>100.4746655716255</v>
@@ -6117,7 +6120,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6131,7 +6134,7 @@
         <v>123.2289469739378</v>
       </c>
       <c r="D90" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E90">
         <v>99.20871347694691</v>
@@ -6167,7 +6170,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6181,7 +6184,7 @@
         <v>123.1525707565027</v>
       </c>
       <c r="D91" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E91">
         <v>99.20871347694691</v>
@@ -6217,7 +6220,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6231,7 +6234,7 @@
         <v>122.9583501275863</v>
       </c>
       <c r="D92" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E92">
         <v>99.02233299604161</v>
@@ -6267,7 +6270,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6281,7 +6284,7 @@
         <v>122.8757612274544</v>
       </c>
       <c r="D93" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E93">
         <v>99.02233299604161</v>
@@ -6317,7 +6320,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6331,7 +6334,7 @@
         <v>124.3519741722009</v>
       </c>
       <c r="D94" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E94">
         <v>99.98222710840369</v>
@@ -6367,7 +6370,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6381,7 +6384,7 @@
         <v>124.3013817424811</v>
       </c>
       <c r="D95" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E95">
         <v>99.98222710840369</v>
@@ -6417,7 +6420,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6431,7 +6434,7 @@
         <v>124.6891745905705</v>
       </c>
       <c r="D96" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E96">
         <v>100.2144824986073</v>
@@ -6467,7 +6470,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6481,7 +6484,7 @@
         <v>124.6463240071908</v>
       </c>
       <c r="D97" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E97">
         <v>100.2144824986073</v>
@@ -6517,7 +6520,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6531,7 +6534,7 @@
         <v>124.4800191586875</v>
       </c>
       <c r="D98" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E98">
         <v>100.0704213593001</v>
@@ -6567,7 +6570,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6581,7 +6584,7 @@
         <v>124.4323665373309</v>
       </c>
       <c r="D99" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E99">
         <v>100.0704213593001</v>
@@ -6617,7 +6620,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6631,7 +6634,7 @@
         <v>123.0108457893896</v>
       </c>
       <c r="D100" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E100">
         <v>99.05849072228368</v>
@@ -6667,7 +6670,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6681,7 +6684,7 @@
         <v>122.9294621467991</v>
       </c>
       <c r="D101" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E101">
         <v>99.05849072228368</v>
@@ -6717,7 +6720,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6731,7 +6734,7 @@
         <v>121.6453568496303</v>
       </c>
       <c r="D102" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E102">
         <v>98.11797538112289</v>
@@ -6767,7 +6770,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6781,7 +6784,7 @@
         <v>121.5326226956677</v>
       </c>
       <c r="D103" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E103">
         <v>98.11797538112289</v>
@@ -6817,7 +6820,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6831,7 +6834,7 @@
         <v>121.0299428079651</v>
       </c>
       <c r="D104" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E104">
         <v>97.69409326058823</v>
@@ -6867,7 +6870,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6881,7 +6884,7 @@
         <v>120.9030792499847</v>
       </c>
       <c r="D105" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E105">
         <v>97.69409326058823</v>
@@ -6917,7 +6920,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6931,7 +6934,7 @@
         <v>120.2680139970007</v>
       </c>
       <c r="D106" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E106">
         <v>97.169295355077</v>
@@ -6967,7 +6970,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6981,7 +6984,7 @@
         <v>120.1236571755032</v>
       </c>
       <c r="D107" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E107">
         <v>97.169295355077</v>
@@ -7017,7 +7020,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7031,7 +7034,7 @@
         <v>119.3894537106139</v>
       </c>
       <c r="D108" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E108">
         <v>96.56416454557592</v>
@@ -7067,7 +7070,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7081,7 +7084,7 @@
         <v>119.2249258621331</v>
       </c>
       <c r="D109" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E109">
         <v>96.56416454557592</v>
@@ -7117,7 +7120,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7131,7 +7134,7 @@
         <v>118.0996069245826</v>
       </c>
       <c r="D110" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E110">
         <v>95.67574966744206</v>
@@ -7167,7 +7170,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7181,7 +7184,7 @@
         <v>117.9054652468306</v>
       </c>
       <c r="D111" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E111">
         <v>95.67574966744206</v>
@@ -7217,7 +7220,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7231,7 +7234,7 @@
         <v>117.1017444652623</v>
       </c>
       <c r="D112" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E112">
         <v>94.98844644291023</v>
@@ -7267,7 +7270,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7281,7 +7284,7 @@
         <v>116.8846926800259</v>
       </c>
       <c r="D113" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E113">
         <v>94.98844644291023</v>
@@ -7317,7 +7320,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7331,7 +7334,7 @@
         <v>115.7903395541055</v>
       </c>
       <c r="D114" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E114">
         <v>94.08518285614407</v>
@@ -7367,7 +7370,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7381,7 +7384,7 @@
         <v>115.5431789826436</v>
       </c>
       <c r="D115" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E115">
         <v>94.08518285614407</v>
@@ -7417,7 +7420,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7431,7 +7434,7 @@
         <v>114.3600161010092</v>
       </c>
       <c r="D116" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E116">
         <v>93.10001108998082</v>
@@ -7467,7 +7470,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7481,7 +7484,7 @@
         <v>114.0800164706752</v>
       </c>
       <c r="D117" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E117">
         <v>93.10001108998082</v>
@@ -7517,7 +7520,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7531,7 +7534,7 @@
         <v>112.9215721869154</v>
       </c>
       <c r="D118" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E118">
         <v>92.10924614915092</v>
@@ -7567,7 +7570,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7581,7 +7584,7 @@
         <v>112.6085470585538</v>
       </c>
       <c r="D119" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E119">
         <v>92.10924614915092</v>
@@ -7617,7 +7620,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7631,7 +7634,7 @@
         <v>111.0753114680939</v>
       </c>
       <c r="D120" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E120">
         <v>91.07689300844227</v>
@@ -7681,7 +7684,7 @@
         <v>109.3637030177276</v>
       </c>
       <c r="D121" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E121">
         <v>89.92443844086398</v>
@@ -7717,7 +7720,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7731,7 +7734,7 @@
         <v>106.6367917601738</v>
       </c>
       <c r="D122" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E122">
         <v>88.08836352929409</v>
@@ -7767,7 +7770,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7781,7 +7784,7 @@
         <v>99.96873044828921</v>
       </c>
       <c r="D123" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E123">
         <v>83.59864643650396</v>
@@ -7817,7 +7820,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7831,7 +7834,7 @@
         <v>39.91051382546476</v>
       </c>
       <c r="D124" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E124">
         <v>42.55014562583152</v>
@@ -7867,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7881,7 +7884,7 @@
         <v>34.76754143004694</v>
       </c>
       <c r="D125" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E125">
         <v>38.11145388461416</v>
@@ -7917,7 +7920,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7931,7 +7934,7 @@
         <v>27.87373902743889</v>
       </c>
       <c r="D126" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E126">
         <v>28.73232502982488</v>
@@ -7967,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7981,7 +7984,7 @@
         <v>52.34452590842368</v>
       </c>
       <c r="D127" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E127">
         <v>60.02089394070224</v>
@@ -8017,7 +8020,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8031,7 +8034,7 @@
         <v>66.2681578761451</v>
       </c>
       <c r="D128" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E128">
         <v>59.00746128062423</v>
@@ -8067,7 +8070,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8081,7 +8084,7 @@
         <v>65.90298372726488</v>
       </c>
       <c r="D129" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E129">
         <v>59.00746128062423</v>
@@ -8117,7 +8120,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8131,7 +8134,7 @@
         <v>75.19054270184851</v>
       </c>
       <c r="D130" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E130">
         <v>82.88620847856147</v>
@@ -8167,7 +8170,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8181,7 +8184,7 @@
         <v>91.01410438583636</v>
       </c>
       <c r="D131" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E131">
         <v>85.34034548895417</v>
@@ -8217,7 +8220,7 @@
         <v>0</v>
       </c>
       <c r="P131" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8231,7 +8234,7 @@
         <v>90.69117289103272</v>
       </c>
       <c r="D132" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E132">
         <v>85.34034548895417</v>
@@ -8267,7 +8270,7 @@
         <v>0</v>
       </c>
       <c r="P132" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8281,7 +8284,7 @@
         <v>106.425283452306</v>
       </c>
       <c r="D133" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E133">
         <v>102.4841645631825</v>
@@ -8331,7 +8334,7 @@
         <v>106.7743510447031</v>
       </c>
       <c r="D134" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E134">
         <v>102.4841645631825</v>
@@ -8381,7 +8384,7 @@
         <v>64.83381773702186</v>
       </c>
       <c r="D135" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E135">
         <v>61.17785949472258</v>
@@ -8417,7 +8420,7 @@
         <v>0</v>
       </c>
       <c r="P135" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8431,7 +8434,7 @@
         <v>53.81062761975522</v>
       </c>
       <c r="D136" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E136">
         <v>45.81713512679965</v>
@@ -8467,7 +8470,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8481,7 +8484,7 @@
         <v>53.43128846396477</v>
       </c>
       <c r="D137" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E137">
         <v>47.7894228477703</v>
@@ -8517,7 +8520,7 @@
         <v>0</v>
       </c>
       <c r="P137" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8531,7 +8534,7 @@
         <v>48.70129852147022</v>
       </c>
       <c r="D138" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E138">
         <v>39.19252273181839</v>
@@ -8567,7 +8570,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8581,7 +8584,7 @@
         <v>44.87334693499027</v>
       </c>
       <c r="D139" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E139">
         <v>34.44403390958535</v>
@@ -8617,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8631,7 +8634,7 @@
         <v>40.45906823400685</v>
       </c>
       <c r="D140" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E140">
         <v>29.40254968722779</v>
@@ -8667,7 +8670,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8681,7 +8684,7 @@
         <v>37.79538016242914</v>
       </c>
       <c r="D141" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E141">
         <v>25.15160114518396</v>
@@ -8717,7 +8720,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8731,7 +8734,7 @@
         <v>37.68076952930594</v>
       </c>
       <c r="D142" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E142">
         <v>25.01802919408082</v>
@@ -8767,7 +8770,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8781,7 +8784,7 @@
         <v>63.15408222226404</v>
       </c>
       <c r="D143" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E143">
         <v>53.56243089690908</v>
@@ -8817,7 +8820,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8831,7 +8834,7 @@
         <v>31.1030054990203</v>
       </c>
       <c r="D144" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E144">
         <v>14.08734435244297</v>
@@ -8867,7 +8870,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8881,7 +8884,7 @@
         <v>25.05484991241799</v>
       </c>
       <c r="D145" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E145">
         <v>6.922187058405115</v>
@@ -8917,7 +8920,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8931,7 +8934,7 @@
         <v>18.81638310475921</v>
       </c>
       <c r="D146" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E146">
         <v>-0.4684290245420044</v>
@@ -8967,7 +8970,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8981,7 +8984,7 @@
         <v>13.01676813424353</v>
       </c>
       <c r="D147" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E147">
         <v>-7.339144057179965</v>
@@ -9017,7 +9020,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9031,7 +9034,7 @@
         <v>8.024396355482963</v>
       </c>
       <c r="D148" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E148">
         <v>-13.25353044372964</v>
@@ -9067,7 +9070,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9081,7 +9084,7 @@
         <v>7.720504878426524</v>
       </c>
       <c r="D149" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E149">
         <v>-13.61354602240461</v>
@@ -9117,7 +9120,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9131,7 +9134,7 @@
         <v>10.31388326476601</v>
       </c>
       <c r="D150" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E150">
         <v>-10.54121036651594</v>
@@ -9167,7 +9170,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9181,7 +9184,7 @@
         <v>11.14758883248732</v>
       </c>
       <c r="D151" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E151">
         <v>-9.553532148900146</v>
@@ -9217,7 +9220,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9231,7 +9234,7 @@
         <v>20.84560393192861</v>
       </c>
       <c r="D152" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E152">
         <v>1.935557811248756</v>
@@ -9267,7 +9270,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9281,7 +9284,7 @@
         <v>21.43389351871438</v>
       </c>
       <c r="D153" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E153">
         <v>2.632495474873352</v>
@@ -9317,7 +9320,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9331,7 +9334,7 @@
         <v>22.6162561113628</v>
       </c>
       <c r="D154" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E154">
         <v>4.033222330128012</v>
@@ -9367,7 +9370,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9381,7 +9384,7 @@
         <v>23.86897930913528</v>
       </c>
       <c r="D155" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E155">
         <v>5.517304316678292</v>
@@ -9417,7 +9420,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9431,7 +9434,7 @@
         <v>24.29022509961407</v>
       </c>
       <c r="D156" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E156">
         <v>6.016347753146405</v>
@@ -9467,7 +9470,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9481,7 +9484,7 @@
         <v>80.77258742920839</v>
       </c>
       <c r="D157" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E157">
         <v>71.50140757768273</v>
@@ -9517,7 +9520,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9531,7 +9534,7 @@
         <v>80.87119828430862</v>
       </c>
       <c r="D158" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E158">
         <v>71.50140757768273</v>
@@ -9567,7 +9570,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9581,7 +9584,7 @@
         <v>82.15331534782203</v>
       </c>
       <c r="D159" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E159">
         <v>71.50140757768273</v>
@@ -9617,7 +9620,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9631,7 +9634,7 @@
         <v>76.19581669669289</v>
       </c>
       <c r="D160" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E160">
         <v>66.74547500154564</v>
@@ -9667,7 +9670,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9681,7 +9684,7 @@
         <v>75.21863715900577</v>
       </c>
       <c r="D161" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E161">
         <v>66.74547500154564</v>
@@ -9717,7 +9720,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9731,7 +9734,7 @@
         <v>77.89414970172665</v>
       </c>
       <c r="D162" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E162">
         <v>66.74547500154564</v>
@@ -9767,7 +9770,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9781,7 +9784,7 @@
         <v>60.11863715900578</v>
       </c>
       <c r="D163" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E163">
         <v>68.03744024109169</v>
@@ -9817,7 +9820,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9831,7 +9834,7 @@
         <v>72.44565132750211</v>
       </c>
       <c r="D164" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E164">
         <v>62.8485060058029</v>
@@ -9867,7 +9870,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9881,7 +9884,7 @@
         <v>71.50850914251097</v>
       </c>
       <c r="D165" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E165">
         <v>62.8485060058029</v>
@@ -9917,7 +9920,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9931,7 +9934,7 @@
         <v>74.40422712505978</v>
       </c>
       <c r="D166" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E166">
         <v>62.8485060058029</v>
@@ -9967,7 +9970,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9981,7 +9984,7 @@
         <v>56.40850914251097</v>
       </c>
       <c r="D167" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E167">
         <v>64.59422790923679</v>
@@ -10017,7 +10020,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10031,7 +10034,7 @@
         <v>67.88820949982238</v>
       </c>
       <c r="D168" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E168">
         <v>60.43722302948107</v>
@@ -10081,7 +10084,7 @@
         <v>70.99880138202717</v>
       </c>
       <c r="D169" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E169">
         <v>60.43722302948107</v>
@@ -10131,7 +10134,7 @@
         <v>52.78820949982239</v>
       </c>
       <c r="D170" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E170">
         <v>61.23438147825242</v>
@@ -10181,7 +10184,7 @@
         <v>64.41272601732022</v>
       </c>
       <c r="D171" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E171">
         <v>56.61794172047242</v>
@@ -10217,7 +10220,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10231,7 +10234,7 @@
         <v>49.31272601732023</v>
       </c>
       <c r="D172" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E172">
         <v>58.0089327786641</v>
@@ -10267,7 +10270,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10281,7 +10284,7 @@
         <v>61.16879231159055</v>
       </c>
       <c r="D173" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E173">
         <v>53.82441738118666</v>
@@ -10317,7 +10320,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10331,7 +10334,7 @@
         <v>46.06879231159056</v>
       </c>
       <c r="D174" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E174">
         <v>54.08446933112747</v>
@@ -10367,7 +10370,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10381,7 +10384,7 @@
         <v>58.07192781203269</v>
       </c>
       <c r="D175" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E175">
         <v>50.68812094147531</v>
@@ -10417,7 +10420,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10431,7 +10434,7 @@
         <v>42.9719278120327</v>
       </c>
       <c r="D176" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E176">
         <v>51.29394934141796</v>
@@ -10467,7 +10470,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10481,7 +10484,7 @@
         <v>72.62623022483724</v>
       </c>
       <c r="D177" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E177">
         <v>78.13274022613687</v>
@@ -10517,7 +10520,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10531,7 +10534,7 @@
         <v>72.14377020837516</v>
       </c>
       <c r="D178" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E178">
         <v>78.53925022743653</v>
@@ -10567,7 +10570,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10581,7 +10584,7 @@
         <v>83.25643025082999</v>
       </c>
       <c r="D179" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E179">
         <v>77.7759602547289</v>
@@ -10617,7 +10620,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10646,7 +10649,7 @@
         <v>71.40000000000001</v>
       </c>
       <c r="P180" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10675,7 +10678,7 @@
         <v>72.09999999999999</v>
       </c>
       <c r="P181" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10689,7 +10692,7 @@
         <v>66.25534327603719</v>
       </c>
       <c r="D182" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E182">
         <v>53.25789242985769</v>
@@ -10739,7 +10742,7 @@
         <v>66.50153349826817</v>
       </c>
       <c r="D183" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E183">
         <v>53.49926887679366</v>
@@ -10775,7 +10778,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10789,7 +10792,7 @@
         <v>65.13958707494101</v>
       </c>
       <c r="D184" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E184">
         <v>53.20617458032149</v>
@@ -10825,7 +10828,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10839,7 +10842,7 @@
         <v>65.2660759255686</v>
       </c>
       <c r="D185" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E185">
         <v>53.20617458032149</v>
@@ -10875,7 +10878,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10889,7 +10892,7 @@
         <v>63.88275361614285</v>
       </c>
       <c r="D186" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E186">
         <v>51.96525040581191</v>
@@ -10925,7 +10928,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10939,7 +10942,7 @@
         <v>82.52792611826956</v>
       </c>
       <c r="D187" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E187">
         <v>99.94767772279653</v>
@@ -10975,7 +10978,7 @@
         <v>0</v>
       </c>
       <c r="P187" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10989,7 +10992,7 @@
         <v>80.81507949145069</v>
       </c>
       <c r="D188" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E188">
         <v>99.94767772279653</v>
@@ -11025,7 +11028,7 @@
         <v>0</v>
       </c>
       <c r="P188" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11039,7 +11042,7 @@
         <v>82.55697724266327</v>
       </c>
       <c r="D189" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E189">
         <v>99.94767772279653</v>
@@ -11075,7 +11078,7 @@
         <v>0</v>
       </c>
       <c r="P189" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11089,7 +11092,7 @@
         <v>80.68386776738032</v>
       </c>
       <c r="D190" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E190">
         <v>99.94767772279653</v>
@@ -11125,7 +11128,7 @@
         <v>0</v>
       </c>
       <c r="P190" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11139,7 +11142,7 @@
         <v>83.46212404051099</v>
       </c>
       <c r="D191" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E191">
         <v>101.9293746430213</v>
@@ -11175,7 +11178,7 @@
         <v>0</v>
       </c>
       <c r="P191" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11189,7 +11192,7 @@
         <v>81.65627098338047</v>
       </c>
       <c r="D192" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E192">
         <v>101.9293746430213</v>
@@ -11225,7 +11228,7 @@
         <v>0</v>
       </c>
       <c r="P192" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11239,7 +11242,7 @@
         <v>83.46017302146748</v>
       </c>
       <c r="D193" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E193">
         <v>101.9293746430213</v>
@@ -11275,7 +11278,7 @@
         <v>0</v>
       </c>
       <c r="P193" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11289,7 +11292,7 @@
         <v>81.57259587924717</v>
       </c>
       <c r="D194" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E194">
         <v>101.9293746430213</v>
@@ -11325,7 +11328,7 @@
         <v>0</v>
       </c>
       <c r="P194" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11375,7 +11378,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11389,7 +11392,7 @@
         <v>33.77481800214022</v>
       </c>
       <c r="D196" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E196">
         <v>39.96346245740297</v>
@@ -11425,7 +11428,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11439,7 +11442,7 @@
         <v>24.63764534106641</v>
       </c>
       <c r="D197" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E197">
         <v>34.16939555445761</v>
@@ -11475,7 +11478,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11489,7 +11492,7 @@
         <v>43.28817453279771</v>
       </c>
       <c r="D198" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E198">
         <v>46.14425779500065</v>
@@ -11525,7 +11528,7 @@
         <v>0</v>
       </c>
       <c r="P198" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11539,7 +11542,7 @@
         <v>24.23598497532834</v>
       </c>
       <c r="D199" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E199">
         <v>33.03819935984974</v>
@@ -11575,7 +11578,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11589,7 +11592,7 @@
         <v>24.17071464201896</v>
       </c>
       <c r="D200" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E200">
         <v>33.03819935984974</v>
@@ -11625,7 +11628,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11639,7 +11642,7 @@
         <v>23.32366123264667</v>
       </c>
       <c r="D201" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E201">
         <v>32.29172372079252</v>
@@ -11689,7 +11692,7 @@
         <v>22.94912669441385</v>
       </c>
       <c r="D202" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E202">
         <v>31.49029169144093</v>
@@ -11725,7 +11728,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11739,7 +11742,7 @@
         <v>22.44844130251504</v>
       </c>
       <c r="D203" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E203">
         <v>30.75050022869873</v>
@@ -11775,7 +11778,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11789,7 +11792,7 @@
         <v>22.12056025614258</v>
       </c>
       <c r="D204" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E204">
         <v>30.75050022869873</v>
@@ -11825,7 +11828,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11839,7 +11842,7 @@
         <v>21.00936580829927</v>
       </c>
       <c r="D205" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E205">
         <v>29.75836232883863</v>
@@ -11889,7 +11892,7 @@
         <v>22.21712321587968</v>
       </c>
       <c r="D206" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E206">
         <v>29.83950116198865</v>
@@ -11925,7 +11928,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11939,7 +11942,7 @@
         <v>22.36605537346383</v>
       </c>
       <c r="D207" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E207">
         <v>29.99532225197207</v>
@@ -11975,7 +11978,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11989,7 +11992,7 @@
         <v>21.71901729202467</v>
       </c>
       <c r="D208" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E208">
         <v>28.96097369076485</v>
@@ -12025,7 +12028,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12039,7 +12042,7 @@
         <v>21.37743590654157</v>
       </c>
       <c r="D209" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E209">
         <v>28.96097369076485</v>
@@ -12075,7 +12078,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12089,7 +12092,7 @@
         <v>21.5505095382167</v>
       </c>
       <c r="D210" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E210">
         <v>29.1420529309536</v>
@@ -12139,7 +12142,7 @@
         <v>21.4477218260166</v>
       </c>
       <c r="D211" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E211">
         <v>29.03451072105261</v>
@@ -12175,7 +12178,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12189,7 +12192,7 @@
         <v>21.93200329930192</v>
       </c>
       <c r="D212" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E212">
         <v>29.03451072105261</v>
@@ -12225,7 +12228,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12239,7 +12242,7 @@
         <v>21.82005829590757</v>
       </c>
       <c r="D213" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E213">
         <v>29.42406980298699</v>
@@ -12275,7 +12278,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12289,7 +12292,7 @@
         <v>22.28137628646834</v>
       </c>
       <c r="D214" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E214">
         <v>29.42406980298699</v>
@@ -12325,7 +12328,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12339,7 +12342,7 @@
         <v>25.08434479788652</v>
       </c>
       <c r="D215" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E215">
         <v>32.83934753082841</v>
@@ -12375,7 +12378,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12389,7 +12392,7 @@
         <v>25.82576998567276</v>
       </c>
       <c r="D216" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E216">
         <v>32.83934753082841</v>
@@ -12425,7 +12428,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12439,7 +12442,7 @@
         <v>25.62576998567276</v>
       </c>
       <c r="D217" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E217">
         <v>32.83934753082841</v>
@@ -12475,7 +12478,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12489,7 +12492,7 @@
         <v>39.54291961010028</v>
       </c>
       <c r="D218" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E218">
         <v>32.24005830276027</v>
@@ -12525,7 +12528,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12539,7 +12542,7 @@
         <v>27.32311840696546</v>
       </c>
       <c r="D219" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E219">
         <v>35.18167674737576</v>
@@ -12575,7 +12578,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12589,7 +12592,7 @@
         <v>27.936331890267</v>
       </c>
       <c r="D220" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E220">
         <v>35.18167674737576</v>
@@ -12625,7 +12628,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12639,7 +12642,7 @@
         <v>27.736331890267</v>
       </c>
       <c r="D221" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E221">
         <v>35.18167674737576</v>
@@ -12675,7 +12678,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12689,7 +12692,7 @@
         <v>41.90990492366392</v>
       </c>
       <c r="D222" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E222">
         <v>34.44924459541966</v>
@@ -12725,7 +12728,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12739,7 +12742,7 @@
         <v>29.32582523799188</v>
       </c>
       <c r="D223" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E223">
         <v>36.94571726179005</v>
@@ -12789,7 +12792,7 @@
         <v>43.69251428559836</v>
       </c>
       <c r="D224" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E224">
         <v>36.11301333322514</v>
@@ -12839,7 +12842,7 @@
         <v>44.11030807122381</v>
       </c>
       <c r="D225" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E225">
         <v>36.50295419980888</v>
@@ -12875,7 +12878,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12889,7 +12892,7 @@
         <v>45.39200591893177</v>
       </c>
       <c r="D226" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E226">
         <v>37.69920552433632</v>
@@ -12939,7 +12942,7 @@
         <v>46.2461284866414</v>
       </c>
       <c r="D227" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E227">
         <v>38.49638658753197</v>
@@ -12975,7 +12978,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12989,7 +12992,7 @@
         <v>46.90307634880546</v>
       </c>
       <c r="D228" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E228">
         <v>39.10953792555176</v>
@@ -13039,7 +13042,7 @@
         <v>33.83569560835785</v>
       </c>
       <c r="D229" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E229">
         <v>40.9206360962427</v>
@@ -13089,7 +13092,7 @@
         <v>46.73201951087134</v>
       </c>
       <c r="D230" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E230">
         <v>38.94988487681324</v>
@@ -13139,7 +13142,7 @@
         <v>33.22416759327695</v>
       </c>
       <c r="D231" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E231">
         <v>40.34408700115657</v>
@@ -13175,7 +13178,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13189,7 +13192,7 @@
         <v>46.15305807647522</v>
       </c>
       <c r="D232" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E232">
         <v>38.40952087137686</v>
@@ -13225,7 +13228,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13239,7 +13242,7 @@
         <v>33.50490381338868</v>
       </c>
       <c r="D233" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E233">
         <v>40.17087450822464</v>
@@ -13275,7 +13278,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13289,7 +13292,7 @@
         <v>45.97912084507914</v>
       </c>
       <c r="D234" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E234">
         <v>38.24717945540719</v>
@@ -13325,7 +13328,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13339,7 +13342,7 @@
         <v>34.16379673036971</v>
       </c>
       <c r="D235" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E235">
         <v>40.85258622752538</v>
@@ -13375,7 +13378,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13389,7 +13392,7 @@
         <v>46.66368491466983</v>
       </c>
       <c r="D236" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E236">
         <v>38.8861059203585</v>
@@ -13425,7 +13428,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13439,7 +13442,7 @@
         <v>35.00523304555671</v>
       </c>
       <c r="D237" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E237">
         <v>41.72316319432058</v>
@@ -13475,7 +13478,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13489,7 +13492,7 @@
         <v>47.53790446291606</v>
       </c>
       <c r="D238" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E238">
         <v>39.70204416538832</v>
@@ -13525,7 +13528,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13539,7 +13542,7 @@
         <v>35.77509163864829</v>
       </c>
       <c r="D239" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E239">
         <v>42.51968355686988</v>
@@ -13575,7 +13578,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13589,7 +13592,7 @@
         <v>48.33775754664758</v>
       </c>
       <c r="D240" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E240">
         <v>40.4485737102044</v>
@@ -13625,7 +13628,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13639,7 +13642,7 @@
         <v>36.40438752667171</v>
       </c>
       <c r="D241" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E241">
         <v>43.17077324188112</v>
@@ -13675,7 +13678,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13689,7 +13692,7 @@
         <v>48.9915714562823</v>
       </c>
       <c r="D242" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E242">
         <v>41.05880002586348</v>
@@ -13725,7 +13728,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13739,7 +13742,7 @@
         <v>32.86635202836143</v>
       </c>
       <c r="D243" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E243">
         <v>23.40810673803942</v>
@@ -13775,7 +13778,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13789,7 +13792,7 @@
         <v>14.22574367387871</v>
       </c>
       <c r="D244" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E244">
         <v>19.5340376774239</v>
@@ -13825,7 +13828,7 @@
         <v>0</v>
       </c>
       <c r="P244" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13839,7 +13842,7 @@
         <v>24.88800304387275</v>
       </c>
       <c r="D245" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E245">
         <v>11.91657154564347</v>
@@ -13875,7 +13878,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13889,7 +13892,7 @@
         <v>39.44906102636678</v>
       </c>
       <c r="D246" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E246">
         <v>28.36395585832523</v>
@@ -13925,7 +13928,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13954,7 +13957,7 @@
         <v>59.4</v>
       </c>
       <c r="P247" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13968,7 +13971,7 @@
         <v>36.85113379578714</v>
       </c>
       <c r="D248" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E248">
         <v>25.5208599983697</v>
@@ -14004,7 +14007,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14018,7 +14021,7 @@
         <v>33.94646019309421</v>
       </c>
       <c r="D249" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E249">
         <v>22.34206984707826</v>
@@ -14054,7 +14057,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14068,7 +14071,7 @@
         <v>33.30875742504994</v>
       </c>
       <c r="D250" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E250">
         <v>21.64418651979802</v>
@@ -14104,7 +14107,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14133,7 +14136,7 @@
         <v>59.5</v>
       </c>
       <c r="P251" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14183,7 +14186,7 @@
         <v>0</v>
       </c>
       <c r="P252" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14197,7 +14200,7 @@
         <v>9.926891175013289</v>
       </c>
       <c r="D253" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E253">
         <v>9.938904864210649</v>
@@ -14233,7 +14236,7 @@
         <v>0</v>
       </c>
       <c r="P253" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14247,7 +14250,7 @@
         <v>8.61566853605617</v>
       </c>
       <c r="D254" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E254">
         <v>9.007561895624264</v>
@@ -14283,7 +14286,7 @@
         <v>0</v>
       </c>
       <c r="P254" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14333,7 +14336,7 @@
         <v>0</v>
       </c>
       <c r="P255" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14347,7 +14350,7 @@
         <v>15.27625616990661</v>
       </c>
       <c r="D256" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E256">
         <v>13.96823074035395</v>
@@ -14383,7 +14386,7 @@
         <v>0</v>
       </c>
       <c r="P256" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14397,7 +14400,7 @@
         <v>14.49984262437423</v>
       </c>
       <c r="D257" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E257">
         <v>14.19011246930496</v>
@@ -14433,7 +14436,7 @@
         <v>0</v>
       </c>
       <c r="P257" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14447,7 +14450,7 @@
         <v>13.68984307357539</v>
       </c>
       <c r="D258" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E258">
         <v>15.44321014679792</v>
@@ -14483,7 +14486,7 @@
         <v>0</v>
       </c>
       <c r="P258" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14497,7 +14500,7 @@
         <v>14.26953725404694</v>
       </c>
       <c r="D259" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E259">
         <v>17.46734434330768</v>
@@ -14533,7 +14536,7 @@
         <v>0</v>
       </c>
       <c r="P259" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14547,7 +14550,7 @@
         <v>59.06263065139578</v>
       </c>
       <c r="D260" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E260">
         <v>59.07357361272927</v>
@@ -14583,7 +14586,7 @@
         <v>0</v>
       </c>
       <c r="P260" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14597,7 +14600,7 @@
         <v>60.66257075424956</v>
       </c>
       <c r="D261" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E261">
         <v>61.38454095582109</v>
@@ -14633,7 +14636,7 @@
         <v>0</v>
       </c>
       <c r="P261" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14647,7 +14650,7 @@
         <v>61.58779745865752</v>
       </c>
       <c r="D262" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E262">
         <v>62.08864679971672</v>
@@ -14683,7 +14686,7 @@
         <v>0</v>
       </c>
       <c r="P262" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14733,7 +14736,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14783,7 +14786,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14833,7 +14836,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14883,7 +14886,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14933,7 +14936,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14983,7 +14986,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15033,7 +15036,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15083,7 +15086,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15133,7 +15136,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15147,7 +15150,7 @@
         <v>-12.91711279591523</v>
       </c>
       <c r="D272" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E272">
         <v>-24.080705554696</v>
@@ -15197,7 +15200,7 @@
         <v>-13.89288092370901</v>
       </c>
       <c r="D273" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E273">
         <v>-24.64699491908532</v>
@@ -15233,7 +15236,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15247,7 +15250,7 @@
         <v>-13.4171424523624</v>
       </c>
       <c r="D274" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E274">
         <v>-24.64699491908532</v>
@@ -15283,7 +15286,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15297,7 +15300,7 @@
         <v>-7.909028461817627</v>
       </c>
       <c r="D275" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E275">
         <v>-18.4089921717041</v>
@@ -15333,7 +15336,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15347,7 +15350,7 @@
         <v>-3.803879058776658</v>
       </c>
       <c r="D276" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E276">
         <v>-13.75986303266694</v>
@@ -15397,7 +15400,7 @@
         <v>-7.200798160312672</v>
       </c>
       <c r="D277" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E277">
         <v>-16.37029482433257</v>
@@ -15447,7 +15450,7 @@
         <v>1.814674940949821</v>
       </c>
       <c r="D278" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E278">
         <v>-6.106103736501311</v>
@@ -15533,7 +15536,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15633,7 +15636,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15647,7 +15650,7 @@
         <v>68.89152801060949</v>
       </c>
       <c r="D282" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E282">
         <v>67.76768139345658</v>
@@ -15683,7 +15686,7 @@
         <v>0</v>
       </c>
       <c r="P282" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15697,7 +15700,7 @@
         <v>68.93096321131679</v>
       </c>
       <c r="D283" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E283">
         <v>67.76768139345658</v>
@@ -15733,7 +15736,7 @@
         <v>0</v>
       </c>
       <c r="P283" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15747,7 +15750,7 @@
         <v>68.53130803182968</v>
       </c>
       <c r="D284" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E284">
         <v>67.76768139345658</v>
@@ -15783,7 +15786,7 @@
         <v>0</v>
       </c>
       <c r="P284" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15797,7 +15800,7 @@
         <v>69.00549946949548</v>
       </c>
       <c r="D285" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E285">
         <v>67.76768139345658</v>
@@ -15833,7 +15836,7 @@
         <v>0</v>
       </c>
       <c r="P285" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15847,7 +15850,7 @@
         <v>77.0344578684535</v>
       </c>
       <c r="D286" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E286">
         <v>79.16818364992574</v>
@@ -15897,7 +15900,7 @@
         <v>76.35596494832328</v>
       </c>
       <c r="D287" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E287">
         <v>79.16818364992574</v>
@@ -15947,7 +15950,7 @@
         <v>77.32922500711149</v>
       </c>
       <c r="D288" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E288">
         <v>79.16818364992574</v>
@@ -15997,7 +16000,7 @@
         <v>79.78847196430716</v>
       </c>
       <c r="D289" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E289">
         <v>84.66094269739213</v>
@@ -16033,7 +16036,7 @@
         <v>0</v>
       </c>
       <c r="P289" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16047,7 +16050,7 @@
         <v>79.029452316228</v>
       </c>
       <c r="D290" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E290">
         <v>84.66094269739213</v>
@@ -16083,7 +16086,7 @@
         <v>0</v>
       </c>
       <c r="P290" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16097,7 +16100,7 @@
         <v>80.07787065443522</v>
       </c>
       <c r="D291" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E291">
         <v>84.66094269739213</v>
@@ -16133,7 +16136,7 @@
         <v>0</v>
       </c>
       <c r="P291" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16183,7 +16186,7 @@
         <v>0</v>
       </c>
       <c r="P292" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16233,7 +16236,7 @@
         <v>0</v>
       </c>
       <c r="P293" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16283,7 +16286,7 @@
         <v>0</v>
       </c>
       <c r="P294" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16297,7 +16300,7 @@
         <v>26.32548638029413</v>
       </c>
       <c r="D295" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E295">
         <v>26.99422663021349</v>
@@ -16333,7 +16336,7 @@
         <v>0</v>
       </c>
       <c r="P295" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16347,7 +16350,7 @@
         <v>22.18948293316849</v>
       </c>
       <c r="D296" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E296">
         <v>24.84672272180288</v>
@@ -16383,7 +16386,7 @@
         <v>0</v>
       </c>
       <c r="P296" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16397,7 +16400,7 @@
         <v>21.86052377863092</v>
       </c>
       <c r="D297" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E297">
         <v>24.84672272180288</v>
@@ -16433,7 +16436,7 @@
         <v>0</v>
       </c>
       <c r="P297" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16447,7 +16450,7 @@
         <v>40.77814878274022</v>
       </c>
       <c r="D298" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E298">
         <v>48.87821615334129</v>
@@ -16483,7 +16486,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16497,7 +16500,7 @@
         <v>40.67981251944272</v>
       </c>
       <c r="D299" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E299">
         <v>48.87821615334129</v>
@@ -16533,7 +16536,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16547,7 +16550,7 @@
         <v>56.75038402863819</v>
       </c>
       <c r="D300" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E300">
         <v>62.17870887338118</v>
@@ -16583,7 +16586,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16597,7 +16600,7 @@
         <v>59.81014784804309</v>
       </c>
       <c r="D301" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E301">
         <v>65.19117101289457</v>
@@ -16633,7 +16636,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16647,7 +16650,7 @@
         <v>60.36835189313004</v>
       </c>
       <c r="D302" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E302">
         <v>65.519432176365</v>
@@ -16683,7 +16686,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16697,7 +16700,7 @@
         <v>61.49835591209959</v>
       </c>
       <c r="D303" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E303">
         <v>65.45054113973049</v>
@@ -16747,7 +16750,7 @@
         <v>61.74303834428476</v>
       </c>
       <c r="D304" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E304">
         <v>65.59070564276428</v>
@@ -16783,7 +16786,7 @@
         <v>0</v>
       </c>
       <c r="P304" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16797,7 +16800,7 @@
         <v>62.08800405152936</v>
       </c>
       <c r="D305" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E305">
         <v>65.70367105582346</v>
@@ -16833,7 +16836,7 @@
         <v>0</v>
       </c>
       <c r="P305" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16847,7 +16850,7 @@
         <v>62.52195117925444</v>
       </c>
       <c r="D306" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E306">
         <v>66.54562713332096</v>
@@ -16883,7 +16886,7 @@
         <v>0</v>
       </c>
       <c r="P306" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16897,7 +16900,7 @@
         <v>63.12382871565654</v>
       </c>
       <c r="D307" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E307">
         <v>66.7862115872222</v>
@@ -16933,7 +16936,7 @@
         <v>0</v>
       </c>
       <c r="P307" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16947,7 +16950,7 @@
         <v>63.43713576842169</v>
       </c>
       <c r="D308" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E308">
         <v>68.73084934526386</v>
@@ -16983,7 +16986,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16997,7 +17000,7 @@
         <v>63.67236578705479</v>
       </c>
       <c r="D309" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E309">
         <v>68.98960236576026</v>
@@ -17033,7 +17036,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17047,7 +17050,7 @@
         <v>63.92214730715632</v>
       </c>
       <c r="D310" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E310">
         <v>69.26436203787196</v>
@@ -17083,7 +17086,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17097,7 +17100,7 @@
         <v>64.84267428552164</v>
       </c>
       <c r="D311" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E311">
         <v>70.2769417140738</v>
@@ -17133,7 +17136,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17147,7 +17150,7 @@
         <v>67.02639425410899</v>
       </c>
       <c r="D312" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E312">
         <v>72.67903367951989</v>
@@ -17183,7 +17186,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17197,7 +17200,7 @@
         <v>48.8201383647419</v>
       </c>
       <c r="D313" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E313">
         <v>53.28068312873989</v>
@@ -17233,7 +17236,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17247,7 +17250,7 @@
         <v>43.78661428769819</v>
       </c>
       <c r="D314" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E314">
         <v>49.20590413019019</v>
@@ -17283,7 +17286,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17297,7 +17300,7 @@
         <v>43.50856722084519</v>
       </c>
       <c r="D315" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E315">
         <v>49.20590413019019</v>
@@ -17333,7 +17336,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17347,7 +17350,7 @@
         <v>38.43277181447034</v>
       </c>
       <c r="D316" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E316">
         <v>43.81134802598723</v>
@@ -17383,7 +17386,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17397,7 +17400,7 @@
         <v>39.10060265112747</v>
       </c>
       <c r="D317" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E317">
         <v>43.81134802598723</v>
@@ -17433,7 +17436,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17447,7 +17450,7 @@
         <v>28.12299460113455</v>
       </c>
       <c r="D318" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E318">
         <v>35.22229514558674</v>
@@ -17483,7 +17486,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17497,7 +17500,7 @@
         <v>27.81471186440677</v>
       </c>
       <c r="D319" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E319">
         <v>34.92338983050847</v>
@@ -17533,7 +17536,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17547,7 +17550,7 @@
         <v>31.34037664954478</v>
       </c>
       <c r="D320" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E320">
         <v>38.34181005944457</v>
@@ -17583,7 +17586,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17597,7 +17600,7 @@
         <v>31.06966226989418</v>
       </c>
       <c r="D321" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E321">
         <v>38.07933033773011</v>
@@ -17633,7 +17636,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17647,7 +17650,7 @@
         <v>30.73117805425061</v>
       </c>
       <c r="D322" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E322">
         <v>37.75114221990079</v>
@@ -17683,7 +17686,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17697,7 +17700,7 @@
         <v>30.23209518986696</v>
       </c>
       <c r="D323" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E323">
         <v>37.26724058333109</v>
@@ -17733,7 +17736,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17747,7 +17750,7 @@
         <v>29.66328200930995</v>
       </c>
       <c r="D324" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E324">
         <v>36.71572970484425</v>
@@ -17783,7 +17786,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17797,7 +17800,7 @@
         <v>29.90527095369034</v>
       </c>
       <c r="D325" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E325">
         <v>36.95035776878722</v>
@@ -17833,7 +17836,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17847,7 +17850,7 @@
         <v>29.61163508265873</v>
       </c>
       <c r="D326" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E326">
         <v>36.66565378736873</v>
@@ -17883,7 +17886,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17897,7 +17900,7 @@
         <v>29.60796663375891</v>
       </c>
       <c r="D327" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E327">
         <v>38.73216492329536</v>
@@ -17933,7 +17936,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17947,7 +17950,7 @@
         <v>29.99267097270676</v>
       </c>
       <c r="D328" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E328">
         <v>39.11028686861102</v>
@@ -17983,7 +17986,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17997,7 +18000,7 @@
         <v>30.47592970891776</v>
       </c>
       <c r="D329" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E329">
         <v>39.58527691922146</v>
@@ -18033,7 +18036,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18062,7 +18065,7 @@
         <v>64.5</v>
       </c>
       <c r="P330" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18076,7 +18079,7 @@
         <v>37.15547839433958</v>
       </c>
       <c r="D331" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E331">
         <v>43.97524497646168</v>
@@ -18112,7 +18115,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18126,7 +18129,7 @@
         <v>37.01610527202449</v>
       </c>
       <c r="D332" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E332">
         <v>43.97524497646168</v>
@@ -18162,7 +18165,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18176,7 +18179,7 @@
         <v>25.78116025897209</v>
       </c>
       <c r="D333" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E333">
         <v>34.97083622412276</v>
@@ -18212,7 +18215,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18226,7 +18229,7 @@
         <v>21.78292834045364</v>
       </c>
       <c r="D334" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E334">
         <v>32.11135258573889</v>
@@ -18262,7 +18265,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18276,7 +18279,7 @@
         <v>16.20611168178342</v>
       </c>
       <c r="D335" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E335">
         <v>27.00103770079773</v>
@@ -18312,7 +18315,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18326,7 +18329,7 @@
         <v>16.50484318653699</v>
       </c>
       <c r="D336" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E336">
         <v>27.00103770079773</v>
@@ -18362,7 +18365,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18376,7 +18379,7 @@
         <v>7.513223702566968</v>
       </c>
       <c r="D337" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E337">
         <v>19.03531145368304</v>
@@ -18412,7 +18415,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18426,7 +18429,7 @@
         <v>7.993745640345985</v>
       </c>
       <c r="D338" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E338">
         <v>19.03531145368304</v>
@@ -18462,7 +18465,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18476,7 +18479,7 @@
         <v>-3.101932223543415</v>
       </c>
       <c r="D339" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E339">
         <v>9.308115338882274</v>
@@ -18512,7 +18515,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18526,7 +18529,7 @@
         <v>-2.399420332936991</v>
       </c>
       <c r="D340" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E340">
         <v>9.308115338882274</v>
@@ -18562,7 +18565,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18576,7 +18579,7 @@
         <v>-2.646016646848999</v>
       </c>
       <c r="D341" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E341">
         <v>9.308115338882274</v>
@@ -18612,7 +18615,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18626,7 +18629,7 @@
         <v>-9.121415898188509</v>
       </c>
       <c r="D342" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E342">
         <v>3.792162618009769</v>
@@ -18662,7 +18665,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18676,7 +18679,7 @@
         <v>-8.59683700961601</v>
       </c>
       <c r="D343" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E343">
         <v>3.792162618009769</v>
@@ -18712,7 +18715,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18726,7 +18729,7 @@
         <v>-12.89770073310627</v>
       </c>
       <c r="D344" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E344">
         <v>0.3317647274577595</v>
@@ -18762,7 +18765,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18776,7 +18779,7 @@
         <v>-14.09288737405897</v>
       </c>
       <c r="D345" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E345">
         <v>-0.7634443237574615</v>
@@ -18812,7 +18815,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18826,7 +18829,7 @@
         <v>59.56360813550708</v>
       </c>
       <c r="D346" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E346">
         <v>75.18159673719033</v>
@@ -18862,7 +18865,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18876,7 +18879,7 @@
         <v>60.31956868780029</v>
       </c>
       <c r="D347" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E347">
         <v>76.03992694760657</v>
@@ -18912,7 +18915,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18926,7 +18929,7 @@
         <v>62.79431714399279</v>
       </c>
       <c r="D348" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E348">
         <v>77.62631903124894</v>
@@ -18962,7 +18965,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18976,7 +18979,7 @@
         <v>64.08298118239738</v>
       </c>
       <c r="D349" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E349">
         <v>79.11665728256037</v>
@@ -19012,7 +19015,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19026,7 +19029,7 @@
         <v>64.68906100731142</v>
       </c>
       <c r="D350" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E350">
         <v>79.81758779625406</v>
@@ -19062,7 +19065,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19076,7 +19079,7 @@
         <v>66.03163316666149</v>
       </c>
       <c r="D351" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E351">
         <v>81.37027071794273</v>
@@ -19112,7 +19115,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19126,7 +19129,7 @@
         <v>65.93064756206419</v>
       </c>
       <c r="D352" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E352">
         <v>81.25348100015911</v>
@@ -19162,7 +19165,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19176,7 +19179,7 @@
         <v>64.84418812133572</v>
       </c>
       <c r="D353" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E353">
         <v>80.16577874075962</v>
@@ -19212,7 +19215,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19226,7 +19229,7 @@
         <v>63.26616721431549</v>
       </c>
       <c r="D354" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E354">
         <v>79.97190339753475</v>
@@ -19262,7 +19265,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19276,7 +19279,7 @@
         <v>61.66554474645639</v>
       </c>
       <c r="D355" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E355">
         <v>78.05285470927927</v>
@@ -19312,7 +19315,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19326,7 +19329,7 @@
         <v>60.62679073828761</v>
       </c>
       <c r="D356" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E356">
         <v>76.80745202574536</v>
@@ -19362,7 +19365,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19376,7 +19379,7 @@
         <v>59.7052486970962</v>
       </c>
       <c r="D357" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E357">
         <v>75.70257933975458</v>
@@ -19412,7 +19415,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19426,7 +19429,7 @@
         <v>50.59926427854958</v>
       </c>
       <c r="D358" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E358">
         <v>64.78505955942813</v>
@@ -19462,7 +19465,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19476,7 +19479,7 @@
         <v>54.80887863487924</v>
       </c>
       <c r="D359" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E359">
         <v>72.15232554251514</v>
@@ -19512,7 +19515,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19523,34 +19526,34 @@
         <v>130</v>
       </c>
       <c r="C360">
-        <v>18.34604038720835</v>
+        <v>22.63799956449154</v>
       </c>
       <c r="D360" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E360">
-        <v>30.18004248156539</v>
+        <v>34.76775640560354</v>
       </c>
       <c r="F360">
         <v>1</v>
       </c>
       <c r="G360">
-        <v>0.1438539596127917</v>
+        <v>0.1349620004355085</v>
       </c>
       <c r="H360">
-        <v>0.1472199575184346</v>
+        <v>0.1426322435943965</v>
       </c>
       <c r="I360">
-        <v>11.83400209435703</v>
+        <v>12.12975684111201</v>
       </c>
       <c r="J360">
-        <v>0.3024287210255019</v>
+        <v>0.2787196051389998</v>
       </c>
       <c r="K360">
-        <v>207.5</v>
+        <v>201.5</v>
       </c>
       <c r="L360">
-        <v>81.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="M360">
         <v>193.5</v>
@@ -19562,7 +19565,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19570,37 +19573,37 @@
         <v>0</v>
       </c>
       <c r="B361" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C361">
-        <v>16.86218987799047</v>
+        <v>21.94224021195173</v>
       </c>
       <c r="D361" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E361">
-        <v>28.54797932714153</v>
+        <v>34.09962025316457</v>
       </c>
       <c r="F361">
         <v>1</v>
       </c>
       <c r="G361">
-        <v>0.1449378101220095</v>
+        <v>0.1356577597880483</v>
       </c>
       <c r="H361">
-        <v>0.1488520206728585</v>
+        <v>0.1433003797468354</v>
       </c>
       <c r="I361">
-        <v>11.68578944915105</v>
+        <v>12.15738004121285</v>
       </c>
       <c r="J361">
-        <v>0.3108631559320851</v>
+        <v>0.2821725051516043</v>
       </c>
       <c r="K361">
-        <v>206</v>
+        <v>201.5</v>
       </c>
       <c r="L361">
-        <v>80.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="M361">
         <v>193.5</v>
@@ -19612,7 +19615,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19620,49 +19623,49 @@
         <v>0</v>
       </c>
       <c r="B362" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C362">
-        <v>9.990756344042168</v>
+        <v>20.45188899670399</v>
       </c>
       <c r="D362" t="s">
         <v>245</v>
       </c>
       <c r="E362">
-        <v>21.4889221484264</v>
+        <v>32.14380973909506</v>
       </c>
       <c r="F362">
         <v>1</v>
       </c>
       <c r="G362">
-        <v>0.1552092436559578</v>
+        <v>0.141748111003296</v>
       </c>
       <c r="H362">
-        <v>0.1653110778515736</v>
+        <v>0.1452561902609049</v>
       </c>
       <c r="I362">
-        <v>11.49816580438423</v>
+        <v>11.69192074239107</v>
       </c>
       <c r="J362">
-        <v>0.3490829021921049</v>
+        <v>0.2922800530279325</v>
       </c>
       <c r="K362">
-        <v>208</v>
+        <v>207.5</v>
       </c>
       <c r="L362">
-        <v>82.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="M362">
-        <v>206</v>
+        <v>193.5</v>
       </c>
       <c r="N362">
-        <v>93.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="O362">
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19670,81 +19673,81 @@
         <v>0</v>
       </c>
       <c r="B363" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C363">
-        <v>8.066617110777202</v>
+        <v>18.55332655028487</v>
       </c>
       <c r="D363" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E363">
-        <v>19.78402126238126</v>
+        <v>30.18004248156539</v>
       </c>
       <c r="F363">
         <v>1</v>
       </c>
       <c r="G363">
-        <v>0.1631333828892228</v>
+        <v>0.1422466734497151</v>
       </c>
       <c r="H363">
-        <v>0.1662159787376188</v>
+        <v>0.1472199575184346</v>
       </c>
       <c r="I363">
-        <v>11.71740415160406</v>
+        <v>11.62671593128051</v>
       </c>
       <c r="J363">
-        <v>0.3597836793003378</v>
+        <v>0.3024287210255019</v>
       </c>
       <c r="K363">
-        <v>215.5</v>
+        <v>204.5</v>
       </c>
       <c r="L363">
-        <v>85.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="M363">
-        <v>203.5</v>
+        <v>193.5</v>
       </c>
       <c r="N363">
-        <v>93</v>
+        <v>88.7</v>
       </c>
       <c r="O363">
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="364" spans="1:16">
       <c r="A364" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B364" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C364">
-        <v>7.76499470552973</v>
+        <v>14.44543186753303</v>
       </c>
       <c r="D364" t="s">
         <v>246</v>
       </c>
       <c r="E364">
-        <v>19.78402126238126</v>
+        <v>25.90076425342215</v>
       </c>
       <c r="F364">
         <v>1</v>
       </c>
       <c r="G364">
-        <v>0.1574350052944703</v>
+        <v>0.150754568132467</v>
       </c>
       <c r="H364">
-        <v>0.1662159787376188</v>
+        <v>0.1608992357465779</v>
       </c>
       <c r="I364">
-        <v>12.01902655685153</v>
+        <v>11.45533238588912</v>
       </c>
       <c r="J364">
-        <v>0.3597836793003378</v>
+        <v>0.3276661929445527</v>
       </c>
       <c r="K364">
         <v>208</v>
@@ -19753,16 +19756,16 @@
         <v>82.59999999999999</v>
       </c>
       <c r="M364">
-        <v>203.5</v>
+        <v>206</v>
       </c>
       <c r="N364">
-        <v>93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="O364">
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>460</v>
+        <v>131</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19770,143 +19773,143 @@
         <v>0</v>
       </c>
       <c r="B365" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C365">
-        <v>-3.562425933343519</v>
+        <v>12.82667623833451</v>
       </c>
       <c r="D365" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E365">
-        <v>8.196361928702586</v>
+        <v>24.29757358219669</v>
       </c>
       <c r="F365">
         <v>1</v>
       </c>
       <c r="G365">
-        <v>0.1663624259333435</v>
+        <v>0.1523733237616655</v>
       </c>
       <c r="H365">
-        <v>0.1798036380712974</v>
+        <v>0.1625024264178033</v>
       </c>
       <c r="I365">
-        <v>11.75878786204611</v>
+        <v>11.47089734386218</v>
       </c>
       <c r="J365">
-        <v>0.4206060689769481</v>
+        <v>0.335448671931084</v>
       </c>
       <c r="K365">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="L365">
-        <v>81.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="M365">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N365">
-        <v>94</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="O365">
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>133</v>
+        <v>460</v>
       </c>
     </row>
     <row r="366" spans="1:16">
       <c r="A366" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B366" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C366">
-        <v>-3.424244140274368</v>
+        <v>10.37263457760139</v>
       </c>
       <c r="D366" t="s">
         <v>247</v>
       </c>
       <c r="E366">
-        <v>8.196361928702586</v>
+        <v>21.96162940390666</v>
       </c>
       <c r="F366">
         <v>1</v>
       </c>
       <c r="G366">
-        <v>0.1690242441402744</v>
+        <v>0.1608273654223986</v>
       </c>
       <c r="H366">
-        <v>0.1798036380712974</v>
+        <v>0.1640383705960933</v>
       </c>
       <c r="I366">
-        <v>11.62060606897695</v>
+        <v>11.58899482630527</v>
       </c>
       <c r="J366">
-        <v>0.4206060689769481</v>
+        <v>0.3490829021921049</v>
       </c>
       <c r="K366">
-        <v>205</v>
+        <v>215.5</v>
       </c>
       <c r="L366">
-        <v>82.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M366">
-        <v>204</v>
+        <v>203.5</v>
       </c>
       <c r="N366">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O366">
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>133</v>
+        <v>461</v>
       </c>
     </row>
     <row r="367" spans="1:16">
       <c r="A367" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B367" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C367">
-        <v>-2.10269534440512</v>
+        <v>9.990756344042168</v>
       </c>
       <c r="D367" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E367">
-        <v>10.74605227334604</v>
+        <v>21.96162940390666</v>
       </c>
       <c r="F367">
         <v>1</v>
       </c>
       <c r="G367">
-        <v>0.1703026953444051</v>
+        <v>0.1552092436559578</v>
       </c>
       <c r="H367">
-        <v>0.185253947726654</v>
+        <v>0.1640383705960933</v>
       </c>
       <c r="I367">
-        <v>12.84874761775116</v>
+        <v>11.97087305986449</v>
       </c>
       <c r="J367">
-        <v>0.4205009528995372</v>
+        <v>0.3490829021921049</v>
       </c>
       <c r="K367">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L367">
-        <v>84.09999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="M367">
-        <v>207.5</v>
+        <v>203.5</v>
       </c>
       <c r="N367">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="O367">
         <v>1</v>
@@ -19917,96 +19920,96 @@
     </row>
     <row r="368" spans="1:16">
       <c r="A368" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B368" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C368">
-        <v>-2.85417914511298</v>
+        <v>8.066617110777202</v>
       </c>
       <c r="D368" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E368">
-        <v>-2.443928668663204</v>
+        <v>19.78402126238126</v>
       </c>
       <c r="F368">
         <v>1</v>
       </c>
       <c r="G368">
-        <v>0.155254179145113</v>
+        <v>0.1631333828892228</v>
       </c>
       <c r="H368">
-        <v>0.1552439286686632</v>
+        <v>0.1662159787376188</v>
       </c>
       <c r="I368">
-        <v>0.4102504764497752</v>
+        <v>11.71740415160406</v>
       </c>
       <c r="J368">
-        <v>0.4205009528995372</v>
+        <v>0.3597836793003378</v>
       </c>
       <c r="K368">
-        <v>188</v>
+        <v>215.5</v>
       </c>
       <c r="L368">
-        <v>76.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M368">
-        <v>187.5</v>
+        <v>203.5</v>
       </c>
       <c r="N368">
-        <v>76.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="O368">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="369" spans="1:16">
       <c r="A369" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B369" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C369">
-        <v>-2.91355538156337</v>
+        <v>8.364994705529739</v>
       </c>
       <c r="D369" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E369">
-        <v>9.925303699149282</v>
+        <v>19.78402126238126</v>
       </c>
       <c r="F369">
         <v>1</v>
       </c>
       <c r="G369">
-        <v>0.1711135553815633</v>
+        <v>0.1580350052944703</v>
       </c>
       <c r="H369">
-        <v>0.1860746963008507</v>
+        <v>0.1662159787376188</v>
       </c>
       <c r="I369">
-        <v>12.83885908071265</v>
+        <v>11.41902655685152</v>
       </c>
       <c r="J369">
-        <v>0.4244563677149432</v>
+        <v>0.3597836793003378</v>
       </c>
       <c r="K369">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L369">
-        <v>84.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="M369">
-        <v>207.5</v>
+        <v>203.5</v>
       </c>
       <c r="N369">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="O369">
         <v>1</v>
@@ -20017,52 +20020,52 @@
     </row>
     <row r="370" spans="1:16">
       <c r="A370" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B370" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C370">
-        <v>-2.397797130409316</v>
+        <v>-3.424244140274368</v>
       </c>
       <c r="D370" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E370">
-        <v>-3.185568946551854</v>
+        <v>10.72424068728326</v>
       </c>
       <c r="F370">
         <v>1</v>
       </c>
       <c r="G370">
-        <v>0.1571977971304093</v>
+        <v>0.1690242441402744</v>
       </c>
       <c r="H370">
-        <v>0.1559855689465519</v>
+        <v>0.1852757593127167</v>
       </c>
       <c r="I370">
-        <v>-0.7877718161425378</v>
+        <v>14.14848482755762</v>
       </c>
       <c r="J370">
-        <v>0.4244563677149432</v>
+        <v>0.4206060689769481</v>
       </c>
       <c r="K370">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="L370">
-        <v>77.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="M370">
-        <v>187.5</v>
+        <v>207.5</v>
       </c>
       <c r="N370">
-        <v>76.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="O370">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>462</v>
+        <v>134</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20070,46 +20073,46 @@
         <v>0</v>
       </c>
       <c r="B371" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C371">
-        <v>-2.4055655425325</v>
+        <v>-2.10269534440512</v>
       </c>
       <c r="D371" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E371">
-        <v>-5.748378514417155</v>
+        <v>10.74605227334604</v>
       </c>
       <c r="F371">
         <v>1</v>
       </c>
       <c r="G371">
-        <v>0.1632055655425325</v>
+        <v>0.1703026953444051</v>
       </c>
       <c r="H371">
-        <v>0.1585483785144172</v>
+        <v>0.185253947726654</v>
       </c>
       <c r="I371">
-        <v>-3.342812971884655</v>
+        <v>12.84874761775116</v>
       </c>
       <c r="J371">
-        <v>0.4381246854102249</v>
+        <v>0.4205009528995372</v>
       </c>
       <c r="K371">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="L371">
-        <v>80.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M371">
-        <v>187.5</v>
+        <v>207.5</v>
       </c>
       <c r="N371">
-        <v>76.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="O371">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P371" t="s">
         <v>463</v>
@@ -20117,52 +20120,31 @@
     </row>
     <row r="372" spans="1:16">
       <c r="A372" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B372" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C372">
-        <v>-38.65235447171061</v>
-      </c>
-      <c r="D372" t="s">
-        <v>249</v>
-      </c>
-      <c r="E372">
-        <v>-41.70749451558592</v>
+        <v>-1.654179145112977</v>
       </c>
       <c r="F372">
         <v>1</v>
       </c>
       <c r="G372">
-        <v>0.1994523544717106</v>
-      </c>
-      <c r="H372">
-        <v>0.1945074945155859</v>
-      </c>
-      <c r="I372">
-        <v>-3.055140043875312</v>
+        <v>0.156454179145113</v>
       </c>
       <c r="J372">
-        <v>0.6299066374164582</v>
+        <v>0.4205009528995372</v>
       </c>
       <c r="K372">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L372">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="M372">
-        <v>187.5</v>
-      </c>
-      <c r="N372">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="O372">
-        <v>0</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="P372" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20173,96 +20155,96 @@
         <v>137</v>
       </c>
       <c r="C373">
-        <v>14.47890124851195</v>
+        <v>-2.91355538156337</v>
       </c>
       <c r="D373" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E373">
-        <v>14.84305310689357</v>
+        <v>9.925303699149282</v>
       </c>
       <c r="F373">
         <v>1</v>
       </c>
       <c r="G373">
-        <v>0.1379210987514881</v>
+        <v>0.1711135553815633</v>
       </c>
       <c r="H373">
-        <v>0.1379569468931064</v>
+        <v>0.1860746963008507</v>
       </c>
       <c r="I373">
-        <v>0.364151858381625</v>
+        <v>12.83885908071265</v>
       </c>
       <c r="J373">
-        <v>0.3283037167632343</v>
+        <v>0.4244563677149432</v>
       </c>
       <c r="K373">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="L373">
-        <v>76.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M373">
-        <v>187.5</v>
+        <v>207.5</v>
       </c>
       <c r="N373">
-        <v>76.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="O373">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="374" spans="1:16">
       <c r="A374" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B374" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C374">
-        <v>12.29886568031696</v>
+        <v>-1.797797130409322</v>
       </c>
       <c r="D374" t="s">
-        <v>249</v>
+        <v>138</v>
       </c>
       <c r="E374">
-        <v>12.66881550563527</v>
+        <v>-2.397797130409316</v>
       </c>
       <c r="F374">
         <v>1</v>
       </c>
       <c r="G374">
-        <v>0.140101134319683</v>
+        <v>0.1577977971304093</v>
       </c>
       <c r="H374">
-        <v>0.1401311844943647</v>
+        <v>0.1571977971304093</v>
       </c>
       <c r="I374">
-        <v>0.3699498253183151</v>
+        <v>-0.5999999999999943</v>
       </c>
       <c r="J374">
-        <v>0.3398996506366119</v>
+        <v>0.4244563677149432</v>
       </c>
       <c r="K374">
         <v>188</v>
       </c>
       <c r="L374">
-        <v>76.2</v>
+        <v>78</v>
       </c>
       <c r="M374">
-        <v>187.5</v>
+        <v>188</v>
       </c>
       <c r="N374">
-        <v>76.40000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O374">
         <v>0</v>
       </c>
       <c r="P374" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20273,46 +20255,196 @@
         <v>140</v>
       </c>
       <c r="C375">
-        <v>0.7748127541194236</v>
+        <v>-1.02931617171204</v>
       </c>
       <c r="D375" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E375">
-        <v>-9.173050211077154</v>
+        <v>-4.96744085712227</v>
       </c>
       <c r="F375">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G375">
-        <v>0.1780251872458806</v>
+        <v>0.162829316171712</v>
       </c>
       <c r="H375">
-        <v>0.1699730502110772</v>
+        <v>0.1597674408571223</v>
       </c>
       <c r="I375">
-        <v>9.947862965196578</v>
+        <v>-3.93812468541023</v>
       </c>
       <c r="J375">
-        <v>0.4739314825982919</v>
+        <v>0.4381246854102249</v>
       </c>
       <c r="K375">
         <v>187</v>
       </c>
       <c r="L375">
-        <v>89.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="M375">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N375">
-        <v>80.40000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O375">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P375" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="376" spans="1:16">
+      <c r="A376" s="1">
+        <v>0</v>
+      </c>
+      <c r="B376" t="s">
+        <v>140</v>
+      </c>
+      <c r="C376">
+        <v>-36.89254119687769</v>
+      </c>
+      <c r="D376" t="s">
+        <v>138</v>
+      </c>
+      <c r="E376">
+        <v>-41.02244783429414</v>
+      </c>
+      <c r="F376">
+        <v>1</v>
+      </c>
+      <c r="G376">
+        <v>0.1986925411968777</v>
+      </c>
+      <c r="H376">
+        <v>0.1958224478342942</v>
+      </c>
+      <c r="I376">
+        <v>-4.129906637416454</v>
+      </c>
+      <c r="J376">
+        <v>0.6299066374164582</v>
+      </c>
+      <c r="K376">
+        <v>187</v>
+      </c>
+      <c r="L376">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="M376">
+        <v>188</v>
+      </c>
+      <c r="N376">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="O376">
+        <v>0</v>
+      </c>
+      <c r="P376" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="377" spans="1:16">
+      <c r="A377" s="1">
+        <v>0</v>
+      </c>
+      <c r="B377" t="s">
+        <v>141</v>
+      </c>
+      <c r="C377">
+        <v>16.56381239880164</v>
+      </c>
+      <c r="D377" t="s">
+        <v>138</v>
+      </c>
+      <c r="E377">
+        <v>15.67890124851195</v>
+      </c>
+      <c r="F377">
+        <v>1</v>
+      </c>
+      <c r="G377">
+        <v>0.1380361876011983</v>
+      </c>
+      <c r="H377">
+        <v>0.1391210987514881</v>
+      </c>
+      <c r="I377">
+        <v>-0.884911150289696</v>
+      </c>
+      <c r="J377">
+        <v>0.3283037167632343</v>
+      </c>
+      <c r="K377">
+        <v>185</v>
+      </c>
+      <c r="L377">
+        <v>77.3</v>
+      </c>
+      <c r="M377">
+        <v>188</v>
+      </c>
+      <c r="N377">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="O377">
+        <v>0</v>
+      </c>
+      <c r="P377" t="s">
         <v>467</v>
+      </c>
+    </row>
+    <row r="378" spans="1:16">
+      <c r="A378" s="1">
+        <v>0</v>
+      </c>
+      <c r="B378" t="s">
+        <v>139</v>
+      </c>
+      <c r="C378">
+        <v>14.09886568031695</v>
+      </c>
+      <c r="D378" t="s">
+        <v>138</v>
+      </c>
+      <c r="E378">
+        <v>13.49886568031696</v>
+      </c>
+      <c r="F378">
+        <v>1</v>
+      </c>
+      <c r="G378">
+        <v>0.141901134319683</v>
+      </c>
+      <c r="H378">
+        <v>0.1413011343196831</v>
+      </c>
+      <c r="I378">
+        <v>-0.5999999999999943</v>
+      </c>
+      <c r="J378">
+        <v>0.3398996506366119</v>
+      </c>
+      <c r="K378">
+        <v>188</v>
+      </c>
+      <c r="L378">
+        <v>78</v>
+      </c>
+      <c r="M378">
+        <v>188</v>
+      </c>
+      <c r="N378">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="O378">
+        <v>0</v>
+      </c>
+      <c r="P378" t="s">
+        <v>468</v>
       </c>
     </row>
   </sheetData>
